--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU130"/>
+  <dimension ref="A1:AU137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G19">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G40">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-08-01 11:30:00</t>
+          <t>2026-08-01 11:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-08-01 12:00:00</t>
+          <t>2026-08-01 11:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-01 12:00:00</t>
+          <t>2026-08-01 11:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-08-01 12:00:00</t>
+          <t>2026-08-01 11:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-08-01 12:00:00</t>
+          <t>2026-08-01 11:00:00</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-08-01 12:00:00</t>
+          <t>2026-08-01 11:30:00</t>
         </is>
       </c>
     </row>
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-08-01 12:30:00</t>
+          <t>2026-08-01 12:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-08-01 12:30:00</t>
+          <t>2026-08-01 12:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.46</v>
+        <v>2.86</v>
       </c>
       <c r="O53">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-08-01 12:30:00</t>
+          <t>2026-08-01 12:00:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-08-01 12:30:00</t>
+          <t>2026-08-01 12:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-08-01 12:30:00</t>
+          <t>2026-08-01 12:00:00</t>
         </is>
       </c>
     </row>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-08-01 13:00:00</t>
+          <t>2026-08-01 12:30:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-08-01 13:00:00</t>
+          <t>2026-08-01 12:30:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-01 13:00:00</t>
+          <t>2026-08-01 12:30:00</t>
         </is>
       </c>
     </row>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-08-01 13:00:00</t>
+          <t>2026-08-01 12:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-01 13:00:00</t>
+          <t>2026-08-01 12:30:00</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G63">
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G64">
@@ -10857,27 +10857,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-08-01 13:30:00</t>
+          <t>2026-08-01 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-08-01 13:30:00</t>
+          <t>2026-08-01 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-08-01 13:30:00</t>
+          <t>2026-08-01 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G68">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-08-01 13:30:00</t>
+          <t>2026-08-01 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-08-01 13:30:00</t>
+          <t>2026-08-01 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11672,27 +11672,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G70">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-08-01 14:00:00</t>
+          <t>2026-08-01 13:30:00</t>
         </is>
       </c>
     </row>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G71">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-08-01 14:00:00</t>
+          <t>2026-08-01 13:30:00</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G72">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-08-01 14:00:00</t>
+          <t>2026-08-01 13:30:00</t>
         </is>
       </c>
     </row>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G73">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-08-01 14:00:00</t>
+          <t>2026-08-01 13:30:00</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-08-01 14:00:00</t>
+          <t>2026-08-01 13:30:00</t>
         </is>
       </c>
     </row>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-08-01 14:30:00</t>
+          <t>2026-08-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O76">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P76">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12742,10 +12742,10 @@
         <v>0</v>
       </c>
       <c r="AC76">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-08-01 14:30:00</t>
+          <t>2026-08-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45:00</t>
+          <t>2026-08-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12976,27 +12976,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-08-01 15:00:00</t>
+          <t>2026-08-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G79">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-08-01 15:00:00</t>
+          <t>2026-08-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -13302,27 +13302,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G80">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-01 15:00:00</t>
+          <t>2026-08-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-01 15:00:00</t>
+          <t>2026-08-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -13628,27 +13628,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-01 15:00:00</t>
+          <t>2026-08-01 14:45:00</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,22 +13959,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G84">
@@ -14117,27 +14117,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-08-01 15:15:00</t>
+          <t>2026-08-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14280,27 +14280,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-08-01 15:15:00</t>
+          <t>2026-08-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14443,27 +14443,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-01 15:15:00</t>
+          <t>2026-08-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-01 15:30:00</t>
+          <t>2026-08-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-01 15:30:00</t>
+          <t>2026-08-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-01 15:30:00</t>
+          <t>2026-08-01 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15095,27 +15095,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-08-01 16:00:00</t>
+          <t>2026-08-01 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-01 16:00:00</t>
+          <t>2026-08-01 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15421,27 +15421,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-01 16:00:00</t>
+          <t>2026-08-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15584,27 +15584,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15664,10 +15664,10 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-08-01 16:00:00</t>
+          <t>2026-08-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15747,27 +15747,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-08-01 17:00:00</t>
+          <t>2026-08-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-08-01 18:15:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-08-01 18:30:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-08-01 18:30:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G99">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16562,27 +16562,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-08-01 19:30:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-08-01 20:00:00</t>
+          <t>2026-08-01 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-08-01 20:00:00</t>
+          <t>2026-08-01 18:15:00</t>
         </is>
       </c>
     </row>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-08-01 20:00:00</t>
+          <t>2026-08-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G104">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -17377,12 +17377,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 19:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G112">
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-08-01 21:30:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-08-01 21:30:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-01 21:30:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-01 21:30:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G122">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-08-01 21:45:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-01 22:00:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-01 22:30:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20637,7 +20637,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-08-01 22:30:00</t>
+          <t>2026-08-01 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G126">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-08-01 23:00:00</t>
+          <t>2026-08-01 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G127">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-08-01 23:00:00</t>
+          <t>2026-08-01 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G128">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-08-01 23:30:00</t>
+          <t>2026-08-01 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-01 23:30:00</t>
+          <t>2026-08-01 21:45:00</t>
         </is>
       </c>
     </row>
@@ -21452,156 +21452,1297 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Cavalry FC</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>York9 FC</t>
+        </is>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>0</v>
+      </c>
+      <c r="R130">
+        <v>0</v>
+      </c>
+      <c r="S130">
+        <v>0</v>
+      </c>
+      <c r="T130">
+        <v>0</v>
+      </c>
+      <c r="U130">
+        <v>0</v>
+      </c>
+      <c r="V130">
+        <v>0</v>
+      </c>
+      <c r="W130">
+        <v>0</v>
+      </c>
+      <c r="X130">
+        <v>0</v>
+      </c>
+      <c r="Y130">
+        <v>0</v>
+      </c>
+      <c r="Z130">
+        <v>0</v>
+      </c>
+      <c r="AA130">
+        <v>0</v>
+      </c>
+      <c r="AB130">
+        <v>0</v>
+      </c>
+      <c r="AC130">
+        <v>0</v>
+      </c>
+      <c r="AD130">
+        <v>0</v>
+      </c>
+      <c r="AE130">
+        <v>0</v>
+      </c>
+      <c r="AF130">
+        <v>0</v>
+      </c>
+      <c r="AG130">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ130">
+        <v>0</v>
+      </c>
+      <c r="AK130">
+        <v>0</v>
+      </c>
+      <c r="AL130">
+        <v>0</v>
+      </c>
+      <c r="AM130">
+        <v>-1</v>
+      </c>
+      <c r="AN130">
+        <v>-1</v>
+      </c>
+      <c r="AO130">
+        <v>-1</v>
+      </c>
+      <c r="AP130">
+        <v>-1</v>
+      </c>
+      <c r="AQ130">
+        <v>0</v>
+      </c>
+      <c r="AR130">
+        <v>0</v>
+      </c>
+      <c r="AS130">
+        <v>0</v>
+      </c>
+      <c r="AT130">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>0</v>
+      </c>
+      <c r="R131">
+        <v>0</v>
+      </c>
+      <c r="S131">
+        <v>0</v>
+      </c>
+      <c r="T131">
+        <v>0</v>
+      </c>
+      <c r="U131">
+        <v>0</v>
+      </c>
+      <c r="V131">
+        <v>0</v>
+      </c>
+      <c r="W131">
+        <v>0</v>
+      </c>
+      <c r="X131">
+        <v>0</v>
+      </c>
+      <c r="Y131">
+        <v>0</v>
+      </c>
+      <c r="Z131">
+        <v>0</v>
+      </c>
+      <c r="AA131">
+        <v>0</v>
+      </c>
+      <c r="AB131">
+        <v>0</v>
+      </c>
+      <c r="AC131">
+        <v>0</v>
+      </c>
+      <c r="AD131">
+        <v>0</v>
+      </c>
+      <c r="AE131">
+        <v>0</v>
+      </c>
+      <c r="AF131">
+        <v>0</v>
+      </c>
+      <c r="AG131">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
+        <v>0</v>
+      </c>
+      <c r="AK131">
+        <v>0</v>
+      </c>
+      <c r="AL131">
+        <v>0</v>
+      </c>
+      <c r="AM131">
+        <v>-1</v>
+      </c>
+      <c r="AN131">
+        <v>-1</v>
+      </c>
+      <c r="AO131">
+        <v>-1</v>
+      </c>
+      <c r="AP131">
+        <v>-1</v>
+      </c>
+      <c r="AQ131">
+        <v>0</v>
+      </c>
+      <c r="AR131">
+        <v>0</v>
+      </c>
+      <c r="AS131">
+        <v>0</v>
+      </c>
+      <c r="AT131">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>0</v>
+      </c>
+      <c r="R132">
+        <v>0</v>
+      </c>
+      <c r="S132">
+        <v>0</v>
+      </c>
+      <c r="T132">
+        <v>0</v>
+      </c>
+      <c r="U132">
+        <v>0</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+      <c r="W132">
+        <v>0</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>0</v>
+      </c>
+      <c r="Z132">
+        <v>0</v>
+      </c>
+      <c r="AA132">
+        <v>0</v>
+      </c>
+      <c r="AB132">
+        <v>0</v>
+      </c>
+      <c r="AC132">
+        <v>0</v>
+      </c>
+      <c r="AD132">
+        <v>0</v>
+      </c>
+      <c r="AE132">
+        <v>0</v>
+      </c>
+      <c r="AF132">
+        <v>0</v>
+      </c>
+      <c r="AG132">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
+        <v>0</v>
+      </c>
+      <c r="AK132">
+        <v>0</v>
+      </c>
+      <c r="AL132">
+        <v>0</v>
+      </c>
+      <c r="AM132">
+        <v>-1</v>
+      </c>
+      <c r="AN132">
+        <v>-1</v>
+      </c>
+      <c r="AO132">
+        <v>-1</v>
+      </c>
+      <c r="AP132">
+        <v>-1</v>
+      </c>
+      <c r="AQ132">
+        <v>0</v>
+      </c>
+      <c r="AR132">
+        <v>0</v>
+      </c>
+      <c r="AS132">
+        <v>0</v>
+      </c>
+      <c r="AT132">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+      <c r="S133">
+        <v>0</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133">
+        <v>0</v>
+      </c>
+      <c r="V133">
+        <v>0</v>
+      </c>
+      <c r="W133">
+        <v>0</v>
+      </c>
+      <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133">
+        <v>0</v>
+      </c>
+      <c r="Z133">
+        <v>0</v>
+      </c>
+      <c r="AA133">
+        <v>0</v>
+      </c>
+      <c r="AB133">
+        <v>0</v>
+      </c>
+      <c r="AC133">
+        <v>0</v>
+      </c>
+      <c r="AD133">
+        <v>0</v>
+      </c>
+      <c r="AE133">
+        <v>0</v>
+      </c>
+      <c r="AF133">
+        <v>0</v>
+      </c>
+      <c r="AG133">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ133">
+        <v>0</v>
+      </c>
+      <c r="AK133">
+        <v>0</v>
+      </c>
+      <c r="AL133">
+        <v>0</v>
+      </c>
+      <c r="AM133">
+        <v>-1</v>
+      </c>
+      <c r="AN133">
+        <v>-1</v>
+      </c>
+      <c r="AO133">
+        <v>-1</v>
+      </c>
+      <c r="AP133">
+        <v>-1</v>
+      </c>
+      <c r="AQ133">
+        <v>0</v>
+      </c>
+      <c r="AR133">
+        <v>0</v>
+      </c>
+      <c r="AS133">
+        <v>0</v>
+      </c>
+      <c r="AT133">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>0</v>
+      </c>
+      <c r="Z134">
+        <v>0</v>
+      </c>
+      <c r="AA134">
+        <v>0</v>
+      </c>
+      <c r="AB134">
+        <v>0</v>
+      </c>
+      <c r="AC134">
+        <v>0</v>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134">
+        <v>0</v>
+      </c>
+      <c r="AF134">
+        <v>0</v>
+      </c>
+      <c r="AG134">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
+        <v>0</v>
+      </c>
+      <c r="AK134">
+        <v>0</v>
+      </c>
+      <c r="AL134">
+        <v>0</v>
+      </c>
+      <c r="AM134">
+        <v>-1</v>
+      </c>
+      <c r="AN134">
+        <v>-1</v>
+      </c>
+      <c r="AO134">
+        <v>-1</v>
+      </c>
+      <c r="AP134">
+        <v>-1</v>
+      </c>
+      <c r="AQ134">
+        <v>0</v>
+      </c>
+      <c r="AR134">
+        <v>0</v>
+      </c>
+      <c r="AS134">
+        <v>0</v>
+      </c>
+      <c r="AT134">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>0</v>
+      </c>
+      <c r="V135">
+        <v>0</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>0</v>
+      </c>
+      <c r="Z135">
+        <v>0</v>
+      </c>
+      <c r="AA135">
+        <v>0</v>
+      </c>
+      <c r="AB135">
+        <v>0</v>
+      </c>
+      <c r="AC135">
+        <v>0</v>
+      </c>
+      <c r="AD135">
+        <v>0</v>
+      </c>
+      <c r="AE135">
+        <v>0</v>
+      </c>
+      <c r="AF135">
+        <v>0</v>
+      </c>
+      <c r="AG135">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>0</v>
+      </c>
+      <c r="AK135">
+        <v>0</v>
+      </c>
+      <c r="AL135">
+        <v>0</v>
+      </c>
+      <c r="AM135">
+        <v>-1</v>
+      </c>
+      <c r="AN135">
+        <v>-1</v>
+      </c>
+      <c r="AO135">
+        <v>-1</v>
+      </c>
+      <c r="AP135">
+        <v>-1</v>
+      </c>
+      <c r="AQ135">
+        <v>0</v>
+      </c>
+      <c r="AR135">
+        <v>0</v>
+      </c>
+      <c r="AS135">
+        <v>0</v>
+      </c>
+      <c r="AT135">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>0</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
+      </c>
+      <c r="S136">
+        <v>0</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136">
+        <v>0</v>
+      </c>
+      <c r="V136">
+        <v>0</v>
+      </c>
+      <c r="W136">
+        <v>0</v>
+      </c>
+      <c r="X136">
+        <v>0</v>
+      </c>
+      <c r="Y136">
+        <v>0</v>
+      </c>
+      <c r="Z136">
+        <v>0</v>
+      </c>
+      <c r="AA136">
+        <v>0</v>
+      </c>
+      <c r="AB136">
+        <v>0</v>
+      </c>
+      <c r="AC136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136">
+        <v>0</v>
+      </c>
+      <c r="AF136">
+        <v>0</v>
+      </c>
+      <c r="AG136">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ136">
+        <v>0</v>
+      </c>
+      <c r="AK136">
+        <v>0</v>
+      </c>
+      <c r="AL136">
+        <v>0</v>
+      </c>
+      <c r="AM136">
+        <v>-1</v>
+      </c>
+      <c r="AN136">
+        <v>-1</v>
+      </c>
+      <c r="AO136">
+        <v>-1</v>
+      </c>
+      <c r="AP136">
+        <v>-1</v>
+      </c>
+      <c r="AQ136">
+        <v>0</v>
+      </c>
+      <c r="AR136">
+        <v>0</v>
+      </c>
+      <c r="AS136">
+        <v>0</v>
+      </c>
+      <c r="AT136">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
-        <v>0</v>
-      </c>
-      <c r="AB130">
-        <v>0</v>
-      </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+      <c r="AA137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>0</v>
+      </c>
+      <c r="AG137">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>0</v>
+      </c>
+      <c r="AK137">
+        <v>0</v>
+      </c>
+      <c r="AL137">
+        <v>0</v>
+      </c>
+      <c r="AM137">
+        <v>-1</v>
+      </c>
+      <c r="AN137">
+        <v>-1</v>
+      </c>
+      <c r="AO137">
+        <v>-1</v>
+      </c>
+      <c r="AP137">
+        <v>-1</v>
+      </c>
+      <c r="AQ137">
+        <v>0</v>
+      </c>
+      <c r="AR137">
+        <v>0</v>
+      </c>
+      <c r="AS137">
+        <v>0</v>
+      </c>
+      <c r="AT137">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
         <is>
           <t>2026-08-01 23:30:00</t>
         </is>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU137"/>
+  <dimension ref="A1:AU140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G35">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G40">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G52">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G68">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G80">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-01 14:30:00</t>
+          <t>2026-08-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD81">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="O82">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="P82">
-        <v>2.71</v>
+        <v>6.89</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13720,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45:00</t>
+          <t>2026-08-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -13791,27 +13791,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-01 15:00:00</t>
+          <t>2026-08-01 14:45:00</t>
         </is>
       </c>
     </row>
@@ -13959,22 +13959,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,22 +14774,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G89">
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-01 15:15:00</t>
+          <t>2026-08-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-08-01 15:15:00</t>
+          <t>2026-08-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G92">
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G93">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-01 15:30:00</t>
+          <t>2026-08-01 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15584,27 +15584,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15664,10 +15664,10 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z94">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-08-01 15:30:00</t>
+          <t>2026-08-01 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G95">
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-08-01 16:00:00</t>
+          <t>2026-08-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA97">
         <v>0</v>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-08-01 16:00:00</t>
+          <t>2026-08-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-08-01 16:00:00</t>
+          <t>2026-08-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G100">
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-08-01 17:00:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-08-01 18:15:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-08-01 18:30:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G104">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-08-01 18:30:00</t>
+          <t>2026-08-01 17:00:00</t>
         </is>
       </c>
     </row>
@@ -17377,12 +17377,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-08-01 18:30:00</t>
+          <t>2026-08-01 18:15:00</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00:00</t>
+          <t>2026-08-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-08-01 19:30:00</t>
+          <t>2026-08-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-08-01 20:00:00</t>
+          <t>2026-08-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-08-01 20:00:00</t>
+          <t>2026-08-01 19:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-08-01 20:00:00</t>
+          <t>2026-08-01 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G119">
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G122">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-08-01 21:30:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G126">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-08-01 21:30:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G127">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-08-01 21:30:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G128">
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-01 21:45:00</t>
+          <t>2026-08-01 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21452,12 +21452,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G130">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-01 22:00:00</t>
+          <t>2026-08-01 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G131">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-01 22:30:00</t>
+          <t>2026-08-01 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G132">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-01 22:30:00</t>
+          <t>2026-08-01 21:45:00</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G133">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-01 23:00:00</t>
+          <t>2026-08-01 22:00:00</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22104,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G134">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-01 23:00:00</t>
+          <t>2026-08-01 22:30:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G135">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-01 23:30:00</t>
+          <t>2026-08-01 22:30:00</t>
         </is>
       </c>
     </row>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G136">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-01 23:30:00</t>
+          <t>2026-08-01 23:00:00</t>
         </is>
       </c>
     </row>
@@ -22593,156 +22593,645 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+      <c r="AA137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>0</v>
+      </c>
+      <c r="AG137">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>0</v>
+      </c>
+      <c r="AK137">
+        <v>0</v>
+      </c>
+      <c r="AL137">
+        <v>0</v>
+      </c>
+      <c r="AM137">
+        <v>-1</v>
+      </c>
+      <c r="AN137">
+        <v>-1</v>
+      </c>
+      <c r="AO137">
+        <v>-1</v>
+      </c>
+      <c r="AP137">
+        <v>-1</v>
+      </c>
+      <c r="AQ137">
+        <v>0</v>
+      </c>
+      <c r="AR137">
+        <v>0</v>
+      </c>
+      <c r="AS137">
+        <v>0</v>
+      </c>
+      <c r="AT137">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+      <c r="AA138">
+        <v>0</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AC138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138">
+        <v>0</v>
+      </c>
+      <c r="AF138">
+        <v>0</v>
+      </c>
+      <c r="AG138">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>0</v>
+      </c>
+      <c r="AK138">
+        <v>0</v>
+      </c>
+      <c r="AL138">
+        <v>0</v>
+      </c>
+      <c r="AM138">
+        <v>-1</v>
+      </c>
+      <c r="AN138">
+        <v>-1</v>
+      </c>
+      <c r="AO138">
+        <v>-1</v>
+      </c>
+      <c r="AP138">
+        <v>-1</v>
+      </c>
+      <c r="AQ138">
+        <v>0</v>
+      </c>
+      <c r="AR138">
+        <v>0</v>
+      </c>
+      <c r="AS138">
+        <v>0</v>
+      </c>
+      <c r="AT138">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>-1</v>
+      </c>
+      <c r="AN139">
+        <v>-1</v>
+      </c>
+      <c r="AO139">
+        <v>-1</v>
+      </c>
+      <c r="AP139">
+        <v>-1</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>0</v>
-      </c>
-      <c r="AB137">
-        <v>0</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>0</v>
+      </c>
+      <c r="R140">
+        <v>0</v>
+      </c>
+      <c r="S140">
+        <v>0</v>
+      </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="U140">
+        <v>0</v>
+      </c>
+      <c r="V140">
+        <v>0</v>
+      </c>
+      <c r="W140">
+        <v>0</v>
+      </c>
+      <c r="X140">
+        <v>0</v>
+      </c>
+      <c r="Y140">
+        <v>0</v>
+      </c>
+      <c r="Z140">
+        <v>0</v>
+      </c>
+      <c r="AA140">
+        <v>0</v>
+      </c>
+      <c r="AB140">
+        <v>0</v>
+      </c>
+      <c r="AC140">
+        <v>0</v>
+      </c>
+      <c r="AD140">
+        <v>0</v>
+      </c>
+      <c r="AE140">
+        <v>0</v>
+      </c>
+      <c r="AF140">
+        <v>0</v>
+      </c>
+      <c r="AG140">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ140">
+        <v>0</v>
+      </c>
+      <c r="AK140">
+        <v>0</v>
+      </c>
+      <c r="AL140">
+        <v>0</v>
+      </c>
+      <c r="AM140">
+        <v>-1</v>
+      </c>
+      <c r="AN140">
+        <v>-1</v>
+      </c>
+      <c r="AO140">
+        <v>-1</v>
+      </c>
+      <c r="AP140">
+        <v>-1</v>
+      </c>
+      <c r="AQ140">
+        <v>0</v>
+      </c>
+      <c r="AR140">
+        <v>0</v>
+      </c>
+      <c r="AS140">
+        <v>0</v>
+      </c>
+      <c r="AT140">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
         <is>
           <t>2026-08-01 23:30:00</t>
         </is>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G21">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G40">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G90">

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G52">

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q41">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q65">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC98">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.96</v>
+        <v>2.28</v>
       </c>
       <c r="O11">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="P11">
-        <v>1.57</v>
+        <v>2.83</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
+        <v>2</v>
+      </c>
+      <c r="AB11">
         <v>1.78</v>
-      </c>
-      <c r="AB11">
-        <v>1.92</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.28</v>
+        <v>4.96</v>
       </c>
       <c r="O12">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="P12">
-        <v>2.83</v>
+        <v>1.57</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB12">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9156,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>7.27</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G80">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19425,10 +19425,10 @@
         <v>0</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19588,10 +19588,10 @@
         <v>0</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE118">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19745,10 +19745,10 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC119">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19914,10 +19914,10 @@
         <v>0</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE120">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20077,10 +20077,10 @@
         <v>0</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE121">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC122">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21218,10 +21218,10 @@
         <v>0</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21381,10 +21381,10 @@
         <v>0</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21544,10 +21544,10 @@
         <v>0</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21707,10 +21707,10 @@
         <v>0</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE131">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22353,10 +22353,10 @@
         <v>0</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC135">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23011,10 +23011,10 @@
         <v>0</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE140">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G79">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G90">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.49</v>
+        <v>1.54</v>
       </c>
       <c r="O112">
-        <v>3.32</v>
+        <v>3.92</v>
       </c>
       <c r="P112">
-        <v>2.46</v>
+        <v>5.11</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.54</v>
+        <v>2.49</v>
       </c>
       <c r="O113">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="P113">
-        <v>5.11</v>
+        <v>2.46</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.16</v>
+        <v>1.99</v>
       </c>
       <c r="O116">
-        <v>3.53</v>
+        <v>4.31</v>
       </c>
       <c r="P116">
-        <v>2.32</v>
+        <v>3.36</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,16 +19256,16 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB116">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,14 +19380,14 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="O117">
+        <v>4.07</v>
+      </c>
+      <c r="P117">
         <v>4.31</v>
       </c>
-      <c r="P117">
-        <v>3.36</v>
-      </c>
       <c r="Q117">
         <v>0</v>
       </c>
@@ -19425,10 +19425,10 @@
         <v>0</v>
       </c>
       <c r="AC117">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AD117">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="O118">
-        <v>4.07</v>
+        <v>3.62</v>
       </c>
       <c r="P118">
-        <v>4.31</v>
+        <v>3.21</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,16 +19582,16 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC118">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD118">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="O119">
-        <v>3.62</v>
+        <v>4.26</v>
       </c>
       <c r="P119">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19745,16 +19745,16 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB119">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="O120">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="P120">
-        <v>3.27</v>
+        <v>4.22</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19914,10 +19914,10 @@
         <v>0</v>
       </c>
       <c r="AC120">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD120">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AE120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.8</v>
+        <v>3.16</v>
       </c>
       <c r="O121">
-        <v>4.22</v>
+        <v>3.53</v>
       </c>
       <c r="P121">
-        <v>4.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20071,16 +20071,16 @@
         <v>0</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC121">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD121">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE121">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O136">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P136">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q137">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G90">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.54</v>
+        <v>2.49</v>
       </c>
       <c r="O112">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="P112">
-        <v>5.11</v>
+        <v>2.46</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.49</v>
+        <v>1.54</v>
       </c>
       <c r="O113">
-        <v>3.32</v>
+        <v>3.92</v>
       </c>
       <c r="P113">
-        <v>2.46</v>
+        <v>5.11</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="O128">
-        <v>4.08</v>
+        <v>4.83</v>
       </c>
       <c r="P128">
-        <v>3.58</v>
+        <v>4.93</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21218,10 +21218,10 @@
         <v>0</v>
       </c>
       <c r="AC128">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD128">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="O129">
-        <v>4.83</v>
+        <v>3.87</v>
       </c>
       <c r="P129">
-        <v>4.93</v>
+        <v>3.1</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21381,10 +21381,10 @@
         <v>0</v>
       </c>
       <c r="AC129">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD129">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.22</v>
+        <v>3.77</v>
       </c>
       <c r="O130">
-        <v>3.87</v>
+        <v>3.74</v>
       </c>
       <c r="P130">
-        <v>3.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21544,10 +21544,10 @@
         <v>0</v>
       </c>
       <c r="AC130">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD130">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>3.77</v>
+        <v>1.98</v>
       </c>
       <c r="O131">
-        <v>3.74</v>
+        <v>4.08</v>
       </c>
       <c r="P131">
-        <v>2.01</v>
+        <v>3.58</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21710,7 +21710,7 @@
         <v>2.2</v>
       </c>
       <c r="AD131">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE131">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3614,10 +3614,10 @@
         <v>0</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3940,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE22">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q95">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G80">

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G68">

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14197,10 +14197,10 @@
         <v>0</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14360,10 +14360,10 @@
         <v>0</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14523,10 +14523,10 @@
         <v>0</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14849,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15012,10 +15012,10 @@
         <v>0</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA90">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G80">

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.61</v>
+        <v>2.04</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AB9">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="P10">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB10">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.28</v>
+        <v>4.96</v>
       </c>
       <c r="O11">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="P11">
-        <v>2.83</v>
+        <v>1.57</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.96</v>
+        <v>2.36</v>
       </c>
       <c r="O12">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G35">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G40">

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G35">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q55">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1296,55 +1296,55 @@
         <v>6.12</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,34 +1459,34 @@
         <v>2.79</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA7">
         <v>1.98</v>
@@ -1495,19 +1495,19 @@
         <v>1.76</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>3.29</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,34 +1785,34 @@
         <v>2.04</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
         <v>1.93</v>
@@ -1821,19 +1821,19 @@
         <v>1.84</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,34 +1948,34 @@
         <v>2.83</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA10">
         <v>2</v>
@@ -1984,19 +1984,19 @@
         <v>1.78</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,34 +2111,34 @@
         <v>1.57</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA11">
         <v>1.78</v>
@@ -2147,19 +2147,19 @@
         <v>1.92</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>2.61</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA12">
         <v>1.78</v>
@@ -2310,19 +2310,19 @@
         <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>2.84</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>3.33</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>2.54</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3578,40 +3578,40 @@
         <v>3.34</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC20">
         <v>1.87</v>
@@ -3620,13 +3620,13 @@
         <v>1.83</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,40 +3741,40 @@
         <v>4.9</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC21">
         <v>1.81</v>
@@ -3783,13 +3783,13 @@
         <v>1.89</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,40 +3904,40 @@
         <v>8.75</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
         <v>1.87</v>
@@ -3946,13 +3946,13 @@
         <v>1.83</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>1.95</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>3.96</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>4.5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5395,31 +5395,31 @@
         <v>0</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>7.7</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G38">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>3</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -7339,10 +7339,10 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W43">
         <v>0</v>
@@ -7357,19 +7357,19 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF43">
         <v>0</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,34 +7490,34 @@
         <v>3.52</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA44">
         <v>1.7</v>
@@ -7526,19 +7526,19 @@
         <v>2</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>1.9</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>4.97</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>2.6</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,34 +8957,34 @@
         <v>2.32</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA53">
         <v>1.73</v>
@@ -8993,19 +8993,19 @@
         <v>1.95</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,40 +9120,40 @@
         <v>1.85</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC54">
         <v>1.95</v>
@@ -9162,13 +9162,13 @@
         <v>1.75</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>3.03</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>2.26</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>1.72</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>3.26</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>1.4</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>1.1</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11565,34 +11565,34 @@
         <v>12.1</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA69">
         <v>1.8</v>
@@ -11601,19 +11601,19 @@
         <v>2</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC136">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="O7">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="P7">
-        <v>2.79</v>
+        <v>3.29</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="R7">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V7">
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AA7">
         <v>1.98</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC7">
-        <v>3.36</v>
+        <v>3.94</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AG7">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="O8">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="P8">
-        <v>3.29</v>
+        <v>2.79</v>
       </c>
       <c r="Q8">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V8">
         <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AA8">
         <v>1.98</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AK8">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,43 +2102,43 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.96</v>
+        <v>2.36</v>
       </c>
       <c r="O11">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="R11">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AA11">
         <v>1.78</v>
@@ -2147,19 +2147,19 @@
         <v>1.92</v>
       </c>
       <c r="AC11">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,43 +2265,43 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.36</v>
+        <v>4.96</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="P12">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q12">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="S12">
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA12">
         <v>1.78</v>
@@ -2310,19 +2310,19 @@
         <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>2.25</v>
       </c>
       <c r="AK12">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="O20">
-        <v>4</v>
+        <v>4.69</v>
       </c>
       <c r="P20">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="Q20">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="R20">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="S20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="V20">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA20">
+        <v>1.33</v>
+      </c>
+      <c r="AB20">
+        <v>3.4</v>
+      </c>
+      <c r="AC20">
+        <v>1.81</v>
+      </c>
+      <c r="AD20">
+        <v>1.89</v>
+      </c>
+      <c r="AE20">
+        <v>1.4</v>
+      </c>
+      <c r="AF20">
         <v>1.36</v>
       </c>
-      <c r="AB20">
-        <v>3.04</v>
-      </c>
-      <c r="AC20">
-        <v>1.87</v>
-      </c>
-      <c r="AD20">
-        <v>1.83</v>
-      </c>
-      <c r="AE20">
-        <v>1.34</v>
-      </c>
-      <c r="AF20">
-        <v>1.34</v>
-      </c>
       <c r="AG20">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.81</v>
+        <v>2.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.59</v>
+        <v>2.01</v>
       </c>
       <c r="O21">
-        <v>4.69</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>4.9</v>
+        <v>3.34</v>
       </c>
       <c r="Q21">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="R21">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="S21">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T21">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U21">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="V21">
+        <v>1.72</v>
+      </c>
+      <c r="W21">
+        <v>1.22</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.11</v>
+      </c>
+      <c r="Z21">
+        <v>6</v>
+      </c>
+      <c r="AA21">
+        <v>1.36</v>
+      </c>
+      <c r="AB21">
+        <v>3.04</v>
+      </c>
+      <c r="AC21">
         <v>1.87</v>
       </c>
-      <c r="W21">
-        <v>1.21</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.07</v>
-      </c>
-      <c r="Z21">
-        <v>6.5</v>
-      </c>
-      <c r="AA21">
-        <v>1.33</v>
-      </c>
-      <c r="AB21">
-        <v>3.4</v>
-      </c>
-      <c r="AC21">
+      <c r="AD21">
+        <v>1.83</v>
+      </c>
+      <c r="AE21">
+        <v>1.34</v>
+      </c>
+      <c r="AF21">
+        <v>1.34</v>
+      </c>
+      <c r="AG21">
+        <v>2.99</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.08</v>
+      </c>
+      <c r="AK21">
         <v>1.81</v>
-      </c>
-      <c r="AD21">
-        <v>1.89</v>
-      </c>
-      <c r="AE21">
-        <v>1.4</v>
-      </c>
-      <c r="AF21">
-        <v>1.36</v>
-      </c>
-      <c r="AG21">
-        <v>2.7</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.17</v>
-      </c>
-      <c r="AK21">
-        <v>2.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="O118">
-        <v>3.62</v>
+        <v>4.26</v>
       </c>
       <c r="P118">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,16 +19582,16 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB118">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="O119">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="P119">
-        <v>3.27</v>
+        <v>4.22</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19751,10 +19751,10 @@
         <v>0</v>
       </c>
       <c r="AC119">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD119">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AE119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.8</v>
+        <v>3.16</v>
       </c>
       <c r="O120">
-        <v>4.22</v>
+        <v>3.53</v>
       </c>
       <c r="P120">
-        <v>4.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19908,16 +19908,16 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC120">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD120">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.16</v>
+        <v>1.79</v>
       </c>
       <c r="O121">
-        <v>3.53</v>
+        <v>4.08</v>
       </c>
       <c r="P121">
-        <v>2.32</v>
+        <v>4.42</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20071,10 +20071,10 @@
         <v>0</v>
       </c>
       <c r="AA121">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AB121">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AC121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="O122">
-        <v>4.08</v>
+        <v>3.62</v>
       </c>
       <c r="P122">
-        <v>4.42</v>
+        <v>3.21</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AB122">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC122">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="P6">
-        <v>6.12</v>
+        <v>3.29</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="U6">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="V6">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z6">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AA6">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AG6">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="O7">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="P7">
-        <v>3.29</v>
+        <v>2.79</v>
       </c>
       <c r="Q7">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Z7">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AA7">
         <v>1.98</v>
       </c>
       <c r="AB7">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC7">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AK7">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.73</v>
+        <v>1.57</v>
       </c>
       <c r="O8">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="P8">
-        <v>2.79</v>
+        <v>6.12</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="R8">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U8">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z8">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="AA8">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AB8">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC8">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.59</v>
+        <v>2.01</v>
       </c>
       <c r="O20">
-        <v>4.69</v>
+        <v>4</v>
       </c>
       <c r="P20">
-        <v>4.9</v>
+        <v>3.34</v>
       </c>
       <c r="Q20">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="R20">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="S20">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T20">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U20">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="V20">
+        <v>1.72</v>
+      </c>
+      <c r="W20">
+        <v>1.22</v>
+      </c>
+      <c r="X20">
+        <v>1.02</v>
+      </c>
+      <c r="Y20">
+        <v>1.11</v>
+      </c>
+      <c r="Z20">
+        <v>6</v>
+      </c>
+      <c r="AA20">
+        <v>1.36</v>
+      </c>
+      <c r="AB20">
+        <v>3.04</v>
+      </c>
+      <c r="AC20">
         <v>1.87</v>
       </c>
-      <c r="W20">
-        <v>1.21</v>
-      </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.07</v>
-      </c>
-      <c r="Z20">
-        <v>6.5</v>
-      </c>
-      <c r="AA20">
-        <v>1.33</v>
-      </c>
-      <c r="AB20">
-        <v>3.4</v>
-      </c>
-      <c r="AC20">
+      <c r="AD20">
+        <v>1.83</v>
+      </c>
+      <c r="AE20">
+        <v>1.34</v>
+      </c>
+      <c r="AF20">
+        <v>1.34</v>
+      </c>
+      <c r="AG20">
+        <v>2.99</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.08</v>
+      </c>
+      <c r="AK20">
         <v>1.81</v>
-      </c>
-      <c r="AD20">
-        <v>1.89</v>
-      </c>
-      <c r="AE20">
-        <v>1.4</v>
-      </c>
-      <c r="AF20">
-        <v>1.36</v>
-      </c>
-      <c r="AG20">
-        <v>2.7</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.17</v>
-      </c>
-      <c r="AK20">
-        <v>2.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>4.69</v>
       </c>
       <c r="P21">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="Q21">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="R21">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="S21">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T21">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="U21">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="V21">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="W21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA21">
+        <v>1.33</v>
+      </c>
+      <c r="AB21">
+        <v>3.4</v>
+      </c>
+      <c r="AC21">
+        <v>1.81</v>
+      </c>
+      <c r="AD21">
+        <v>1.89</v>
+      </c>
+      <c r="AE21">
+        <v>1.4</v>
+      </c>
+      <c r="AF21">
         <v>1.36</v>
       </c>
-      <c r="AB21">
-        <v>3.04</v>
-      </c>
-      <c r="AC21">
-        <v>1.87</v>
-      </c>
-      <c r="AD21">
-        <v>1.83</v>
-      </c>
-      <c r="AE21">
-        <v>1.34</v>
-      </c>
-      <c r="AF21">
-        <v>1.34</v>
-      </c>
       <c r="AG21">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>1.81</v>
+        <v>2.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>4.01</v>
+        <v>2.77</v>
       </c>
       <c r="O88">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="P88">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14686,10 +14686,10 @@
         <v>0</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="O89">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14849,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Z89">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.72</v>
+        <v>4.01</v>
       </c>
       <c r="O90">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="P90">
-        <v>2.68</v>
+        <v>1.96</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15012,10 +15012,10 @@
         <v>0</v>
       </c>
       <c r="Y90">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z90">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA90">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.08</v>
+        <v>1.79</v>
       </c>
       <c r="O123">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="P123">
-        <v>2.1</v>
+        <v>3.79</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.79</v>
+        <v>3.08</v>
       </c>
       <c r="O124">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="P124">
-        <v>3.79</v>
+        <v>2.1</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC124">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="O6">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>3.29</v>
+        <v>6.12</v>
       </c>
       <c r="Q6">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="U6">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA6">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC6">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK6">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="O7">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="P7">
-        <v>2.79</v>
+        <v>3.29</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="R7">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V7">
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AA7">
         <v>1.98</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC7">
-        <v>3.36</v>
+        <v>3.94</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AG7">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.57</v>
+        <v>2.73</v>
       </c>
       <c r="O8">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="P8">
-        <v>6.12</v>
+        <v>2.79</v>
       </c>
       <c r="Q8">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="V8">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
+        <v>1.04</v>
+      </c>
+      <c r="X8">
         <v>1.06</v>
       </c>
-      <c r="X8">
+      <c r="Y8">
+        <v>1.27</v>
+      </c>
+      <c r="Z8">
+        <v>3.18</v>
+      </c>
+      <c r="AA8">
+        <v>1.98</v>
+      </c>
+      <c r="AB8">
+        <v>1.76</v>
+      </c>
+      <c r="AC8">
+        <v>3.36</v>
+      </c>
+      <c r="AD8">
+        <v>1.28</v>
+      </c>
+      <c r="AE8">
         <v>1.07</v>
       </c>
-      <c r="Y8">
-        <v>1.32</v>
-      </c>
-      <c r="Z8">
-        <v>2.89</v>
-      </c>
-      <c r="AA8">
-        <v>2.14</v>
-      </c>
-      <c r="AB8">
-        <v>1.67</v>
-      </c>
-      <c r="AC8">
-        <v>4.2</v>
-      </c>
-      <c r="AD8">
-        <v>1.22</v>
-      </c>
-      <c r="AE8">
-        <v>1.02</v>
-      </c>
       <c r="AF8">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AG8">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AK8">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2</v>
+        <v>3.02</v>
       </c>
       <c r="O86">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P86">
-        <v>3.97</v>
+        <v>2.47</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="Y86">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z86">
         <v>2.25</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="O87">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P87">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14523,10 +14523,10 @@
         <v>0</v>
       </c>
       <c r="Y87">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Z87">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AA87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.77</v>
+        <v>4.01</v>
       </c>
       <c r="O88">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="P88">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14686,10 +14686,10 @@
         <v>0</v>
       </c>
       <c r="Y88">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z88">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA88">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>4.01</v>
+        <v>2</v>
       </c>
       <c r="O90">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="P90">
-        <v>1.96</v>
+        <v>3.97</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15012,10 +15012,10 @@
         <v>0</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA90">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -7333,10 +7333,10 @@
         <v>2.65</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U43">
         <v>1.75</v>
@@ -7345,16 +7345,16 @@
         <v>1.84</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA43">
         <v>1.27</v>
@@ -7372,10 +7372,10 @@
         <v>1.4</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -10913,55 +10913,55 @@
         <v>3.4</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,55 +11891,55 @@
         <v>4.69</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,34 +12054,34 @@
         <v>4.09</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA72">
         <v>1.83</v>
@@ -12090,19 +12090,19 @@
         <v>1.84</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,34 +12380,34 @@
         <v>1.95</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA74">
         <v>1.66</v>
@@ -12416,19 +12416,19 @@
         <v>2.05</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13684,40 +13684,40 @@
         <v>6.89</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC82">
         <v>2.3</v>
@@ -13726,13 +13726,13 @@
         <v>1.53</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13847,55 +13847,55 @@
         <v>2.71</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,34 +14010,34 @@
         <v>3.7</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA84">
         <v>2</v>
@@ -14046,19 +14046,19 @@
         <v>1.8</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,28 +14173,28 @@
         <v>3.17</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y85">
         <v>1.63</v>
@@ -14203,25 +14203,25 @@
         <v>2.1</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="O86">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P86">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y86">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Z86">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.77</v>
+        <v>4.01</v>
       </c>
       <c r="O87">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="P87">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y87">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="Z87">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>4.01</v>
+        <v>2.72</v>
       </c>
       <c r="O88">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="P88">
-        <v>1.96</v>
+        <v>2.68</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.72</v>
+        <v>3.02</v>
       </c>
       <c r="O89">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P89">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y89">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="Z89">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,28 +14988,28 @@
         <v>3.97</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y90">
         <v>1.57</v>
@@ -15018,25 +15018,25 @@
         <v>2.25</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>3.68</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,55 +15640,55 @@
         <v>3.44</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>2.46</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,55 +15966,55 @@
         <v>2.68</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,28 +16129,28 @@
         <v>4.66</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y97">
         <v>1.65</v>
@@ -16159,25 +16159,25 @@
         <v>2.1</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16292,34 +16292,34 @@
         <v>6.93</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA98">
         <v>1.9</v>
@@ -16328,19 +16328,19 @@
         <v>1.79</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL126">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.96</v>
+        <v>2.28</v>
       </c>
       <c r="O11">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="P11">
-        <v>1.57</v>
+        <v>2.83</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R11">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.91</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
+        <v>1.3</v>
+      </c>
+      <c r="Z11">
+        <v>2.95</v>
+      </c>
+      <c r="AA11">
+        <v>2</v>
+      </c>
+      <c r="AB11">
+        <v>1.78</v>
+      </c>
+      <c r="AC11">
+        <v>3.4</v>
+      </c>
+      <c r="AD11">
         <v>1.24</v>
       </c>
-      <c r="Z11">
-        <v>3.7</v>
-      </c>
-      <c r="AA11">
-        <v>1.78</v>
-      </c>
-      <c r="AB11">
-        <v>1.92</v>
-      </c>
-      <c r="AC11">
-        <v>2.95</v>
-      </c>
-      <c r="AD11">
-        <v>1.3</v>
-      </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.28</v>
+        <v>4.96</v>
       </c>
       <c r="O12">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="P12">
-        <v>2.83</v>
+        <v>1.57</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
+        <v>1.24</v>
+      </c>
+      <c r="Z12">
+        <v>3.7</v>
+      </c>
+      <c r="AA12">
+        <v>1.78</v>
+      </c>
+      <c r="AB12">
+        <v>1.92</v>
+      </c>
+      <c r="AC12">
+        <v>2.95</v>
+      </c>
+      <c r="AD12">
         <v>1.3</v>
       </c>
-      <c r="Z12">
-        <v>2.95</v>
-      </c>
-      <c r="AA12">
-        <v>2</v>
-      </c>
-      <c r="AB12">
-        <v>1.78</v>
-      </c>
-      <c r="AC12">
-        <v>3.4</v>
-      </c>
-      <c r="AD12">
-        <v>1.24</v>
-      </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.02</v>
+        <v>4.01</v>
       </c>
       <c r="O90">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="P90">
-        <v>2.47</v>
+        <v>1.96</v>
       </c>
       <c r="Q90">
-        <v>3.32</v>
+        <v>4.94</v>
       </c>
       <c r="R90">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="S90">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T90">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U90">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V90">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W90">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X90">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y90">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z90">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AA90">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="AB90">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AC90">
-        <v>5.1</v>
+        <v>5.43</v>
       </c>
       <c r="AD90">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE90">
         <v>1.01</v>
       </c>
       <c r="AF90">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AG90">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AK90">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,65 +15142,65 @@
         </is>
       </c>
       <c r="N91">
-        <v>4.01</v>
+        <v>2.41</v>
       </c>
       <c r="O91">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="P91">
-        <v>1.96</v>
+        <v>3.17</v>
       </c>
       <c r="Q91">
-        <v>4.94</v>
+        <v>3.01</v>
       </c>
       <c r="R91">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="S91">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="T91">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="U91">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="V91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y91">
+        <v>1.63</v>
+      </c>
+      <c r="Z91">
+        <v>2.1</v>
+      </c>
+      <c r="AA91">
+        <v>3.1</v>
+      </c>
+      <c r="AB91">
+        <v>1.33</v>
+      </c>
+      <c r="AC91">
+        <v>6.22</v>
+      </c>
+      <c r="AD91">
+        <v>1.11</v>
+      </c>
+      <c r="AE91">
+        <v>1.03</v>
+      </c>
+      <c r="AF91">
+        <v>2.32</v>
+      </c>
+      <c r="AG91">
         <v>1.53</v>
       </c>
-      <c r="Z91">
-        <v>2.43</v>
-      </c>
-      <c r="AA91">
-        <v>2.52</v>
-      </c>
-      <c r="AB91">
-        <v>1.41</v>
-      </c>
-      <c r="AC91">
-        <v>5.43</v>
-      </c>
-      <c r="AD91">
-        <v>1.13</v>
-      </c>
-      <c r="AE91">
-        <v>1.01</v>
-      </c>
-      <c r="AF91">
-        <v>2.25</v>
-      </c>
-      <c r="AG91">
-        <v>1.6</v>
-      </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AK91">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,65 +15305,65 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
       <c r="O92">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P92">
-        <v>3.17</v>
+        <v>2.47</v>
       </c>
       <c r="Q92">
-        <v>3.01</v>
+        <v>3.32</v>
       </c>
       <c r="R92">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="S92">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="T92">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="U92">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="V92">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W92">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X92">
+        <v>1.05</v>
+      </c>
+      <c r="Y92">
+        <v>1.55</v>
+      </c>
+      <c r="Z92">
+        <v>2.25</v>
+      </c>
+      <c r="AA92">
+        <v>2.87</v>
+      </c>
+      <c r="AB92">
+        <v>1.46</v>
+      </c>
+      <c r="AC92">
+        <v>5.1</v>
+      </c>
+      <c r="AD92">
         <v>1.1</v>
       </c>
-      <c r="Y92">
+      <c r="AE92">
+        <v>1.01</v>
+      </c>
+      <c r="AF92">
+        <v>2.09</v>
+      </c>
+      <c r="AG92">
         <v>1.63</v>
       </c>
-      <c r="Z92">
-        <v>2.1</v>
-      </c>
-      <c r="AA92">
-        <v>3.1</v>
-      </c>
-      <c r="AB92">
-        <v>1.33</v>
-      </c>
-      <c r="AC92">
-        <v>6.22</v>
-      </c>
-      <c r="AD92">
-        <v>1.11</v>
-      </c>
-      <c r="AE92">
-        <v>1.03</v>
-      </c>
-      <c r="AF92">
-        <v>2.32</v>
-      </c>
-      <c r="AG92">
-        <v>1.53</v>
-      </c>
       <c r="AH92" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK92">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.65</v>
+        <v>1.54</v>
       </c>
       <c r="O117">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="P117">
-        <v>1.87</v>
+        <v>5.11</v>
       </c>
       <c r="Q117">
-        <v>4.25</v>
+        <v>2.07</v>
       </c>
       <c r="R117">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="S117">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T117">
-        <v>2.9</v>
+        <v>3.27</v>
       </c>
       <c r="U117">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="V117">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>3.34</v>
+        <v>3.82</v>
       </c>
       <c r="AA117">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AB117">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="AC117">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="AD117">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE117">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF117">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG117">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK117">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.54</v>
+        <v>3.65</v>
       </c>
       <c r="O118">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="P118">
-        <v>5.11</v>
+        <v>1.87</v>
       </c>
       <c r="Q118">
-        <v>2.07</v>
+        <v>4.25</v>
       </c>
       <c r="R118">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="S118">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T118">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="U118">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="V118">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W118">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z118">
-        <v>3.82</v>
+        <v>3.34</v>
       </c>
       <c r="AA118">
+        <v>1.84</v>
+      </c>
+      <c r="AB118">
+        <v>1.84</v>
+      </c>
+      <c r="AC118">
+        <v>3.05</v>
+      </c>
+      <c r="AD118">
+        <v>1.33</v>
+      </c>
+      <c r="AE118">
+        <v>1.12</v>
+      </c>
+      <c r="AF118">
         <v>1.72</v>
       </c>
-      <c r="AB118">
-        <v>2.07</v>
-      </c>
-      <c r="AC118">
-        <v>2.7</v>
-      </c>
-      <c r="AD118">
-        <v>1.36</v>
-      </c>
-      <c r="AE118">
-        <v>1.13</v>
-      </c>
-      <c r="AF118">
-        <v>1.73</v>
-      </c>
       <c r="AG118">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O121">
-        <v>4.22</v>
+        <v>3.62</v>
       </c>
       <c r="P121">
-        <v>4.22</v>
+        <v>3.21</v>
       </c>
       <c r="Q121">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R121">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S121">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T121">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U121">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V121">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W121">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X121">
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z121">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA121">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AB121">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC121">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD121">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE121">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF121">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG121">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK121">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.16</v>
+        <v>1.79</v>
       </c>
       <c r="O122">
-        <v>3.53</v>
+        <v>4.08</v>
       </c>
       <c r="P122">
-        <v>2.32</v>
+        <v>4.42</v>
       </c>
       <c r="Q122">
-        <v>3.35</v>
+        <v>2.1</v>
       </c>
       <c r="R122">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S122">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T122">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U122">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="V122">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="AA122">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AB122">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AC122">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF122">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG122">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK122">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="O123">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="P123">
-        <v>3.21</v>
+        <v>2.32</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA123">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AB123">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O124">
-        <v>4.07</v>
+        <v>4.22</v>
       </c>
       <c r="P124">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="Q124">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="R124">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S124">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="T124">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="U124">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="V124">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="W124">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X124">
         <v>0</v>
       </c>
       <c r="Y124">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z124">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AA124">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AB124">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC124">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AD124">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AE124">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AF124">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG124">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>1.2</v>
       </c>
       <c r="AK124">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="O125">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="P125">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="Q125">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R125">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S125">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="T125">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U125">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="V125">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="W125">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z125">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AA125">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AB125">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AC125">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AD125">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AE125">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AF125">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AG125">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,80 +20684,80 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="O125">
-        <v>4.07</v>
+        <v>4.31</v>
       </c>
       <c r="P125">
-        <v>4.31</v>
+        <v>3.36</v>
       </c>
       <c r="Q125">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="R125">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="S125">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="T125">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U125">
+        <v>1.85</v>
+      </c>
+      <c r="V125">
         <v>1.91</v>
       </c>
-      <c r="V125">
-        <v>1.8</v>
-      </c>
       <c r="W125">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X125">
         <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z125">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA125">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB125">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AC125">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AD125">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE125">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF125">
+        <v>1.29</v>
+      </c>
+      <c r="AG125">
+        <v>3.4</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
         <v>1.36</v>
       </c>
-      <c r="AG125">
-        <v>2.88</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.2</v>
-      </c>
       <c r="AK125">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="O126">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="P126">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="Q126">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="R126">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="S126">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T126">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="U126">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V126">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W126">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X126">
         <v>0</v>
       </c>
       <c r="Y126">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z126">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="AA126">
         <v>1.3</v>
       </c>
       <c r="AB126">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AC126">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AD126">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AE126">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF126">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AG126">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK126">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
+        <v>1.81</v>
+      </c>
+      <c r="O127">
+        <v>4.07</v>
+      </c>
+      <c r="P127">
+        <v>4.31</v>
+      </c>
+      <c r="Q127">
         <v>2.04</v>
       </c>
-      <c r="O127">
-        <v>4.26</v>
-      </c>
-      <c r="P127">
-        <v>3.27</v>
-      </c>
-      <c r="Q127">
-        <v>2.35</v>
-      </c>
       <c r="R127">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="S127">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T127">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="U127">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="V127">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="W127">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X127">
         <v>0</v>
       </c>
       <c r="Y127">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z127">
         <v>7</v>
       </c>
       <c r="AA127">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AB127">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC127">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD127">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AE127">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF127">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG127">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK127">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AL127">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
         <v>6.12</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
         <v>3.15</v>
@@ -1314,7 +1314,7 @@
         <v>1.31</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1.07</v>
@@ -1326,10 +1326,10 @@
         <v>2.89</v>
       </c>
       <c r="AA6">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC6">
         <v>4.2</v>
@@ -1338,13 +1338,13 @@
         <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
         <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK6">
         <v>2.5</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="O7">
         <v>2.88</v>
       </c>
       <c r="P7">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
         <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
         <v>3.18</v>
       </c>
       <c r="AA7">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
         <v>1.42</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="P8">
-        <v>3.29</v>
+        <v>3.54</v>
       </c>
       <c r="Q8">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="R8">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
         <v>1.44</v>
@@ -1634,13 +1634,13 @@
         <v>2.59</v>
       </c>
       <c r="U8">
-        <v>2.85</v>
+        <v>3.19</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1.07</v>
@@ -1649,25 +1649,25 @@
         <v>1.38</v>
       </c>
       <c r="Z8">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AA8">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AB8">
         <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG8">
         <v>1.85</v>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,34 +1776,34 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q9">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="R9">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="U9">
         <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.03</v>
@@ -1812,44 +1812,44 @@
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA9">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AC9">
         <v>2.74</v>
       </c>
       <c r="AD9">
+        <v>1.35</v>
+      </c>
+      <c r="AE9">
+        <v>1.1</v>
+      </c>
+      <c r="AF9">
+        <v>1.6</v>
+      </c>
+      <c r="AG9">
+        <v>2.14</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.77</v>
+      </c>
+      <c r="AK9">
         <v>1.3</v>
-      </c>
-      <c r="AE9">
-        <v>1.14</v>
-      </c>
-      <c r="AF9">
-        <v>1.68</v>
-      </c>
-      <c r="AG9">
-        <v>2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.22</v>
-      </c>
-      <c r="AK9">
-        <v>1.19</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P10">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="Q10">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="R10">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
         <v>3</v>
       </c>
       <c r="U10">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AA10">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
         <v>2.92</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="O11">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="P11">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="Q11">
         <v>3</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="U11">
         <v>2.91</v>
@@ -2129,37 +2129,37 @@
         <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE11">
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG11">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2277,52 +2277,52 @@
         <v>5</v>
       </c>
       <c r="R12">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK12">
         <v>1.1</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q13">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="S13">
         <v>1.29</v>
@@ -2449,43 +2449,43 @@
         <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
         <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13">
         <v>2.12</v>
       </c>
       <c r="AC13">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AD13">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE13">
         <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AK13">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,49 +2591,49 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="O14">
         <v>3.6</v>
       </c>
       <c r="P14">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="Q14">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="U14">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB14">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
         <v>2.38</v>
@@ -2642,13 +2642,13 @@
         <v>1.49</v>
       </c>
       <c r="AE14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF14">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG14">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="O15">
-        <v>3.46</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="R15">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="S15">
         <v>1.43</v>
@@ -2784,31 +2784,31 @@
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA15">
         <v>2.18</v>
       </c>
       <c r="AB15">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AC15">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AD15">
         <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG15">
         <v>1.88</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK15">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3569,43 +3569,43 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="O20">
         <v>4</v>
       </c>
       <c r="P20">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="Q20">
         <v>2.22</v>
       </c>
       <c r="R20">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="S20">
+        <v>1.2</v>
+      </c>
+      <c r="T20">
+        <v>4.8</v>
+      </c>
+      <c r="U20">
+        <v>1.97</v>
+      </c>
+      <c r="V20">
+        <v>1.81</v>
+      </c>
+      <c r="W20">
         <v>1.18</v>
       </c>
-      <c r="T20">
-        <v>4.4</v>
-      </c>
-      <c r="U20">
-        <v>2</v>
-      </c>
-      <c r="V20">
-        <v>1.72</v>
-      </c>
-      <c r="W20">
-        <v>1.22</v>
-      </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>1.36</v>
@@ -3614,19 +3614,19 @@
         <v>3.04</v>
       </c>
       <c r="AC20">
+        <v>1.89</v>
+      </c>
+      <c r="AD20">
         <v>1.87</v>
       </c>
-      <c r="AD20">
-        <v>1.83</v>
-      </c>
       <c r="AE20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF20">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O21">
-        <v>4.69</v>
+        <v>4.15</v>
       </c>
       <c r="P21">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Q21">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R21">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="S21">
         <v>1.16</v>
@@ -3753,7 +3753,7 @@
         <v>4.33</v>
       </c>
       <c r="U21">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="V21">
         <v>1.87</v>
@@ -3765,7 +3765,7 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z21">
         <v>6.5</v>
@@ -3774,22 +3774,22 @@
         <v>1.33</v>
       </c>
       <c r="AB21">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC21">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AD21">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AE21">
         <v>1.4</v>
       </c>
       <c r="AF21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O22">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>8.75</v>
+        <v>6.7</v>
       </c>
       <c r="Q22">
         <v>1.68</v>
       </c>
       <c r="R22">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="S22">
+        <v>1.2</v>
+      </c>
+      <c r="T22">
+        <v>3.6</v>
+      </c>
+      <c r="U22">
+        <v>2.03</v>
+      </c>
+      <c r="V22">
+        <v>1.72</v>
+      </c>
+      <c r="W22">
         <v>1.17</v>
       </c>
-      <c r="T22">
-        <v>4.5</v>
-      </c>
-      <c r="U22">
-        <v>2.02</v>
-      </c>
-      <c r="V22">
-        <v>1.66</v>
-      </c>
-      <c r="W22">
-        <v>1.2</v>
-      </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>5.75</v>
+        <v>6.32</v>
       </c>
       <c r="AA22">
         <v>1.4</v>
       </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC22">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AD22">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AE22">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF22">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK22">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,46 +4221,46 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="P24">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="Q24">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="R24">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="V24">
         <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z24">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AA24">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="AB24">
         <v>1.77</v>
@@ -4269,7 +4269,7 @@
         <v>3.25</v>
       </c>
       <c r="AD24">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE24">
         <v>1.04</v>
@@ -4278,7 +4278,7 @@
         <v>1.88</v>
       </c>
       <c r="AG24">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>1.72</v>
       </c>
       <c r="Q26">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S26">
         <v>1.4</v>
@@ -4586,10 +4586,10 @@
         <v>3.05</v>
       </c>
       <c r="AA26">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AB26">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AC26">
         <v>3.5</v>
@@ -4604,7 +4604,7 @@
         <v>1.97</v>
       </c>
       <c r="AG26">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="O27">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>3.91</v>
+        <v>3.25</v>
       </c>
       <c r="Q27">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R27">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
         <v>1.28</v>
@@ -4731,10 +4731,10 @@
         <v>3.28</v>
       </c>
       <c r="U27">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W27">
         <v>1.11</v>
@@ -4746,7 +4746,7 @@
         <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA27">
         <v>1.6</v>
@@ -4761,13 +4761,13 @@
         <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O28">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="Q28">
         <v>2.2</v>
@@ -4888,49 +4888,49 @@
         <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W28">
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB28">
         <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
         <v>1.16</v>
       </c>
       <c r="AF28">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,58 +5199,58 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="O30">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U30">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="V30">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W30">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA30">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AB30">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC30">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AD30">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE30">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
         <v>1.47</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="Q31">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="R31">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U31">
         <v>2.23</v>
@@ -5389,16 +5389,16 @@
         <v>1.5</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AA31">
         <v>1.58</v>
@@ -5407,19 +5407,19 @@
         <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AD31">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AE31">
         <v>1.17</v>
       </c>
       <c r="AF31">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG31">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="O32">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="P32">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q32">
         <v>1.92</v>
       </c>
       <c r="R32">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S32">
         <v>1.31</v>
@@ -5558,7 +5558,7 @@
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
         <v>4.15</v>
@@ -5567,22 +5567,22 @@
         <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC32">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD32">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE32">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG32">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK32">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O37">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P37">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Q37">
         <v>3.3</v>
@@ -6355,10 +6355,10 @@
         <v>1.87</v>
       </c>
       <c r="S37">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T37">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="U37">
         <v>3.25</v>
@@ -6367,16 +6367,16 @@
         <v>1.25</v>
       </c>
       <c r="W37">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Z37">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AA37">
         <v>2.35</v>
@@ -6385,10 +6385,10 @@
         <v>1.53</v>
       </c>
       <c r="AC37">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD37">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE37">
         <v>1</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.76</v>
+        <v>4.97</v>
       </c>
       <c r="O39">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="P39">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q39">
-        <v>4.22</v>
+        <v>5.25</v>
       </c>
       <c r="R39">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V39">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z39">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA39">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB39">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC39">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AD39">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
         <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O41">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="Q41">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S41">
         <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="U41">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="AA41">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB41">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC41">
         <v>2.55</v>
       </c>
       <c r="AD41">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE41">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,49 +7318,49 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="O43">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
       </c>
       <c r="R43">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="S43">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U43">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="V43">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="W43">
         <v>1.2</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z43">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA43">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AB43">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC43">
         <v>1.71</v>
@@ -7369,13 +7369,13 @@
         <v>1.94</v>
       </c>
       <c r="AE43">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AF43">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG43">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,28 +7481,28 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O44">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="P44">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="Q44">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R44">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="S44">
         <v>1.29</v>
       </c>
       <c r="T44">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="U44">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V44">
         <v>1.48</v>
@@ -7511,31 +7511,31 @@
         <v>1.06</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z44">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="AA44">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB44">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC44">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AD44">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE44">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF44">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG44">
         <v>2.2</v>
@@ -7554,7 +7554,7 @@
         <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="O45">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="P45">
         <v>1.9</v>
       </c>
       <c r="Q45">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S45">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U45">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V45">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
         <v>1.03</v>
@@ -7683,10 +7683,10 @@
         <v>3</v>
       </c>
       <c r="AA45">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AB45">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC45">
         <v>3.5</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK45">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="P50">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="Q50">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S50">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z50">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="AA50">
         <v>1.91</v>
       </c>
       <c r="AB50">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC50">
         <v>2.97</v>
       </c>
       <c r="AD50">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
         <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG50">
         <v>1.85</v>
@@ -8532,7 +8532,7 @@
         <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,22 +8631,22 @@
         <v>4.97</v>
       </c>
       <c r="Q51">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R51">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T51">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="U51">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V51">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W51">
         <v>1.13</v>
@@ -8655,28 +8655,28 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
         <v>4.8</v>
       </c>
       <c r="AA51">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB51">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AC51">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AD51">
         <v>1.62</v>
       </c>
       <c r="AE51">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG51">
         <v>2.28</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8812,7 +8812,7 @@
         <v>1.54</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,13 +8821,13 @@
         <v>1.18</v>
       </c>
       <c r="Z52">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA52">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB52">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AC52">
         <v>2.5</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P53">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="Q53">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R53">
         <v>2.21</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T53">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V53">
         <v>1.46</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AA53">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB53">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AC53">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AD53">
         <v>1.42</v>
       </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
         <v>1.63</v>
       </c>
       <c r="AG53">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
         <v>1.25</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O54">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q54">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R54">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9132,13 +9132,13 @@
         <v>4</v>
       </c>
       <c r="U54">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="V54">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W54">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X54">
         <v>1.02</v>
@@ -9147,25 +9147,25 @@
         <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AA54">
         <v>1.41</v>
       </c>
       <c r="AB54">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC54">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AD54">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE54">
         <v>1.27</v>
       </c>
       <c r="AF54">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG54">
         <v>2.88</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
         <v>1.3</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="O55">
         <v>3.03</v>
@@ -9283,16 +9283,16 @@
         <v>3.03</v>
       </c>
       <c r="Q55">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R55">
         <v>1.96</v>
       </c>
       <c r="S55">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T55">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U55">
         <v>3.2</v>
@@ -9301,7 +9301,7 @@
         <v>1.3</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X55">
         <v>1.04</v>
@@ -9310,7 +9310,7 @@
         <v>1.36</v>
       </c>
       <c r="Z55">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA55">
         <v>2.21</v>
@@ -9322,7 +9322,7 @@
         <v>3.8</v>
       </c>
       <c r="AD55">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE55">
         <v>1.03</v>
@@ -9331,7 +9331,7 @@
         <v>1.9</v>
       </c>
       <c r="AG55">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK55">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -13847,55 +13847,55 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="O125">
+        <v>4.07</v>
+      </c>
+      <c r="P125">
         <v>4.31</v>
       </c>
-      <c r="P125">
-        <v>3.36</v>
-      </c>
       <c r="Q125">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="R125">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="S125">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="T125">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U125">
+        <v>1.91</v>
+      </c>
+      <c r="V125">
+        <v>1.8</v>
+      </c>
+      <c r="W125">
+        <v>1.19</v>
+      </c>
+      <c r="X125">
+        <v>0</v>
+      </c>
+      <c r="Y125">
+        <v>1.08</v>
+      </c>
+      <c r="Z125">
+        <v>7</v>
+      </c>
+      <c r="AA125">
+        <v>1.32</v>
+      </c>
+      <c r="AB125">
+        <v>3.1</v>
+      </c>
+      <c r="AC125">
+        <v>1.87</v>
+      </c>
+      <c r="AD125">
         <v>1.85</v>
       </c>
-      <c r="V125">
-        <v>1.91</v>
-      </c>
-      <c r="W125">
-        <v>1.22</v>
-      </c>
-      <c r="X125">
-        <v>0</v>
-      </c>
-      <c r="Y125">
-        <v>1.03</v>
-      </c>
-      <c r="Z125">
-        <v>7.3</v>
-      </c>
-      <c r="AA125">
-        <v>1.3</v>
-      </c>
-      <c r="AB125">
-        <v>3.35</v>
-      </c>
-      <c r="AC125">
-        <v>1.89</v>
-      </c>
-      <c r="AD125">
-        <v>1.83</v>
-      </c>
       <c r="AE125">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF125">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AG125">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,65 +20847,65 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="O126">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
       <c r="P126">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="Q126">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R126">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="S126">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T126">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="U126">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V126">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W126">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X126">
         <v>0</v>
       </c>
       <c r="Y126">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z126">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA126">
         <v>1.3</v>
       </c>
       <c r="AB126">
+        <v>3.35</v>
+      </c>
+      <c r="AC126">
+        <v>1.89</v>
+      </c>
+      <c r="AD126">
+        <v>1.83</v>
+      </c>
+      <c r="AE126">
+        <v>1.44</v>
+      </c>
+      <c r="AF126">
+        <v>1.29</v>
+      </c>
+      <c r="AG126">
         <v>3.4</v>
       </c>
-      <c r="AC126">
-        <v>1.91</v>
-      </c>
-      <c r="AD126">
-        <v>1.81</v>
-      </c>
-      <c r="AE126">
-        <v>1.4</v>
-      </c>
-      <c r="AF126">
-        <v>1.33</v>
-      </c>
-      <c r="AG126">
-        <v>3.2</v>
-      </c>
       <c r="AH126" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK126">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="O127">
-        <v>4.07</v>
+        <v>4.26</v>
       </c>
       <c r="P127">
-        <v>4.31</v>
+        <v>3.27</v>
       </c>
       <c r="Q127">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="R127">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="S127">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T127">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="U127">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V127">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="W127">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X127">
         <v>0</v>
       </c>
       <c r="Y127">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z127">
         <v>7</v>
       </c>
       <c r="AA127">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB127">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AC127">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD127">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE127">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF127">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG127">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK127">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AL127">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -7333,19 +7333,19 @@
         <v>2.43</v>
       </c>
       <c r="S43">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="U43">
         <v>2.02</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W43">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7357,25 +7357,25 @@
         <v>5.7</v>
       </c>
       <c r="AA43">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB43">
         <v>2.75</v>
       </c>
       <c r="AC43">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AD43">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AE43">
         <v>1.27</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AG43">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AK43">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="O51">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
-        <v>4.97</v>
+        <v>2.6</v>
       </c>
       <c r="Q51">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="R51">
+        <v>2.3</v>
+      </c>
+      <c r="S51">
+        <v>1.28</v>
+      </c>
+      <c r="T51">
+        <v>3.28</v>
+      </c>
+      <c r="U51">
+        <v>2.25</v>
+      </c>
+      <c r="V51">
+        <v>1.54</v>
+      </c>
+      <c r="W51">
+        <v>1.11</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
+        <v>1.18</v>
+      </c>
+      <c r="Z51">
+        <v>4.75</v>
+      </c>
+      <c r="AA51">
+        <v>1.61</v>
+      </c>
+      <c r="AB51">
+        <v>2.12</v>
+      </c>
+      <c r="AC51">
         <v>2.5</v>
       </c>
-      <c r="S51">
-        <v>1.24</v>
-      </c>
-      <c r="T51">
-        <v>3.8</v>
-      </c>
-      <c r="U51">
-        <v>2.05</v>
-      </c>
-      <c r="V51">
-        <v>1.61</v>
-      </c>
-      <c r="W51">
-        <v>1.13</v>
-      </c>
-      <c r="X51">
-        <v>1.02</v>
-      </c>
-      <c r="Y51">
-        <v>1.17</v>
-      </c>
-      <c r="Z51">
-        <v>4.8</v>
-      </c>
-      <c r="AA51">
+      <c r="AD51">
         <v>1.45</v>
       </c>
-      <c r="AB51">
-        <v>2.41</v>
-      </c>
-      <c r="AC51">
-        <v>2.24</v>
-      </c>
-      <c r="AD51">
-        <v>1.62</v>
-      </c>
       <c r="AE51">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF51">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG51">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>2.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.34</v>
+        <v>1.56</v>
       </c>
       <c r="O52">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P52">
-        <v>2.6</v>
+        <v>4.97</v>
       </c>
       <c r="Q52">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T52">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="U52">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V52">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA52">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AB52">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="AC52">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AD52">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE52">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF52">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG52">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.5</v>
+        <v>2.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>4.01</v>
+        <v>3.02</v>
       </c>
       <c r="O90">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="P90">
-        <v>1.96</v>
+        <v>2.47</v>
       </c>
       <c r="Q90">
-        <v>4.94</v>
+        <v>3.32</v>
       </c>
       <c r="R90">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="S90">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T90">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U90">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V90">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W90">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X90">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y90">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z90">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AA90">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="AB90">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AC90">
-        <v>5.43</v>
+        <v>5.1</v>
       </c>
       <c r="AD90">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE90">
         <v>1.01</v>
       </c>
       <c r="AF90">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AG90">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AK90">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.41</v>
+        <v>4.01</v>
       </c>
       <c r="O91">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="P91">
-        <v>3.17</v>
+        <v>1.96</v>
       </c>
       <c r="Q91">
-        <v>3.01</v>
+        <v>4.94</v>
       </c>
       <c r="R91">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="S91">
+        <v>1.58</v>
+      </c>
+      <c r="T91">
+        <v>2.45</v>
+      </c>
+      <c r="U91">
+        <v>3.5</v>
+      </c>
+      <c r="V91">
+        <v>1.22</v>
+      </c>
+      <c r="W91">
+        <v>1.04</v>
+      </c>
+      <c r="X91">
+        <v>1.08</v>
+      </c>
+      <c r="Y91">
+        <v>1.53</v>
+      </c>
+      <c r="Z91">
+        <v>2.43</v>
+      </c>
+      <c r="AA91">
+        <v>2.52</v>
+      </c>
+      <c r="AB91">
+        <v>1.41</v>
+      </c>
+      <c r="AC91">
+        <v>5.43</v>
+      </c>
+      <c r="AD91">
+        <v>1.13</v>
+      </c>
+      <c r="AE91">
+        <v>1.01</v>
+      </c>
+      <c r="AF91">
+        <v>2.25</v>
+      </c>
+      <c r="AG91">
+        <v>1.6</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
         <v>1.65</v>
       </c>
-      <c r="T91">
-        <v>2.18</v>
-      </c>
-      <c r="U91">
-        <v>3.92</v>
-      </c>
-      <c r="V91">
+      <c r="AK91">
         <v>1.2</v>
-      </c>
-      <c r="W91">
-        <v>1.03</v>
-      </c>
-      <c r="X91">
-        <v>1.1</v>
-      </c>
-      <c r="Y91">
-        <v>1.63</v>
-      </c>
-      <c r="Z91">
-        <v>2.1</v>
-      </c>
-      <c r="AA91">
-        <v>3.1</v>
-      </c>
-      <c r="AB91">
-        <v>1.33</v>
-      </c>
-      <c r="AC91">
-        <v>6.22</v>
-      </c>
-      <c r="AD91">
-        <v>1.11</v>
-      </c>
-      <c r="AE91">
-        <v>1.03</v>
-      </c>
-      <c r="AF91">
-        <v>2.32</v>
-      </c>
-      <c r="AG91">
-        <v>1.53</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.35</v>
-      </c>
-      <c r="AK91">
-        <v>1.55</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.02</v>
+        <v>2.41</v>
       </c>
       <c r="O92">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="P92">
-        <v>2.47</v>
+        <v>3.17</v>
       </c>
       <c r="Q92">
-        <v>3.32</v>
+        <v>3.01</v>
       </c>
       <c r="R92">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="S92">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="T92">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="U92">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="V92">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W92">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y92">
+        <v>1.63</v>
+      </c>
+      <c r="Z92">
+        <v>2.1</v>
+      </c>
+      <c r="AA92">
+        <v>3.1</v>
+      </c>
+      <c r="AB92">
+        <v>1.33</v>
+      </c>
+      <c r="AC92">
+        <v>6.22</v>
+      </c>
+      <c r="AD92">
+        <v>1.11</v>
+      </c>
+      <c r="AE92">
+        <v>1.03</v>
+      </c>
+      <c r="AF92">
+        <v>2.32</v>
+      </c>
+      <c r="AG92">
+        <v>1.53</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.35</v>
+      </c>
+      <c r="AK92">
         <v>1.55</v>
-      </c>
-      <c r="Z92">
-        <v>2.25</v>
-      </c>
-      <c r="AA92">
-        <v>2.87</v>
-      </c>
-      <c r="AB92">
-        <v>1.46</v>
-      </c>
-      <c r="AC92">
-        <v>5.1</v>
-      </c>
-      <c r="AD92">
-        <v>1.1</v>
-      </c>
-      <c r="AE92">
-        <v>1.01</v>
-      </c>
-      <c r="AF92">
-        <v>2.09</v>
-      </c>
-      <c r="AG92">
-        <v>1.63</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.36</v>
-      </c>
-      <c r="AK92">
-        <v>1.44</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="O108">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="P108">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q108">
         <v>3.45</v>
@@ -17928,10 +17928,10 @@
         <v>1.94</v>
       </c>
       <c r="S108">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T108">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U108">
         <v>3.12</v>
@@ -17940,34 +17940,34 @@
         <v>1.29</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X108">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z108">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AA108">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AB108">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC108">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="AD108">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE108">
         <v>1.03</v>
       </c>
       <c r="AF108">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG108">
         <v>1.82</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,80 +20684,80 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="O125">
-        <v>4.07</v>
+        <v>4.31</v>
       </c>
       <c r="P125">
-        <v>4.31</v>
+        <v>3.36</v>
       </c>
       <c r="Q125">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="R125">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="S125">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="T125">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U125">
+        <v>1.85</v>
+      </c>
+      <c r="V125">
         <v>1.91</v>
       </c>
-      <c r="V125">
-        <v>1.8</v>
-      </c>
       <c r="W125">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X125">
         <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z125">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA125">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB125">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AC125">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AD125">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE125">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF125">
+        <v>1.29</v>
+      </c>
+      <c r="AG125">
+        <v>3.4</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
         <v>1.36</v>
       </c>
-      <c r="AG125">
-        <v>2.88</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.2</v>
-      </c>
       <c r="AK125">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="O126">
+        <v>4.07</v>
+      </c>
+      <c r="P126">
         <v>4.31</v>
       </c>
-      <c r="P126">
-        <v>3.36</v>
-      </c>
       <c r="Q126">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="R126">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="S126">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="T126">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U126">
+        <v>1.91</v>
+      </c>
+      <c r="V126">
+        <v>1.8</v>
+      </c>
+      <c r="W126">
+        <v>1.19</v>
+      </c>
+      <c r="X126">
+        <v>0</v>
+      </c>
+      <c r="Y126">
+        <v>1.08</v>
+      </c>
+      <c r="Z126">
+        <v>7</v>
+      </c>
+      <c r="AA126">
+        <v>1.32</v>
+      </c>
+      <c r="AB126">
+        <v>3.1</v>
+      </c>
+      <c r="AC126">
+        <v>1.87</v>
+      </c>
+      <c r="AD126">
         <v>1.85</v>
       </c>
-      <c r="V126">
-        <v>1.91</v>
-      </c>
-      <c r="W126">
-        <v>1.22</v>
-      </c>
-      <c r="X126">
-        <v>0</v>
-      </c>
-      <c r="Y126">
-        <v>1.03</v>
-      </c>
-      <c r="Z126">
-        <v>7.3</v>
-      </c>
-      <c r="AA126">
-        <v>1.3</v>
-      </c>
-      <c r="AB126">
-        <v>3.35</v>
-      </c>
-      <c r="AC126">
-        <v>1.89</v>
-      </c>
-      <c r="AD126">
-        <v>1.83</v>
-      </c>
       <c r="AE126">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF126">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AG126">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK126">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AL126">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -11882,31 +11882,31 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="O71">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P71">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q71">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R71">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S71">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="U71">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V71">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W71">
         <v>1.06</v>
@@ -11915,31 +11915,31 @@
         <v>1.01</v>
       </c>
       <c r="Y71">
+        <v>1.26</v>
+      </c>
+      <c r="Z71">
+        <v>3.2</v>
+      </c>
+      <c r="AA71">
+        <v>1.95</v>
+      </c>
+      <c r="AB71">
+        <v>1.87</v>
+      </c>
+      <c r="AC71">
+        <v>3.27</v>
+      </c>
+      <c r="AD71">
         <v>1.27</v>
       </c>
-      <c r="Z71">
-        <v>3.14</v>
-      </c>
-      <c r="AA71">
-        <v>2.05</v>
-      </c>
-      <c r="AB71">
-        <v>1.75</v>
-      </c>
-      <c r="AC71">
-        <v>3.2</v>
-      </c>
-      <c r="AD71">
-        <v>1.26</v>
-      </c>
       <c r="AE71">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF71">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG71">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G81">
@@ -13521,55 +13521,55 @@
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G82">
@@ -13684,55 +13684,55 @@
         <v>0</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14490,55 +14490,55 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="O87">
         <v>2.65</v>
       </c>
       <c r="P87">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q87">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R87">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S87">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="T87">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U87">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="V87">
         <v>1.16</v>
       </c>
       <c r="W87">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X87">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y87">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Z87">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AA87">
         <v>3.5</v>
       </c>
       <c r="AB87">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AC87">
         <v>5.8</v>
       </c>
       <c r="AD87">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE87">
         <v>1.02</v>
@@ -14547,7 +14547,7 @@
         <v>2.4</v>
       </c>
       <c r="AG87">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AK87">
         <v>1.4</v>
@@ -14653,28 +14653,28 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="O88">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="P88">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="Q88">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R88">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S88">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="T88">
         <v>1.95</v>
       </c>
       <c r="U88">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="V88">
         <v>1.17</v>
@@ -14683,19 +14683,19 @@
         <v>1.02</v>
       </c>
       <c r="X88">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y88">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Z88">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AA88">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB88">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC88">
         <v>6.4</v>
@@ -14707,10 +14707,10 @@
         <v>1.02</v>
       </c>
       <c r="AF88">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AG88">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK88">
         <v>1.36</v>
@@ -14816,55 +14816,55 @@
         </is>
       </c>
       <c r="N89">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="O89">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P89">
-        <v>3.97</v>
+        <v>4.65</v>
       </c>
       <c r="Q89">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R89">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="S89">
         <v>1.64</v>
       </c>
       <c r="T89">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="U89">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="V89">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W89">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y89">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z89">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AA89">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="AB89">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC89">
         <v>5.25</v>
       </c>
       <c r="AD89">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE89">
         <v>1.03</v>
@@ -14873,7 +14873,7 @@
         <v>2.34</v>
       </c>
       <c r="AG89">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="O90">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P90">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q90">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S90">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T90">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="U90">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="V90">
         <v>1.25</v>
       </c>
       <c r="W90">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X90">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y90">
         <v>1.55</v>
       </c>
       <c r="Z90">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AA90">
         <v>2.87</v>
       </c>
       <c r="AB90">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AC90">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="AD90">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE90">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF90">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AG90">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK90">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>4.01</v>
+        <v>2.25</v>
       </c>
       <c r="O91">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="P91">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q91">
-        <v>4.94</v>
+        <v>3.01</v>
       </c>
       <c r="R91">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="S91">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T91">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="U91">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="V91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y91">
+        <v>1.62</v>
+      </c>
+      <c r="Z91">
+        <v>2.16</v>
+      </c>
+      <c r="AA91">
+        <v>2.81</v>
+      </c>
+      <c r="AB91">
+        <v>1.36</v>
+      </c>
+      <c r="AC91">
+        <v>6.22</v>
+      </c>
+      <c r="AD91">
+        <v>1.11</v>
+      </c>
+      <c r="AE91">
+        <v>1.03</v>
+      </c>
+      <c r="AF91">
+        <v>2.32</v>
+      </c>
+      <c r="AG91">
+        <v>1.57</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
+        <v>1.33</v>
+      </c>
+      <c r="AK91">
         <v>1.53</v>
-      </c>
-      <c r="Z91">
-        <v>2.43</v>
-      </c>
-      <c r="AA91">
-        <v>2.52</v>
-      </c>
-      <c r="AB91">
-        <v>1.41</v>
-      </c>
-      <c r="AC91">
-        <v>5.43</v>
-      </c>
-      <c r="AD91">
-        <v>1.13</v>
-      </c>
-      <c r="AE91">
-        <v>1.01</v>
-      </c>
-      <c r="AF91">
-        <v>2.25</v>
-      </c>
-      <c r="AG91">
-        <v>1.6</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.65</v>
-      </c>
-      <c r="AK91">
-        <v>1.2</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.41</v>
+        <v>4.01</v>
       </c>
       <c r="O92">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="P92">
-        <v>3.17</v>
+        <v>1.96</v>
       </c>
       <c r="Q92">
-        <v>3.01</v>
+        <v>4.94</v>
       </c>
       <c r="R92">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S92">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="T92">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="U92">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="V92">
+        <v>1.25</v>
+      </c>
+      <c r="W92">
+        <v>1</v>
+      </c>
+      <c r="X92">
+        <v>1.08</v>
+      </c>
+      <c r="Y92">
+        <v>1.52</v>
+      </c>
+      <c r="Z92">
+        <v>2.43</v>
+      </c>
+      <c r="AA92">
+        <v>2.48</v>
+      </c>
+      <c r="AB92">
+        <v>1.46</v>
+      </c>
+      <c r="AC92">
+        <v>4.7</v>
+      </c>
+      <c r="AD92">
+        <v>1.14</v>
+      </c>
+      <c r="AE92">
+        <v>1.04</v>
+      </c>
+      <c r="AF92">
+        <v>2.17</v>
+      </c>
+      <c r="AG92">
+        <v>1.6</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.73</v>
+      </c>
+      <c r="AK92">
         <v>1.2</v>
-      </c>
-      <c r="W92">
-        <v>1.03</v>
-      </c>
-      <c r="X92">
-        <v>1.1</v>
-      </c>
-      <c r="Y92">
-        <v>1.63</v>
-      </c>
-      <c r="Z92">
-        <v>2.1</v>
-      </c>
-      <c r="AA92">
-        <v>3.1</v>
-      </c>
-      <c r="AB92">
-        <v>1.33</v>
-      </c>
-      <c r="AC92">
-        <v>6.22</v>
-      </c>
-      <c r="AD92">
-        <v>1.11</v>
-      </c>
-      <c r="AE92">
-        <v>1.03</v>
-      </c>
-      <c r="AF92">
-        <v>2.32</v>
-      </c>
-      <c r="AG92">
-        <v>1.53</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.35</v>
-      </c>
-      <c r="AK92">
-        <v>1.55</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17113,16 +17113,16 @@
         <v>1.98</v>
       </c>
       <c r="S103">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T103">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U103">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="V103">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W103">
         <v>1.03</v>
@@ -17131,31 +17131,31 @@
         <v>1.1</v>
       </c>
       <c r="Y103">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z103">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AA103">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AB103">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC103">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
       <c r="AD103">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE103">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF103">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AG103">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AK103">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P106">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q106">
         <v>4</v>
@@ -17602,49 +17602,49 @@
         <v>2.2</v>
       </c>
       <c r="S106">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U106">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="V106">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W106">
         <v>1.1</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y106">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z106">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
         <v>1.85</v>
       </c>
       <c r="AB106">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AC106">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="AD106">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE106">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF106">
         <v>1.7</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="O113">
         <v>3.2</v>
@@ -18737,46 +18737,46 @@
         <v>2.5</v>
       </c>
       <c r="Q113">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R113">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S113">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T113">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="U113">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V113">
         <v>1.32</v>
       </c>
       <c r="W113">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X113">
         <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z113">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AA113">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB113">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC113">
         <v>3.7</v>
       </c>
       <c r="AD113">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE113">
         <v>1.04</v>
@@ -18801,7 +18801,7 @@
         <v>1.27</v>
       </c>
       <c r="AK113">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL113">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -5371,10 +5371,10 @@
         <v>3.4</v>
       </c>
       <c r="Q31">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="R31">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="S31">
         <v>1.3</v>
@@ -5398,28 +5398,28 @@
         <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="AA31">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB31">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD31">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG31">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>2.47</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11402,25 +11402,25 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R68">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S68">
+        <v>1.35</v>
+      </c>
+      <c r="T68">
+        <v>2.79</v>
+      </c>
+      <c r="U68">
+        <v>2.75</v>
+      </c>
+      <c r="V68">
         <v>1.36</v>
       </c>
-      <c r="T68">
-        <v>2.9</v>
-      </c>
-      <c r="U68">
-        <v>2.88</v>
-      </c>
-      <c r="V68">
-        <v>1.4</v>
-      </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11432,10 +11432,10 @@
         <v>3.28</v>
       </c>
       <c r="AA68">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB68">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC68">
         <v>3.2</v>
@@ -11447,7 +11447,7 @@
         <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG68">
         <v>2.05</v>
@@ -11466,7 +11466,7 @@
         <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>2.77</v>
       </c>
       <c r="R69">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S69">
         <v>1.31</v>
@@ -11577,7 +11577,7 @@
         <v>2.97</v>
       </c>
       <c r="U69">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="V69">
         <v>1.44</v>
@@ -11595,10 +11595,10 @@
         <v>3.74</v>
       </c>
       <c r="AA69">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB69">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC69">
         <v>2.69</v>
@@ -13032,55 +13032,55 @@
         <v>3.58</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>4.17</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>2.88</v>
+      </c>
+      <c r="R80">
+        <v>1.91</v>
+      </c>
+      <c r="S80">
+        <v>1.47</v>
+      </c>
+      <c r="T80">
+        <v>2.55</v>
+      </c>
+      <c r="U80">
+        <v>3.3</v>
+      </c>
+      <c r="V80">
+        <v>1.29</v>
+      </c>
+      <c r="W80">
+        <v>1.05</v>
+      </c>
+      <c r="X80">
+        <v>1.04</v>
+      </c>
+      <c r="Y80">
         <v>1.41</v>
       </c>
-      <c r="O80">
-        <v>4.25</v>
-      </c>
-      <c r="P80">
-        <v>6.35</v>
-      </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>0</v>
-      </c>
-      <c r="S80">
-        <v>0</v>
-      </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>0</v>
-      </c>
       <c r="Z80">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G81">
@@ -13521,55 +13521,55 @@
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="R81">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="T81">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U81">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="V81">
+        <v>1.36</v>
+      </c>
+      <c r="W81">
+        <v>1.08</v>
+      </c>
+      <c r="X81">
+        <v>1.02</v>
+      </c>
+      <c r="Y81">
         <v>1.26</v>
       </c>
-      <c r="W81">
-        <v>1.05</v>
-      </c>
-      <c r="X81">
-        <v>1.04</v>
-      </c>
-      <c r="Y81">
-        <v>1.41</v>
-      </c>
       <c r="Z81">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="AA81">
-        <v>2.34</v>
+        <v>1.89</v>
       </c>
       <c r="AB81">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC81">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AD81">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AE81">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF81">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AG81">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Q82">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U82">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="V82">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W82">
         <v>1.08</v>
@@ -13708,31 +13708,31 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA82">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AB82">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC82">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AD82">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE82">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF82">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG82">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK82">
-        <v>1.73</v>
+        <v>2.78</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.25</v>
+        <v>4.01</v>
       </c>
       <c r="O91">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="P91">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q91">
-        <v>3.01</v>
+        <v>4.94</v>
       </c>
       <c r="R91">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S91">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T91">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="U91">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="V91">
+        <v>1.25</v>
+      </c>
+      <c r="W91">
+        <v>1</v>
+      </c>
+      <c r="X91">
+        <v>1.08</v>
+      </c>
+      <c r="Y91">
+        <v>1.52</v>
+      </c>
+      <c r="Z91">
+        <v>2.43</v>
+      </c>
+      <c r="AA91">
+        <v>2.48</v>
+      </c>
+      <c r="AB91">
+        <v>1.46</v>
+      </c>
+      <c r="AC91">
+        <v>4.7</v>
+      </c>
+      <c r="AD91">
+        <v>1.14</v>
+      </c>
+      <c r="AE91">
+        <v>1.04</v>
+      </c>
+      <c r="AF91">
+        <v>2.17</v>
+      </c>
+      <c r="AG91">
+        <v>1.6</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
+        <v>1.73</v>
+      </c>
+      <c r="AK91">
         <v>1.2</v>
-      </c>
-      <c r="W91">
-        <v>1.03</v>
-      </c>
-      <c r="X91">
-        <v>1.14</v>
-      </c>
-      <c r="Y91">
-        <v>1.62</v>
-      </c>
-      <c r="Z91">
-        <v>2.16</v>
-      </c>
-      <c r="AA91">
-        <v>2.81</v>
-      </c>
-      <c r="AB91">
-        <v>1.36</v>
-      </c>
-      <c r="AC91">
-        <v>6.22</v>
-      </c>
-      <c r="AD91">
-        <v>1.11</v>
-      </c>
-      <c r="AE91">
-        <v>1.03</v>
-      </c>
-      <c r="AF91">
-        <v>2.32</v>
-      </c>
-      <c r="AG91">
-        <v>1.57</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.33</v>
-      </c>
-      <c r="AK91">
-        <v>1.53</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>4.01</v>
+        <v>2.25</v>
       </c>
       <c r="O92">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="P92">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q92">
-        <v>4.94</v>
+        <v>3.01</v>
       </c>
       <c r="R92">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S92">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T92">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U92">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="V92">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W92">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y92">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z92">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AA92">
-        <v>2.48</v>
+        <v>2.81</v>
       </c>
       <c r="AB92">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AC92">
-        <v>4.7</v>
+        <v>6.22</v>
       </c>
       <c r="AD92">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE92">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF92">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AG92">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK92">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17913,10 +17913,10 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O108">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P108">
         <v>2.3</v>
@@ -17928,13 +17928,13 @@
         <v>1.94</v>
       </c>
       <c r="S108">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T108">
         <v>2.75</v>
       </c>
       <c r="U108">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="V108">
         <v>1.29</v>
@@ -17949,19 +17949,19 @@
         <v>1.35</v>
       </c>
       <c r="Z108">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="AA108">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AB108">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC108">
-        <v>3.89</v>
+        <v>4.08</v>
       </c>
       <c r="AD108">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE108">
         <v>1.03</v>
@@ -18891,49 +18891,49 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O114">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="P114">
-        <v>6.73</v>
+        <v>6.3</v>
       </c>
       <c r="Q114">
         <v>1.95</v>
       </c>
       <c r="R114">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S114">
         <v>1.33</v>
       </c>
       <c r="T114">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="U114">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V114">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W114">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z114">
         <v>3.58</v>
       </c>
       <c r="AA114">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AB114">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC114">
         <v>2.92</v>
@@ -18945,7 +18945,7 @@
         <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG114">
         <v>1.74</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK114">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="O125">
+        <v>4.07</v>
+      </c>
+      <c r="P125">
         <v>4.31</v>
       </c>
-      <c r="P125">
-        <v>3.36</v>
-      </c>
       <c r="Q125">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="R125">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="S125">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="T125">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U125">
+        <v>1.91</v>
+      </c>
+      <c r="V125">
+        <v>1.8</v>
+      </c>
+      <c r="W125">
+        <v>1.19</v>
+      </c>
+      <c r="X125">
+        <v>0</v>
+      </c>
+      <c r="Y125">
+        <v>1.08</v>
+      </c>
+      <c r="Z125">
+        <v>7</v>
+      </c>
+      <c r="AA125">
+        <v>1.32</v>
+      </c>
+      <c r="AB125">
+        <v>3.1</v>
+      </c>
+      <c r="AC125">
+        <v>1.87</v>
+      </c>
+      <c r="AD125">
         <v>1.85</v>
       </c>
-      <c r="V125">
-        <v>1.91</v>
-      </c>
-      <c r="W125">
-        <v>1.22</v>
-      </c>
-      <c r="X125">
-        <v>0</v>
-      </c>
-      <c r="Y125">
-        <v>1.03</v>
-      </c>
-      <c r="Z125">
-        <v>7.3</v>
-      </c>
-      <c r="AA125">
-        <v>1.3</v>
-      </c>
-      <c r="AB125">
-        <v>3.35</v>
-      </c>
-      <c r="AC125">
-        <v>1.89</v>
-      </c>
-      <c r="AD125">
-        <v>1.83</v>
-      </c>
       <c r="AE125">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF125">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AG125">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,80 +20847,80 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="O126">
-        <v>4.07</v>
+        <v>4.31</v>
       </c>
       <c r="P126">
-        <v>4.31</v>
+        <v>3.36</v>
       </c>
       <c r="Q126">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="R126">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="S126">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="T126">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U126">
+        <v>1.85</v>
+      </c>
+      <c r="V126">
         <v>1.91</v>
       </c>
-      <c r="V126">
-        <v>1.8</v>
-      </c>
       <c r="W126">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X126">
         <v>0</v>
       </c>
       <c r="Y126">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z126">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA126">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB126">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AC126">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AD126">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE126">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF126">
+        <v>1.29</v>
+      </c>
+      <c r="AG126">
+        <v>3.4</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
         <v>1.36</v>
       </c>
-      <c r="AG126">
-        <v>2.88</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.2</v>
-      </c>
       <c r="AK126">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AL126">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -4263,7 +4263,7 @@
         <v>2.11</v>
       </c>
       <c r="AB24">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
         <v>3.6</v>
@@ -4275,7 +4275,7 @@
         <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AG24">
         <v>1.84</v>
@@ -5890,10 +5890,10 @@
         <v>3.84</v>
       </c>
       <c r="AA34">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC34">
         <v>2.7</v>
@@ -9778,19 +9778,19 @@
         <v>2</v>
       </c>
       <c r="S58">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U58">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V58">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
         <v>1.04</v>
@@ -9799,7 +9799,7 @@
         <v>1.36</v>
       </c>
       <c r="Z58">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA58">
         <v>2.21</v>
@@ -9836,7 +9836,7 @@
         <v>1.35</v>
       </c>
       <c r="AK58">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O75">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P75">
         <v>12</v>
@@ -12555,7 +12555,7 @@
         <v>3.23</v>
       </c>
       <c r="U75">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V75">
         <v>1.47</v>
@@ -12564,7 +12564,7 @@
         <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
         <v>1.18</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Q86">
-        <v>2.58</v>
+        <v>1.8</v>
       </c>
       <c r="R86">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T86">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U86">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V86">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W86">
         <v>1.08</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z86">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA86">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AB86">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC86">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD86">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE86">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF86">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG86">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK86">
-        <v>1.73</v>
+        <v>2.78</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>1.8</v>
+        <v>2.58</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S87">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T87">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U87">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V87">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
         <v>1.08</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z87">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA87">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AB87">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC87">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD87">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE87">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG87">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK87">
-        <v>2.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.01</v>
+        <v>2.3</v>
       </c>
       <c r="O96">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="P96">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q96">
-        <v>4.94</v>
+        <v>3.01</v>
       </c>
       <c r="R96">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S96">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T96">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U96">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="V96">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W96">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X96">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y96">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z96">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AA96">
-        <v>2.48</v>
+        <v>2.81</v>
       </c>
       <c r="AB96">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AC96">
-        <v>4.7</v>
+        <v>6.22</v>
       </c>
       <c r="AD96">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE96">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AG96">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK96">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.3</v>
+        <v>4.01</v>
       </c>
       <c r="O97">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="P97">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q97">
-        <v>3.01</v>
+        <v>4.94</v>
       </c>
       <c r="R97">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S97">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T97">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="U97">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="V97">
+        <v>1.25</v>
+      </c>
+      <c r="W97">
+        <v>1</v>
+      </c>
+      <c r="X97">
+        <v>1.08</v>
+      </c>
+      <c r="Y97">
+        <v>1.52</v>
+      </c>
+      <c r="Z97">
+        <v>2.43</v>
+      </c>
+      <c r="AA97">
+        <v>2.48</v>
+      </c>
+      <c r="AB97">
+        <v>1.46</v>
+      </c>
+      <c r="AC97">
+        <v>4.7</v>
+      </c>
+      <c r="AD97">
+        <v>1.14</v>
+      </c>
+      <c r="AE97">
+        <v>1.04</v>
+      </c>
+      <c r="AF97">
+        <v>2.17</v>
+      </c>
+      <c r="AG97">
+        <v>1.6</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.73</v>
+      </c>
+      <c r="AK97">
         <v>1.2</v>
-      </c>
-      <c r="W97">
-        <v>1.03</v>
-      </c>
-      <c r="X97">
-        <v>1.14</v>
-      </c>
-      <c r="Y97">
-        <v>1.62</v>
-      </c>
-      <c r="Z97">
-        <v>2.16</v>
-      </c>
-      <c r="AA97">
-        <v>2.81</v>
-      </c>
-      <c r="AB97">
-        <v>1.36</v>
-      </c>
-      <c r="AC97">
-        <v>6.22</v>
-      </c>
-      <c r="AD97">
-        <v>1.11</v>
-      </c>
-      <c r="AE97">
-        <v>1.03</v>
-      </c>
-      <c r="AF97">
-        <v>2.32</v>
-      </c>
-      <c r="AG97">
-        <v>1.57</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.33</v>
-      </c>
-      <c r="AK97">
-        <v>1.53</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O106">
         <v>3.3</v>
@@ -17614,7 +17614,7 @@
         <v>1.36</v>
       </c>
       <c r="W106">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X106">
         <v>1.01</v>
@@ -17626,10 +17626,10 @@
         <v>3.1</v>
       </c>
       <c r="AA106">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB106">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC106">
         <v>3.42</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
+        <v>1.57</v>
+      </c>
+      <c r="O20">
+        <v>4.6</v>
+      </c>
+      <c r="P20">
+        <v>4.25</v>
+      </c>
+      <c r="Q20">
         <v>1.94</v>
       </c>
-      <c r="O20">
-        <v>4</v>
-      </c>
-      <c r="P20">
-        <v>3.2</v>
-      </c>
-      <c r="Q20">
-        <v>2.4</v>
-      </c>
       <c r="R20">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S20">
         <v>1.18</v>
       </c>
       <c r="T20">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U20">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="V20">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,28 +3605,28 @@
         <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="AC20">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AD20">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AE20">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="O21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
         <v>1.18</v>
       </c>
       <c r="T21">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U21">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V21">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="W21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,28 +3768,28 @@
         <v>1.06</v>
       </c>
       <c r="Z21">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
+        <v>1.36</v>
+      </c>
+      <c r="AB21">
+        <v>3.07</v>
+      </c>
+      <c r="AC21">
+        <v>1.93</v>
+      </c>
+      <c r="AD21">
+        <v>1.8</v>
+      </c>
+      <c r="AE21">
         <v>1.33</v>
       </c>
-      <c r="AB21">
-        <v>3.2</v>
-      </c>
-      <c r="AC21">
-        <v>1.82</v>
-      </c>
-      <c r="AD21">
-        <v>1.86</v>
-      </c>
-      <c r="AE21">
-        <v>1.4</v>
-      </c>
       <c r="AF21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG21">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK21">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R52">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U52">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V52">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA52">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AB52">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AC52">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="AD52">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G53">
@@ -8957,55 +8957,55 @@
         <v>0</v>
       </c>
       <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>1.8</v>
+      </c>
+      <c r="AB53">
         <v>2</v>
       </c>
-      <c r="R53">
-        <v>2.3</v>
-      </c>
-      <c r="S53">
-        <v>1.32</v>
-      </c>
-      <c r="T53">
-        <v>3.24</v>
-      </c>
-      <c r="U53">
-        <v>2.45</v>
-      </c>
-      <c r="V53">
-        <v>1.45</v>
-      </c>
-      <c r="W53">
-        <v>1.08</v>
-      </c>
-      <c r="X53">
-        <v>1.04</v>
-      </c>
-      <c r="Y53">
-        <v>1.17</v>
-      </c>
-      <c r="Z53">
-        <v>4</v>
-      </c>
-      <c r="AA53">
-        <v>1.68</v>
-      </c>
-      <c r="AB53">
-        <v>2.12</v>
-      </c>
       <c r="AC53">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD53">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF53">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK53">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="P54">
-        <v>2.55</v>
+        <v>4.7</v>
       </c>
       <c r="Q54">
-        <v>2.91</v>
+        <v>2.03</v>
       </c>
       <c r="R54">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="U54">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="V54">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="W54">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA54">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AB54">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="AC54">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="AD54">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AE54">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AF54">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG54">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK54">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="O55">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>4.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q55">
-        <v>2.03</v>
+        <v>2.91</v>
       </c>
       <c r="R55">
+        <v>2.41</v>
+      </c>
+      <c r="S55">
+        <v>1.29</v>
+      </c>
+      <c r="T55">
+        <v>3.22</v>
+      </c>
+      <c r="U55">
+        <v>2.25</v>
+      </c>
+      <c r="V55">
+        <v>1.54</v>
+      </c>
+      <c r="W55">
+        <v>1.12</v>
+      </c>
+      <c r="X55">
+        <v>1.01</v>
+      </c>
+      <c r="Y55">
+        <v>1.15</v>
+      </c>
+      <c r="Z55">
+        <v>4.75</v>
+      </c>
+      <c r="AA55">
+        <v>1.61</v>
+      </c>
+      <c r="AB55">
+        <v>2.28</v>
+      </c>
+      <c r="AC55">
+        <v>2.47</v>
+      </c>
+      <c r="AD55">
+        <v>1.45</v>
+      </c>
+      <c r="AE55">
+        <v>1.19</v>
+      </c>
+      <c r="AF55">
+        <v>1.49</v>
+      </c>
+      <c r="AG55">
         <v>2.5</v>
       </c>
-      <c r="S55">
-        <v>1.22</v>
-      </c>
-      <c r="T55">
-        <v>3.8</v>
-      </c>
-      <c r="U55">
-        <v>2.13</v>
-      </c>
-      <c r="V55">
-        <v>1.67</v>
-      </c>
-      <c r="W55">
-        <v>1.15</v>
-      </c>
-      <c r="X55">
-        <v>1.02</v>
-      </c>
-      <c r="Y55">
-        <v>1.1</v>
-      </c>
-      <c r="Z55">
-        <v>5.5</v>
-      </c>
-      <c r="AA55">
-        <v>1.43</v>
-      </c>
-      <c r="AB55">
-        <v>2.49</v>
-      </c>
-      <c r="AC55">
-        <v>2.16</v>
-      </c>
-      <c r="AD55">
-        <v>1.66</v>
-      </c>
-      <c r="AE55">
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
         <v>1.26</v>
       </c>
-      <c r="AF55">
-        <v>1.51</v>
-      </c>
-      <c r="AG55">
-        <v>2.39</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.17</v>
-      </c>
       <c r="AK55">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O96">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P96">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q96">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="R96">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S96">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="T96">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="U96">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="V96">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W96">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X96">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y96">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Z96">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="AA96">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="AB96">
+        <v>1.27</v>
+      </c>
+      <c r="AC96">
+        <v>6.45</v>
+      </c>
+      <c r="AD96">
+        <v>1.05</v>
+      </c>
+      <c r="AE96">
+        <v>1.02</v>
+      </c>
+      <c r="AF96">
+        <v>2.45</v>
+      </c>
+      <c r="AG96">
+        <v>1.48</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.4</v>
+      </c>
+      <c r="AK96">
         <v>1.36</v>
-      </c>
-      <c r="AC96">
-        <v>6.22</v>
-      </c>
-      <c r="AD96">
-        <v>1.11</v>
-      </c>
-      <c r="AE96">
-        <v>1.03</v>
-      </c>
-      <c r="AF96">
-        <v>2.32</v>
-      </c>
-      <c r="AG96">
-        <v>1.57</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.33</v>
-      </c>
-      <c r="AK96">
-        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>4.01</v>
+        <v>2.3</v>
       </c>
       <c r="O97">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="P97">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q97">
-        <v>4.94</v>
+        <v>3.01</v>
       </c>
       <c r="R97">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S97">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T97">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U97">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="V97">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W97">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X97">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y97">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z97">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AA97">
-        <v>2.48</v>
+        <v>2.81</v>
       </c>
       <c r="AB97">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AC97">
-        <v>4.7</v>
+        <v>6.22</v>
       </c>
       <c r="AD97">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE97">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AG97">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.8</v>
+        <v>4.01</v>
       </c>
       <c r="O98">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="P98">
-        <v>2.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q98">
-        <v>3.6</v>
+        <v>4.94</v>
       </c>
       <c r="R98">
         <v>1.8</v>
       </c>
       <c r="S98">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T98">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="U98">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="V98">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W98">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X98">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y98">
+        <v>1.52</v>
+      </c>
+      <c r="Z98">
+        <v>2.43</v>
+      </c>
+      <c r="AA98">
+        <v>2.48</v>
+      </c>
+      <c r="AB98">
+        <v>1.46</v>
+      </c>
+      <c r="AC98">
+        <v>4.7</v>
+      </c>
+      <c r="AD98">
+        <v>1.14</v>
+      </c>
+      <c r="AE98">
+        <v>1.04</v>
+      </c>
+      <c r="AF98">
+        <v>2.17</v>
+      </c>
+      <c r="AG98">
+        <v>1.6</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
         <v>1.73</v>
       </c>
-      <c r="Z98">
-        <v>2.01</v>
-      </c>
-      <c r="AA98">
-        <v>3.14</v>
-      </c>
-      <c r="AB98">
-        <v>1.27</v>
-      </c>
-      <c r="AC98">
-        <v>6.45</v>
-      </c>
-      <c r="AD98">
-        <v>1.05</v>
-      </c>
-      <c r="AE98">
-        <v>1.02</v>
-      </c>
-      <c r="AF98">
-        <v>2.45</v>
-      </c>
-      <c r="AG98">
-        <v>1.48</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.4</v>
-      </c>
       <c r="AK98">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,80 +21662,80 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="O131">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P131">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="Q131">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="R131">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="S131">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T131">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="U131">
+        <v>1.86</v>
+      </c>
+      <c r="V131">
+        <v>1.98</v>
+      </c>
+      <c r="W131">
+        <v>1.29</v>
+      </c>
+      <c r="X131">
+        <v>0</v>
+      </c>
+      <c r="Y131">
+        <v>1.09</v>
+      </c>
+      <c r="Z131">
+        <v>8</v>
+      </c>
+      <c r="AA131">
+        <v>1.29</v>
+      </c>
+      <c r="AB131">
+        <v>3.35</v>
+      </c>
+      <c r="AC131">
+        <v>1.8</v>
+      </c>
+      <c r="AD131">
         <v>2</v>
       </c>
-      <c r="V131">
+      <c r="AE131">
+        <v>1.46</v>
+      </c>
+      <c r="AF131">
+        <v>1.29</v>
+      </c>
+      <c r="AG131">
+        <v>3.3</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
+        <v>1.21</v>
+      </c>
+      <c r="AK131">
         <v>1.8</v>
-      </c>
-      <c r="W131">
-        <v>1.19</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>1.06</v>
-      </c>
-      <c r="Z131">
-        <v>6.8</v>
-      </c>
-      <c r="AA131">
-        <v>1.33</v>
-      </c>
-      <c r="AB131">
-        <v>3.1</v>
-      </c>
-      <c r="AC131">
-        <v>1.9</v>
-      </c>
-      <c r="AD131">
-        <v>1.85</v>
-      </c>
-      <c r="AE131">
-        <v>1.33</v>
-      </c>
-      <c r="AF131">
-        <v>1.38</v>
-      </c>
-      <c r="AG131">
-        <v>2.88</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>1.2</v>
-      </c>
-      <c r="AK131">
-        <v>2.15</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="O132">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P132">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="Q132">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="R132">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="S132">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T132">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U132">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="V132">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="W132">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X132">
         <v>0</v>
       </c>
       <c r="Y132">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z132">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AA132">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB132">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AC132">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD132">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AE132">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AF132">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AG132">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK132">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O133">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P133">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="Q133">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="R133">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="S133">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="T133">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="U133">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V133">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="W133">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X133">
         <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z133">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA133">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AB133">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="AC133">
         <v>1.8</v>
       </c>
       <c r="AD133">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE133">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AF133">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG133">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK133">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL133">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="O15">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
         <v>2.35</v>
@@ -2766,13 +2766,13 @@
         <v>3.25</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T15">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
         <v>3.19</v>
@@ -2787,31 +2787,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="AA15">
         <v>2.18</v>
       </c>
       <c r="AB15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AD15">
         <v>1.25</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK15">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4233,7 +4233,7 @@
         <v>4.1</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S24">
         <v>1.36</v>
@@ -4254,16 +4254,16 @@
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
         <v>3.6</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
         <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q27">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="R27">
         <v>2</v>
@@ -4740,34 +4740,34 @@
         <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA27">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC27">
         <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
         <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q28">
         <v>2.65</v>
       </c>
       <c r="R28">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="S28">
         <v>1.5</v>
@@ -4906,16 +4906,16 @@
         <v>1.1</v>
       </c>
       <c r="Y28">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AA28">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AB28">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
         <v>4.44</v>
@@ -4924,13 +4924,13 @@
         <v>1.18</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK28">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>1.97</v>
       </c>
       <c r="AG29">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>2.19</v>
       </c>
       <c r="AK29">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>1.48</v>
       </c>
       <c r="O35">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="P35">
-        <v>5.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
         <v>2.05</v>
@@ -6035,16 +6035,16 @@
         <v>3.32</v>
       </c>
       <c r="U35">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
         <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y35">
         <v>1.19</v>
@@ -6059,19 +6059,19 @@
         <v>2.13</v>
       </c>
       <c r="AC35">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD35">
         <v>1.42</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
         <v>1.78</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6829,43 +6829,43 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O40">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P40">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="Q40">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="R40">
         <v>2</v>
       </c>
       <c r="S40">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T40">
         <v>2.45</v>
       </c>
       <c r="U40">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="V40">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W40">
         <v>1.03</v>
       </c>
       <c r="X40">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
         <v>1.43</v>
       </c>
       <c r="Z40">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AA40">
         <v>2.35</v>
@@ -6877,7 +6877,7 @@
         <v>4.1</v>
       </c>
       <c r="AD40">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE40">
         <v>1.03</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK40">
         <v>1.43</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="N42">
-        <v>5.02</v>
+        <v>4.8</v>
       </c>
       <c r="O42">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
         <v>1.58</v>
@@ -7173,13 +7173,13 @@
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U42">
         <v>2.53</v>
       </c>
       <c r="V42">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
         <v>1.07</v>
@@ -7191,7 +7191,7 @@
         <v>1.19</v>
       </c>
       <c r="Z42">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="AA42">
         <v>1.72</v>
@@ -7200,7 +7200,7 @@
         <v>2</v>
       </c>
       <c r="AC42">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD42">
         <v>1.36</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
         <v>1.15</v>
@@ -7973,10 +7973,10 @@
         <v>2</v>
       </c>
       <c r="O47">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7991,7 +7991,7 @@
         <v>3.22</v>
       </c>
       <c r="U47">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V47">
         <v>1.48</v>
@@ -8000,19 +8000,19 @@
         <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA47">
         <v>1.8</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC47">
         <v>2.8</v>
@@ -8021,13 +8021,13 @@
         <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG47">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK47">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="O48">
         <v>3.2</v>
@@ -8142,10 +8142,10 @@
         <v>1.9</v>
       </c>
       <c r="Q48">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R48">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S48">
         <v>1.38</v>
@@ -8166,10 +8166,10 @@
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z48">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA48">
         <v>2.06</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
         <v>1.81</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O51">
         <v>3.5</v>
       </c>
       <c r="P51">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q51">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
         <v>1.36</v>
@@ -8652,34 +8652,34 @@
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
         <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB51">
         <v>1.9</v>
       </c>
       <c r="AC51">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD51">
         <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,34 +8794,34 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R52">
         <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="U52">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AA52">
         <v>1.68</v>
@@ -8830,13 +8830,13 @@
         <v>2.12</v>
       </c>
       <c r="AC52">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AD52">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
         <v>1.67</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
         <v>2.3</v>
@@ -9437,37 +9437,37 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="O56">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q56">
         <v>4.2</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
         <v>1.3</v>
       </c>
       <c r="T56">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U56">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V56">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W56">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.22</v>
@@ -9476,10 +9476,10 @@
         <v>3.95</v>
       </c>
       <c r="AA56">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AB56">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC56">
         <v>2.84</v>
@@ -9488,7 +9488,7 @@
         <v>1.41</v>
       </c>
       <c r="AE56">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
         <v>1.63</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AK56">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9781,7 +9781,7 @@
         <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U58">
         <v>3</v>
@@ -9799,7 +9799,7 @@
         <v>1.36</v>
       </c>
       <c r="Z58">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
         <v>2.21</v>
@@ -9811,7 +9811,7 @@
         <v>3.8</v>
       </c>
       <c r="AD58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE58">
         <v>1.03</v>
@@ -9836,7 +9836,7 @@
         <v>1.35</v>
       </c>
       <c r="AK58">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10267,10 +10267,10 @@
         <v>1.89</v>
       </c>
       <c r="S61">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T61">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="U61">
         <v>3.5</v>
@@ -10291,13 +10291,13 @@
         <v>2.49</v>
       </c>
       <c r="AA61">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB61">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC61">
-        <v>5.02</v>
+        <v>5.25</v>
       </c>
       <c r="AD61">
         <v>1.15</v>
@@ -10306,10 +10306,10 @@
         <v>1.04</v>
       </c>
       <c r="AF61">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AG61">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="O63">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="P63">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -10596,10 +10596,10 @@
         <v>1.45</v>
       </c>
       <c r="T63">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U63">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="V63">
         <v>1.35</v>
@@ -10614,7 +10614,7 @@
         <v>1.33</v>
       </c>
       <c r="Z63">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="AA63">
         <v>2.1</v>
@@ -11088,10 +11088,10 @@
         <v>2.92</v>
       </c>
       <c r="U66">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="V66">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
         <v>1.1</v>
@@ -11124,7 +11124,7 @@
         <v>1.66</v>
       </c>
       <c r="AG66">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="O67">
-        <v>3.65</v>
+        <v>3.92</v>
       </c>
       <c r="P67">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q67">
         <v>3.8</v>
       </c>
       <c r="R67">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11263,16 +11263,16 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z67">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AA67">
         <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AC67">
         <v>2.38</v>
@@ -11281,10 +11281,10 @@
         <v>1.56</v>
       </c>
       <c r="AE67">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG67">
         <v>2.38</v>
@@ -11402,22 +11402,22 @@
         <v>3.26</v>
       </c>
       <c r="Q68">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R68">
         <v>2.32</v>
       </c>
       <c r="S68">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="U68">
         <v>2.15</v>
       </c>
       <c r="V68">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W68">
         <v>1.14</v>
@@ -11426,25 +11426,25 @@
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z68">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AA68">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AB68">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AC68">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD68">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE68">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF68">
         <v>1.44</v>
@@ -11556,28 +11556,28 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O69">
         <v>3.3</v>
       </c>
       <c r="P69">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q69">
         <v>2.97</v>
       </c>
       <c r="R69">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="S69">
         <v>1.35</v>
       </c>
       <c r="T69">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="U69">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V69">
         <v>1.41</v>
@@ -11586,7 +11586,7 @@
         <v>1.08</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
         <v>1.28</v>
@@ -11595,7 +11595,7 @@
         <v>3.42</v>
       </c>
       <c r="AA69">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB69">
         <v>1.9</v>
@@ -11604,16 +11604,16 @@
         <v>3.12</v>
       </c>
       <c r="AD69">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE69">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF69">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG69">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O71">
         <v>3.55</v>
@@ -11891,10 +11891,10 @@
         <v>3</v>
       </c>
       <c r="Q71">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R71">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="S71">
         <v>1.18</v>
@@ -11927,10 +11927,10 @@
         <v>2.89</v>
       </c>
       <c r="AC71">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AD71">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AE71">
         <v>1.3</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12048,13 +12048,13 @@
         <v>3.3</v>
       </c>
       <c r="O72">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="P72">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q72">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R72">
         <v>2.28</v>
@@ -12075,28 +12075,28 @@
         <v>1.11</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y72">
         <v>1.16</v>
       </c>
       <c r="Z72">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA72">
         <v>1.66</v>
       </c>
       <c r="AB72">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AC72">
         <v>2.51</v>
       </c>
       <c r="AD72">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE72">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF72">
         <v>1.57</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q73">
         <v>3.18</v>
@@ -12223,10 +12223,10 @@
         <v>2.06</v>
       </c>
       <c r="S73">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T73">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="U73">
         <v>2.75</v>
@@ -12235,7 +12235,7 @@
         <v>1.36</v>
       </c>
       <c r="W73">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
         <v>1.01</v>
@@ -12247,10 +12247,10 @@
         <v>3.28</v>
       </c>
       <c r="AA73">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB73">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC73">
         <v>3.2</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q74">
         <v>2.77</v>
@@ -12386,10 +12386,10 @@
         <v>2.2</v>
       </c>
       <c r="S74">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T74">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U74">
         <v>2.63</v>
@@ -12401,16 +12401,16 @@
         <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z74">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA74">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB74">
         <v>2.05</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK74">
         <v>1.53</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O75">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="P75">
-        <v>12</v>
+        <v>8.9</v>
       </c>
       <c r="Q75">
         <v>1.62</v>
@@ -12558,10 +12558,10 @@
         <v>2.5</v>
       </c>
       <c r="V75">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12570,28 +12570,28 @@
         <v>1.18</v>
       </c>
       <c r="Z75">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA75">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB75">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AC75">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AD75">
         <v>1.38</v>
       </c>
       <c r="AE75">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF75">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AG75">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12863,10 +12863,10 @@
         <v>1.92</v>
       </c>
       <c r="O77">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P77">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q77">
         <v>2.55</v>
@@ -12875,7 +12875,7 @@
         <v>1.95</v>
       </c>
       <c r="S77">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T77">
         <v>2.39</v>
@@ -12896,7 +12896,7 @@
         <v>1.38</v>
       </c>
       <c r="Z77">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AA77">
         <v>2.31</v>
@@ -12905,7 +12905,7 @@
         <v>1.59</v>
       </c>
       <c r="AC77">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="AD77">
         <v>1.2</v>
@@ -13023,28 +13023,28 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O78">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P78">
         <v>3.8</v>
       </c>
       <c r="Q78">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R78">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="S78">
         <v>1.29</v>
       </c>
       <c r="T78">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U78">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V78">
         <v>1.5</v>
@@ -13053,16 +13053,16 @@
         <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z78">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="AA78">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB78">
         <v>2.12</v>
@@ -13074,13 +13074,13 @@
         <v>1.38</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF78">
         <v>1.63</v>
       </c>
       <c r="AG78">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P80">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="Q80">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R80">
         <v>2.3</v>
@@ -13370,13 +13370,13 @@
         <v>3.3</v>
       </c>
       <c r="U80">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="V80">
         <v>1.48</v>
       </c>
       <c r="W80">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X80">
         <v>1.04</v>
@@ -13388,7 +13388,7 @@
         <v>4.1</v>
       </c>
       <c r="AA80">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB80">
         <v>2.1</v>
@@ -13400,13 +13400,13 @@
         <v>1.4</v>
       </c>
       <c r="AE80">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF80">
         <v>1.57</v>
       </c>
       <c r="AG80">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK80">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13859,13 +13859,13 @@
         <v>2.46</v>
       </c>
       <c r="U83">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="V83">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
         <v>1.04</v>
@@ -13880,7 +13880,7 @@
         <v>2.23</v>
       </c>
       <c r="AB83">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC83">
         <v>4.05</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK83">
         <v>1.67</v>
@@ -14016,10 +14016,10 @@
         <v>2.3</v>
       </c>
       <c r="S84">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T84">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U84">
         <v>2.53</v>
@@ -14028,7 +14028,7 @@
         <v>1.42</v>
       </c>
       <c r="W84">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X84">
         <v>1.01</v>
@@ -14055,10 +14055,10 @@
         <v>1.1</v>
       </c>
       <c r="AF84">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG84">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>1.29</v>
       </c>
       <c r="W85">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X85">
         <v>1.04</v>
@@ -14221,7 +14221,7 @@
         <v>1.97</v>
       </c>
       <c r="AG85">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK85">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,10 +14336,10 @@
         <v>6.35</v>
       </c>
       <c r="Q86">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R86">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S86">
         <v>1.29</v>
@@ -14348,13 +14348,13 @@
         <v>3.3</v>
       </c>
       <c r="U86">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="V86">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
         <v>1.01</v>
@@ -14363,28 +14363,28 @@
         <v>1.18</v>
       </c>
       <c r="Z86">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA86">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC86">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD86">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE86">
         <v>1.12</v>
       </c>
       <c r="AF86">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG86">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,7 +14499,7 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R87">
         <v>2.1</v>
@@ -14511,13 +14511,13 @@
         <v>2.88</v>
       </c>
       <c r="U87">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V87">
         <v>1.36</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
         <v>1.73</v>
@@ -14653,16 +14653,16 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O88">
         <v>3.45</v>
       </c>
       <c r="P88">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q88">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R88">
         <v>2.14</v>
@@ -14674,7 +14674,7 @@
         <v>3.1</v>
       </c>
       <c r="U88">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V88">
         <v>1.44</v>
@@ -14686,10 +14686,10 @@
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z88">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="AA88">
         <v>1.73</v>
@@ -14710,7 +14710,7 @@
         <v>1.59</v>
       </c>
       <c r="AG88">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.43</v>
       </c>
       <c r="AK88">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O89">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P89">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="Q89">
         <v>1.71</v>
@@ -14831,19 +14831,19 @@
         <v>2.7</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T89">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="V89">
         <v>1.62</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
         <v>1.02</v>
@@ -14864,7 +14864,7 @@
         <v>2.29</v>
       </c>
       <c r="AD89">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE89">
         <v>1.19</v>
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="O90">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="P90">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q90">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="R90">
         <v>2.04</v>
       </c>
       <c r="S90">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U90">
         <v>3.08</v>
@@ -15015,19 +15015,19 @@
         <v>1.33</v>
       </c>
       <c r="Z90">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AA90">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB90">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC90">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD90">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE90">
         <v>1.05</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AK90">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P91">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15326,7 +15326,7 @@
         <v>3</v>
       </c>
       <c r="U92">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V92">
         <v>1.36</v>
@@ -15335,22 +15335,22 @@
         <v>1.06</v>
       </c>
       <c r="X92">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA92">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB92">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC92">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD92">
         <v>1.29</v>
@@ -15362,7 +15362,7 @@
         <v>1.68</v>
       </c>
       <c r="AG92">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.3</v>
+        <v>4.01</v>
       </c>
       <c r="O97">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="P97">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q97">
-        <v>3.01</v>
+        <v>4.94</v>
       </c>
       <c r="R97">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S97">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T97">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="U97">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="V97">
+        <v>1.25</v>
+      </c>
+      <c r="W97">
+        <v>1</v>
+      </c>
+      <c r="X97">
+        <v>1.08</v>
+      </c>
+      <c r="Y97">
+        <v>1.52</v>
+      </c>
+      <c r="Z97">
+        <v>2.43</v>
+      </c>
+      <c r="AA97">
+        <v>2.48</v>
+      </c>
+      <c r="AB97">
+        <v>1.46</v>
+      </c>
+      <c r="AC97">
+        <v>4.7</v>
+      </c>
+      <c r="AD97">
+        <v>1.14</v>
+      </c>
+      <c r="AE97">
+        <v>1.04</v>
+      </c>
+      <c r="AF97">
+        <v>2.17</v>
+      </c>
+      <c r="AG97">
+        <v>1.6</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.73</v>
+      </c>
+      <c r="AK97">
         <v>1.2</v>
-      </c>
-      <c r="W97">
-        <v>1.03</v>
-      </c>
-      <c r="X97">
-        <v>1.14</v>
-      </c>
-      <c r="Y97">
-        <v>1.62</v>
-      </c>
-      <c r="Z97">
-        <v>2.16</v>
-      </c>
-      <c r="AA97">
-        <v>2.81</v>
-      </c>
-      <c r="AB97">
-        <v>1.36</v>
-      </c>
-      <c r="AC97">
-        <v>6.22</v>
-      </c>
-      <c r="AD97">
-        <v>1.11</v>
-      </c>
-      <c r="AE97">
-        <v>1.03</v>
-      </c>
-      <c r="AF97">
-        <v>2.32</v>
-      </c>
-      <c r="AG97">
-        <v>1.57</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.33</v>
-      </c>
-      <c r="AK97">
-        <v>1.53</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.01</v>
+        <v>2.3</v>
       </c>
       <c r="O98">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="P98">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q98">
-        <v>4.94</v>
+        <v>3.01</v>
       </c>
       <c r="R98">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S98">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T98">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U98">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="V98">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W98">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X98">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y98">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z98">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AA98">
-        <v>2.48</v>
+        <v>2.81</v>
       </c>
       <c r="AB98">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AC98">
-        <v>4.7</v>
+        <v>6.22</v>
       </c>
       <c r="AD98">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE98">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF98">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AG98">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16455,16 +16455,16 @@
         <v>6.5</v>
       </c>
       <c r="Q99">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R99">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="S99">
         <v>1.24</v>
       </c>
       <c r="T99">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="U99">
         <v>2.16</v>
@@ -16479,16 +16479,16 @@
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z99">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA99">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB99">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC99">
         <v>2.16</v>
@@ -16500,10 +16500,10 @@
         <v>1.24</v>
       </c>
       <c r="AF99">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG99">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK99">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17261,25 +17261,25 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="O104">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q104">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="R104">
         <v>2.4</v>
       </c>
       <c r="S104">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T104">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U104">
         <v>2.05</v>
@@ -17288,37 +17288,37 @@
         <v>1.7</v>
       </c>
       <c r="W104">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X104">
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z104">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="AA104">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB104">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AC104">
         <v>2.14</v>
       </c>
       <c r="AD104">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE104">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF104">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG104">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK104">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17587,28 +17587,28 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O106">
         <v>3.3</v>
       </c>
       <c r="P106">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q106">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R106">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T106">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U106">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="V106">
         <v>1.36</v>
@@ -17620,7 +17620,7 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z106">
         <v>3.1</v>
@@ -17638,13 +17638,13 @@
         <v>1.23</v>
       </c>
       <c r="AE106">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF106">
         <v>1.83</v>
       </c>
       <c r="AG106">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.28</v>
       </c>
       <c r="AK106">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O107">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P107">
-        <v>2.54</v>
+        <v>2.37</v>
       </c>
       <c r="Q107">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="R107">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="S107">
         <v>1.19</v>
@@ -17771,10 +17771,10 @@
         <v>3.98</v>
       </c>
       <c r="U107">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="V107">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W107">
         <v>1.17</v>
@@ -17783,7 +17783,7 @@
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z107">
         <v>5.8</v>
@@ -17792,16 +17792,16 @@
         <v>1.4</v>
       </c>
       <c r="AB107">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="AC107">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AD107">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AE107">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AF107">
         <v>1.38</v>
@@ -17925,7 +17925,7 @@
         <v>2.97</v>
       </c>
       <c r="R108">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S108">
         <v>1.36</v>
@@ -17943,13 +17943,13 @@
         <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
         <v>1.3</v>
       </c>
       <c r="Z108">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA108">
         <v>1.95</v>
@@ -17958,19 +17958,19 @@
         <v>1.8</v>
       </c>
       <c r="AC108">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD108">
         <v>1.28</v>
       </c>
       <c r="AE108">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF108">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG108">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
         <v>1.48</v>
@@ -18239,10 +18239,10 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O110">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P110">
         <v>5.75</v>
@@ -18254,7 +18254,7 @@
         <v>2.15</v>
       </c>
       <c r="S110">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T110">
         <v>2.65</v>
@@ -18266,25 +18266,25 @@
         <v>1.31</v>
       </c>
       <c r="W110">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y110">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z110">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="AA110">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB110">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC110">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AD110">
         <v>1.19</v>
@@ -18296,7 +18296,7 @@
         <v>2.2</v>
       </c>
       <c r="AG110">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,80 +21825,80 @@
         </is>
       </c>
       <c r="N132">
+        <v>2.03</v>
+      </c>
+      <c r="O132">
+        <v>3.9</v>
+      </c>
+      <c r="P132">
+        <v>2.85</v>
+      </c>
+      <c r="Q132">
+        <v>2.38</v>
+      </c>
+      <c r="R132">
+        <v>2.79</v>
+      </c>
+      <c r="S132">
+        <v>1.13</v>
+      </c>
+      <c r="T132">
+        <v>5.2</v>
+      </c>
+      <c r="U132">
+        <v>1.83</v>
+      </c>
+      <c r="V132">
+        <v>1.87</v>
+      </c>
+      <c r="W132">
+        <v>1.22</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>1.03</v>
+      </c>
+      <c r="Z132">
+        <v>7</v>
+      </c>
+      <c r="AA132">
+        <v>1.32</v>
+      </c>
+      <c r="AB132">
+        <v>3.18</v>
+      </c>
+      <c r="AC132">
+        <v>1.8</v>
+      </c>
+      <c r="AD132">
+        <v>1.98</v>
+      </c>
+      <c r="AE132">
+        <v>1.37</v>
+      </c>
+      <c r="AF132">
+        <v>1.3</v>
+      </c>
+      <c r="AG132">
+        <v>3.24</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
+        <v>1.36</v>
+      </c>
+      <c r="AK132">
         <v>1.67</v>
-      </c>
-      <c r="O132">
-        <v>4</v>
-      </c>
-      <c r="P132">
-        <v>4</v>
-      </c>
-      <c r="Q132">
-        <v>2.13</v>
-      </c>
-      <c r="R132">
-        <v>2.7</v>
-      </c>
-      <c r="S132">
-        <v>1.14</v>
-      </c>
-      <c r="T132">
-        <v>4.6</v>
-      </c>
-      <c r="U132">
-        <v>2</v>
-      </c>
-      <c r="V132">
-        <v>1.8</v>
-      </c>
-      <c r="W132">
-        <v>1.19</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>1.06</v>
-      </c>
-      <c r="Z132">
-        <v>6.8</v>
-      </c>
-      <c r="AA132">
-        <v>1.33</v>
-      </c>
-      <c r="AB132">
-        <v>3.1</v>
-      </c>
-      <c r="AC132">
-        <v>1.9</v>
-      </c>
-      <c r="AD132">
-        <v>1.85</v>
-      </c>
-      <c r="AE132">
-        <v>1.33</v>
-      </c>
-      <c r="AF132">
-        <v>1.38</v>
-      </c>
-      <c r="AG132">
-        <v>2.88</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>1.2</v>
-      </c>
-      <c r="AK132">
-        <v>2.15</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="O133">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P133">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="Q133">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="R133">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="S133">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T133">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U133">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="V133">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="W133">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X133">
         <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z133">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AA133">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB133">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AC133">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD133">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AE133">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AF133">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AG133">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK133">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AL133">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P6">
         <v>5.6</v>
@@ -1302,13 +1302,13 @@
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
         <v>2.65</v>
       </c>
       <c r="U6">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
         <v>1.3</v>
@@ -1317,25 +1317,25 @@
         <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z6">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA6">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC6">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
         <v>1.02</v>
@@ -1360,7 +1360,7 @@
         <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O7">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P7">
         <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
         <v>1.93</v>
       </c>
       <c r="S7">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
         <v>2.56</v>
       </c>
       <c r="U7">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="V7">
         <v>1.37</v>
@@ -1480,7 +1480,7 @@
         <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
         <v>1.27</v>
@@ -1492,13 +1492,13 @@
         <v>2</v>
       </c>
       <c r="AB7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q8">
         <v>2.51</v>
       </c>
       <c r="R8">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
         <v>1.44</v>
@@ -1649,16 +1649,16 @@
         <v>1.37</v>
       </c>
       <c r="Z8">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA8">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AB8">
         <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="AD8">
         <v>1.21</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O9">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
         <v>2</v>
@@ -1788,13 +1788,13 @@
         <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S9">
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
         <v>2.5</v>
@@ -1809,7 +1809,7 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
         <v>4</v>
@@ -1818,7 +1818,7 @@
         <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC9">
         <v>2.74</v>
@@ -1833,7 +1833,7 @@
         <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="P10">
         <v>2.65</v>
@@ -1966,10 +1966,10 @@
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
         <v>1.25</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
         <v>2.6</v>
       </c>
       <c r="Q11">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="U11">
         <v>3</v>
@@ -2156,10 +2156,10 @@
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
         <v>2.97</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="O13">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="R13">
         <v>2.17</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
         <v>2.33</v>
@@ -2455,7 +2455,7 @@
         <v>1.52</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2464,7 +2464,7 @@
         <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>4.33</v>
+        <v>4.56</v>
       </c>
       <c r="AA13">
         <v>1.64</v>
@@ -2479,13 +2479,13 @@
         <v>1.42</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.47</v>
       </c>
       <c r="AK13">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="O14">
         <v>3.6</v>
@@ -2609,7 +2609,7 @@
         <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
         <v>2.38</v>
@@ -2627,22 +2627,22 @@
         <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>4.67</v>
       </c>
       <c r="AA14">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
         <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF14">
         <v>1.51</v>
@@ -2664,7 +2664,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3572,13 +3572,13 @@
         <v>1.57</v>
       </c>
       <c r="O20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P20">
-        <v>4.25</v>
+        <v>4.92</v>
       </c>
       <c r="Q20">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R20">
         <v>2.56</v>
@@ -3587,7 +3587,7 @@
         <v>1.18</v>
       </c>
       <c r="T20">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U20">
         <v>1.9</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA20">
         <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AC20">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD20">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AE20">
         <v>1.4</v>
       </c>
       <c r="AF20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="Q21">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="S21">
         <v>1.18</v>
       </c>
       <c r="T21">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="W21">
         <v>1.2</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AA21">
+        <v>1.33</v>
+      </c>
+      <c r="AB21">
+        <v>3.1</v>
+      </c>
+      <c r="AC21">
+        <v>1.92</v>
+      </c>
+      <c r="AD21">
+        <v>1.9</v>
+      </c>
+      <c r="AE21">
         <v>1.36</v>
       </c>
-      <c r="AB21">
-        <v>3.07</v>
-      </c>
-      <c r="AC21">
-        <v>1.93</v>
-      </c>
-      <c r="AD21">
-        <v>1.8</v>
-      </c>
-      <c r="AE21">
+      <c r="AF21">
         <v>1.33</v>
       </c>
-      <c r="AF21">
-        <v>1.36</v>
-      </c>
       <c r="AG21">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>1.34</v>
       </c>
       <c r="O22">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="Q22">
         <v>1.7</v>
@@ -3916,10 +3916,10 @@
         <v>4.5</v>
       </c>
       <c r="U22">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="V22">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W22">
         <v>1.17</v>
@@ -3931,28 +3931,28 @@
         <v>1.12</v>
       </c>
       <c r="Z22">
-        <v>5.99</v>
+        <v>5.3</v>
       </c>
       <c r="AA22">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AD22">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE22">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
         <v>1.71</v>
       </c>
       <c r="AG22">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.13</v>
       </c>
       <c r="AK22">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P25">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="Q25">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="R25">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
         <v>1.1</v>
@@ -4417,16 +4417,16 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA25">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
         <v>2.75</v>
@@ -4435,13 +4435,13 @@
         <v>1.38</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q30">
         <v>2.49</v>
@@ -5214,7 +5214,7 @@
         <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
         <v>3.4</v>
@@ -5223,7 +5223,7 @@
         <v>2.36</v>
       </c>
       <c r="V30">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W30">
         <v>1.11</v>
@@ -5238,13 +5238,13 @@
         <v>4.4</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB30">
         <v>2.25</v>
       </c>
       <c r="AC30">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD30">
         <v>1.44</v>
@@ -5362,55 +5362,55 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P31">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
         <v>2.56</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W31">
         <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.85</v>
+        <v>4.11</v>
       </c>
       <c r="AA31">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB31">
         <v>2.1</v>
       </c>
       <c r="AC31">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AD31">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE31">
         <v>1.16</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="O33">
         <v>3.85</v>
       </c>
       <c r="P33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q33">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="R33">
         <v>2.48</v>
@@ -5706,13 +5706,13 @@
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="U33">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.15</v>
@@ -5724,28 +5724,28 @@
         <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB33">
         <v>2.4</v>
       </c>
       <c r="AC33">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD33">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
         <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,49 +5851,49 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O34">
         <v>3.5</v>
       </c>
       <c r="P34">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q34">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R34">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T34">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="U34">
         <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA34">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AB34">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC34">
         <v>2.7</v>
@@ -5902,13 +5902,13 @@
         <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG34">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
         <v>3.05</v>
@@ -7499,7 +7499,7 @@
         <v>1.33</v>
       </c>
       <c r="T44">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="U44">
         <v>2.45</v>
@@ -7508,7 +7508,7 @@
         <v>1.48</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
         <v>1</v>
@@ -7517,7 +7517,7 @@
         <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA44">
         <v>1.76</v>
@@ -7529,7 +7529,7 @@
         <v>2.8</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE44">
         <v>1.11</v>
@@ -7554,7 +7554,7 @@
         <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.35</v>
+        <v>2.81</v>
       </c>
       <c r="O46">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="P46">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q46">
         <v>3.5</v>
@@ -7822,16 +7822,16 @@
         <v>2.65</v>
       </c>
       <c r="S46">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T46">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="U46">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W46">
         <v>1.2</v>
@@ -7843,22 +7843,22 @@
         <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="AA46">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AB46">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="AC46">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="AD46">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE46">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF46">
         <v>1.39</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
         <v>1.27</v>
@@ -9111,34 +9111,34 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O54">
-        <v>4.3</v>
+        <v>4.08</v>
       </c>
       <c r="P54">
-        <v>4.7</v>
+        <v>4.54</v>
       </c>
       <c r="Q54">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S54">
         <v>1.22</v>
       </c>
       <c r="T54">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V54">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X54">
         <v>1.02</v>
@@ -9147,10 +9147,10 @@
         <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>5.5</v>
+        <v>5.88</v>
       </c>
       <c r="AA54">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB54">
         <v>2.49</v>
@@ -9162,13 +9162,13 @@
         <v>1.66</v>
       </c>
       <c r="AE54">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF54">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG54">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P55">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="Q55">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="R55">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="S55">
         <v>1.29</v>
@@ -9298,40 +9298,40 @@
         <v>2.25</v>
       </c>
       <c r="V55">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W55">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA55">
         <v>1.61</v>
       </c>
       <c r="AB55">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AC55">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AD55">
         <v>1.45</v>
       </c>
       <c r="AE55">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF55">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG55">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,31 +9600,31 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="O57">
+        <v>3.55</v>
+      </c>
+      <c r="P57">
+        <v>1.95</v>
+      </c>
+      <c r="Q57">
         <v>3.6</v>
       </c>
-      <c r="P57">
-        <v>2</v>
-      </c>
-      <c r="Q57">
-        <v>3.7</v>
-      </c>
       <c r="R57">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
         <v>4</v>
       </c>
       <c r="U57">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V57">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W57">
         <v>1.16</v>
@@ -9639,10 +9639,10 @@
         <v>5.6</v>
       </c>
       <c r="AA57">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AC57">
         <v>2.02</v>
@@ -9651,7 +9651,7 @@
         <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF57">
         <v>1.4</v>
@@ -10424,55 +10424,55 @@
         <v>1.83</v>
       </c>
       <c r="Q62">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T62">
         <v>3.6</v>
       </c>
       <c r="U62">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W62">
         <v>1.1</v>
       </c>
       <c r="X62">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z62">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA62">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB62">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC62">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD62">
         <v>1.47</v>
       </c>
       <c r="AE62">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
         <v>1.58</v>
       </c>
       <c r="AG62">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
         <v>1.22</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="O70">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="P70">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q70">
         <v>4.8</v>
@@ -11737,13 +11737,13 @@
         <v>1.23</v>
       </c>
       <c r="T70">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="U70">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V70">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W70">
         <v>1.17</v>
@@ -11752,10 +11752,10 @@
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z70">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA70">
         <v>1.5</v>
@@ -11764,10 +11764,10 @@
         <v>2.45</v>
       </c>
       <c r="AC70">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AD70">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE70">
         <v>1.22</v>
@@ -11792,7 +11792,7 @@
         <v>2.56</v>
       </c>
       <c r="AK70">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q76">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R76">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
         <v>1.36</v>
@@ -12718,19 +12718,19 @@
         <v>2.69</v>
       </c>
       <c r="U76">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V76">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z76">
         <v>3.2</v>
@@ -12745,7 +12745,7 @@
         <v>3.27</v>
       </c>
       <c r="AD76">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE76">
         <v>1.09</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O79">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P79">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q79">
         <v>2.7</v>
@@ -13204,7 +13204,7 @@
         <v>1.36</v>
       </c>
       <c r="T79">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="U79">
         <v>2.77</v>
@@ -13216,7 +13216,7 @@
         <v>1.07</v>
       </c>
       <c r="X79">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
         <v>1.25</v>
@@ -13225,10 +13225,10 @@
         <v>3.6</v>
       </c>
       <c r="AA79">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB79">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AC79">
         <v>2.83</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK79">
         <v>1.67</v>
@@ -15471,7 +15471,7 @@
         <v>2.62</v>
       </c>
       <c r="O93">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P93">
         <v>2.8</v>
@@ -15489,7 +15489,7 @@
         <v>2.1</v>
       </c>
       <c r="U93">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="V93">
         <v>1.16</v>
@@ -15498,10 +15498,10 @@
         <v>1.02</v>
       </c>
       <c r="X93">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Y93">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Z93">
         <v>2.04</v>
@@ -15510,7 +15510,7 @@
         <v>3.04</v>
       </c>
       <c r="AB93">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC93">
         <v>5.8</v>
@@ -15525,7 +15525,7 @@
         <v>2.4</v>
       </c>
       <c r="AG93">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.37</v>
       </c>
       <c r="AK93">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15634,10 +15634,10 @@
         <v>1.95</v>
       </c>
       <c r="O94">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P94">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q94">
         <v>2.75</v>
@@ -15649,22 +15649,22 @@
         <v>1.64</v>
       </c>
       <c r="T94">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="U94">
         <v>3.78</v>
       </c>
       <c r="V94">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W94">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X94">
         <v>1.09</v>
       </c>
       <c r="Y94">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z94">
         <v>2.29</v>
@@ -15679,7 +15679,7 @@
         <v>5.25</v>
       </c>
       <c r="AD94">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AE94">
         <v>1.03</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O95">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P95">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -15812,13 +15812,13 @@
         <v>1.59</v>
       </c>
       <c r="T95">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="U95">
         <v>3.82</v>
       </c>
       <c r="V95">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W95">
         <v>1.01</v>
@@ -15836,22 +15836,22 @@
         <v>2.62</v>
       </c>
       <c r="AB95">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC95">
         <v>5.45</v>
       </c>
       <c r="AD95">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE95">
         <v>1.04</v>
       </c>
       <c r="AF95">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG95">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15972,10 +15972,10 @@
         <v>1.8</v>
       </c>
       <c r="S96">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="T96">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="U96">
         <v>4.3</v>
@@ -15990,22 +15990,22 @@
         <v>1.13</v>
       </c>
       <c r="Y96">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="Z96">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AA96">
         <v>3.14</v>
       </c>
       <c r="AB96">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AC96">
         <v>6.45</v>
       </c>
       <c r="AD96">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE96">
         <v>1.02</v>
@@ -16129,19 +16129,19 @@
         <v>1.96</v>
       </c>
       <c r="Q97">
-        <v>4.94</v>
+        <v>4.5</v>
       </c>
       <c r="R97">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="S97">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="T97">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="U97">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="V97">
         <v>1.25</v>
@@ -16150,7 +16150,7 @@
         <v>1</v>
       </c>
       <c r="X97">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y97">
         <v>1.52</v>
@@ -16162,16 +16162,16 @@
         <v>2.48</v>
       </c>
       <c r="AB97">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AC97">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD97">
         <v>1.14</v>
       </c>
       <c r="AE97">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF97">
         <v>2.17</v>
@@ -16193,7 +16193,7 @@
         <v>1.73</v>
       </c>
       <c r="AK97">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O98">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P98">
         <v>3.3</v>
@@ -16298,10 +16298,10 @@
         <v>1.85</v>
       </c>
       <c r="S98">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="T98">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="U98">
         <v>3.9</v>
@@ -16313,22 +16313,22 @@
         <v>1.03</v>
       </c>
       <c r="X98">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y98">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z98">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AA98">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AB98">
         <v>1.36</v>
       </c>
       <c r="AC98">
-        <v>6.22</v>
+        <v>6.12</v>
       </c>
       <c r="AD98">
         <v>1.11</v>
@@ -16337,7 +16337,7 @@
         <v>1.03</v>
       </c>
       <c r="AF98">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG98">
         <v>1.57</v>
@@ -17448,7 +17448,7 @@
         <v>3.16</v>
       </c>
       <c r="V105">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W105">
         <v>1.02</v>
@@ -18091,16 +18091,16 @@
         <v>1.98</v>
       </c>
       <c r="S109">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="T109">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U109">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="V109">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W109">
         <v>1.03</v>
@@ -18115,7 +18115,7 @@
         <v>2.13</v>
       </c>
       <c r="AA109">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AB109">
         <v>1.34</v>
@@ -18130,7 +18130,7 @@
         <v>1.02</v>
       </c>
       <c r="AF109">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AG109">
         <v>1.37</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK109">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="O112">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P112">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -18586,43 +18586,43 @@
         <v>3</v>
       </c>
       <c r="U112">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="V112">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W112">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z112">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA112">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB112">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AC112">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AD112">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE112">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
         <v>1.7</v>
       </c>
       <c r="AG112">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18891,10 +18891,10 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O114">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P114">
         <v>2.3</v>
@@ -18906,43 +18906,43 @@
         <v>1.94</v>
       </c>
       <c r="S114">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="U114">
         <v>3.29</v>
       </c>
       <c r="V114">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W114">
         <v>1.03</v>
       </c>
       <c r="X114">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y114">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z114">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="AA114">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AB114">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC114">
-        <v>4.08</v>
+        <v>3.85</v>
       </c>
       <c r="AD114">
         <v>1.22</v>
       </c>
       <c r="AE114">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF114">
         <v>1.8</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK114">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19057,7 +19057,7 @@
         <v>2.37</v>
       </c>
       <c r="O115">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="P115">
         <v>2.75</v>
@@ -19087,7 +19087,7 @@
         <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z115">
         <v>2.88</v>
@@ -19096,22 +19096,22 @@
         <v>2.19</v>
       </c>
       <c r="AB115">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC115">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AD115">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE115">
         <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG115">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK115">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O119">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P119">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q119">
         <v>3.3</v>
       </c>
       <c r="R119">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S119">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T119">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U119">
         <v>3.15</v>
       </c>
       <c r="V119">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W119">
         <v>1.07</v>
       </c>
       <c r="X119">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y119">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z119">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AA119">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB119">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC119">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD119">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE119">
         <v>1.04</v>
       </c>
       <c r="AF119">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG119">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AK119">
         <v>1.4</v>
@@ -19872,16 +19872,16 @@
         <v>1.43</v>
       </c>
       <c r="O120">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P120">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="Q120">
         <v>1.95</v>
       </c>
       <c r="R120">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S120">
         <v>1.33</v>
@@ -19896,22 +19896,22 @@
         <v>1.44</v>
       </c>
       <c r="W120">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X120">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z120">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA120">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB120">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC120">
         <v>2.92</v>
@@ -19926,7 +19926,7 @@
         <v>1.93</v>
       </c>
       <c r="AG120">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>3.12</v>
       </c>
       <c r="U123">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V123">
         <v>1.45</v>
@@ -20388,7 +20388,7 @@
         <v>1.07</v>
       </c>
       <c r="X123">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y123">
         <v>1.19</v>
@@ -20403,13 +20403,13 @@
         <v>2.07</v>
       </c>
       <c r="AC123">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD123">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE123">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF123">
         <v>1.75</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="O124">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P124">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q124">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R124">
         <v>2.2</v>
       </c>
       <c r="S124">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T124">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U124">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V124">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W124">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X124">
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z124">
-        <v>3.52</v>
+        <v>3.89</v>
       </c>
       <c r="AA124">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB124">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC124">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="AD124">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE124">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF124">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG124">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK124">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,31 +20684,31 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="O125">
         <v>3.4</v>
       </c>
       <c r="P125">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="Q125">
         <v>2.63</v>
       </c>
       <c r="R125">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S125">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T125">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U125">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="V125">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W125">
         <v>1.1</v>
@@ -20717,31 +20717,31 @@
         <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z125">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA125">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB125">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC125">
         <v>2.6</v>
       </c>
       <c r="AD125">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE125">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF125">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG125">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O126">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P126">
-        <v>6</v>
+        <v>5.15</v>
       </c>
       <c r="Q126">
         <v>1.8</v>
@@ -20865,28 +20865,28 @@
         <v>1.2</v>
       </c>
       <c r="T126">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U126">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V126">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W126">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X126">
         <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z126">
         <v>5.45</v>
       </c>
       <c r="AA126">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB126">
         <v>2.5</v>
@@ -20895,16 +20895,16 @@
         <v>2.14</v>
       </c>
       <c r="AD126">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE126">
         <v>1.22</v>
       </c>
       <c r="AF126">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG126">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK126">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="O127">
         <v>3.6</v>
@@ -21179,7 +21179,7 @@
         <v>4</v>
       </c>
       <c r="P128">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="Q128">
         <v>2.15</v>
@@ -21200,7 +21200,7 @@
         <v>1.55</v>
       </c>
       <c r="W128">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X128">
         <v>1.01</v>
@@ -21218,7 +21218,7 @@
         <v>2.17</v>
       </c>
       <c r="AC128">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD128">
         <v>1.54</v>
@@ -21227,10 +21227,10 @@
         <v>1.2</v>
       </c>
       <c r="AF128">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG128">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK128">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,19 +21336,19 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="O129">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P129">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
       </c>
       <c r="R129">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S129">
         <v>1.36</v>
@@ -21357,10 +21357,10 @@
         <v>2.9</v>
       </c>
       <c r="U129">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="V129">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W129">
         <v>1.08</v>
@@ -21375,25 +21375,25 @@
         <v>3.52</v>
       </c>
       <c r="AA129">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AB129">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC129">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="AD129">
         <v>1.35</v>
       </c>
       <c r="AE129">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF129">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG129">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O130">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="P130">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="Q130">
         <v>2.25</v>
@@ -21520,10 +21520,10 @@
         <v>3.5</v>
       </c>
       <c r="U130">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V130">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W130">
         <v>1.17</v>
@@ -21541,7 +21541,7 @@
         <v>1.55</v>
       </c>
       <c r="AB130">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AC130">
         <v>2.25</v>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK130">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,40 +21662,40 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="O131">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P131">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="Q131">
         <v>2.37</v>
       </c>
       <c r="R131">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="S131">
         <v>1.16</v>
       </c>
       <c r="T131">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="U131">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="V131">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="W131">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X131">
         <v>0</v>
       </c>
       <c r="Y131">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z131">
         <v>8</v>
@@ -21704,22 +21704,22 @@
         <v>1.29</v>
       </c>
       <c r="AB131">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AC131">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD131">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE131">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AF131">
         <v>1.29</v>
       </c>
       <c r="AG131">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>1.21</v>
       </c>
       <c r="AK131">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,22 +21825,22 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O132">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P132">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="Q132">
         <v>2.38</v>
       </c>
       <c r="R132">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="S132">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T132">
         <v>5.2</v>
@@ -21849,7 +21849,7 @@
         <v>1.83</v>
       </c>
       <c r="V132">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W132">
         <v>1.22</v>
@@ -21861,28 +21861,28 @@
         <v>1.03</v>
       </c>
       <c r="Z132">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA132">
         <v>1.32</v>
       </c>
       <c r="AB132">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="AC132">
         <v>1.8</v>
       </c>
       <c r="AD132">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AE132">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AF132">
         <v>1.3</v>
       </c>
       <c r="AG132">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK132">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,28 +21988,28 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O133">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P133">
-        <v>4</v>
+        <v>3.51</v>
       </c>
       <c r="Q133">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="R133">
         <v>2.7</v>
       </c>
       <c r="S133">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T133">
         <v>4.6</v>
       </c>
       <c r="U133">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V133">
         <v>1.8</v>
@@ -22021,31 +22021,31 @@
         <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z133">
-        <v>6.8</v>
+        <v>6.73</v>
       </c>
       <c r="AA133">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AB133">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="AC133">
         <v>1.9</v>
       </c>
       <c r="AD133">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE133">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF133">
         <v>1.38</v>
       </c>
       <c r="AG133">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK133">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,31 +22151,31 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="O134">
-        <v>3.62</v>
+        <v>3.28</v>
       </c>
       <c r="P134">
-        <v>3.79</v>
+        <v>2.88</v>
       </c>
       <c r="Q134">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R134">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S134">
         <v>1.28</v>
       </c>
       <c r="T134">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U134">
         <v>2.63</v>
       </c>
       <c r="V134">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W134">
         <v>1.08</v>
@@ -22184,22 +22184,22 @@
         <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z134">
         <v>3.98</v>
       </c>
       <c r="AA134">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AB134">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC134">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AD134">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AE134">
         <v>1.12</v>
@@ -22208,7 +22208,7 @@
         <v>1.58</v>
       </c>
       <c r="AG134">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK134">
         <v>1.83</v>
@@ -22314,16 +22314,16 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="O135">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="P135">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q135">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="R135">
         <v>2.13</v>
@@ -22335,13 +22335,13 @@
         <v>2.75</v>
       </c>
       <c r="U135">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V135">
         <v>1.4</v>
       </c>
       <c r="W135">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
         <v>1.01</v>
@@ -22359,10 +22359,10 @@
         <v>1.9</v>
       </c>
       <c r="AC135">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD135">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE135">
         <v>1.08</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
         <v>1.28</v>
@@ -22480,10 +22480,10 @@
         <v>2.05</v>
       </c>
       <c r="O136">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P136">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="Q136">
         <v>2.53</v>
@@ -22492,34 +22492,34 @@
         <v>2.28</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T136">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U136">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V136">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W136">
         <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
         <v>1.28</v>
       </c>
       <c r="Z136">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AA136">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB136">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC136">
         <v>3.05</v>
@@ -22531,10 +22531,10 @@
         <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22640,16 +22640,16 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O137">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P137">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q137">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="R137">
         <v>2.1</v>
@@ -22664,7 +22664,7 @@
         <v>3.25</v>
       </c>
       <c r="V137">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W137">
         <v>1.02</v>
@@ -22673,10 +22673,10 @@
         <v>1.04</v>
       </c>
       <c r="Y137">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z137">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AA137">
         <v>2.1</v>
@@ -22685,7 +22685,7 @@
         <v>1.63</v>
       </c>
       <c r="AC137">
-        <v>3.75</v>
+        <v>4.38</v>
       </c>
       <c r="AD137">
         <v>1.21</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK137">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O139">
-        <v>4.12</v>
+        <v>3.4</v>
       </c>
       <c r="P139">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q139">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R139">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S139">
         <v>1.29</v>
       </c>
       <c r="T139">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="U139">
         <v>2.25</v>
       </c>
       <c r="V139">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W139">
         <v>1.1</v>
       </c>
       <c r="X139">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y139">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z139">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA139">
         <v>1.58</v>
       </c>
       <c r="AB139">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AC139">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AD139">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE139">
         <v>1.22</v>
       </c>
       <c r="AF139">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG139">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
+        <v>1.25</v>
+      </c>
+      <c r="AK139">
         <v>1.3</v>
-      </c>
-      <c r="AK139">
-        <v>1.33</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23138,40 +23138,40 @@
         <v>3.58</v>
       </c>
       <c r="Q140">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="R140">
         <v>2.55</v>
       </c>
       <c r="S140">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T140">
         <v>3.7</v>
       </c>
       <c r="U140">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="V140">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W140">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X140">
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z140">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA140">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB140">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AC140">
         <v>2.18</v>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O141">
         <v>4.76</v>
@@ -23301,19 +23301,19 @@
         <v>5.14</v>
       </c>
       <c r="Q141">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R141">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="S141">
         <v>1.2</v>
       </c>
       <c r="T141">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="U141">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V141">
         <v>1.65</v>
@@ -23325,13 +23325,13 @@
         <v>0</v>
       </c>
       <c r="Y141">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z141">
         <v>6</v>
       </c>
       <c r="AA141">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB141">
         <v>2.83</v>
@@ -23340,16 +23340,16 @@
         <v>2.13</v>
       </c>
       <c r="AD141">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE141">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF141">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG141">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>1.15</v>
       </c>
       <c r="AK141">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,19 +23455,19 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O142">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P142">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q142">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R142">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="S142">
         <v>1.25</v>
@@ -23476,13 +23476,13 @@
         <v>3.75</v>
       </c>
       <c r="U142">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="V142">
         <v>1.62</v>
       </c>
       <c r="W142">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X142">
         <v>1.01</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="O145">
         <v>3.45</v>
       </c>
       <c r="P145">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q145">
         <v>3.3</v>
@@ -23965,10 +23965,10 @@
         <v>3.02</v>
       </c>
       <c r="U145">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V145">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W145">
         <v>1.11</v>
@@ -23983,22 +23983,22 @@
         <v>3.58</v>
       </c>
       <c r="AA145">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AB145">
         <v>2</v>
       </c>
       <c r="AC145">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD145">
         <v>1.39</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF145">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
         <v>2.18</v>
@@ -24110,22 +24110,22 @@
         <v>1.7</v>
       </c>
       <c r="O146">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="P146">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="Q146">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R146">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S146">
         <v>1.27</v>
       </c>
       <c r="T146">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U146">
         <v>2.2</v>
@@ -24140,13 +24140,13 @@
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z146">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA146">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AB146">
         <v>2.31</v>
@@ -24164,7 +24164,7 @@
         <v>1.57</v>
       </c>
       <c r="AG146">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>2.88</v>
       </c>
       <c r="U147">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="V147">
         <v>1.35</v>
@@ -24303,19 +24303,19 @@
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z147">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA147">
         <v>2</v>
       </c>
       <c r="AB147">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC147">
-        <v>3.57</v>
+        <v>3.34</v>
       </c>
       <c r="AD147">
         <v>1.27</v>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK147">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="O148">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="P148">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="Q148">
         <v>2.7</v>
@@ -24448,22 +24448,22 @@
         <v>2.19</v>
       </c>
       <c r="S148">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T148">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U148">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="V148">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W148">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X148">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y148">
         <v>1.19</v>
@@ -24475,10 +24475,10 @@
         <v>1.78</v>
       </c>
       <c r="AB148">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC148">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AD148">
         <v>1.34</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O149">
         <v>3.45</v>
@@ -24605,25 +24605,25 @@
         <v>2.45</v>
       </c>
       <c r="Q149">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="R149">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="S149">
         <v>1.3</v>
       </c>
       <c r="T149">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U149">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="V149">
         <v>1.48</v>
       </c>
       <c r="W149">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X149">
         <v>1</v>
@@ -24632,19 +24632,19 @@
         <v>1.19</v>
       </c>
       <c r="Z149">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA149">
         <v>1.72</v>
       </c>
       <c r="AB149">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC149">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AD149">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE149">
         <v>1.16</v>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
+        <v>1.24</v>
+      </c>
+      <c r="AK149">
         <v>1.42</v>
-      </c>
-      <c r="AK149">
-        <v>1.43</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24759,31 +24759,31 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="O150">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P150">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="Q150">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="R150">
         <v>2.45</v>
       </c>
       <c r="S150">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T150">
         <v>3.7</v>
       </c>
       <c r="U150">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V150">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W150">
         <v>1.17</v>
@@ -24801,7 +24801,7 @@
         <v>1.5</v>
       </c>
       <c r="AB150">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC150">
         <v>2.36</v>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK150">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O151">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P151">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="Q151">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="R151">
         <v>2.45</v>
@@ -24949,7 +24949,7 @@
         <v>1.7</v>
       </c>
       <c r="W151">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X151">
         <v>1.01</v>
@@ -24976,10 +24976,10 @@
         <v>1.23</v>
       </c>
       <c r="AF151">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG151">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="O54">
-        <v>4.08</v>
+        <v>3.35</v>
       </c>
       <c r="P54">
-        <v>4.54</v>
+        <v>2.61</v>
       </c>
       <c r="Q54">
-        <v>2</v>
+        <v>2.89</v>
       </c>
       <c r="R54">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="S54">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U54">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V54">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="W54">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>5.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA54">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AB54">
-        <v>2.49</v>
+        <v>2.14</v>
       </c>
       <c r="AC54">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="AD54">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AE54">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF54">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="O55">
-        <v>3.35</v>
+        <v>4.08</v>
       </c>
       <c r="P55">
-        <v>2.61</v>
+        <v>4.54</v>
       </c>
       <c r="Q55">
-        <v>2.89</v>
+        <v>2</v>
       </c>
       <c r="R55">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="S55">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U55">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V55">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W55">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z55">
-        <v>4.1</v>
+        <v>5.88</v>
       </c>
       <c r="AA55">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AB55">
-        <v>2.14</v>
+        <v>2.49</v>
       </c>
       <c r="AC55">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="AD55">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AE55">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF55">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG55">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK55">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Q85">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="R85">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="S85">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="T85">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="U85">
-        <v>3.3</v>
+        <v>2.46</v>
       </c>
       <c r="V85">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W85">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="Z85">
-        <v>2.52</v>
+        <v>3.88</v>
       </c>
       <c r="AA85">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AB85">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AC85">
-        <v>4.45</v>
+        <v>2.59</v>
       </c>
       <c r="AD85">
+        <v>1.39</v>
+      </c>
+      <c r="AE85">
+        <v>1.12</v>
+      </c>
+      <c r="AF85">
+        <v>1.9</v>
+      </c>
+      <c r="AG85">
+        <v>1.78</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
         <v>1.14</v>
       </c>
-      <c r="AE85">
-        <v>1</v>
-      </c>
-      <c r="AF85">
-        <v>1.97</v>
-      </c>
-      <c r="AG85">
-        <v>1.69</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.33</v>
-      </c>
       <c r="AK85">
-        <v>1.52</v>
+        <v>2.74</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="R86">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S86">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T86">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U86">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="V86">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W86">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z86">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA86">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AB86">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC86">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD86">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG86">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>2.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G87">
@@ -14499,55 +14499,55 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R87">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S87">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="T87">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="U87">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="V87">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W87">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="Z87">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="AA87">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="AB87">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC87">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="AD87">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AE87">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF87">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AG87">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK87">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>4.01</v>
+        <v>2.17</v>
       </c>
       <c r="O97">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="P97">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q97">
-        <v>4.5</v>
+        <v>3.01</v>
       </c>
       <c r="R97">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S97">
+        <v>1.65</v>
+      </c>
+      <c r="T97">
+        <v>2.19</v>
+      </c>
+      <c r="U97">
+        <v>3.9</v>
+      </c>
+      <c r="V97">
+        <v>1.2</v>
+      </c>
+      <c r="W97">
+        <v>1.03</v>
+      </c>
+      <c r="X97">
+        <v>1.13</v>
+      </c>
+      <c r="Y97">
         <v>1.61</v>
       </c>
-      <c r="T97">
-        <v>2.45</v>
-      </c>
-      <c r="U97">
-        <v>3.6</v>
-      </c>
-      <c r="V97">
-        <v>1.25</v>
-      </c>
-      <c r="W97">
-        <v>1</v>
-      </c>
-      <c r="X97">
-        <v>1.09</v>
-      </c>
-      <c r="Y97">
-        <v>1.52</v>
-      </c>
       <c r="Z97">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="AA97">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="AB97">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC97">
-        <v>4.8</v>
+        <v>6.12</v>
       </c>
       <c r="AD97">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE97">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AG97">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
+        <v>4.01</v>
+      </c>
+      <c r="O98">
+        <v>2.94</v>
+      </c>
+      <c r="P98">
+        <v>1.96</v>
+      </c>
+      <c r="Q98">
+        <v>4.5</v>
+      </c>
+      <c r="R98">
+        <v>1.95</v>
+      </c>
+      <c r="S98">
+        <v>1.61</v>
+      </c>
+      <c r="T98">
+        <v>2.45</v>
+      </c>
+      <c r="U98">
+        <v>3.6</v>
+      </c>
+      <c r="V98">
+        <v>1.25</v>
+      </c>
+      <c r="W98">
+        <v>1</v>
+      </c>
+      <c r="X98">
+        <v>1.09</v>
+      </c>
+      <c r="Y98">
+        <v>1.52</v>
+      </c>
+      <c r="Z98">
+        <v>2.43</v>
+      </c>
+      <c r="AA98">
+        <v>2.48</v>
+      </c>
+      <c r="AB98">
+        <v>1.41</v>
+      </c>
+      <c r="AC98">
+        <v>4.8</v>
+      </c>
+      <c r="AD98">
+        <v>1.14</v>
+      </c>
+      <c r="AE98">
+        <v>1</v>
+      </c>
+      <c r="AF98">
         <v>2.17</v>
       </c>
-      <c r="O98">
-        <v>2.7</v>
-      </c>
-      <c r="P98">
-        <v>3.3</v>
-      </c>
-      <c r="Q98">
-        <v>3.01</v>
-      </c>
-      <c r="R98">
-        <v>1.85</v>
-      </c>
-      <c r="S98">
-        <v>1.65</v>
-      </c>
-      <c r="T98">
-        <v>2.19</v>
-      </c>
-      <c r="U98">
-        <v>3.9</v>
-      </c>
-      <c r="V98">
-        <v>1.2</v>
-      </c>
-      <c r="W98">
-        <v>1.03</v>
-      </c>
-      <c r="X98">
-        <v>1.13</v>
-      </c>
-      <c r="Y98">
-        <v>1.61</v>
-      </c>
-      <c r="Z98">
-        <v>2.17</v>
-      </c>
-      <c r="AA98">
-        <v>2.78</v>
-      </c>
-      <c r="AB98">
-        <v>1.36</v>
-      </c>
-      <c r="AC98">
-        <v>6.12</v>
-      </c>
-      <c r="AD98">
-        <v>1.11</v>
-      </c>
-      <c r="AE98">
-        <v>1.03</v>
-      </c>
-      <c r="AF98">
-        <v>2.3</v>
-      </c>
       <c r="AG98">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AK98">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,80 +21825,80 @@
         </is>
       </c>
       <c r="N132">
+        <v>1.65</v>
+      </c>
+      <c r="O132">
+        <v>4.15</v>
+      </c>
+      <c r="P132">
+        <v>3.51</v>
+      </c>
+      <c r="Q132">
         <v>2</v>
       </c>
-      <c r="O132">
-        <v>4.05</v>
-      </c>
-      <c r="P132">
-        <v>2.63</v>
-      </c>
-      <c r="Q132">
-        <v>2.38</v>
-      </c>
       <c r="R132">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S132">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T132">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U132">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="V132">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W132">
+        <v>1.19</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>1.11</v>
+      </c>
+      <c r="Z132">
+        <v>6.73</v>
+      </c>
+      <c r="AA132">
+        <v>1.38</v>
+      </c>
+      <c r="AB132">
+        <v>3.01</v>
+      </c>
+      <c r="AC132">
+        <v>1.9</v>
+      </c>
+      <c r="AD132">
+        <v>1.87</v>
+      </c>
+      <c r="AE132">
+        <v>1.38</v>
+      </c>
+      <c r="AF132">
+        <v>1.38</v>
+      </c>
+      <c r="AG132">
+        <v>2.9</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
         <v>1.22</v>
       </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>1.03</v>
-      </c>
-      <c r="Z132">
-        <v>7.5</v>
-      </c>
-      <c r="AA132">
-        <v>1.32</v>
-      </c>
-      <c r="AB132">
-        <v>3.42</v>
-      </c>
-      <c r="AC132">
-        <v>1.8</v>
-      </c>
-      <c r="AD132">
-        <v>2.01</v>
-      </c>
-      <c r="AE132">
-        <v>1.4</v>
-      </c>
-      <c r="AF132">
-        <v>1.3</v>
-      </c>
-      <c r="AG132">
-        <v>3.2</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>1.34</v>
-      </c>
       <c r="AK132">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="O133">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P133">
-        <v>3.51</v>
+        <v>2.63</v>
       </c>
       <c r="Q133">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="R133">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S133">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T133">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="U133">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V133">
+        <v>1.88</v>
+      </c>
+      <c r="W133">
+        <v>1.22</v>
+      </c>
+      <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133">
+        <v>1.03</v>
+      </c>
+      <c r="Z133">
+        <v>7.5</v>
+      </c>
+      <c r="AA133">
+        <v>1.32</v>
+      </c>
+      <c r="AB133">
+        <v>3.42</v>
+      </c>
+      <c r="AC133">
         <v>1.8</v>
       </c>
-      <c r="W133">
-        <v>1.19</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>1.11</v>
-      </c>
-      <c r="Z133">
-        <v>6.73</v>
-      </c>
-      <c r="AA133">
-        <v>1.38</v>
-      </c>
-      <c r="AB133">
-        <v>3.01</v>
-      </c>
-      <c r="AC133">
-        <v>1.9</v>
-      </c>
       <c r="AD133">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AE133">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF133">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AG133">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK133">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="AL133">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
+        <v>4.01</v>
+      </c>
+      <c r="O97">
+        <v>2.94</v>
+      </c>
+      <c r="P97">
+        <v>1.96</v>
+      </c>
+      <c r="Q97">
+        <v>4.5</v>
+      </c>
+      <c r="R97">
+        <v>1.95</v>
+      </c>
+      <c r="S97">
+        <v>1.61</v>
+      </c>
+      <c r="T97">
+        <v>2.45</v>
+      </c>
+      <c r="U97">
+        <v>3.6</v>
+      </c>
+      <c r="V97">
+        <v>1.25</v>
+      </c>
+      <c r="W97">
+        <v>1</v>
+      </c>
+      <c r="X97">
+        <v>1.09</v>
+      </c>
+      <c r="Y97">
+        <v>1.52</v>
+      </c>
+      <c r="Z97">
+        <v>2.43</v>
+      </c>
+      <c r="AA97">
+        <v>2.48</v>
+      </c>
+      <c r="AB97">
+        <v>1.41</v>
+      </c>
+      <c r="AC97">
+        <v>4.8</v>
+      </c>
+      <c r="AD97">
+        <v>1.14</v>
+      </c>
+      <c r="AE97">
+        <v>1</v>
+      </c>
+      <c r="AF97">
         <v>2.17</v>
       </c>
-      <c r="O97">
-        <v>2.7</v>
-      </c>
-      <c r="P97">
-        <v>3.3</v>
-      </c>
-      <c r="Q97">
-        <v>3.01</v>
-      </c>
-      <c r="R97">
-        <v>1.85</v>
-      </c>
-      <c r="S97">
-        <v>1.65</v>
-      </c>
-      <c r="T97">
-        <v>2.19</v>
-      </c>
-      <c r="U97">
-        <v>3.9</v>
-      </c>
-      <c r="V97">
-        <v>1.2</v>
-      </c>
-      <c r="W97">
-        <v>1.03</v>
-      </c>
-      <c r="X97">
-        <v>1.13</v>
-      </c>
-      <c r="Y97">
-        <v>1.61</v>
-      </c>
-      <c r="Z97">
-        <v>2.17</v>
-      </c>
-      <c r="AA97">
-        <v>2.78</v>
-      </c>
-      <c r="AB97">
-        <v>1.36</v>
-      </c>
-      <c r="AC97">
-        <v>6.12</v>
-      </c>
-      <c r="AD97">
-        <v>1.11</v>
-      </c>
-      <c r="AE97">
-        <v>1.03</v>
-      </c>
-      <c r="AF97">
-        <v>2.3</v>
-      </c>
       <c r="AG97">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AK97">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.01</v>
+        <v>2.17</v>
       </c>
       <c r="O98">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="P98">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q98">
-        <v>4.5</v>
+        <v>3.01</v>
       </c>
       <c r="R98">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S98">
+        <v>1.65</v>
+      </c>
+      <c r="T98">
+        <v>2.19</v>
+      </c>
+      <c r="U98">
+        <v>3.9</v>
+      </c>
+      <c r="V98">
+        <v>1.2</v>
+      </c>
+      <c r="W98">
+        <v>1.03</v>
+      </c>
+      <c r="X98">
+        <v>1.13</v>
+      </c>
+      <c r="Y98">
         <v>1.61</v>
       </c>
-      <c r="T98">
-        <v>2.45</v>
-      </c>
-      <c r="U98">
-        <v>3.6</v>
-      </c>
-      <c r="V98">
-        <v>1.25</v>
-      </c>
-      <c r="W98">
-        <v>1</v>
-      </c>
-      <c r="X98">
-        <v>1.09</v>
-      </c>
-      <c r="Y98">
-        <v>1.52</v>
-      </c>
       <c r="Z98">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="AA98">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="AB98">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC98">
-        <v>4.8</v>
+        <v>6.12</v>
       </c>
       <c r="AD98">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE98">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF98">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AG98">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL98">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O15">
         <v>3.15</v>
       </c>
       <c r="P15">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q15">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="R15">
         <v>2.02</v>
@@ -2787,7 +2787,7 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z15">
         <v>2.95</v>
@@ -2796,7 +2796,7 @@
         <v>2.18</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC15">
         <v>3.84</v>
@@ -2811,7 +2811,7 @@
         <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK15">
         <v>1.42</v>
@@ -4230,10 +4230,10 @@
         <v>2.13</v>
       </c>
       <c r="Q24">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="R24">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S24">
         <v>1.36</v>
@@ -4245,7 +4245,7 @@
         <v>2.65</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4257,28 +4257,28 @@
         <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB24">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
         <v>3.6</v>
       </c>
       <c r="AD24">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE24">
         <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AG24">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,16 +4387,16 @@
         <v>2.42</v>
       </c>
       <c r="O25">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="Q25">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="S25">
         <v>1.33</v>
@@ -4405,10 +4405,10 @@
         <v>3</v>
       </c>
       <c r="U25">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V25">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W25">
         <v>1.1</v>
@@ -4438,10 +4438,10 @@
         <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AG25">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O27">
         <v>3.1</v>
@@ -4719,10 +4719,10 @@
         <v>3.4</v>
       </c>
       <c r="Q27">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S27">
         <v>1.41</v>
@@ -4743,22 +4743,22 @@
         <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z27">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA27">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB27">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC27">
         <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
         <v>1.08</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>2.6</v>
       </c>
       <c r="AA28">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AB28">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC28">
         <v>4.44</v>
@@ -4927,7 +4927,7 @@
         <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AG28">
         <v>1.67</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK28">
         <v>1.7</v>
@@ -5078,7 +5078,7 @@
         <v>2.08</v>
       </c>
       <c r="AB29">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AC29">
         <v>3.5</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>2.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK29">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="O35">
         <v>4.05</v>
       </c>
       <c r="P35">
-        <v>4.8</v>
+        <v>5.85</v>
       </c>
       <c r="Q35">
         <v>2.05</v>
@@ -6035,10 +6035,10 @@
         <v>3.32</v>
       </c>
       <c r="U35">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6050,19 +6050,19 @@
         <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="AA35">
         <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
         <v>2.74</v>
       </c>
       <c r="AD35">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
         <v>1.11</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
         <v>2.55</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O40">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P40">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="Q40">
         <v>3.26</v>
@@ -6871,10 +6871,10 @@
         <v>2.35</v>
       </c>
       <c r="AB40">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC40">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD40">
         <v>1.14</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AK40">
         <v>1.43</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="Q42">
         <v>5</v>
@@ -7173,10 +7173,10 @@
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="U42">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
         <v>1.44</v>
@@ -7188,31 +7188,31 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AD42">
         <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
         <v>1.67</v>
       </c>
       <c r="AG42">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7988,7 +7988,7 @@
         <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="U47">
         <v>2.55</v>
@@ -8006,7 +8006,7 @@
         <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA47">
         <v>1.8</v>
@@ -8021,10 +8021,10 @@
         <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
         <v>2.1</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O48">
         <v>3.2</v>
       </c>
       <c r="P48">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q48">
         <v>5</v>
@@ -8501,7 +8501,7 @@
         <v>2.28</v>
       </c>
       <c r="AB50">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC50">
         <v>4.1</v>
@@ -8516,7 +8516,7 @@
         <v>1.97</v>
       </c>
       <c r="AG50">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK50">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P51">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -8664,7 +8664,7 @@
         <v>1.9</v>
       </c>
       <c r="AB51">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC51">
         <v>2.92</v>
@@ -8797,28 +8797,28 @@
         <v>2.06</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
         <v>2.38</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z52">
         <v>3.94</v>
@@ -8836,26 +8836,26 @@
         <v>1.4</v>
       </c>
       <c r="AE52">
+        <v>1.14</v>
+      </c>
+      <c r="AF52">
+        <v>1.75</v>
+      </c>
+      <c r="AG52">
+        <v>1.95</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.12</v>
-      </c>
-      <c r="AF52">
-        <v>1.67</v>
-      </c>
-      <c r="AG52">
-        <v>2</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.19</v>
       </c>
       <c r="AK52">
         <v>2.3</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB53">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q56">
         <v>4.2</v>
@@ -9467,7 +9467,7 @@
         <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
         <v>1.22</v>
@@ -9476,7 +9476,7 @@
         <v>3.95</v>
       </c>
       <c r="AA56">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB56">
         <v>2.05</v>
@@ -9488,13 +9488,13 @@
         <v>1.41</v>
       </c>
       <c r="AE56">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF56">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG56">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9775,13 +9775,13 @@
         <v>3.1</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S58">
         <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U58">
         <v>3</v>
@@ -9802,10 +9802,10 @@
         <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB58">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC58">
         <v>3.8</v>
@@ -9820,7 +9820,7 @@
         <v>1.78</v>
       </c>
       <c r="AG58">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.35</v>
       </c>
       <c r="AK58">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O61">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P61">
         <v>4.33</v>
@@ -10264,7 +10264,7 @@
         <v>2.55</v>
       </c>
       <c r="R61">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S61">
         <v>1.55</v>
@@ -10282,19 +10282,19 @@
         <v>1.01</v>
       </c>
       <c r="X61">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y61">
         <v>1.5</v>
       </c>
       <c r="Z61">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AA61">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AB61">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC61">
         <v>5.25</v>
@@ -10325,7 +10325,7 @@
         <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>1.83</v>
       </c>
       <c r="Q62">
-        <v>4.64</v>
+        <v>4.11</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S62">
         <v>1.29</v>
@@ -10436,10 +10436,10 @@
         <v>3.6</v>
       </c>
       <c r="U62">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="V62">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
         <v>1.1</v>
@@ -10448,31 +10448,31 @@
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z62">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA62">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB62">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC62">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AD62">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE62">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.27</v>
+        <v>3.48</v>
       </c>
       <c r="O63">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -10614,7 +10614,7 @@
         <v>1.33</v>
       </c>
       <c r="Z63">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="AA63">
         <v>2.1</v>
@@ -11076,7 +11076,7 @@
         <v>2.47</v>
       </c>
       <c r="Q66">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="R66">
         <v>2.12</v>
@@ -11097,7 +11097,7 @@
         <v>1.1</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y66">
         <v>1.23</v>
@@ -11106,7 +11106,7 @@
         <v>3.42</v>
       </c>
       <c r="AA66">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB66">
         <v>1.85</v>
@@ -11124,7 +11124,7 @@
         <v>1.66</v>
       </c>
       <c r="AG66">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,10 +11230,10 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="O67">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P67">
         <v>1.94</v>
@@ -11266,13 +11266,13 @@
         <v>1.12</v>
       </c>
       <c r="Z67">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AA67">
         <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="AC67">
         <v>2.38</v>
@@ -11284,10 +11284,10 @@
         <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG67">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK67">
         <v>1.29</v>
@@ -11408,16 +11408,16 @@
         <v>2.32</v>
       </c>
       <c r="S68">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="U68">
         <v>2.15</v>
       </c>
       <c r="V68">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W68">
         <v>1.14</v>
@@ -11429,16 +11429,16 @@
         <v>1.15</v>
       </c>
       <c r="Z68">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="AA68">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB68">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AC68">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD68">
         <v>1.59</v>
@@ -11559,13 +11559,13 @@
         <v>2.37</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q69">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="R69">
         <v>2.06</v>
@@ -11574,37 +11574,37 @@
         <v>1.35</v>
       </c>
       <c r="T69">
-        <v>2.82</v>
+        <v>3.07</v>
       </c>
       <c r="U69">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V69">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z69">
         <v>3.42</v>
       </c>
       <c r="AA69">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB69">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC69">
         <v>3.12</v>
       </c>
       <c r="AD69">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE69">
         <v>1.06</v>
@@ -11885,13 +11885,13 @@
         <v>1.91</v>
       </c>
       <c r="O71">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P71">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q71">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R71">
         <v>2.62</v>
@@ -11909,7 +11909,7 @@
         <v>1.73</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
         <v>1.01</v>
@@ -11955,7 +11955,7 @@
         <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,37 +12045,37 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O72">
-        <v>3.43</v>
+        <v>3.7</v>
       </c>
       <c r="P72">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="Q72">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R72">
         <v>2.28</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U72">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V72">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W72">
         <v>1.11</v>
       </c>
       <c r="X72">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
         <v>1.16</v>
@@ -12099,10 +12099,10 @@
         <v>1.14</v>
       </c>
       <c r="AF72">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG72">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.85</v>
       </c>
       <c r="AK72">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O73">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q73">
         <v>3.18</v>
@@ -12223,19 +12223,19 @@
         <v>2.06</v>
       </c>
       <c r="S73">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T73">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U73">
         <v>2.75</v>
       </c>
       <c r="V73">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X73">
         <v>1.01</v>
@@ -12247,10 +12247,10 @@
         <v>3.28</v>
       </c>
       <c r="AA73">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB73">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC73">
         <v>3.2</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK73">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O74">
         <v>3.17</v>
       </c>
       <c r="P74">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="Q74">
         <v>2.77</v>
@@ -12386,10 +12386,10 @@
         <v>2.2</v>
       </c>
       <c r="S74">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U74">
         <v>2.63</v>
@@ -12534,16 +12534,16 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O75">
         <v>5.75</v>
       </c>
       <c r="P75">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="Q75">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R75">
         <v>2.57</v>
@@ -12555,7 +12555,7 @@
         <v>3.23</v>
       </c>
       <c r="U75">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V75">
         <v>1.48</v>
@@ -12567,22 +12567,22 @@
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z75">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="AA75">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB75">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AC75">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="AD75">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE75">
         <v>1.12</v>
@@ -12591,7 +12591,7 @@
         <v>2.4</v>
       </c>
       <c r="AG75">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AK75">
         <v>4.15</v>
@@ -12860,16 +12860,16 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O77">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="P77">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="Q77">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="R77">
         <v>1.95</v>
@@ -12881,10 +12881,10 @@
         <v>2.39</v>
       </c>
       <c r="U77">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="V77">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W77">
         <v>1.01</v>
@@ -12893,31 +12893,31 @@
         <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z77">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA77">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AB77">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC77">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
       <c r="AD77">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE77">
         <v>1.02</v>
       </c>
       <c r="AF77">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AG77">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="O78">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q78">
         <v>2.28</v>
@@ -13044,7 +13044,7 @@
         <v>3.22</v>
       </c>
       <c r="U78">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="V78">
         <v>1.5</v>
@@ -13059,10 +13059,10 @@
         <v>1.16</v>
       </c>
       <c r="Z78">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="AA78">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB78">
         <v>2.12</v>
@@ -13080,7 +13080,7 @@
         <v>1.63</v>
       </c>
       <c r="AG78">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>3.3</v>
       </c>
       <c r="P79">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
         <v>2.7</v>
@@ -13204,7 +13204,7 @@
         <v>1.36</v>
       </c>
       <c r="T79">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="U79">
         <v>2.77</v>
@@ -13222,13 +13222,13 @@
         <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA79">
         <v>1.9</v>
       </c>
       <c r="AB79">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC79">
         <v>2.83</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,19 +13349,19 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O80">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P80">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q80">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S80">
         <v>1.3</v>
@@ -13370,43 +13370,43 @@
         <v>3.3</v>
       </c>
       <c r="U80">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="V80">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W80">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
         <v>1.04</v>
       </c>
       <c r="Y80">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z80">
         <v>4.1</v>
       </c>
       <c r="AA80">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB80">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC80">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AD80">
         <v>1.4</v>
       </c>
       <c r="AE80">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF80">
         <v>1.57</v>
       </c>
       <c r="AG80">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK80">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13847,16 +13847,16 @@
         <v>3.58</v>
       </c>
       <c r="Q83">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="R83">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S83">
         <v>1.44</v>
       </c>
       <c r="T83">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="U83">
         <v>3.14</v>
@@ -13868,19 +13868,19 @@
         <v>1.04</v>
       </c>
       <c r="X83">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z83">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA83">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AB83">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC83">
         <v>4.05</v>
@@ -13892,10 +13892,10 @@
         <v>1.02</v>
       </c>
       <c r="AF83">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG83">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14013,13 +14013,13 @@
         <v>2.25</v>
       </c>
       <c r="R84">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S84">
         <v>1.33</v>
       </c>
       <c r="T84">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U84">
         <v>2.53</v>
@@ -14058,7 +14058,7 @@
         <v>1.7</v>
       </c>
       <c r="AG84">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK84">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>6.35</v>
       </c>
       <c r="Q85">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R85">
         <v>2.4</v>
@@ -14185,13 +14185,13 @@
         <v>3.3</v>
       </c>
       <c r="U85">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="V85">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W85">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
         <v>1.01</v>
@@ -14200,13 +14200,13 @@
         <v>1.18</v>
       </c>
       <c r="Z85">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA85">
         <v>1.7</v>
       </c>
       <c r="AB85">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC85">
         <v>2.59</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK85">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,7 +14336,7 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R86">
         <v>2.1</v>
@@ -14400,7 +14400,7 @@
         <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14505,10 +14505,10 @@
         <v>1.91</v>
       </c>
       <c r="S87">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T87">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="U87">
         <v>3.3</v>
@@ -14520,34 +14520,34 @@
         <v>1.03</v>
       </c>
       <c r="X87">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z87">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AA87">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AB87">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AC87">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="AD87">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE87">
         <v>1</v>
       </c>
       <c r="AF87">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG87">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>1.33</v>
       </c>
       <c r="AK87">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,10 +14662,10 @@
         <v>2.5</v>
       </c>
       <c r="Q88">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R88">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S88">
         <v>1.3</v>
@@ -14674,7 +14674,7 @@
         <v>3.1</v>
       </c>
       <c r="U88">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V88">
         <v>1.44</v>
@@ -14692,10 +14692,10 @@
         <v>3.94</v>
       </c>
       <c r="AA88">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB88">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AC88">
         <v>2.74</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AK88">
         <v>1.43</v>
@@ -14816,22 +14816,22 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O89">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P89">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="Q89">
         <v>1.71</v>
       </c>
       <c r="R89">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="S89">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
         <v>4</v>
@@ -14861,10 +14861,10 @@
         <v>2.55</v>
       </c>
       <c r="AC89">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD89">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE89">
         <v>1.19</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O90">
         <v>3.08</v>
@@ -14988,22 +14988,22 @@
         <v>2.35</v>
       </c>
       <c r="Q90">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="R90">
         <v>2.04</v>
       </c>
       <c r="S90">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T90">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U90">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="V90">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W90">
         <v>1.05</v>
@@ -15027,16 +15027,16 @@
         <v>3.58</v>
       </c>
       <c r="AD90">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
         <v>1.05</v>
       </c>
       <c r="AF90">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG90">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15148,28 +15148,28 @@
         <v>3.25</v>
       </c>
       <c r="P91">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q91">
-        <v>5.39</v>
+        <v>5.25</v>
       </c>
       <c r="R91">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
         <v>1.44</v>
       </c>
       <c r="T91">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U91">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V91">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W91">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15184,19 +15184,19 @@
         <v>2.21</v>
       </c>
       <c r="AB91">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC91">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AD91">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE91">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG91">
         <v>1.68</v>
@@ -15320,19 +15320,19 @@
         <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T92">
         <v>3</v>
       </c>
       <c r="U92">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V92">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W92">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X92">
         <v>1.06</v>
@@ -15344,10 +15344,10 @@
         <v>3.5</v>
       </c>
       <c r="AA92">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB92">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC92">
         <v>3.3</v>
@@ -15362,7 +15362,7 @@
         <v>1.68</v>
       </c>
       <c r="AG92">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>4.01</v>
+        <v>2.17</v>
       </c>
       <c r="O97">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="P97">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q97">
-        <v>4.5</v>
+        <v>3.01</v>
       </c>
       <c r="R97">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S97">
+        <v>1.65</v>
+      </c>
+      <c r="T97">
+        <v>2.19</v>
+      </c>
+      <c r="U97">
+        <v>3.9</v>
+      </c>
+      <c r="V97">
+        <v>1.2</v>
+      </c>
+      <c r="W97">
+        <v>1.03</v>
+      </c>
+      <c r="X97">
+        <v>1.13</v>
+      </c>
+      <c r="Y97">
         <v>1.61</v>
       </c>
-      <c r="T97">
-        <v>2.45</v>
-      </c>
-      <c r="U97">
-        <v>3.6</v>
-      </c>
-      <c r="V97">
-        <v>1.25</v>
-      </c>
-      <c r="W97">
-        <v>1</v>
-      </c>
-      <c r="X97">
-        <v>1.09</v>
-      </c>
-      <c r="Y97">
-        <v>1.52</v>
-      </c>
       <c r="Z97">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="AA97">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="AB97">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC97">
-        <v>4.8</v>
+        <v>6.12</v>
       </c>
       <c r="AD97">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE97">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AG97">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
+        <v>4.01</v>
+      </c>
+      <c r="O98">
+        <v>2.94</v>
+      </c>
+      <c r="P98">
+        <v>1.96</v>
+      </c>
+      <c r="Q98">
+        <v>4.5</v>
+      </c>
+      <c r="R98">
+        <v>1.95</v>
+      </c>
+      <c r="S98">
+        <v>1.61</v>
+      </c>
+      <c r="T98">
+        <v>2.45</v>
+      </c>
+      <c r="U98">
+        <v>3.6</v>
+      </c>
+      <c r="V98">
+        <v>1.25</v>
+      </c>
+      <c r="W98">
+        <v>1</v>
+      </c>
+      <c r="X98">
+        <v>1.09</v>
+      </c>
+      <c r="Y98">
+        <v>1.52</v>
+      </c>
+      <c r="Z98">
+        <v>2.43</v>
+      </c>
+      <c r="AA98">
+        <v>2.48</v>
+      </c>
+      <c r="AB98">
+        <v>1.41</v>
+      </c>
+      <c r="AC98">
+        <v>4.8</v>
+      </c>
+      <c r="AD98">
+        <v>1.14</v>
+      </c>
+      <c r="AE98">
+        <v>1</v>
+      </c>
+      <c r="AF98">
         <v>2.17</v>
       </c>
-      <c r="O98">
-        <v>2.7</v>
-      </c>
-      <c r="P98">
-        <v>3.3</v>
-      </c>
-      <c r="Q98">
-        <v>3.01</v>
-      </c>
-      <c r="R98">
-        <v>1.85</v>
-      </c>
-      <c r="S98">
-        <v>1.65</v>
-      </c>
-      <c r="T98">
-        <v>2.19</v>
-      </c>
-      <c r="U98">
-        <v>3.9</v>
-      </c>
-      <c r="V98">
-        <v>1.2</v>
-      </c>
-      <c r="W98">
-        <v>1.03</v>
-      </c>
-      <c r="X98">
-        <v>1.13</v>
-      </c>
-      <c r="Y98">
-        <v>1.61</v>
-      </c>
-      <c r="Z98">
-        <v>2.17</v>
-      </c>
-      <c r="AA98">
-        <v>2.78</v>
-      </c>
-      <c r="AB98">
-        <v>1.36</v>
-      </c>
-      <c r="AC98">
-        <v>6.12</v>
-      </c>
-      <c r="AD98">
-        <v>1.11</v>
-      </c>
-      <c r="AE98">
-        <v>1.03</v>
-      </c>
-      <c r="AF98">
-        <v>2.3</v>
-      </c>
       <c r="AG98">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AK98">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16458,7 +16458,7 @@
         <v>1.86</v>
       </c>
       <c r="R99">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S99">
         <v>1.24</v>
@@ -16467,10 +16467,10 @@
         <v>3.7</v>
       </c>
       <c r="U99">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V99">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W99">
         <v>1.14</v>
@@ -16479,10 +16479,10 @@
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z99">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA99">
         <v>1.43</v>
@@ -16500,7 +16500,7 @@
         <v>1.24</v>
       </c>
       <c r="AF99">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG99">
         <v>2.13</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O104">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P104">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -17288,25 +17288,25 @@
         <v>1.7</v>
       </c>
       <c r="W104">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X104">
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z104">
         <v>5</v>
       </c>
       <c r="AA104">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="AC104">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AD104">
         <v>1.63</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="O105">
         <v>3</v>
@@ -17433,40 +17433,40 @@
         <v>2.6</v>
       </c>
       <c r="Q105">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="R105">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="S105">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T105">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="U105">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="V105">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W105">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X105">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y105">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z105">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA105">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AB105">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC105">
         <v>3.84</v>
@@ -17478,10 +17478,10 @@
         <v>1.02</v>
       </c>
       <c r="AF105">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG105">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK105">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="Q106">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R106">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S106">
         <v>1.38</v>
       </c>
       <c r="T106">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="U106">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="V106">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W106">
         <v>1.08</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y106">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z106">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA106">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB106">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC106">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD106">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE106">
         <v>1.05</v>
       </c>
       <c r="AF106">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG106">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17750,16 +17750,16 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O107">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="P107">
         <v>2.37</v>
       </c>
       <c r="Q107">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R107">
         <v>2.64</v>
@@ -17771,10 +17771,10 @@
         <v>3.98</v>
       </c>
       <c r="U107">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="V107">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W107">
         <v>1.17</v>
@@ -17783,25 +17783,25 @@
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z107">
-        <v>5.8</v>
+        <v>6.23</v>
       </c>
       <c r="AA107">
         <v>1.4</v>
       </c>
       <c r="AB107">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="AC107">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AD107">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE107">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF107">
         <v>1.38</v>
@@ -17823,7 +17823,7 @@
         <v>1.24</v>
       </c>
       <c r="AK107">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O108">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="P108">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q108">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R108">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S108">
         <v>1.36</v>
@@ -17934,31 +17934,31 @@
         <v>2.75</v>
       </c>
       <c r="U108">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V108">
         <v>1.36</v>
       </c>
       <c r="W108">
+        <v>1.03</v>
+      </c>
+      <c r="X108">
         <v>1.05</v>
       </c>
-      <c r="X108">
-        <v>1.01</v>
-      </c>
       <c r="Y108">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z108">
         <v>3.28</v>
       </c>
       <c r="AA108">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB108">
         <v>1.8</v>
       </c>
       <c r="AC108">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD108">
         <v>1.28</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK108">
         <v>1.48</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O110">
-        <v>3.85</v>
+        <v>4.65</v>
       </c>
       <c r="P110">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="Q110">
         <v>2</v>
@@ -18260,7 +18260,7 @@
         <v>2.65</v>
       </c>
       <c r="U110">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="V110">
         <v>1.31</v>
@@ -18269,19 +18269,19 @@
         <v>1.02</v>
       </c>
       <c r="X110">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z110">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA110">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB110">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC110">
         <v>3.75</v>
@@ -18296,7 +18296,7 @@
         <v>2.2</v>
       </c>
       <c r="AG110">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -19057,25 +19057,25 @@
         <v>2.37</v>
       </c>
       <c r="O115">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="P115">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q115">
         <v>3</v>
       </c>
       <c r="R115">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S115">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U115">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V115">
         <v>1.32</v>
@@ -19087,7 +19087,7 @@
         <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z115">
         <v>2.88</v>
@@ -19096,10 +19096,10 @@
         <v>2.19</v>
       </c>
       <c r="AB115">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC115">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AD115">
         <v>1.23</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK115">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -20367,7 +20367,7 @@
         <v>5.11</v>
       </c>
       <c r="Q123">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R123">
         <v>2.3</v>
@@ -20409,7 +20409,7 @@
         <v>1.4</v>
       </c>
       <c r="AE123">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF123">
         <v>1.75</v>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK123">
         <v>2.2</v>
@@ -20536,49 +20536,49 @@
         <v>2.2</v>
       </c>
       <c r="S124">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T124">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U124">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="V124">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W124">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X124">
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z124">
-        <v>3.89</v>
+        <v>3.39</v>
       </c>
       <c r="AA124">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB124">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC124">
-        <v>2.84</v>
+        <v>3.08</v>
       </c>
       <c r="AD124">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE124">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF124">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG124">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK124">
         <v>1.21</v>
@@ -20687,31 +20687,31 @@
         <v>2.09</v>
       </c>
       <c r="O125">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P125">
         <v>2.93</v>
       </c>
       <c r="Q125">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R125">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S125">
         <v>1.33</v>
       </c>
       <c r="T125">
-        <v>3.16</v>
+        <v>2.91</v>
       </c>
       <c r="U125">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="V125">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W125">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X125">
         <v>1.01</v>
@@ -20850,10 +20850,10 @@
         <v>1.33</v>
       </c>
       <c r="O126">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="P126">
-        <v>5.15</v>
+        <v>6.8</v>
       </c>
       <c r="Q126">
         <v>1.8</v>
@@ -20874,7 +20874,7 @@
         <v>1.67</v>
       </c>
       <c r="W126">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X126">
         <v>1.02</v>
@@ -20901,10 +20901,10 @@
         <v>1.22</v>
       </c>
       <c r="AF126">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG126">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -22169,19 +22169,19 @@
         <v>1.28</v>
       </c>
       <c r="T134">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U134">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="V134">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W134">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y134">
         <v>1.16</v>
@@ -22193,7 +22193,7 @@
         <v>1.67</v>
       </c>
       <c r="AB134">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC134">
         <v>2.59</v>
@@ -22208,7 +22208,7 @@
         <v>1.58</v>
       </c>
       <c r="AG134">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22332,10 +22332,10 @@
         <v>1.33</v>
       </c>
       <c r="T135">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U135">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V135">
         <v>1.4</v>
@@ -22356,7 +22356,7 @@
         <v>1.9</v>
       </c>
       <c r="AB135">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC135">
         <v>3.04</v>
@@ -22387,7 +22387,7 @@
         <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -23947,16 +23947,16 @@
         <v>2.73</v>
       </c>
       <c r="O145">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="P145">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q145">
         <v>3.3</v>
       </c>
       <c r="R145">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S145">
         <v>1.31</v>
@@ -23983,22 +23983,22 @@
         <v>3.58</v>
       </c>
       <c r="AA145">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB145">
         <v>2</v>
       </c>
       <c r="AC145">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD145">
         <v>1.39</v>
       </c>
       <c r="AE145">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG145">
         <v>2.18</v>
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O147">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P147">
         <v>2.75</v>
@@ -24297,25 +24297,25 @@
         <v>1.35</v>
       </c>
       <c r="W147">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X147">
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z147">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AA147">
         <v>2</v>
       </c>
       <c r="AB147">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC147">
-        <v>3.34</v>
+        <v>3.57</v>
       </c>
       <c r="AD147">
         <v>1.27</v>
@@ -24327,7 +24327,7 @@
         <v>1.76</v>
       </c>
       <c r="AG147">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>1.26</v>
       </c>
       <c r="AK147">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24436,10 +24436,10 @@
         <v>2.08</v>
       </c>
       <c r="O148">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="P148">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="Q148">
         <v>2.7</v>
@@ -24454,13 +24454,13 @@
         <v>3.12</v>
       </c>
       <c r="U148">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V148">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W148">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X148">
         <v>1.03</v>
@@ -24472,10 +24472,10 @@
         <v>3.75</v>
       </c>
       <c r="AA148">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB148">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC148">
         <v>2.83</v>
@@ -24599,7 +24599,7 @@
         <v>2.43</v>
       </c>
       <c r="O149">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="P149">
         <v>2.45</v>
@@ -24608,19 +24608,19 @@
         <v>3.08</v>
       </c>
       <c r="R149">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="S149">
         <v>1.3</v>
       </c>
       <c r="T149">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U149">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="V149">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W149">
         <v>1.11</v>
@@ -24632,22 +24632,22 @@
         <v>1.19</v>
       </c>
       <c r="Z149">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA149">
         <v>1.72</v>
       </c>
       <c r="AB149">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC149">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AD149">
         <v>1.38</v>
       </c>
       <c r="AE149">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF149">
         <v>1.53</v>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK149">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AL149">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -638,10 +638,10 @@
         <v>2.28</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P2">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>3</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O6">
         <v>3.8</v>
       </c>
       <c r="P6">
-        <v>5.6</v>
+        <v>6.12</v>
       </c>
       <c r="Q6">
         <v>2.02</v>
@@ -1305,7 +1305,7 @@
         <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
         <v>3.1</v>
@@ -1317,7 +1317,7 @@
         <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.38</v>
@@ -1329,13 +1329,13 @@
         <v>2.13</v>
       </c>
       <c r="AB6">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE6">
         <v>1.02</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
         <v>2.6</v>
@@ -1468,7 +1468,7 @@
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U7">
         <v>2.85</v>
@@ -1489,10 +1489,10 @@
         <v>3.18</v>
       </c>
       <c r="AA7">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC7">
         <v>3.6</v>
@@ -1619,13 +1619,13 @@
         <v>3.34</v>
       </c>
       <c r="P8">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q8">
         <v>2.51</v>
       </c>
       <c r="R8">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="S8">
         <v>1.44</v>
@@ -1646,10 +1646,10 @@
         <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="AA8">
         <v>2.13</v>
@@ -1686,7 +1686,7 @@
         <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>2.32</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
         <v>3.25</v>
@@ -1803,10 +1803,10 @@
         <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
         <v>1.19</v>
@@ -1824,16 +1824,16 @@
         <v>2.74</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
         <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
         <v>2.99</v>
@@ -1969,10 +1969,10 @@
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
         <v>3.35</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="R11">
         <v>2.15</v>
@@ -2138,7 +2138,7 @@
         <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
         <v>1.98</v>
@@ -2156,10 +2156,10 @@
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
         <v>2.5</v>
@@ -2455,16 +2455,16 @@
         <v>1.52</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="AA13">
         <v>1.64</v>
@@ -2479,10 +2479,10 @@
         <v>1.42</v>
       </c>
       <c r="AE13">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
         <v>2.39</v>
@@ -2606,7 +2606,7 @@
         <v>2.4</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
         <v>3.4</v>
@@ -2618,31 +2618,31 @@
         <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
         <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE14">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
         <v>1.51</v>
@@ -2664,7 +2664,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="O20">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="P20">
-        <v>4.92</v>
+        <v>4.45</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -3596,22 +3596,22 @@
         <v>1.87</v>
       </c>
       <c r="W20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20">
         <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AC20">
         <v>1.87</v>
@@ -3626,7 +3626,7 @@
         <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="O21">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P21">
         <v>2.77</v>
@@ -3753,13 +3753,13 @@
         <v>4</v>
       </c>
       <c r="U21">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V21">
         <v>1.8</v>
       </c>
       <c r="W21">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,7 +3768,7 @@
         <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="AA21">
         <v>1.33</v>
@@ -3777,19 +3777,19 @@
         <v>3.1</v>
       </c>
       <c r="AC21">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD21">
         <v>1.9</v>
       </c>
       <c r="AE21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG21">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O22">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="P22">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Q22">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R22">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="S22">
         <v>1.23</v>
@@ -3922,34 +3922,34 @@
         <v>1.75</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>5.3</v>
+        <v>5.94</v>
       </c>
       <c r="AA22">
         <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC22">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD22">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE22">
         <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
         <v>2.25</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK22">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4254,22 +4254,22 @@
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z24">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
         <v>3.6</v>
       </c>
       <c r="AD24">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE24">
         <v>1.04</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
+        <v>1.3</v>
+      </c>
+      <c r="AK24">
         <v>1.29</v>
-      </c>
-      <c r="AK24">
-        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>3.4</v>
       </c>
       <c r="Q30">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
         <v>2.3</v>
@@ -5229,34 +5229,34 @@
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
         <v>4.4</v>
       </c>
       <c r="AA30">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB30">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AC30">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AD30">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE30">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG30">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="O31">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -5377,49 +5377,49 @@
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
         <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AA31">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AB31">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC31">
         <v>2.75</v>
       </c>
       <c r="AD31">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF31">
         <v>1.65</v>
       </c>
       <c r="AG31">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="O33">
         <v>3.85</v>
       </c>
       <c r="P33">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="Q33">
         <v>2.23</v>
@@ -5706,13 +5706,13 @@
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
         <v>2.15</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W33">
         <v>1.15</v>
@@ -5721,10 +5721,10 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA33">
         <v>1.52</v>
@@ -5745,7 +5745,7 @@
         <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
         <v>3.6</v>
       </c>
       <c r="Q34">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S34">
         <v>1.31</v>
@@ -5872,28 +5872,28 @@
         <v>2.97</v>
       </c>
       <c r="U34">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA34">
         <v>1.71</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC34">
         <v>2.7</v>
@@ -5902,13 +5902,13 @@
         <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
         <v>1.63</v>
       </c>
       <c r="AG34">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
+        <v>2.02</v>
+      </c>
+      <c r="O36">
+        <v>3.75</v>
+      </c>
+      <c r="P36">
         <v>3</v>
       </c>
-      <c r="O36">
-        <v>3.15</v>
-      </c>
-      <c r="P36">
+      <c r="Q36">
+        <v>2.6</v>
+      </c>
+      <c r="R36">
+        <v>2.43</v>
+      </c>
+      <c r="S36">
+        <v>1.25</v>
+      </c>
+      <c r="T36">
+        <v>3.5</v>
+      </c>
+      <c r="U36">
+        <v>2.36</v>
+      </c>
+      <c r="V36">
+        <v>1.56</v>
+      </c>
+      <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.18</v>
+      </c>
+      <c r="Z36">
+        <v>4.6</v>
+      </c>
+      <c r="AA36">
+        <v>1.61</v>
+      </c>
+      <c r="AB36">
         <v>2.25</v>
       </c>
-      <c r="Q36">
-        <v>3.64</v>
-      </c>
-      <c r="R36">
-        <v>2.14</v>
-      </c>
-      <c r="S36">
-        <v>1.41</v>
-      </c>
-      <c r="T36">
-        <v>2.8</v>
-      </c>
-      <c r="U36">
-        <v>3.07</v>
-      </c>
-      <c r="V36">
-        <v>1.35</v>
-      </c>
-      <c r="W36">
-        <v>1.04</v>
-      </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.33</v>
-      </c>
-      <c r="Z36">
-        <v>3.17</v>
-      </c>
-      <c r="AA36">
-        <v>2.06</v>
-      </c>
-      <c r="AB36">
-        <v>1.68</v>
-      </c>
       <c r="AC36">
-        <v>3.64</v>
+        <v>2.46</v>
       </c>
       <c r="AD36">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="AE36">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AF36">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="Q37">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="R37">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="U37">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="V37">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>3.28</v>
       </c>
       <c r="AA37">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AB37">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC37">
-        <v>2.46</v>
+        <v>3.34</v>
       </c>
       <c r="AD37">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF37">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P38">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q38">
-        <v>2.39</v>
+        <v>3.64</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="S38">
+        <v>1.41</v>
+      </c>
+      <c r="T38">
+        <v>2.8</v>
+      </c>
+      <c r="U38">
+        <v>3.07</v>
+      </c>
+      <c r="V38">
         <v>1.35</v>
       </c>
-      <c r="T38">
-        <v>2.82</v>
-      </c>
-      <c r="U38">
-        <v>2.78</v>
-      </c>
-      <c r="V38">
-        <v>1.36</v>
-      </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z38">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="AA38">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB38">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC38">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="AD38">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
         <v>1.04</v>
       </c>
       <c r="AF38">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG38">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AK38">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7502,10 +7502,10 @@
         <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
         <v>1.08</v>
@@ -7517,16 +7517,16 @@
         <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA44">
         <v>1.76</v>
       </c>
       <c r="AB44">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC44">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AD44">
         <v>1.42</v>
@@ -7816,19 +7816,19 @@
         <v>1.85</v>
       </c>
       <c r="Q46">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R46">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="S46">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="U46">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V46">
         <v>1.67</v>
@@ -7843,22 +7843,22 @@
         <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AA46">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AB46">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC46">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AD46">
         <v>1.73</v>
       </c>
       <c r="AE46">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF46">
         <v>1.39</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF48">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-08-01 11:00:00</t>
+          <t>2026-08-01 11:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,27 +8249,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-08-01 11:30:00</t>
+          <t>2026-08-01 12:00:00</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="O50">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>4.17</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="V50">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z50">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="AB50">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC50">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD50">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK50">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AA51">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AB51">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AC51">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK51">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G52">
@@ -8794,55 +8794,55 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB52">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB53">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="O54">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="P54">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="Q54">
-        <v>2.89</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="U54">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V54">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W54">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA54">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB54">
-        <v>2.14</v>
+        <v>2.49</v>
       </c>
       <c r="AC54">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="AD54">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AE54">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF54">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG54">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK54">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.57</v>
+        <v>3.35</v>
       </c>
       <c r="O55">
-        <v>4.08</v>
+        <v>3.6</v>
       </c>
       <c r="P55">
-        <v>4.54</v>
+        <v>1.84</v>
       </c>
       <c r="Q55">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="R55">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
+        <v>1.3</v>
+      </c>
+      <c r="T55">
+        <v>3.25</v>
+      </c>
+      <c r="U55">
+        <v>2.45</v>
+      </c>
+      <c r="V55">
+        <v>1.48</v>
+      </c>
+      <c r="W55">
+        <v>1.11</v>
+      </c>
+      <c r="X55">
+        <v>1.04</v>
+      </c>
+      <c r="Y55">
         <v>1.22</v>
       </c>
-      <c r="T55">
-        <v>3.6</v>
-      </c>
-      <c r="U55">
-        <v>2.1</v>
-      </c>
-      <c r="V55">
-        <v>1.64</v>
-      </c>
-      <c r="W55">
-        <v>1.14</v>
-      </c>
-      <c r="X55">
-        <v>1.02</v>
-      </c>
-      <c r="Y55">
-        <v>1.1</v>
-      </c>
       <c r="Z55">
-        <v>5.88</v>
+        <v>3.95</v>
       </c>
       <c r="AA55">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AB55">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="AC55">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="AD55">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AE55">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF55">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>2.37</v>
+        <v>2.14</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AK55">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="O56">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P56">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="Q56">
-        <v>4.2</v>
+        <v>3.64</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S56">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="V56">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z56">
-        <v>3.95</v>
+        <v>5.55</v>
       </c>
       <c r="AA56">
+        <v>1.42</v>
+      </c>
+      <c r="AB56">
+        <v>2.62</v>
+      </c>
+      <c r="AC56">
+        <v>2.02</v>
+      </c>
+      <c r="AD56">
         <v>1.75</v>
       </c>
-      <c r="AB56">
-        <v>2.05</v>
-      </c>
-      <c r="AC56">
-        <v>2.84</v>
-      </c>
-      <c r="AD56">
-        <v>1.41</v>
-      </c>
       <c r="AE56">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF56">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AG56">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="O57">
-        <v>3.55</v>
+        <v>3.03</v>
       </c>
       <c r="P57">
-        <v>1.95</v>
+        <v>3.03</v>
       </c>
       <c r="Q57">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="S57">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="U57">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="V57">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="W57">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="Z57">
-        <v>5.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA57">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="AB57">
-        <v>2.82</v>
+        <v>1.65</v>
       </c>
       <c r="AC57">
-        <v>2.02</v>
+        <v>3.8</v>
       </c>
       <c r="AD57">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AG57">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK57">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V58">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA58">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC58">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK58">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-01 12:00:00</t>
+          <t>2026-08-01 12:30:00</t>
         </is>
       </c>
     </row>
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>12.84</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,68 +10085,68 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60">
+        <v>1.83</v>
+      </c>
+      <c r="O60">
+        <v>3</v>
+      </c>
+      <c r="P60">
+        <v>4.33</v>
+      </c>
+      <c r="Q60">
+        <v>2.55</v>
+      </c>
+      <c r="R60">
+        <v>1.88</v>
+      </c>
+      <c r="S60">
+        <v>1.55</v>
+      </c>
+      <c r="T60">
+        <v>2.28</v>
+      </c>
+      <c r="U60">
+        <v>3.5</v>
+      </c>
+      <c r="V60">
+        <v>1.23</v>
+      </c>
+      <c r="W60">
+        <v>1.01</v>
+      </c>
+      <c r="X60">
+        <v>1.11</v>
+      </c>
+      <c r="Y60">
+        <v>1.5</v>
+      </c>
+      <c r="Z60">
+        <v>2.41</v>
+      </c>
+      <c r="AA60">
+        <v>2.6</v>
+      </c>
+      <c r="AB60">
+        <v>1.48</v>
+      </c>
+      <c r="AC60">
+        <v>5.25</v>
+      </c>
+      <c r="AD60">
         <v>1.15</v>
       </c>
-      <c r="O60">
-        <v>6.22</v>
-      </c>
-      <c r="P60">
-        <v>12.84</v>
-      </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
-      </c>
-      <c r="V60">
-        <v>0</v>
-      </c>
-      <c r="W60">
-        <v>0</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
-      </c>
-      <c r="Y60">
-        <v>0</v>
-      </c>
-      <c r="Z60">
-        <v>0</v>
-      </c>
-      <c r="AA60">
-        <v>0</v>
-      </c>
-      <c r="AB60">
-        <v>0</v>
-      </c>
-      <c r="AC60">
-        <v>0</v>
-      </c>
-      <c r="AD60">
-        <v>0</v>
-      </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,65 +10252,65 @@
         </is>
       </c>
       <c r="N61">
+        <v>3.75</v>
+      </c>
+      <c r="O61">
+        <v>3.8</v>
+      </c>
+      <c r="P61">
         <v>1.83</v>
       </c>
-      <c r="O61">
-        <v>3</v>
-      </c>
-      <c r="P61">
+      <c r="Q61">
+        <v>4.11</v>
+      </c>
+      <c r="R61">
+        <v>2.27</v>
+      </c>
+      <c r="S61">
+        <v>1.29</v>
+      </c>
+      <c r="T61">
+        <v>3.6</v>
+      </c>
+      <c r="U61">
+        <v>2.42</v>
+      </c>
+      <c r="V61">
+        <v>1.53</v>
+      </c>
+      <c r="W61">
+        <v>1.1</v>
+      </c>
+      <c r="X61">
+        <v>1.03</v>
+      </c>
+      <c r="Y61">
+        <v>1.2</v>
+      </c>
+      <c r="Z61">
         <v>4.33</v>
       </c>
-      <c r="Q61">
-        <v>2.55</v>
-      </c>
-      <c r="R61">
-        <v>1.88</v>
-      </c>
-      <c r="S61">
+      <c r="AA61">
+        <v>1.59</v>
+      </c>
+      <c r="AB61">
+        <v>2.17</v>
+      </c>
+      <c r="AC61">
+        <v>2.43</v>
+      </c>
+      <c r="AD61">
+        <v>1.44</v>
+      </c>
+      <c r="AE61">
+        <v>1.15</v>
+      </c>
+      <c r="AF61">
         <v>1.55</v>
       </c>
-      <c r="T61">
+      <c r="AG61">
         <v>2.28</v>
       </c>
-      <c r="U61">
-        <v>3.5</v>
-      </c>
-      <c r="V61">
-        <v>1.23</v>
-      </c>
-      <c r="W61">
-        <v>1.01</v>
-      </c>
-      <c r="X61">
-        <v>1.11</v>
-      </c>
-      <c r="Y61">
-        <v>1.5</v>
-      </c>
-      <c r="Z61">
-        <v>2.41</v>
-      </c>
-      <c r="AA61">
-        <v>2.6</v>
-      </c>
-      <c r="AB61">
-        <v>1.48</v>
-      </c>
-      <c r="AC61">
-        <v>5.25</v>
-      </c>
-      <c r="AD61">
-        <v>1.15</v>
-      </c>
-      <c r="AE61">
-        <v>1.04</v>
-      </c>
-      <c r="AF61">
-        <v>2.2</v>
-      </c>
-      <c r="AG61">
-        <v>1.57</v>
-      </c>
       <c r="AH61" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="O62">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
+        <v>2.09</v>
+      </c>
+      <c r="Q62">
+        <v>4.2</v>
+      </c>
+      <c r="R62">
+        <v>2.17</v>
+      </c>
+      <c r="S62">
+        <v>1.45</v>
+      </c>
+      <c r="T62">
+        <v>2.66</v>
+      </c>
+      <c r="U62">
+        <v>3.09</v>
+      </c>
+      <c r="V62">
+        <v>1.35</v>
+      </c>
+      <c r="W62">
+        <v>1.04</v>
+      </c>
+      <c r="X62">
+        <v>1.02</v>
+      </c>
+      <c r="Y62">
+        <v>1.33</v>
+      </c>
+      <c r="Z62">
+        <v>3.05</v>
+      </c>
+      <c r="AA62">
+        <v>2.1</v>
+      </c>
+      <c r="AB62">
+        <v>1.74</v>
+      </c>
+      <c r="AC62">
+        <v>3.65</v>
+      </c>
+      <c r="AD62">
+        <v>1.24</v>
+      </c>
+      <c r="AE62">
+        <v>1.04</v>
+      </c>
+      <c r="AF62">
         <v>1.83</v>
       </c>
-      <c r="Q62">
-        <v>4.11</v>
-      </c>
-      <c r="R62">
-        <v>2.27</v>
-      </c>
-      <c r="S62">
-        <v>1.29</v>
-      </c>
-      <c r="T62">
-        <v>3.6</v>
-      </c>
-      <c r="U62">
-        <v>2.42</v>
-      </c>
-      <c r="V62">
-        <v>1.53</v>
-      </c>
-      <c r="W62">
-        <v>1.1</v>
-      </c>
-      <c r="X62">
-        <v>1.03</v>
-      </c>
-      <c r="Y62">
-        <v>1.2</v>
-      </c>
-      <c r="Z62">
-        <v>4.33</v>
-      </c>
-      <c r="AA62">
-        <v>1.59</v>
-      </c>
-      <c r="AB62">
-        <v>2.17</v>
-      </c>
-      <c r="AC62">
-        <v>2.43</v>
-      </c>
-      <c r="AD62">
-        <v>1.44</v>
-      </c>
-      <c r="AE62">
-        <v>1.15</v>
-      </c>
-      <c r="AF62">
-        <v>1.55</v>
-      </c>
       <c r="AG62">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="AK62">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.48</v>
+        <v>2.57</v>
       </c>
       <c r="O63">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="P63">
-        <v>2.09</v>
+        <v>2.69</v>
       </c>
       <c r="Q63">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>2.47</v>
+        <v>1.94</v>
       </c>
       <c r="Q66">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="R66">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="S66">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="U66">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="V66">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z66">
-        <v>3.42</v>
+        <v>4.7</v>
       </c>
       <c r="AA66">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AC66">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="AD66">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="AE66">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF66">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AG66">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,11 +11137,11 @@
         </is>
       </c>
       <c r="AJ66">
+        <v>1.73</v>
+      </c>
+      <c r="AK66">
         <v>1.29</v>
       </c>
-      <c r="AK66">
-        <v>1.41</v>
-      </c>
       <c r="AL66">
         <v>0</v>
       </c>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-08-01 12:30:00</t>
+          <t>2026-08-01 13:00:00</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="P67">
-        <v>1.94</v>
+        <v>3.26</v>
       </c>
       <c r="Q67">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="R67">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S67">
         <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U67">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V67">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W67">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z67">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AB67">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AC67">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD67">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE67">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF67">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG67">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.02</v>
+        <v>2.37</v>
       </c>
       <c r="O68">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
-        <v>3.26</v>
+        <v>2.62</v>
       </c>
       <c r="Q68">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="R68">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="S68">
+        <v>1.35</v>
+      </c>
+      <c r="T68">
+        <v>3.07</v>
+      </c>
+      <c r="U68">
+        <v>2.75</v>
+      </c>
+      <c r="V68">
+        <v>1.4</v>
+      </c>
+      <c r="W68">
+        <v>1.07</v>
+      </c>
+      <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
+        <v>1.23</v>
+      </c>
+      <c r="Z68">
+        <v>3.42</v>
+      </c>
+      <c r="AA68">
+        <v>1.85</v>
+      </c>
+      <c r="AB68">
+        <v>1.85</v>
+      </c>
+      <c r="AC68">
+        <v>3.12</v>
+      </c>
+      <c r="AD68">
+        <v>1.33</v>
+      </c>
+      <c r="AE68">
+        <v>1.06</v>
+      </c>
+      <c r="AF68">
+        <v>1.66</v>
+      </c>
+      <c r="AG68">
+        <v>2.07</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.25</v>
       </c>
-      <c r="T68">
-        <v>3.55</v>
-      </c>
-      <c r="U68">
-        <v>2.15</v>
-      </c>
-      <c r="V68">
-        <v>1.62</v>
-      </c>
-      <c r="W68">
-        <v>1.14</v>
-      </c>
-      <c r="X68">
-        <v>1.02</v>
-      </c>
-      <c r="Y68">
-        <v>1.15</v>
-      </c>
-      <c r="Z68">
-        <v>5.25</v>
-      </c>
-      <c r="AA68">
-        <v>1.49</v>
-      </c>
-      <c r="AB68">
-        <v>2.38</v>
-      </c>
-      <c r="AC68">
-        <v>2.25</v>
-      </c>
-      <c r="AD68">
-        <v>1.59</v>
-      </c>
-      <c r="AE68">
-        <v>1.22</v>
-      </c>
-      <c r="AF68">
-        <v>1.44</v>
-      </c>
-      <c r="AG68">
-        <v>2.55</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.33</v>
-      </c>
       <c r="AK68">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="O69">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="P69">
-        <v>2.62</v>
+        <v>1.49</v>
       </c>
       <c r="Q69">
-        <v>2.96</v>
+        <v>4.8</v>
       </c>
       <c r="R69">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="S69">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T69">
-        <v>3.07</v>
+        <v>3.58</v>
       </c>
       <c r="U69">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z69">
-        <v>3.42</v>
+        <v>4.95</v>
       </c>
       <c r="AA69">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB69">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC69">
-        <v>3.12</v>
+        <v>2.14</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AE69">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AF69">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.25</v>
+        <v>2.55</v>
       </c>
       <c r="AK69">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>5.85</v>
+        <v>1.91</v>
       </c>
       <c r="O70">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P70">
-        <v>1.49</v>
+        <v>3.15</v>
       </c>
       <c r="Q70">
-        <v>4.8</v>
+        <v>2.36</v>
       </c>
       <c r="R70">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S70">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="T70">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U70">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="V70">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z70">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="AA70">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AB70">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="AC70">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="AD70">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AE70">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF70">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AG70">
-        <v>2.21</v>
+        <v>2.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>2.56</v>
+        <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,80 +11882,80 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="O71">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P71">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q71">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="R71">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="S71">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="T71">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="U71">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="V71">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="W71">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z71">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA71">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AB71">
-        <v>2.89</v>
+        <v>2.1</v>
       </c>
       <c r="AC71">
-        <v>1.98</v>
+        <v>2.51</v>
       </c>
       <c r="AD71">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="AE71">
+        <v>1.14</v>
+      </c>
+      <c r="AF71">
+        <v>1.54</v>
+      </c>
+      <c r="AG71">
+        <v>2.3</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.85</v>
+      </c>
+      <c r="AK71">
         <v>1.3</v>
-      </c>
-      <c r="AF71">
-        <v>1.36</v>
-      </c>
-      <c r="AG71">
-        <v>2.85</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.18</v>
-      </c>
-      <c r="AK71">
-        <v>1.74</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="O72">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="Q72">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="R72">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="S72">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T72">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="U72">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="V72">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W72">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA72">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AB72">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC72">
-        <v>2.51</v>
+        <v>3.2</v>
       </c>
       <c r="AD72">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF72">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AG72">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AK72">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="O73">
+        <v>3.17</v>
+      </c>
+      <c r="P73">
+        <v>2.75</v>
+      </c>
+      <c r="Q73">
+        <v>2.77</v>
+      </c>
+      <c r="R73">
+        <v>2.2</v>
+      </c>
+      <c r="S73">
+        <v>1.3</v>
+      </c>
+      <c r="T73">
         <v>3.2</v>
       </c>
-      <c r="P73">
-        <v>2.37</v>
-      </c>
-      <c r="Q73">
-        <v>3.18</v>
-      </c>
-      <c r="R73">
-        <v>2.06</v>
-      </c>
-      <c r="S73">
-        <v>1.35</v>
-      </c>
-      <c r="T73">
-        <v>2.79</v>
-      </c>
       <c r="U73">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V73">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z73">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="AA73">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AB73">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AC73">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="AD73">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE73">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF73">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG73">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AK73">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.16</v>
+        <v>1.22</v>
       </c>
       <c r="O74">
-        <v>3.17</v>
+        <v>5.75</v>
       </c>
       <c r="P74">
-        <v>2.75</v>
+        <v>10</v>
       </c>
       <c r="Q74">
-        <v>2.77</v>
+        <v>1.65</v>
       </c>
       <c r="R74">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="S74">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T74">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="U74">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V74">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W74">
         <v>1.08</v>
@@ -12404,31 +12404,31 @@
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z74">
-        <v>3.72</v>
+        <v>4.06</v>
       </c>
       <c r="AA74">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB74">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AC74">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD74">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE74">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF74">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AG74">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AK74">
-        <v>1.53</v>
+        <v>4.15</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12487,27 +12487,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,31 +12534,31 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="O75">
-        <v>5.75</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="Q75">
-        <v>1.65</v>
+        <v>2.95</v>
       </c>
       <c r="R75">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="U75">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V75">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W75">
         <v>1.08</v>
@@ -12567,31 +12567,31 @@
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z75">
-        <v>4.06</v>
+        <v>3.3</v>
       </c>
       <c r="AA75">
+        <v>1.95</v>
+      </c>
+      <c r="AB75">
+        <v>1.85</v>
+      </c>
+      <c r="AC75">
+        <v>3.14</v>
+      </c>
+      <c r="AD75">
+        <v>1.27</v>
+      </c>
+      <c r="AE75">
+        <v>1.09</v>
+      </c>
+      <c r="AF75">
         <v>1.7</v>
       </c>
-      <c r="AB75">
-        <v>2.11</v>
-      </c>
-      <c r="AC75">
-        <v>2.7</v>
-      </c>
-      <c r="AD75">
-        <v>1.4</v>
-      </c>
-      <c r="AE75">
-        <v>1.12</v>
-      </c>
-      <c r="AF75">
-        <v>2.4</v>
-      </c>
       <c r="AG75">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>4.15</v>
+        <v>1.45</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-08-01 13:00:00</t>
+          <t>2026-08-01 13:30:00</t>
         </is>
       </c>
     </row>
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O76">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P76">
+        <v>4.05</v>
+      </c>
+      <c r="Q76">
+        <v>2.64</v>
+      </c>
+      <c r="R76">
+        <v>1.95</v>
+      </c>
+      <c r="S76">
+        <v>1.5</v>
+      </c>
+      <c r="T76">
+        <v>2.39</v>
+      </c>
+      <c r="U76">
+        <v>3.22</v>
+      </c>
+      <c r="V76">
+        <v>1.29</v>
+      </c>
+      <c r="W76">
+        <v>1.01</v>
+      </c>
+      <c r="X76">
+        <v>1.04</v>
+      </c>
+      <c r="Y76">
+        <v>1.36</v>
+      </c>
+      <c r="Z76">
         <v>2.7</v>
       </c>
-      <c r="Q76">
-        <v>2.95</v>
-      </c>
-      <c r="R76">
-        <v>2.1</v>
-      </c>
-      <c r="S76">
-        <v>1.36</v>
-      </c>
-      <c r="T76">
-        <v>2.69</v>
-      </c>
-      <c r="U76">
-        <v>2.84</v>
-      </c>
-      <c r="V76">
-        <v>1.36</v>
-      </c>
-      <c r="W76">
-        <v>1.07</v>
-      </c>
-      <c r="X76">
+      <c r="AA76">
+        <v>2.26</v>
+      </c>
+      <c r="AB76">
+        <v>1.62</v>
+      </c>
+      <c r="AC76">
+        <v>4.13</v>
+      </c>
+      <c r="AD76">
+        <v>1.18</v>
+      </c>
+      <c r="AE76">
         <v>1.02</v>
       </c>
-      <c r="Y76">
-        <v>1.28</v>
-      </c>
-      <c r="Z76">
-        <v>3.2</v>
-      </c>
-      <c r="AA76">
-        <v>1.95</v>
-      </c>
-      <c r="AB76">
-        <v>1.87</v>
-      </c>
-      <c r="AC76">
-        <v>3.27</v>
-      </c>
-      <c r="AD76">
-        <v>1.29</v>
-      </c>
-      <c r="AE76">
-        <v>1.09</v>
-      </c>
       <c r="AF76">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AG76">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="O77">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="P77">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="Q77">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="R77">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="S77">
+        <v>1.29</v>
+      </c>
+      <c r="T77">
+        <v>3.22</v>
+      </c>
+      <c r="U77">
+        <v>2.54</v>
+      </c>
+      <c r="V77">
         <v>1.5</v>
       </c>
-      <c r="T77">
-        <v>2.39</v>
-      </c>
-      <c r="U77">
-        <v>3.22</v>
-      </c>
-      <c r="V77">
-        <v>1.29</v>
-      </c>
       <c r="W77">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="Z77">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA77">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="AB77">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AC77">
-        <v>4.13</v>
+        <v>2.62</v>
       </c>
       <c r="AD77">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AE77">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF77">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="AG77">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK77">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="O78">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P78">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="R78">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T78">
-        <v>3.22</v>
+        <v>2.75</v>
       </c>
       <c r="U78">
-        <v>2.54</v>
+        <v>2.77</v>
       </c>
       <c r="V78">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
         <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA78">
+        <v>1.9</v>
+      </c>
+      <c r="AB78">
+        <v>1.85</v>
+      </c>
+      <c r="AC78">
+        <v>2.83</v>
+      </c>
+      <c r="AD78">
+        <v>1.33</v>
+      </c>
+      <c r="AE78">
+        <v>1.07</v>
+      </c>
+      <c r="AF78">
         <v>1.7</v>
       </c>
-      <c r="AB78">
-        <v>2.12</v>
-      </c>
-      <c r="AC78">
-        <v>2.62</v>
-      </c>
-      <c r="AD78">
-        <v>1.38</v>
-      </c>
-      <c r="AE78">
-        <v>1.15</v>
-      </c>
-      <c r="AF78">
-        <v>1.63</v>
-      </c>
       <c r="AG78">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
+        <v>3</v>
+      </c>
+      <c r="O79">
+        <v>3.52</v>
+      </c>
+      <c r="P79">
+        <v>2.19</v>
+      </c>
+      <c r="Q79">
+        <v>3.6</v>
+      </c>
+      <c r="R79">
+        <v>2.25</v>
+      </c>
+      <c r="S79">
+        <v>1.3</v>
+      </c>
+      <c r="T79">
+        <v>3.3</v>
+      </c>
+      <c r="U79">
+        <v>2.59</v>
+      </c>
+      <c r="V79">
+        <v>1.46</v>
+      </c>
+      <c r="W79">
+        <v>1.08</v>
+      </c>
+      <c r="X79">
+        <v>1.04</v>
+      </c>
+      <c r="Y79">
+        <v>1.19</v>
+      </c>
+      <c r="Z79">
+        <v>4.1</v>
+      </c>
+      <c r="AA79">
+        <v>1.74</v>
+      </c>
+      <c r="AB79">
         <v>2.05</v>
       </c>
-      <c r="O79">
-        <v>3.3</v>
-      </c>
-      <c r="P79">
-        <v>3.1</v>
-      </c>
-      <c r="Q79">
-        <v>2.7</v>
-      </c>
-      <c r="R79">
-        <v>2.2</v>
-      </c>
-      <c r="S79">
-        <v>1.36</v>
-      </c>
-      <c r="T79">
-        <v>2.75</v>
-      </c>
-      <c r="U79">
-        <v>2.77</v>
-      </c>
-      <c r="V79">
-        <v>1.44</v>
-      </c>
-      <c r="W79">
-        <v>1.07</v>
-      </c>
-      <c r="X79">
-        <v>1.03</v>
-      </c>
-      <c r="Y79">
-        <v>1.25</v>
-      </c>
-      <c r="Z79">
-        <v>3.5</v>
-      </c>
-      <c r="AA79">
-        <v>1.9</v>
-      </c>
-      <c r="AB79">
-        <v>1.85</v>
-      </c>
       <c r="AC79">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD79">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE79">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF79">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG79">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-01 13:30:00</t>
+          <t>2026-08-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="O83">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="P83">
-        <v>3.58</v>
+        <v>4.17</v>
       </c>
       <c r="Q83">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T83">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="U83">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="V83">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="W83">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z83">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA83">
-        <v>2.21</v>
+        <v>1.76</v>
       </c>
       <c r="AB83">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AC83">
-        <v>4.05</v>
+        <v>2.81</v>
       </c>
       <c r="AD83">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AE83">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF83">
+        <v>1.7</v>
+      </c>
+      <c r="AG83">
+        <v>1.99</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.21</v>
+      </c>
+      <c r="AK83">
         <v>1.93</v>
-      </c>
-      <c r="AG83">
-        <v>1.72</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.26</v>
-      </c>
-      <c r="AK83">
-        <v>1.67</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="O84">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="P84">
-        <v>4.17</v>
+        <v>6.35</v>
       </c>
       <c r="Q84">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="R84">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S84">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T84">
         <v>3.3</v>
       </c>
       <c r="U84">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V84">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W84">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z84">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA84">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB84">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC84">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AD84">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE84">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF84">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG84">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK84">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>1.83</v>
+        <v>2.58</v>
       </c>
       <c r="R85">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T85">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U85">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V85">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z85">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA85">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AB85">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC85">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD85">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE85">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG85">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK85">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G86">
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="R86">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S86">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T86">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="U86">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="V86">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W86">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z86">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AA86">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB86">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AC86">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD86">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AE86">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF86">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG86">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK86">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q87">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="R87">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="S87">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="U87">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="V87">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="Z87">
-        <v>2.66</v>
+        <v>3.94</v>
       </c>
       <c r="AA87">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AB87">
-        <v>1.56</v>
+        <v>2.03</v>
       </c>
       <c r="AC87">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="AD87">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AE87">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF87">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AG87">
-        <v>1.77</v>
+        <v>2.19</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-01 14:00:00</t>
+          <t>2026-08-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.45</v>
+        <v>1.29</v>
       </c>
       <c r="O88">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P88">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q88">
-        <v>3.15</v>
+        <v>1.71</v>
       </c>
       <c r="R88">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="V88">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W88">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z88">
-        <v>3.94</v>
+        <v>5.25</v>
       </c>
       <c r="AA88">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB88">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="AC88">
-        <v>2.74</v>
+        <v>2.27</v>
       </c>
       <c r="AD88">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="AE88">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF88">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AG88">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AK88">
-        <v>1.43</v>
+        <v>3.42</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.29</v>
+        <v>2.9</v>
       </c>
       <c r="O89">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="P89">
-        <v>7.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q89">
-        <v>1.71</v>
+        <v>3.68</v>
       </c>
       <c r="R89">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U89">
-        <v>2.15</v>
+        <v>3.09</v>
       </c>
       <c r="V89">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="W89">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z89">
-        <v>5.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA89">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB89">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC89">
-        <v>2.27</v>
+        <v>3.58</v>
       </c>
       <c r="AD89">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AE89">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF89">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG89">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="AK89">
-        <v>3.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-01 14:30:00</t>
+          <t>2026-08-01 14:45:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,31 +14979,31 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O90">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="Q90">
-        <v>3.68</v>
+        <v>5.25</v>
       </c>
       <c r="R90">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T90">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U90">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="V90">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W90">
         <v>1.05</v>
@@ -15012,47 +15012,47 @@
         <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z90">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="AA90">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AB90">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AC90">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AD90">
+        <v>1.16</v>
+      </c>
+      <c r="AE90">
+        <v>1.06</v>
+      </c>
+      <c r="AF90">
+        <v>2.05</v>
+      </c>
+      <c r="AG90">
+        <v>1.68</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
         <v>1.25</v>
       </c>
-      <c r="AE90">
-        <v>1.05</v>
-      </c>
-      <c r="AF90">
-        <v>1.81</v>
-      </c>
-      <c r="AG90">
-        <v>1.89</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.37</v>
-      </c>
       <c r="AK90">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45:00</t>
+          <t>2026-08-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>4.2</v>
+        <v>1.91</v>
       </c>
       <c r="O91">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P91">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q91">
-        <v>5.25</v>
+        <v>2.55</v>
       </c>
       <c r="R91">
         <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T91">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U91">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="V91">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W91">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y91">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z91">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA91">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AB91">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="AC91">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD91">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF91">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AG91">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK91">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="P92">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="Q92">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="R92">
+        <v>1.69</v>
+      </c>
+      <c r="S92">
+        <v>1.74</v>
+      </c>
+      <c r="T92">
         <v>2.1</v>
       </c>
-      <c r="S92">
-        <v>1.38</v>
-      </c>
-      <c r="T92">
-        <v>3</v>
-      </c>
       <c r="U92">
-        <v>2.65</v>
+        <v>4.33</v>
       </c>
       <c r="V92">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="W92">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X92">
+        <v>1.13</v>
+      </c>
+      <c r="Y92">
+        <v>1.75</v>
+      </c>
+      <c r="Z92">
+        <v>2.04</v>
+      </c>
+      <c r="AA92">
+        <v>3.08</v>
+      </c>
+      <c r="AB92">
+        <v>1.28</v>
+      </c>
+      <c r="AC92">
+        <v>5.8</v>
+      </c>
+      <c r="AD92">
         <v>1.06</v>
       </c>
-      <c r="Y92">
-        <v>1.22</v>
-      </c>
-      <c r="Z92">
-        <v>3.5</v>
-      </c>
-      <c r="AA92">
-        <v>1.83</v>
-      </c>
-      <c r="AB92">
-        <v>1.83</v>
-      </c>
-      <c r="AC92">
-        <v>3.3</v>
-      </c>
-      <c r="AD92">
-        <v>1.29</v>
-      </c>
       <c r="AE92">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF92">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="AG92">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK92">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="O93">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="P93">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q93">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="R93">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="S93">
+        <v>1.62</v>
+      </c>
+      <c r="T93">
+        <v>2.25</v>
+      </c>
+      <c r="U93">
+        <v>3.78</v>
+      </c>
+      <c r="V93">
+        <v>1.22</v>
+      </c>
+      <c r="W93">
+        <v>1.03</v>
+      </c>
+      <c r="X93">
+        <v>1.09</v>
+      </c>
+      <c r="Y93">
+        <v>1.58</v>
+      </c>
+      <c r="Z93">
+        <v>2.28</v>
+      </c>
+      <c r="AA93">
+        <v>2.69</v>
+      </c>
+      <c r="AB93">
+        <v>1.38</v>
+      </c>
+      <c r="AC93">
+        <v>5.25</v>
+      </c>
+      <c r="AD93">
+        <v>1.12</v>
+      </c>
+      <c r="AE93">
+        <v>1.03</v>
+      </c>
+      <c r="AF93">
+        <v>2.34</v>
+      </c>
+      <c r="AG93">
+        <v>1.62</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
+        <v>1.32</v>
+      </c>
+      <c r="AK93">
         <v>1.74</v>
-      </c>
-      <c r="T93">
-        <v>2.1</v>
-      </c>
-      <c r="U93">
-        <v>4.15</v>
-      </c>
-      <c r="V93">
-        <v>1.16</v>
-      </c>
-      <c r="W93">
-        <v>1.02</v>
-      </c>
-      <c r="X93">
-        <v>1.17</v>
-      </c>
-      <c r="Y93">
-        <v>1.75</v>
-      </c>
-      <c r="Z93">
-        <v>2.04</v>
-      </c>
-      <c r="AA93">
-        <v>3.04</v>
-      </c>
-      <c r="AB93">
-        <v>1.29</v>
-      </c>
-      <c r="AC93">
-        <v>5.8</v>
-      </c>
-      <c r="AD93">
-        <v>1.06</v>
-      </c>
-      <c r="AE93">
-        <v>1.02</v>
-      </c>
-      <c r="AF93">
-        <v>2.4</v>
-      </c>
-      <c r="AG93">
-        <v>1.53</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.37</v>
-      </c>
-      <c r="AK93">
-        <v>1.44</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="O94">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P94">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q94">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R94">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="S94">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="T94">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="U94">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="V94">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W94">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y94">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="Z94">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="AA94">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AB94">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AC94">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="AD94">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE94">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF94">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AG94">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK94">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O95">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="P95">
         <v>2.9</v>
       </c>
       <c r="Q95">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R95">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S95">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="T95">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="U95">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="V95">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W95">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X95">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y95">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="Z95">
-        <v>2.39</v>
+        <v>1.98</v>
       </c>
       <c r="AA95">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AB95">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AC95">
-        <v>5.45</v>
+        <v>6.5</v>
       </c>
       <c r="AD95">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE95">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF95">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AG95">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK95">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.8</v>
+        <v>4.01</v>
       </c>
       <c r="O96">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="P96">
-        <v>2.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q96">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R96">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="S96">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="T96">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="U96">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="V96">
+        <v>1.22</v>
+      </c>
+      <c r="W96">
+        <v>1.04</v>
+      </c>
+      <c r="X96">
+        <v>1.09</v>
+      </c>
+      <c r="Y96">
+        <v>1.52</v>
+      </c>
+      <c r="Z96">
+        <v>2.43</v>
+      </c>
+      <c r="AA96">
+        <v>2.52</v>
+      </c>
+      <c r="AB96">
+        <v>1.41</v>
+      </c>
+      <c r="AC96">
+        <v>4.8</v>
+      </c>
+      <c r="AD96">
+        <v>1.14</v>
+      </c>
+      <c r="AE96">
+        <v>1.04</v>
+      </c>
+      <c r="AF96">
+        <v>2.17</v>
+      </c>
+      <c r="AG96">
+        <v>1.6</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.33</v>
+      </c>
+      <c r="AK96">
         <v>1.17</v>
-      </c>
-      <c r="W96">
-        <v>1.02</v>
-      </c>
-      <c r="X96">
-        <v>1.13</v>
-      </c>
-      <c r="Y96">
-        <v>1.62</v>
-      </c>
-      <c r="Z96">
-        <v>1.99</v>
-      </c>
-      <c r="AA96">
-        <v>3.14</v>
-      </c>
-      <c r="AB96">
-        <v>1.34</v>
-      </c>
-      <c r="AC96">
-        <v>6.45</v>
-      </c>
-      <c r="AD96">
-        <v>1.1</v>
-      </c>
-      <c r="AE96">
-        <v>1.02</v>
-      </c>
-      <c r="AF96">
-        <v>2.45</v>
-      </c>
-      <c r="AG96">
-        <v>1.48</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.4</v>
-      </c>
-      <c r="AK96">
-        <v>1.36</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O97">
         <v>2.7</v>
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.01</v>
+        <v>1.42</v>
       </c>
       <c r="O98">
-        <v>2.94</v>
+        <v>4.8</v>
       </c>
       <c r="P98">
-        <v>1.96</v>
+        <v>6.5</v>
       </c>
       <c r="Q98">
-        <v>4.5</v>
+        <v>1.86</v>
       </c>
       <c r="R98">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="S98">
+        <v>1.24</v>
+      </c>
+      <c r="T98">
+        <v>3.7</v>
+      </c>
+      <c r="U98">
+        <v>2.14</v>
+      </c>
+      <c r="V98">
         <v>1.61</v>
       </c>
-      <c r="T98">
-        <v>2.45</v>
-      </c>
-      <c r="U98">
-        <v>3.6</v>
-      </c>
-      <c r="V98">
-        <v>1.25</v>
-      </c>
       <c r="W98">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="X98">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="Z98">
-        <v>2.43</v>
+        <v>5</v>
       </c>
       <c r="AA98">
-        <v>2.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB98">
-        <v>1.41</v>
+        <v>2.35</v>
       </c>
       <c r="AC98">
-        <v>4.8</v>
+        <v>2.16</v>
       </c>
       <c r="AD98">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
       <c r="AE98">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AF98">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AG98">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.73</v>
+        <v>1.07</v>
       </c>
       <c r="AK98">
-        <v>1.17</v>
+        <v>2.79</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q99">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="R99">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S99">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T99">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U99">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V99">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W99">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y99">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z99">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA99">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB99">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD99">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE99">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF99">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG99">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK99">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -18085,10 +18085,10 @@
         <v>4.66</v>
       </c>
       <c r="Q109">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R109">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S109">
         <v>1.53</v>
@@ -18124,16 +18124,16 @@
         <v>6.26</v>
       </c>
       <c r="AD109">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE109">
         <v>1.02</v>
       </c>
       <c r="AF109">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="AG109">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="O112">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P112">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -18607,16 +18607,16 @@
         <v>1.83</v>
       </c>
       <c r="AB112">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC112">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD112">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE112">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
         <v>1.7</v>
@@ -18891,19 +18891,19 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="O114">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P114">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q114">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R114">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S114">
         <v>1.4</v>
@@ -18921,31 +18921,31 @@
         <v>1.03</v>
       </c>
       <c r="X114">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y114">
         <v>1.38</v>
       </c>
       <c r="Z114">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="AA114">
         <v>2.19</v>
       </c>
       <c r="AB114">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC114">
         <v>3.85</v>
       </c>
       <c r="AD114">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE114">
         <v>1.07</v>
       </c>
       <c r="AF114">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG114">
         <v>1.82</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK114">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19706,19 +19706,19 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O119">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P119">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="Q119">
         <v>3.3</v>
       </c>
       <c r="R119">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S119">
         <v>1.4</v>
@@ -19727,34 +19727,34 @@
         <v>2.75</v>
       </c>
       <c r="U119">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V119">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W119">
         <v>1.07</v>
       </c>
       <c r="X119">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z119">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA119">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB119">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC119">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="AD119">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE119">
         <v>1.04</v>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AK119">
         <v>1.4</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O120">
         <v>4</v>
       </c>
       <c r="P120">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="Q120">
         <v>1.95</v>
@@ -19887,10 +19887,10 @@
         <v>1.33</v>
       </c>
       <c r="T120">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="U120">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="V120">
         <v>1.44</v>
@@ -19902,7 +19902,7 @@
         <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z120">
         <v>3.5</v>
@@ -19923,10 +19923,10 @@
         <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG120">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20071,10 +20071,10 @@
         <v>0</v>
       </c>
       <c r="AA121">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB121">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC121">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20367,7 +20367,7 @@
         <v>5.11</v>
       </c>
       <c r="Q123">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R123">
         <v>2.3</v>
@@ -20379,7 +20379,7 @@
         <v>3.12</v>
       </c>
       <c r="U123">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="V123">
         <v>1.45</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="O124">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="P124">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -20563,22 +20563,22 @@
         <v>1.9</v>
       </c>
       <c r="AB124">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC124">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD124">
         <v>1.31</v>
       </c>
       <c r="AE124">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF124">
         <v>1.75</v>
       </c>
       <c r="AG124">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK124">
         <v>1.21</v>
@@ -20684,16 +20684,16 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="O125">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="P125">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="Q125">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R125">
         <v>2.12</v>
@@ -20723,10 +20723,10 @@
         <v>3.8</v>
       </c>
       <c r="AA125">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB125">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC125">
         <v>2.6</v>
@@ -20850,7 +20850,7 @@
         <v>1.33</v>
       </c>
       <c r="O126">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="P126">
         <v>6.8</v>
@@ -21173,7 +21173,7 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O128">
         <v>4</v>
@@ -21185,13 +21185,13 @@
         <v>2.15</v>
       </c>
       <c r="R128">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S128">
         <v>1.29</v>
       </c>
       <c r="T128">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U128">
         <v>2.3</v>
@@ -21200,37 +21200,37 @@
         <v>1.55</v>
       </c>
       <c r="W128">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y128">
         <v>1.18</v>
       </c>
       <c r="Z128">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA128">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB128">
         <v>2.17</v>
       </c>
       <c r="AC128">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD128">
         <v>1.54</v>
       </c>
       <c r="AE128">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF128">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG128">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK128">
         <v>2.05</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O129">
         <v>3.3</v>
       </c>
       <c r="P129">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -21354,13 +21354,13 @@
         <v>1.36</v>
       </c>
       <c r="T129">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U129">
         <v>2.62</v>
       </c>
       <c r="V129">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W129">
         <v>1.08</v>
@@ -21372,16 +21372,16 @@
         <v>1.28</v>
       </c>
       <c r="Z129">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AA129">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB129">
         <v>1.95</v>
       </c>
       <c r="AC129">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD129">
         <v>1.35</v>
@@ -21393,7 +21393,7 @@
         <v>1.65</v>
       </c>
       <c r="AG129">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21502,16 +21502,16 @@
         <v>1.73</v>
       </c>
       <c r="O130">
-        <v>4.34</v>
+        <v>3.75</v>
       </c>
       <c r="P130">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="Q130">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R130">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S130">
         <v>1.24</v>
@@ -21520,7 +21520,7 @@
         <v>3.5</v>
       </c>
       <c r="U130">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="V130">
         <v>1.6</v>
@@ -21535,13 +21535,13 @@
         <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA130">
         <v>1.55</v>
       </c>
       <c r="AB130">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AC130">
         <v>2.25</v>
@@ -21556,7 +21556,7 @@
         <v>1.5</v>
       </c>
       <c r="AG130">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O131">
         <v>3.9</v>
@@ -21674,22 +21674,22 @@
         <v>2.37</v>
       </c>
       <c r="R131">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S131">
         <v>1.16</v>
       </c>
       <c r="T131">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U131">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V131">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W131">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X131">
         <v>0</v>
@@ -21707,19 +21707,19 @@
         <v>3.4</v>
       </c>
       <c r="AC131">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AD131">
         <v>2.01</v>
       </c>
       <c r="AE131">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AF131">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AG131">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,16 +21825,16 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O132">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P132">
-        <v>3.51</v>
+        <v>4.25</v>
       </c>
       <c r="Q132">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R132">
         <v>2.7</v>
@@ -21858,31 +21858,31 @@
         <v>0</v>
       </c>
       <c r="Y132">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z132">
-        <v>6.73</v>
+        <v>6.8</v>
       </c>
       <c r="AA132">
         <v>1.38</v>
       </c>
       <c r="AB132">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="AC132">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AD132">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AE132">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF132">
         <v>1.38</v>
       </c>
       <c r="AG132">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK132">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21994,7 +21994,7 @@
         <v>4.05</v>
       </c>
       <c r="P133">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="Q133">
         <v>2.38</v>
@@ -22009,7 +22009,7 @@
         <v>5.2</v>
       </c>
       <c r="U133">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V133">
         <v>1.88</v>
@@ -22030,7 +22030,7 @@
         <v>1.32</v>
       </c>
       <c r="AB133">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AC133">
         <v>1.8</v>
@@ -22042,10 +22042,10 @@
         <v>1.4</v>
       </c>
       <c r="AF133">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG133">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>2.88</v>
       </c>
       <c r="Q134">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R134">
         <v>2.22</v>
@@ -22172,10 +22172,10 @@
         <v>3.2</v>
       </c>
       <c r="U134">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V134">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W134">
         <v>1.11</v>
@@ -22205,10 +22205,10 @@
         <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG134">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>1.22</v>
       </c>
       <c r="AK134">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22326,19 +22326,19 @@
         <v>3.6</v>
       </c>
       <c r="R135">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S135">
         <v>1.33</v>
       </c>
       <c r="T135">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="U135">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V135">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W135">
         <v>1.1</v>
@@ -22347,25 +22347,25 @@
         <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z135">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA135">
         <v>1.9</v>
       </c>
       <c r="AB135">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC135">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AD135">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE135">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF135">
         <v>1.7</v>
@@ -22480,13 +22480,13 @@
         <v>2.05</v>
       </c>
       <c r="O136">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="Q136">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="R136">
         <v>2.28</v>
@@ -22513,7 +22513,7 @@
         <v>1.28</v>
       </c>
       <c r="Z136">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA136">
         <v>1.9</v>
@@ -22522,7 +22522,7 @@
         <v>1.92</v>
       </c>
       <c r="AC136">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD136">
         <v>1.35</v>
@@ -22640,28 +22640,28 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O137">
+        <v>3.1</v>
+      </c>
+      <c r="P137">
         <v>3</v>
       </c>
-      <c r="P137">
-        <v>3.1</v>
-      </c>
       <c r="Q137">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="R137">
         <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="T137">
         <v>2.33</v>
       </c>
       <c r="U137">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V137">
         <v>1.26</v>
@@ -22685,13 +22685,13 @@
         <v>1.63</v>
       </c>
       <c r="AC137">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AD137">
         <v>1.21</v>
       </c>
       <c r="AE137">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF137">
         <v>2</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK137">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22966,16 +22966,16 @@
         </is>
       </c>
       <c r="N139">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O139">
         <v>3.4</v>
       </c>
       <c r="P139">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q139">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R139">
         <v>2.3</v>
@@ -22996,7 +22996,7 @@
         <v>1.1</v>
       </c>
       <c r="X139">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y139">
         <v>1.14</v>
@@ -23011,7 +23011,7 @@
         <v>2.3</v>
       </c>
       <c r="AC139">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AD139">
         <v>1.55</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK139">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23138,13 +23138,13 @@
         <v>3.58</v>
       </c>
       <c r="Q140">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="R140">
         <v>2.55</v>
       </c>
       <c r="S140">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T140">
         <v>3.7</v>
@@ -23153,10 +23153,10 @@
         <v>2.16</v>
       </c>
       <c r="V140">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W140">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X140">
         <v>1.01</v>
@@ -23165,13 +23165,13 @@
         <v>1.13</v>
       </c>
       <c r="Z140">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA140">
         <v>1.5</v>
       </c>
       <c r="AB140">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="AC140">
         <v>2.18</v>
@@ -23186,7 +23186,7 @@
         <v>1.44</v>
       </c>
       <c r="AG140">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="O141">
-        <v>4.76</v>
+        <v>4.5</v>
       </c>
       <c r="P141">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="Q141">
         <v>1.95</v>
@@ -23310,13 +23310,13 @@
         <v>1.2</v>
       </c>
       <c r="T141">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="U141">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V141">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W141">
         <v>1.17</v>
@@ -23337,19 +23337,19 @@
         <v>2.83</v>
       </c>
       <c r="AC141">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD141">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE141">
         <v>1.26</v>
       </c>
       <c r="AF141">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG141">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23473,13 +23473,13 @@
         <v>1.25</v>
       </c>
       <c r="T142">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U142">
         <v>2.21</v>
       </c>
       <c r="V142">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W142">
         <v>1.13</v>
@@ -23497,16 +23497,16 @@
         <v>1.51</v>
       </c>
       <c r="AB142">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AC142">
         <v>2.33</v>
       </c>
       <c r="AD142">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE142">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF142">
         <v>1.44</v>
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK142">
         <v>1.67</v>
@@ -23947,10 +23947,10 @@
         <v>2.73</v>
       </c>
       <c r="O145">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="P145">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q145">
         <v>3.3</v>
@@ -24110,10 +24110,10 @@
         <v>1.7</v>
       </c>
       <c r="O146">
-        <v>3.75</v>
+        <v>4.36</v>
       </c>
       <c r="P146">
-        <v>3.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q146">
         <v>2.2</v>
@@ -24122,10 +24122,10 @@
         <v>2.35</v>
       </c>
       <c r="S146">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T146">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="U146">
         <v>2.2</v>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK146">
         <v>2</v>
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O147">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P147">
         <v>2.75</v>
@@ -24436,10 +24436,10 @@
         <v>2.08</v>
       </c>
       <c r="O148">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P148">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="Q148">
         <v>2.7</v>
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
+        <v>2.5</v>
+      </c>
+      <c r="O149">
+        <v>3.35</v>
+      </c>
+      <c r="P149">
         <v>2.43</v>
-      </c>
-      <c r="O149">
-        <v>3.32</v>
-      </c>
-      <c r="P149">
-        <v>2.45</v>
       </c>
       <c r="Q149">
         <v>3.08</v>
@@ -24759,16 +24759,16 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O150">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="P150">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q150">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="R150">
         <v>2.45</v>
@@ -24780,10 +24780,10 @@
         <v>3.7</v>
       </c>
       <c r="U150">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V150">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W150">
         <v>1.17</v>
@@ -24801,19 +24801,19 @@
         <v>1.5</v>
       </c>
       <c r="AB150">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AC150">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AD150">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE150">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF150">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG150">
         <v>2.55</v>
@@ -24925,25 +24925,25 @@
         <v>2.05</v>
       </c>
       <c r="O151">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P151">
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="Q151">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R151">
         <v>2.45</v>
       </c>
       <c r="S151">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T151">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U151">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V151">
         <v>1.7</v>
@@ -24955,25 +24955,25 @@
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z151">
-        <v>5.79</v>
+        <v>5.5</v>
       </c>
       <c r="AA151">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB151">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="AC151">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD151">
         <v>1.64</v>
       </c>
       <c r="AE151">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF151">
         <v>1.4</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
         <v>1.65</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU151"/>
+  <dimension ref="A1:AU152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="Q3">
-        <v>2.59</v>
+        <v>2.37</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
         <v>3.25</v>
       </c>
       <c r="U3">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB3">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>1.58</v>
@@ -1003,7 +1003,7 @@
         <v>1.59</v>
       </c>
       <c r="AB4">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
         <v>2.46</v>
@@ -1034,7 +1034,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>2.08</v>
       </c>
       <c r="AB29">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
         <v>3.5</v>
@@ -5875,7 +5875,7 @@
         <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
         <v>1.07</v>
@@ -5884,16 +5884,16 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA34">
         <v>1.71</v>
       </c>
       <c r="AB34">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC34">
         <v>2.7</v>
@@ -7976,7 +7976,7 @@
         <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -11073,7 +11073,7 @@
         <v>4</v>
       </c>
       <c r="P66">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q66">
         <v>3.8</v>
@@ -11121,10 +11121,10 @@
         <v>1.18</v>
       </c>
       <c r="AF66">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG66">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U67">
         <v>2.15</v>
@@ -11429,7 +11429,7 @@
         <v>1.23</v>
       </c>
       <c r="Z68">
-        <v>3.42</v>
+        <v>3.62</v>
       </c>
       <c r="AA68">
         <v>1.85</v>
@@ -11447,10 +11447,10 @@
         <v>1.06</v>
       </c>
       <c r="AF68">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -12697,25 +12697,25 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O76">
         <v>3.05</v>
       </c>
       <c r="P76">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q76">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="R76">
         <v>1.95</v>
       </c>
       <c r="S76">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T76">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="U76">
         <v>3.22</v>
@@ -12736,13 +12736,13 @@
         <v>2.7</v>
       </c>
       <c r="AA76">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AB76">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC76">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="AD76">
         <v>1.18</v>
@@ -13192,7 +13192,7 @@
         <v>3.52</v>
       </c>
       <c r="P79">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -13210,7 +13210,7 @@
         <v>2.59</v>
       </c>
       <c r="V79">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W79">
         <v>1.08</v>
@@ -13259,7 +13259,7 @@
         <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14448,22 +14448,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
+        <v>2.75</v>
+      </c>
+      <c r="O87">
+        <v>2.5</v>
+      </c>
+      <c r="P87">
+        <v>2.9</v>
+      </c>
+      <c r="Q87">
+        <v>3.6</v>
+      </c>
+      <c r="R87">
+        <v>1.8</v>
+      </c>
+      <c r="S87">
+        <v>1.75</v>
+      </c>
+      <c r="T87">
+        <v>2.02</v>
+      </c>
+      <c r="U87">
+        <v>4.5</v>
+      </c>
+      <c r="V87">
+        <v>1.17</v>
+      </c>
+      <c r="W87">
+        <v>1.02</v>
+      </c>
+      <c r="X87">
+        <v>1.13</v>
+      </c>
+      <c r="Y87">
+        <v>1.74</v>
+      </c>
+      <c r="Z87">
+        <v>1.98</v>
+      </c>
+      <c r="AA87">
+        <v>3.14</v>
+      </c>
+      <c r="AB87">
+        <v>1.27</v>
+      </c>
+      <c r="AC87">
+        <v>6.5</v>
+      </c>
+      <c r="AD87">
+        <v>1.1</v>
+      </c>
+      <c r="AE87">
+        <v>1.02</v>
+      </c>
+      <c r="AF87">
         <v>2.45</v>
       </c>
-      <c r="O87">
-        <v>3.45</v>
-      </c>
-      <c r="P87">
-        <v>2.5</v>
-      </c>
-      <c r="Q87">
-        <v>3.15</v>
-      </c>
-      <c r="R87">
-        <v>2.3</v>
-      </c>
-      <c r="S87">
-        <v>1.3</v>
-      </c>
-      <c r="T87">
-        <v>3.1</v>
-      </c>
-      <c r="U87">
-        <v>2.6</v>
-      </c>
-      <c r="V87">
-        <v>1.44</v>
-      </c>
-      <c r="W87">
-        <v>1.07</v>
-      </c>
-      <c r="X87">
-        <v>1.01</v>
-      </c>
-      <c r="Y87">
-        <v>1.23</v>
-      </c>
-      <c r="Z87">
-        <v>3.94</v>
-      </c>
-      <c r="AA87">
-        <v>1.75</v>
-      </c>
-      <c r="AB87">
-        <v>2.03</v>
-      </c>
-      <c r="AC87">
-        <v>2.74</v>
-      </c>
-      <c r="AD87">
-        <v>1.35</v>
-      </c>
-      <c r="AE87">
-        <v>1.11</v>
-      </c>
-      <c r="AF87">
-        <v>1.59</v>
-      </c>
       <c r="AG87">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK87">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.29</v>
+        <v>2.45</v>
       </c>
       <c r="O88">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="P88">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q88">
-        <v>1.71</v>
+        <v>3.15</v>
       </c>
       <c r="R88">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U88">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="V88">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W88">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="Z88">
-        <v>5.25</v>
+        <v>3.94</v>
       </c>
       <c r="AA88">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB88">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="AC88">
-        <v>2.27</v>
+        <v>2.74</v>
       </c>
       <c r="AD88">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AE88">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF88">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AG88">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AK88">
-        <v>3.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.9</v>
+        <v>1.29</v>
       </c>
       <c r="O89">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="P89">
-        <v>2.35</v>
+        <v>7.5</v>
       </c>
       <c r="Q89">
-        <v>3.68</v>
+        <v>1.71</v>
       </c>
       <c r="R89">
-        <v>2.04</v>
+        <v>2.53</v>
       </c>
       <c r="S89">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>3.09</v>
+        <v>2.15</v>
       </c>
       <c r="V89">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="W89">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>3.24</v>
+        <v>5.25</v>
       </c>
       <c r="AA89">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AB89">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="AC89">
-        <v>3.58</v>
+        <v>2.27</v>
       </c>
       <c r="AD89">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AE89">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AF89">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG89">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="AK89">
-        <v>1.43</v>
+        <v>3.42</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45:00</t>
+          <t>2026-08-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,31 +14979,31 @@
         </is>
       </c>
       <c r="N90">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O90">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="P90">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q90">
-        <v>5.25</v>
+        <v>3.68</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S90">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T90">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="U90">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="V90">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W90">
         <v>1.05</v>
@@ -15012,31 +15012,31 @@
         <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z90">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="AA90">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AB90">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AC90">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AD90">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF90">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AG90">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AK90">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-01 15:00:00</t>
+          <t>2026-08-01 14:45:00</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,65 +15142,65 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="O91">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P91">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q91">
-        <v>2.55</v>
+        <v>5.25</v>
       </c>
       <c r="R91">
         <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T91">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="U91">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="V91">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X91">
+        <v>1.03</v>
+      </c>
+      <c r="Y91">
+        <v>1.36</v>
+      </c>
+      <c r="Z91">
+        <v>2.7</v>
+      </c>
+      <c r="AA91">
+        <v>2.21</v>
+      </c>
+      <c r="AB91">
+        <v>1.59</v>
+      </c>
+      <c r="AC91">
+        <v>4.05</v>
+      </c>
+      <c r="AD91">
+        <v>1.16</v>
+      </c>
+      <c r="AE91">
         <v>1.06</v>
       </c>
-      <c r="Y91">
-        <v>1.22</v>
-      </c>
-      <c r="Z91">
-        <v>3.5</v>
-      </c>
-      <c r="AA91">
-        <v>1.83</v>
-      </c>
-      <c r="AB91">
-        <v>1.83</v>
-      </c>
-      <c r="AC91">
-        <v>3.3</v>
-      </c>
-      <c r="AD91">
-        <v>1.29</v>
-      </c>
-      <c r="AE91">
-        <v>1.07</v>
-      </c>
       <c r="AF91">
+        <v>2.05</v>
+      </c>
+      <c r="AG91">
         <v>1.68</v>
       </c>
-      <c r="AG91">
-        <v>2.04</v>
-      </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,65 +15305,65 @@
         </is>
       </c>
       <c r="N92">
+        <v>1.91</v>
+      </c>
+      <c r="O92">
+        <v>3.5</v>
+      </c>
+      <c r="P92">
+        <v>3.7</v>
+      </c>
+      <c r="Q92">
         <v>2.55</v>
       </c>
-      <c r="O92">
-        <v>2.62</v>
-      </c>
-      <c r="P92">
+      <c r="R92">
+        <v>2.1</v>
+      </c>
+      <c r="S92">
+        <v>1.38</v>
+      </c>
+      <c r="T92">
         <v>3</v>
       </c>
-      <c r="Q92">
-        <v>3.6</v>
-      </c>
-      <c r="R92">
-        <v>1.69</v>
-      </c>
-      <c r="S92">
-        <v>1.74</v>
-      </c>
-      <c r="T92">
-        <v>2.1</v>
-      </c>
       <c r="U92">
-        <v>4.33</v>
+        <v>2.65</v>
       </c>
       <c r="V92">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="W92">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X92">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
+        <v>3.5</v>
+      </c>
+      <c r="AA92">
+        <v>1.83</v>
+      </c>
+      <c r="AB92">
+        <v>1.83</v>
+      </c>
+      <c r="AC92">
+        <v>3.3</v>
+      </c>
+      <c r="AD92">
+        <v>1.29</v>
+      </c>
+      <c r="AE92">
+        <v>1.07</v>
+      </c>
+      <c r="AF92">
+        <v>1.68</v>
+      </c>
+      <c r="AG92">
         <v>2.04</v>
       </c>
-      <c r="AA92">
-        <v>3.08</v>
-      </c>
-      <c r="AB92">
-        <v>1.28</v>
-      </c>
-      <c r="AC92">
-        <v>5.8</v>
-      </c>
-      <c r="AD92">
-        <v>1.06</v>
-      </c>
-      <c r="AE92">
-        <v>1.02</v>
-      </c>
-      <c r="AF92">
-        <v>2.4</v>
-      </c>
-      <c r="AG92">
-        <v>1.53</v>
-      </c>
       <c r="AH92" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK92">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="O93">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P93">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Q93">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="R93">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="S93">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="T93">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U93">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="V93">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X93">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y93">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="Z93">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AA93">
-        <v>2.69</v>
+        <v>3.08</v>
       </c>
       <c r="AB93">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AC93">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="AD93">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AE93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF93">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG93">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK93">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="O94">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P94">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q94">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R94">
         <v>1.83</v>
       </c>
       <c r="S94">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="T94">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U94">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="V94">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W94">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X94">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y94">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="Z94">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AA94">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AB94">
         <v>1.38</v>
       </c>
       <c r="AC94">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="AD94">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE94">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF94">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AG94">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AK94">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O95">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P95">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q95">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R95">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S95">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="T95">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="U95">
-        <v>4.5</v>
+        <v>3.82</v>
       </c>
       <c r="V95">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W95">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X95">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y95">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="Z95">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="AA95">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AB95">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AC95">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="AD95">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE95">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF95">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="AG95">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>1.4</v>
       </c>
       <c r="AK95">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,10 +15966,10 @@
         <v>1.96</v>
       </c>
       <c r="Q96">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="R96">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S96">
         <v>1.58</v>
@@ -15993,7 +15993,7 @@
         <v>1.52</v>
       </c>
       <c r="Z96">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="AA96">
         <v>2.52</v>
@@ -16014,7 +16014,7 @@
         <v>2.17</v>
       </c>
       <c r="AG96">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O97">
+        <v>2.65</v>
+      </c>
+      <c r="P97">
         <v>2.7</v>
       </c>
-      <c r="P97">
-        <v>3.3</v>
-      </c>
       <c r="Q97">
-        <v>3.01</v>
+        <v>3.7</v>
       </c>
       <c r="R97">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="S97">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="T97">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="U97">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="V97">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W97">
         <v>1.03</v>
       </c>
       <c r="X97">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y97">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Z97">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AA97">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AB97">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC97">
-        <v>6.12</v>
+        <v>6.4</v>
       </c>
       <c r="AD97">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AE97">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF97">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AG97">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK97">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17267,7 +17267,7 @@
         <v>3.6</v>
       </c>
       <c r="P104">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -17279,7 +17279,7 @@
         <v>1.22</v>
       </c>
       <c r="T104">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U104">
         <v>2.05</v>
@@ -17753,7 +17753,7 @@
         <v>2.3</v>
       </c>
       <c r="O107">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="P107">
         <v>2.37</v>
@@ -17774,7 +17774,7 @@
         <v>2.05</v>
       </c>
       <c r="V107">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W107">
         <v>1.17</v>
@@ -17786,7 +17786,7 @@
         <v>1.07</v>
       </c>
       <c r="Z107">
-        <v>6.23</v>
+        <v>5.8</v>
       </c>
       <c r="AA107">
         <v>1.4</v>
@@ -17795,7 +17795,7 @@
         <v>2.72</v>
       </c>
       <c r="AC107">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AD107">
         <v>1.8</v>
@@ -17804,10 +17804,10 @@
         <v>1.29</v>
       </c>
       <c r="AF107">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AG107">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -18085,13 +18085,13 @@
         <v>4.66</v>
       </c>
       <c r="Q109">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="R109">
         <v>2</v>
       </c>
       <c r="S109">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="T109">
         <v>2.1</v>
@@ -18133,7 +18133,7 @@
         <v>2.78</v>
       </c>
       <c r="AG109">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="O110">
-        <v>4.65</v>
+        <v>2.7</v>
       </c>
       <c r="P110">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q110">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="R110">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="S110">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="T110">
-        <v>2.65</v>
+        <v>2.19</v>
       </c>
       <c r="U110">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="V110">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="W110">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X110">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Y110">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="Z110">
-        <v>2.83</v>
+        <v>2.23</v>
       </c>
       <c r="AA110">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="AB110">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AC110">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="AD110">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AE110">
         <v>1.03</v>
       </c>
       <c r="AF110">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AG110">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK110">
-        <v>2.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="O111">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="P111">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-08-01 16:00:00</t>
+          <t>2026-08-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.05</v>
+        <v>1.46</v>
       </c>
       <c r="O112">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P112">
-        <v>1.98</v>
+        <v>5.4</v>
       </c>
       <c r="Q112">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R112">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S112">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T112">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U112">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V112">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W112">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y112">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z112">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB112">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC112">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD112">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF112">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG112">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK112">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="O113">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P113">
-        <v>3.4</v>
+        <v>1.98</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.91</v>
+        <v>1.8</v>
       </c>
       <c r="O114">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P114">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q114">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S114">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T114">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U114">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="V114">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W114">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X114">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y114">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z114">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA114">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB114">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC114">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD114">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE114">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF114">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG114">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK114">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.37</v>
+        <v>2.91</v>
       </c>
       <c r="O115">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q115">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R115">
         <v>2</v>
@@ -19072,46 +19072,46 @@
         <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="U115">
-        <v>2.89</v>
+        <v>3.29</v>
       </c>
       <c r="V115">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W115">
+        <v>1.03</v>
+      </c>
+      <c r="X115">
         <v>1.04</v>
       </c>
-      <c r="X115">
-        <v>1.03</v>
-      </c>
       <c r="Y115">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z115">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA115">
         <v>2.19</v>
       </c>
       <c r="AB115">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC115">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AD115">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE115">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF115">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG115">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK115">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.57</v>
+        <v>2.37</v>
       </c>
       <c r="O116">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="P116">
-        <v>4.61</v>
+        <v>2.85</v>
       </c>
       <c r="Q116">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="R116">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S116">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T116">
-        <v>3.6</v>
+        <v>2.69</v>
       </c>
       <c r="U116">
-        <v>2.08</v>
+        <v>2.89</v>
       </c>
       <c r="V116">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="W116">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X116">
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="Z116">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA116">
-        <v>1.46</v>
+        <v>2.19</v>
       </c>
       <c r="AB116">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC116">
-        <v>2.17</v>
+        <v>4</v>
       </c>
       <c r="AD116">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AE116">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="AG116">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AK116">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-08-01 17:00:00</t>
+          <t>2026-08-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-01 18:15:00</t>
+          <t>2026-08-01 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P118">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-08-01 18:30:00</t>
+          <t>2026-08-01 18:15:00</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="O119">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P119">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="Q119">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R119">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S119">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T119">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U119">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V119">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W119">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X119">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z119">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA119">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB119">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC119">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD119">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE119">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF119">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG119">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK119">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
+        <v>2.5</v>
+      </c>
+      <c r="O120">
+        <v>3.25</v>
+      </c>
+      <c r="P120">
+        <v>2.65</v>
+      </c>
+      <c r="Q120">
+        <v>3.3</v>
+      </c>
+      <c r="R120">
+        <v>1.95</v>
+      </c>
+      <c r="S120">
         <v>1.4</v>
       </c>
-      <c r="O120">
-        <v>4</v>
-      </c>
-      <c r="P120">
-        <v>5.75</v>
-      </c>
-      <c r="Q120">
-        <v>1.95</v>
-      </c>
-      <c r="R120">
-        <v>2.25</v>
-      </c>
-      <c r="S120">
-        <v>1.33</v>
-      </c>
       <c r="T120">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="U120">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="V120">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W120">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z120">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AA120">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AB120">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC120">
-        <v>2.92</v>
+        <v>3.58</v>
       </c>
       <c r="AD120">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AE120">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF120">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG120">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AK120">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="O121">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P121">
+        <v>5.75</v>
+      </c>
+      <c r="Q121">
+        <v>1.95</v>
+      </c>
+      <c r="R121">
+        <v>2.25</v>
+      </c>
+      <c r="S121">
+        <v>1.33</v>
+      </c>
+      <c r="T121">
         <v>3.11</v>
       </c>
-      <c r="Q121">
-        <v>0</v>
-      </c>
-      <c r="R121">
-        <v>0</v>
-      </c>
-      <c r="S121">
-        <v>0</v>
-      </c>
-      <c r="T121">
-        <v>0</v>
-      </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA121">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB121">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00:00</t>
+          <t>2026-08-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="O122">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="P122">
         <v>3.11</v>
       </c>
       <c r="Q122">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R122">
+        <v>0</v>
+      </c>
+      <c r="S122">
+        <v>0</v>
+      </c>
+      <c r="T122">
+        <v>0</v>
+      </c>
+      <c r="U122">
+        <v>0</v>
+      </c>
+      <c r="V122">
+        <v>0</v>
+      </c>
+      <c r="W122">
+        <v>0</v>
+      </c>
+      <c r="X122">
+        <v>0</v>
+      </c>
+      <c r="Y122">
+        <v>0</v>
+      </c>
+      <c r="Z122">
+        <v>0</v>
+      </c>
+      <c r="AA122">
+        <v>1.61</v>
+      </c>
+      <c r="AB122">
         <v>2.25</v>
       </c>
-      <c r="S122">
-        <v>1.33</v>
-      </c>
-      <c r="T122">
-        <v>2.88</v>
-      </c>
-      <c r="U122">
-        <v>2.5</v>
-      </c>
-      <c r="V122">
-        <v>1.4</v>
-      </c>
-      <c r="W122">
-        <v>1.07</v>
-      </c>
-      <c r="X122">
-        <v>1</v>
-      </c>
-      <c r="Y122">
-        <v>1.24</v>
-      </c>
-      <c r="Z122">
-        <v>3.4</v>
-      </c>
-      <c r="AA122">
-        <v>1.83</v>
-      </c>
-      <c r="AB122">
-        <v>1.83</v>
-      </c>
       <c r="AC122">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD122">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE122">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF122">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK122">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-08-01 19:30:00</t>
+          <t>2026-08-01 19:00:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,61 +20358,61 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="O123">
-        <v>3.92</v>
+        <v>3.34</v>
       </c>
       <c r="P123">
-        <v>5.11</v>
+        <v>3.11</v>
       </c>
       <c r="Q123">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="R123">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S123">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U123">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V123">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W123">
         <v>1.07</v>
       </c>
       <c r="X123">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y123">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z123">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA123">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB123">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AC123">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD123">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE123">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF123">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG123">
         <v>2</v>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AK123">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-01 20:00:00</t>
+          <t>2026-08-01 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.45</v>
+        <v>1.54</v>
       </c>
       <c r="O124">
-        <v>3.35</v>
+        <v>3.92</v>
       </c>
       <c r="P124">
-        <v>1.88</v>
+        <v>5.11</v>
       </c>
       <c r="Q124">
-        <v>4</v>
+        <v>2.08</v>
       </c>
       <c r="R124">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S124">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T124">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="U124">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="V124">
+        <v>1.45</v>
+      </c>
+      <c r="W124">
+        <v>1.07</v>
+      </c>
+      <c r="X124">
+        <v>1.03</v>
+      </c>
+      <c r="Y124">
+        <v>1.19</v>
+      </c>
+      <c r="Z124">
+        <v>3.8</v>
+      </c>
+      <c r="AA124">
+        <v>1.72</v>
+      </c>
+      <c r="AB124">
+        <v>2.07</v>
+      </c>
+      <c r="AC124">
+        <v>2.7</v>
+      </c>
+      <c r="AD124">
         <v>1.4</v>
       </c>
-      <c r="W124">
-        <v>1.08</v>
-      </c>
-      <c r="X124">
-        <v>1.01</v>
-      </c>
-      <c r="Y124">
-        <v>1.29</v>
-      </c>
-      <c r="Z124">
-        <v>3.39</v>
-      </c>
-      <c r="AA124">
-        <v>1.9</v>
-      </c>
-      <c r="AB124">
-        <v>1.82</v>
-      </c>
-      <c r="AC124">
-        <v>3.14</v>
-      </c>
-      <c r="AD124">
-        <v>1.31</v>
-      </c>
       <c r="AE124">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF124">
         <v>1.75</v>
       </c>
       <c r="AG124">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AK124">
-        <v>1.21</v>
+        <v>2.2</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,80 +20684,80 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="O125">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="P125">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="Q125">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="R125">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S125">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T125">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U125">
-        <v>2.56</v>
+        <v>2.87</v>
       </c>
       <c r="V125">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W125">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X125">
         <v>1.01</v>
       </c>
       <c r="Y125">
+        <v>1.29</v>
+      </c>
+      <c r="Z125">
+        <v>3.39</v>
+      </c>
+      <c r="AA125">
+        <v>1.9</v>
+      </c>
+      <c r="AB125">
+        <v>1.82</v>
+      </c>
+      <c r="AC125">
+        <v>3.14</v>
+      </c>
+      <c r="AD125">
+        <v>1.31</v>
+      </c>
+      <c r="AE125">
+        <v>1.11</v>
+      </c>
+      <c r="AF125">
+        <v>1.75</v>
+      </c>
+      <c r="AG125">
+        <v>1.92</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
+        <v>1.23</v>
+      </c>
+      <c r="AK125">
         <v>1.21</v>
-      </c>
-      <c r="Z125">
-        <v>3.8</v>
-      </c>
-      <c r="AA125">
-        <v>1.65</v>
-      </c>
-      <c r="AB125">
-        <v>1.98</v>
-      </c>
-      <c r="AC125">
-        <v>2.6</v>
-      </c>
-      <c r="AD125">
-        <v>1.33</v>
-      </c>
-      <c r="AE125">
-        <v>1.09</v>
-      </c>
-      <c r="AF125">
-        <v>1.56</v>
-      </c>
-      <c r="AG125">
-        <v>2.23</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.25</v>
-      </c>
-      <c r="AK125">
-        <v>1.55</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20800,7 +20800,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
+        <v>2.18</v>
+      </c>
+      <c r="O126">
+        <v>3.19</v>
+      </c>
+      <c r="P126">
+        <v>2.7</v>
+      </c>
+      <c r="Q126">
+        <v>2.74</v>
+      </c>
+      <c r="R126">
+        <v>2.12</v>
+      </c>
+      <c r="S126">
         <v>1.33</v>
       </c>
-      <c r="O126">
-        <v>4.9</v>
-      </c>
-      <c r="P126">
-        <v>6.8</v>
-      </c>
-      <c r="Q126">
-        <v>1.8</v>
-      </c>
-      <c r="R126">
-        <v>2.62</v>
-      </c>
-      <c r="S126">
-        <v>1.2</v>
-      </c>
       <c r="T126">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="U126">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="V126">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="W126">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z126">
-        <v>5.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA126">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB126">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AC126">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AD126">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AE126">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AF126">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG126">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK126">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-08-01 20:30:00</t>
+          <t>2026-08-01 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
+        <v>1.33</v>
+      </c>
+      <c r="O127">
+        <v>4.9</v>
+      </c>
+      <c r="P127">
+        <v>6.8</v>
+      </c>
+      <c r="Q127">
+        <v>1.8</v>
+      </c>
+      <c r="R127">
+        <v>2.62</v>
+      </c>
+      <c r="S127">
+        <v>1.2</v>
+      </c>
+      <c r="T127">
+        <v>4</v>
+      </c>
+      <c r="U127">
+        <v>2.1</v>
+      </c>
+      <c r="V127">
+        <v>1.67</v>
+      </c>
+      <c r="W127">
+        <v>1.13</v>
+      </c>
+      <c r="X127">
+        <v>1.02</v>
+      </c>
+      <c r="Y127">
+        <v>1.14</v>
+      </c>
+      <c r="Z127">
+        <v>5.45</v>
+      </c>
+      <c r="AA127">
+        <v>1.4</v>
+      </c>
+      <c r="AB127">
+        <v>2.5</v>
+      </c>
+      <c r="AC127">
         <v>2.14</v>
       </c>
-      <c r="O127">
-        <v>3.6</v>
-      </c>
-      <c r="P127">
-        <v>2.87</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>0</v>
-      </c>
-      <c r="Z127">
-        <v>0</v>
-      </c>
-      <c r="AA127">
-        <v>1.68</v>
-      </c>
-      <c r="AB127">
-        <v>2.05</v>
-      </c>
-      <c r="AC127">
-        <v>0</v>
-      </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="O128">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P128">
-        <v>4.33</v>
+        <v>2.87</v>
       </c>
       <c r="Q128">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R128">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S128">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T128">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U128">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V128">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W128">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X128">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y128">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z128">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA128">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AB128">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC128">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD128">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE128">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF128">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG128">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK128">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.85</v>
+        <v>1.72</v>
       </c>
       <c r="O129">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P129">
-        <v>2.37</v>
+        <v>4.33</v>
       </c>
       <c r="Q129">
-        <v>3.35</v>
+        <v>2.15</v>
       </c>
       <c r="R129">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S129">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T129">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U129">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="V129">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W129">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X129">
         <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z129">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA129">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AB129">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AC129">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AD129">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF129">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG129">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK129">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="O130">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P130">
-        <v>3.8</v>
+        <v>2.37</v>
       </c>
       <c r="Q130">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="R130">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S130">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="T130">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U130">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="V130">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W130">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z130">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA130">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AB130">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="AC130">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD130">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AE130">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF130">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG130">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK130">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="O131">
         <v>3.9</v>
       </c>
       <c r="P131">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q131">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="R131">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S131">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="T131">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="U131">
-        <v>1.77</v>
+        <v>2.29</v>
       </c>
       <c r="V131">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="W131">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X131">
         <v>0</v>
       </c>
       <c r="Y131">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z131">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="AA131">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AB131">
-        <v>3.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC131">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD131">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AE131">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AF131">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG131">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK131">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,80 +21825,80 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="O132">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P132">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q132">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="R132">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S132">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T132">
         <v>4.6</v>
       </c>
       <c r="U132">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="V132">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="W132">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="X132">
         <v>0</v>
       </c>
       <c r="Y132">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z132">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AA132">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AB132">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC132">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AD132">
+        <v>2.01</v>
+      </c>
+      <c r="AE132">
+        <v>1.41</v>
+      </c>
+      <c r="AF132">
+        <v>1.29</v>
+      </c>
+      <c r="AG132">
+        <v>3.3</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
+        <v>1.25</v>
+      </c>
+      <c r="AK132">
         <v>1.82</v>
-      </c>
-      <c r="AE132">
-        <v>1.35</v>
-      </c>
-      <c r="AF132">
-        <v>1.38</v>
-      </c>
-      <c r="AG132">
-        <v>2.8</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>1.2</v>
-      </c>
-      <c r="AK132">
-        <v>2.02</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="O133">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P133">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="Q133">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="R133">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S133">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T133">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U133">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V133">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W133">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X133">
         <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z133">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA133">
+        <v>1.38</v>
+      </c>
+      <c r="AB133">
+        <v>3.1</v>
+      </c>
+      <c r="AC133">
+        <v>1.85</v>
+      </c>
+      <c r="AD133">
+        <v>1.9</v>
+      </c>
+      <c r="AE133">
         <v>1.32</v>
       </c>
-      <c r="AB133">
-        <v>3.4</v>
-      </c>
-      <c r="AC133">
-        <v>1.8</v>
-      </c>
-      <c r="AD133">
-        <v>2.01</v>
-      </c>
-      <c r="AE133">
-        <v>1.4</v>
-      </c>
       <c r="AF133">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AG133">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AK133">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O134">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="P134">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Q134">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R134">
-        <v>2.22</v>
+        <v>2.79</v>
       </c>
       <c r="S134">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="T134">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="U134">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="V134">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="W134">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
         <v>1.03</v>
       </c>
-      <c r="Y134">
-        <v>1.16</v>
-      </c>
       <c r="Z134">
-        <v>3.98</v>
+        <v>7.5</v>
       </c>
       <c r="AA134">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AB134">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="AC134">
-        <v>2.59</v>
+        <v>1.8</v>
       </c>
       <c r="AD134">
-        <v>1.39</v>
+        <v>2.01</v>
       </c>
       <c r="AE134">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AF134">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AG134">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK134">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-01 21:00:00</t>
+          <t>2026-08-01 20:30:00</t>
         </is>
       </c>
     </row>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="O135">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="P135">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="Q135">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="R135">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="S135">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T135">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U135">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="V135">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W135">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y135">
+        <v>1.16</v>
+      </c>
+      <c r="Z135">
+        <v>3.98</v>
+      </c>
+      <c r="AA135">
+        <v>1.67</v>
+      </c>
+      <c r="AB135">
+        <v>2.08</v>
+      </c>
+      <c r="AC135">
+        <v>2.59</v>
+      </c>
+      <c r="AD135">
+        <v>1.39</v>
+      </c>
+      <c r="AE135">
+        <v>1.12</v>
+      </c>
+      <c r="AF135">
+        <v>1.57</v>
+      </c>
+      <c r="AG135">
+        <v>2.19</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
         <v>1.22</v>
       </c>
-      <c r="Z135">
-        <v>3.5</v>
-      </c>
-      <c r="AA135">
-        <v>1.9</v>
-      </c>
-      <c r="AB135">
-        <v>1.93</v>
-      </c>
-      <c r="AC135">
-        <v>2.83</v>
-      </c>
-      <c r="AD135">
-        <v>1.33</v>
-      </c>
-      <c r="AE135">
-        <v>1.1</v>
-      </c>
-      <c r="AF135">
-        <v>1.7</v>
-      </c>
-      <c r="AG135">
-        <v>1.98</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.25</v>
-      </c>
       <c r="AK135">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="O136">
+        <v>3.16</v>
+      </c>
+      <c r="P136">
+        <v>2.03</v>
+      </c>
+      <c r="Q136">
+        <v>3.6</v>
+      </c>
+      <c r="R136">
+        <v>2.17</v>
+      </c>
+      <c r="S136">
+        <v>1.33</v>
+      </c>
+      <c r="T136">
+        <v>2.96</v>
+      </c>
+      <c r="U136">
+        <v>2.53</v>
+      </c>
+      <c r="V136">
+        <v>1.43</v>
+      </c>
+      <c r="W136">
+        <v>1.1</v>
+      </c>
+      <c r="X136">
+        <v>1.01</v>
+      </c>
+      <c r="Y136">
+        <v>1.22</v>
+      </c>
+      <c r="Z136">
         <v>3.5</v>
-      </c>
-      <c r="P136">
-        <v>2.93</v>
-      </c>
-      <c r="Q136">
-        <v>2.57</v>
-      </c>
-      <c r="R136">
-        <v>2.28</v>
-      </c>
-      <c r="S136">
-        <v>1.34</v>
-      </c>
-      <c r="T136">
-        <v>3</v>
-      </c>
-      <c r="U136">
-        <v>2.6</v>
-      </c>
-      <c r="V136">
-        <v>1.44</v>
-      </c>
-      <c r="W136">
-        <v>1.08</v>
-      </c>
-      <c r="X136">
-        <v>1.02</v>
-      </c>
-      <c r="Y136">
-        <v>1.28</v>
-      </c>
-      <c r="Z136">
-        <v>3.45</v>
       </c>
       <c r="AA136">
         <v>1.9</v>
       </c>
       <c r="AB136">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC136">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AD136">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF136">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG136">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,65 +22640,65 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O137">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
+        <v>2.93</v>
+      </c>
+      <c r="Q137">
+        <v>2.57</v>
+      </c>
+      <c r="R137">
+        <v>2.28</v>
+      </c>
+      <c r="S137">
+        <v>1.34</v>
+      </c>
+      <c r="T137">
         <v>3</v>
       </c>
-      <c r="Q137">
-        <v>2.88</v>
-      </c>
-      <c r="R137">
-        <v>2.1</v>
-      </c>
-      <c r="S137">
-        <v>1.5</v>
-      </c>
-      <c r="T137">
-        <v>2.33</v>
-      </c>
       <c r="U137">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="V137">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="W137">
+        <v>1.08</v>
+      </c>
+      <c r="X137">
         <v>1.02</v>
       </c>
-      <c r="X137">
-        <v>1.04</v>
-      </c>
       <c r="Y137">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Z137">
-        <v>2.71</v>
+        <v>3.45</v>
       </c>
       <c r="AA137">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB137">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AC137">
-        <v>4.33</v>
+        <v>3.04</v>
       </c>
       <c r="AD137">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AE137">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
+        <v>1.67</v>
+      </c>
+      <c r="AG137">
         <v>2</v>
       </c>
-      <c r="AG137">
-        <v>1.7</v>
-      </c>
       <c r="AH137" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK137">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>6.3</v>
+        <v>2.15</v>
       </c>
       <c r="O138">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="P138">
-        <v>1.45</v>
+        <v>3</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA138">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB138">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="O139">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="P139">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="Q139">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R139">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S139">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T139">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U139">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V139">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W139">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X139">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y139">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z139">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA139">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AB139">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AC139">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD139">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE139">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF139">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG139">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK139">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-08-01 21:30:00</t>
+          <t>2026-08-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>1.98</v>
+        <v>2.9</v>
       </c>
       <c r="O140">
-        <v>4.08</v>
+        <v>3.4</v>
       </c>
       <c r="P140">
-        <v>3.58</v>
+        <v>2.1</v>
       </c>
       <c r="Q140">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="R140">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="S140">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T140">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="U140">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="V140">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W140">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y140">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z140">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA140">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB140">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="AC140">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="AD140">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE140">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF140">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG140">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK140">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="O141">
-        <v>4.5</v>
+        <v>4.08</v>
       </c>
       <c r="P141">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="Q141">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="R141">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="S141">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T141">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="U141">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V141">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W141">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z141">
-        <v>6</v>
+        <v>5.36</v>
       </c>
       <c r="AA141">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB141">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="AC141">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AD141">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE141">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF141">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG141">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK141">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X143">
         <v>0</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-08-01 21:45:00</t>
+          <t>2026-08-01 21:30:00</t>
         </is>
       </c>
     </row>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-08-01 22:00:00</t>
+          <t>2026-08-01 21:45:00</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O145">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P145">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q145">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R145">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S145">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T145">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U145">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V145">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W145">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y145">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z145">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA145">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB145">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC145">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD145">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF145">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG145">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK145">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-08-01 22:30:00</t>
+          <t>2026-08-01 22:00:00</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.7</v>
+        <v>2.73</v>
       </c>
       <c r="O146">
-        <v>4.36</v>
+        <v>3.45</v>
       </c>
       <c r="P146">
-        <v>4.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q146">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R146">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S146">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T146">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="U146">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V146">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="W146">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z146">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA146">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB146">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AC146">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="AD146">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AE146">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF146">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG146">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK146">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24223,12 +24223,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,81 +24270,81 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="O147">
-        <v>3.35</v>
+        <v>4.36</v>
       </c>
       <c r="P147">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
       <c r="Q147">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="R147">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="S147">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T147">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U147">
-        <v>3.02</v>
+        <v>2.2</v>
       </c>
       <c r="V147">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="W147">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X147">
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z147">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA147">
+        <v>1.57</v>
+      </c>
+      <c r="AB147">
+        <v>2.31</v>
+      </c>
+      <c r="AC147">
+        <v>2.58</v>
+      </c>
+      <c r="AD147">
+        <v>1.51</v>
+      </c>
+      <c r="AE147">
+        <v>1.2</v>
+      </c>
+      <c r="AF147">
+        <v>1.57</v>
+      </c>
+      <c r="AG147">
+        <v>2.25</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ147">
+        <v>1.2</v>
+      </c>
+      <c r="AK147">
         <v>2</v>
       </c>
-      <c r="AB147">
-        <v>1.76</v>
-      </c>
-      <c r="AC147">
-        <v>3.57</v>
-      </c>
-      <c r="AD147">
-        <v>1.27</v>
-      </c>
-      <c r="AE147">
-        <v>1.05</v>
-      </c>
-      <c r="AF147">
-        <v>1.76</v>
-      </c>
-      <c r="AG147">
-        <v>2</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>1.26</v>
-      </c>
-      <c r="AK147">
-        <v>1.53</v>
-      </c>
       <c r="AL147">
         <v>0</v>
       </c>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-01 23:00:00</t>
+          <t>2026-08-01 22:30:00</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O148">
         <v>3.35</v>
       </c>
       <c r="P148">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="Q148">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R148">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S148">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T148">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U148">
-        <v>2.63</v>
+        <v>3.02</v>
       </c>
       <c r="V148">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W148">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X148">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z148">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA148">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB148">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AC148">
-        <v>2.83</v>
+        <v>3.57</v>
       </c>
       <c r="AD148">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE148">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF148">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AG148">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK148">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24549,7 +24549,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="O149">
         <v>3.35</v>
       </c>
       <c r="P149">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="Q149">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="R149">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S149">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T149">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U149">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="V149">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W149">
         <v>1.11</v>
       </c>
       <c r="X149">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y149">
         <v>1.19</v>
       </c>
       <c r="Z149">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA149">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB149">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AC149">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD149">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE149">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF149">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG149">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK149">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-08-01 23:30:00</t>
+          <t>2026-08-01 23:00:00</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="O150">
-        <v>4.19</v>
+        <v>3.35</v>
       </c>
       <c r="P150">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="Q150">
-        <v>2.55</v>
+        <v>3.08</v>
       </c>
       <c r="R150">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="S150">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T150">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="U150">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="V150">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W150">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X150">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y150">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="Z150">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AA150">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AB150">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="AC150">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="AD150">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AE150">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF150">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG150">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>1.25</v>
       </c>
       <c r="AK150">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O151">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P151">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q151">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R151">
         <v>2.45</v>
       </c>
       <c r="S151">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T151">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U151">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V151">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W151">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z151">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA151">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB151">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="AC151">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="AD151">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE151">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF151">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG151">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -25027,6 +25027,169 @@
       <c r="AU151" t="inlineStr">
         <is>
           <t>2026-08-01 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N152">
+        <v>2.09</v>
+      </c>
+      <c r="O152">
+        <v>3.9</v>
+      </c>
+      <c r="P152">
+        <v>2.68</v>
+      </c>
+      <c r="Q152">
+        <v>2.5</v>
+      </c>
+      <c r="R152">
+        <v>2.45</v>
+      </c>
+      <c r="S152">
+        <v>1.2</v>
+      </c>
+      <c r="T152">
+        <v>4</v>
+      </c>
+      <c r="U152">
+        <v>2.05</v>
+      </c>
+      <c r="V152">
+        <v>1.7</v>
+      </c>
+      <c r="W152">
+        <v>1.15</v>
+      </c>
+      <c r="X152">
+        <v>1.01</v>
+      </c>
+      <c r="Y152">
+        <v>1.13</v>
+      </c>
+      <c r="Z152">
+        <v>5.75</v>
+      </c>
+      <c r="AA152">
+        <v>1.41</v>
+      </c>
+      <c r="AB152">
+        <v>2.54</v>
+      </c>
+      <c r="AC152">
+        <v>2.08</v>
+      </c>
+      <c r="AD152">
+        <v>1.64</v>
+      </c>
+      <c r="AE152">
+        <v>1.25</v>
+      </c>
+      <c r="AF152">
+        <v>1.4</v>
+      </c>
+      <c r="AG152">
+        <v>2.7</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ152">
+        <v>1.25</v>
+      </c>
+      <c r="AK152">
+        <v>1.65</v>
+      </c>
+      <c r="AL152">
+        <v>0</v>
+      </c>
+      <c r="AM152">
+        <v>-1</v>
+      </c>
+      <c r="AN152">
+        <v>-1</v>
+      </c>
+      <c r="AO152">
+        <v>-1</v>
+      </c>
+      <c r="AP152">
+        <v>-1</v>
+      </c>
+      <c r="AQ152">
+        <v>0</v>
+      </c>
+      <c r="AR152">
+        <v>0</v>
+      </c>
+      <c r="AS152">
+        <v>0</v>
+      </c>
+      <c r="AT152">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:45:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="O133">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P133">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="Q133">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="R133">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="S133">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T133">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="U133">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="V133">
+        <v>1.88</v>
+      </c>
+      <c r="W133">
+        <v>1.22</v>
+      </c>
+      <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133">
+        <v>1.03</v>
+      </c>
+      <c r="Z133">
+        <v>7.5</v>
+      </c>
+      <c r="AA133">
+        <v>1.32</v>
+      </c>
+      <c r="AB133">
+        <v>3.4</v>
+      </c>
+      <c r="AC133">
         <v>1.8</v>
       </c>
-      <c r="W133">
-        <v>1.19</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>1.11</v>
-      </c>
-      <c r="Z133">
-        <v>6.8</v>
-      </c>
-      <c r="AA133">
-        <v>1.38</v>
-      </c>
-      <c r="AB133">
-        <v>3.1</v>
-      </c>
-      <c r="AC133">
-        <v>1.85</v>
-      </c>
       <c r="AD133">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AE133">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AF133">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AG133">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AK133">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="O134">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P134">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="Q134">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="R134">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="S134">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T134">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U134">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V134">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W134">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X134">
         <v>0</v>
       </c>
       <c r="Y134">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z134">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA134">
+        <v>1.38</v>
+      </c>
+      <c r="AB134">
+        <v>3.1</v>
+      </c>
+      <c r="AC134">
+        <v>1.85</v>
+      </c>
+      <c r="AD134">
+        <v>1.9</v>
+      </c>
+      <c r="AE134">
         <v>1.32</v>
       </c>
-      <c r="AB134">
-        <v>3.4</v>
-      </c>
-      <c r="AC134">
-        <v>1.8</v>
-      </c>
-      <c r="AD134">
-        <v>2.01</v>
-      </c>
-      <c r="AE134">
-        <v>1.4</v>
-      </c>
       <c r="AF134">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AG134">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AK134">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AL134">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="R7">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U7">
+        <v>3.04</v>
+      </c>
+      <c r="V7">
+        <v>1.33</v>
+      </c>
+      <c r="W7">
+        <v>1.03</v>
+      </c>
+      <c r="X7">
+        <v>1.05</v>
+      </c>
+      <c r="Y7">
+        <v>1.33</v>
+      </c>
+      <c r="Z7">
         <v>2.85</v>
       </c>
-      <c r="V7">
-        <v>1.37</v>
-      </c>
-      <c r="W7">
+      <c r="AA7">
+        <v>2.13</v>
+      </c>
+      <c r="AB7">
+        <v>1.7</v>
+      </c>
+      <c r="AC7">
+        <v>3.94</v>
+      </c>
+      <c r="AD7">
+        <v>1.21</v>
+      </c>
+      <c r="AE7">
         <v>1.04</v>
       </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.27</v>
-      </c>
-      <c r="Z7">
-        <v>3.18</v>
-      </c>
-      <c r="AA7">
-        <v>1.93</v>
-      </c>
-      <c r="AB7">
-        <v>1.76</v>
-      </c>
-      <c r="AC7">
-        <v>3.6</v>
-      </c>
-      <c r="AD7">
-        <v>1.25</v>
-      </c>
-      <c r="AE7">
-        <v>1.06</v>
-      </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG7">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="O8">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q8">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="R8">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U8">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
+        <v>1.04</v>
+      </c>
+      <c r="X8">
         <v>1.03</v>
       </c>
-      <c r="X8">
-        <v>1.05</v>
-      </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="AA8">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AB8">
+        <v>1.76</v>
+      </c>
+      <c r="AC8">
+        <v>3.6</v>
+      </c>
+      <c r="AD8">
+        <v>1.25</v>
+      </c>
+      <c r="AE8">
+        <v>1.06</v>
+      </c>
+      <c r="AF8">
         <v>1.7</v>
       </c>
-      <c r="AC8">
-        <v>3.94</v>
-      </c>
-      <c r="AD8">
-        <v>1.21</v>
-      </c>
-      <c r="AE8">
-        <v>1.04</v>
-      </c>
-      <c r="AF8">
-        <v>1.86</v>
-      </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>2.32</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
         <v>3.25</v>
@@ -1824,7 +1824,7 @@
         <v>2.74</v>
       </c>
       <c r="AD9">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE9">
         <v>1.14</v>
@@ -1833,7 +1833,7 @@
         <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,58 +1939,58 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="P10">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q10">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="U10">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
         <v>3.35</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD10">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
         <v>1.62</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="O11">
+        <v>3.13</v>
+      </c>
+      <c r="P11">
+        <v>2.38</v>
+      </c>
+      <c r="Q11">
         <v>3.3</v>
-      </c>
-      <c r="P11">
-        <v>2.58</v>
-      </c>
-      <c r="Q11">
-        <v>3.18</v>
       </c>
       <c r="R11">
         <v>2.15</v>
@@ -2135,7 +2135,7 @@
         <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
         <v>3.25</v>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.96</v>
+        <v>4.45</v>
       </c>
       <c r="O12">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R12">
         <v>2.32</v>
@@ -2304,7 +2304,7 @@
         <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB12">
         <v>1.9</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK12">
         <v>1.1</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
         <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="R13">
         <v>2.17</v>
       </c>
       <c r="S13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
         <v>2.33</v>
@@ -2482,7 +2482,7 @@
         <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG13">
         <v>2.39</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AK13">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="O15">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="P15">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q15">
         <v>3.7</v>
@@ -2769,10 +2769,10 @@
         <v>2.02</v>
       </c>
       <c r="S15">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T15">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U15">
         <v>3.19</v>
@@ -2796,10 +2796,10 @@
         <v>2.18</v>
       </c>
       <c r="AB15">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="AD15">
         <v>1.25</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="O20">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -3587,7 +3587,7 @@
         <v>1.18</v>
       </c>
       <c r="T20">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="U20">
         <v>1.9</v>
@@ -3602,10 +3602,10 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA20">
         <v>1.33</v>
@@ -3614,13 +3614,13 @@
         <v>3.2</v>
       </c>
       <c r="AC20">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD20">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE20">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AF20">
         <v>1.36</v>
@@ -3642,7 +3642,7 @@
         <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>1.82</v>
       </c>
       <c r="O21">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="P21">
         <v>2.77</v>
@@ -3750,10 +3750,10 @@
         <v>1.18</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U21">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V21">
         <v>1.8</v>
@@ -3777,13 +3777,13 @@
         <v>3.1</v>
       </c>
       <c r="AC21">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AD21">
         <v>1.9</v>
       </c>
       <c r="AE21">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF21">
         <v>1.3</v>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,16 +3898,16 @@
         <v>1.25</v>
       </c>
       <c r="O22">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="P22">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q22">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R22">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="S22">
         <v>1.23</v>
@@ -3919,25 +3919,25 @@
         <v>2.06</v>
       </c>
       <c r="V22">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z22">
-        <v>5.94</v>
+        <v>6.5</v>
       </c>
       <c r="AA22">
         <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
         <v>2</v>
@@ -3949,10 +3949,10 @@
         <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4233,7 +4233,7 @@
         <v>2.8</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
         <v>1.36</v>
@@ -4245,40 +4245,40 @@
         <v>2.65</v>
       </c>
       <c r="V24">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
         <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB24">
         <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD24">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="P25">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
       </c>
       <c r="R25">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S25">
         <v>1.33</v>
@@ -4411,7 +4411,7 @@
         <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4438,10 +4438,10 @@
         <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O26">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -4746,13 +4746,13 @@
         <v>1.31</v>
       </c>
       <c r="Z27">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="AA27">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AB27">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
         <v>3.5</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="O28">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="P28">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q28">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="R28">
         <v>2.03</v>
@@ -4906,13 +4906,13 @@
         <v>1.1</v>
       </c>
       <c r="Y28">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z28">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AA28">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AB28">
         <v>1.53</v>
@@ -4927,7 +4927,7 @@
         <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG28">
         <v>1.67</v>
@@ -5048,7 +5048,7 @@
         <v>5.65</v>
       </c>
       <c r="R29">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S29">
         <v>1.4</v>
@@ -5057,10 +5057,10 @@
         <v>2.69</v>
       </c>
       <c r="U29">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
         <v>1.02</v>
@@ -5072,13 +5072,13 @@
         <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA29">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AB29">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC29">
         <v>3.5</v>
@@ -5087,13 +5087,13 @@
         <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>2.97</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>1.07</v>
@@ -5896,7 +5896,7 @@
         <v>2</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD34">
         <v>1.36</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="O35">
         <v>4.05</v>
       </c>
       <c r="P35">
-        <v>5.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="R35">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S35">
         <v>1.31</v>
@@ -6035,10 +6035,10 @@
         <v>3.32</v>
       </c>
       <c r="U35">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6050,19 +6050,19 @@
         <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="AA35">
         <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC35">
         <v>2.74</v>
       </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE35">
         <v>1.11</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="O36">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="Q36">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="R36">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T36">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="V36">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA36">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AB36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC36">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AD36">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE36">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF36">
         <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK36">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q37">
-        <v>2.39</v>
+        <v>3.86</v>
       </c>
       <c r="R37">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T37">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="U37">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W37">
+        <v>1.05</v>
+      </c>
+      <c r="X37">
         <v>1.06</v>
       </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
       <c r="Y37">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA37">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB37">
+        <v>1.75</v>
+      </c>
+      <c r="AC37">
+        <v>3.42</v>
+      </c>
+      <c r="AD37">
+        <v>1.25</v>
+      </c>
+      <c r="AE37">
+        <v>1.07</v>
+      </c>
+      <c r="AF37">
         <v>1.8</v>
       </c>
-      <c r="AC37">
-        <v>3.34</v>
-      </c>
-      <c r="AD37">
-        <v>1.24</v>
-      </c>
-      <c r="AE37">
-        <v>1.04</v>
-      </c>
-      <c r="AF37">
-        <v>1.83</v>
-      </c>
       <c r="AG37">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="O38">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="Q38">
-        <v>3.64</v>
+        <v>2.27</v>
       </c>
       <c r="R38">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S38">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U38">
-        <v>3.07</v>
+        <v>2.77</v>
       </c>
       <c r="V38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z38">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="AA38">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AB38">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AC38">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="AD38">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE38">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG38">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AK38">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="O40">
         <v>2.9</v>
@@ -6847,7 +6847,7 @@
         <v>1.49</v>
       </c>
       <c r="T40">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U40">
         <v>3.17</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK40">
         <v>1.43</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.65</v>
+        <v>1.63</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>1.51</v>
+        <v>4.6</v>
       </c>
       <c r="Q42">
-        <v>5</v>
+        <v>2.21</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="T42">
-        <v>3.23</v>
+        <v>2.53</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
+        <v>1.33</v>
+      </c>
+      <c r="Z42">
+        <v>2.83</v>
+      </c>
+      <c r="AA42">
+        <v>2.15</v>
+      </c>
+      <c r="AB42">
+        <v>1.66</v>
+      </c>
+      <c r="AC42">
+        <v>3.72</v>
+      </c>
+      <c r="AD42">
         <v>1.2</v>
       </c>
-      <c r="Z42">
-        <v>4.1</v>
-      </c>
-      <c r="AA42">
-        <v>1.7</v>
-      </c>
-      <c r="AB42">
+      <c r="AE42">
+        <v>1.03</v>
+      </c>
+      <c r="AF42">
+        <v>2.05</v>
+      </c>
+      <c r="AG42">
+        <v>1.67</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.22</v>
+      </c>
+      <c r="AK42">
         <v>2.1</v>
-      </c>
-      <c r="AC42">
-        <v>2.8</v>
-      </c>
-      <c r="AD42">
-        <v>1.36</v>
-      </c>
-      <c r="AE42">
-        <v>1.14</v>
-      </c>
-      <c r="AF42">
-        <v>1.67</v>
-      </c>
-      <c r="AG42">
-        <v>1.93</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.21</v>
-      </c>
-      <c r="AK42">
-        <v>1.08</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,34 +7816,34 @@
         <v>1.85</v>
       </c>
       <c r="Q46">
-        <v>3.24</v>
+        <v>4.16</v>
       </c>
       <c r="R46">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T46">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="V46">
         <v>1.67</v>
       </c>
       <c r="W46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z46">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA46">
         <v>1.35</v>
@@ -7855,16 +7855,16 @@
         <v>1.9</v>
       </c>
       <c r="AD46">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE46">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF46">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG46">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="AK46">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -8021,13 +8021,13 @@
         <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
         <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>2.28</v>
       </c>
       <c r="AB49">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC49">
         <v>4.1</v>
@@ -8353,7 +8353,7 @@
         <v>1.97</v>
       </c>
       <c r="AG49">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O50">
         <v>3.65</v>
@@ -8622,49 +8622,49 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q51">
         <v>2.06</v>
       </c>
       <c r="R51">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="S51">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="U51">
         <v>2.38</v>
       </c>
       <c r="V51">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AA51">
         <v>1.68</v>
       </c>
       <c r="AB51">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
         <v>2.87</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK51">
         <v>2.3</v>
@@ -8785,65 +8785,65 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA52">
         <v>1.75</v>
       </c>
       <c r="AB52">
+        <v>2.15</v>
+      </c>
+      <c r="AC52">
+        <v>2.77</v>
+      </c>
+      <c r="AD52">
+        <v>1.41</v>
+      </c>
+      <c r="AE52">
+        <v>1.16</v>
+      </c>
+      <c r="AF52">
+        <v>1.76</v>
+      </c>
+      <c r="AG52">
         <v>2.05</v>
       </c>
-      <c r="AC52">
-        <v>0</v>
-      </c>
-      <c r="AD52">
-        <v>0</v>
-      </c>
-      <c r="AE52">
-        <v>0</v>
-      </c>
-      <c r="AF52">
-        <v>0</v>
-      </c>
-      <c r="AG52">
-        <v>0</v>
-      </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O55">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P55">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q55">
         <v>4.2</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S55">
         <v>1.3</v>
@@ -9313,10 +9313,10 @@
         <v>3.95</v>
       </c>
       <c r="AA55">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB55">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC55">
         <v>2.84</v>
@@ -9600,28 +9600,28 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="O57">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="P57">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="Q57">
         <v>3.1</v>
       </c>
       <c r="R57">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="S57">
         <v>1.4</v>
       </c>
       <c r="T57">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U57">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V57">
         <v>1.32</v>
@@ -9648,7 +9648,7 @@
         <v>3.8</v>
       </c>
       <c r="AD57">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE57">
         <v>1.03</v>
@@ -9657,7 +9657,7 @@
         <v>1.78</v>
       </c>
       <c r="AG57">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.35</v>
       </c>
       <c r="AK57">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10095,10 +10095,10 @@
         <v>3</v>
       </c>
       <c r="P60">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q60">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R60">
         <v>1.88</v>
@@ -10128,7 +10128,7 @@
         <v>2.41</v>
       </c>
       <c r="AA60">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB60">
         <v>1.48</v>
@@ -10143,7 +10143,7 @@
         <v>1.04</v>
       </c>
       <c r="AF60">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG60">
         <v>1.57</v>
@@ -10162,7 +10162,7 @@
         <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="O61">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="P61">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q61">
         <v>4.11</v>
@@ -10282,19 +10282,19 @@
         <v>1.1</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
         <v>1.2</v>
       </c>
       <c r="Z61">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA61">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB61">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC61">
         <v>2.43</v>
@@ -10309,7 +10309,7 @@
         <v>1.55</v>
       </c>
       <c r="AG61">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>2.66</v>
       </c>
       <c r="U62">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="V62">
         <v>1.35</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="O63">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P63">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK65">
         <v>1.41</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="O66">
         <v>4</v>
       </c>
       <c r="P66">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q66">
         <v>3.8</v>
@@ -11097,7 +11097,7 @@
         <v>1.11</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
         <v>1.12</v>
@@ -11109,13 +11109,13 @@
         <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="AC66">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD66">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE66">
         <v>1.18</v>
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="O67">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="P67">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q67">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R67">
         <v>2.32</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U67">
         <v>2.15</v>
       </c>
       <c r="V67">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W67">
         <v>1.14</v>
@@ -11275,13 +11275,13 @@
         <v>2.38</v>
       </c>
       <c r="AC67">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD67">
         <v>1.59</v>
       </c>
       <c r="AE67">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF67">
         <v>1.44</v>
@@ -11414,25 +11414,25 @@
         <v>3.07</v>
       </c>
       <c r="U68">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V68">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W68">
         <v>1.07</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
         <v>1.23</v>
       </c>
       <c r="Z68">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="AA68">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB68">
         <v>1.85</v>
@@ -11441,7 +11441,7 @@
         <v>3.12</v>
       </c>
       <c r="AD68">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE68">
         <v>1.06</v>
@@ -11722,16 +11722,16 @@
         <v>1.91</v>
       </c>
       <c r="O70">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P70">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q70">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="R70">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="S70">
         <v>1.18</v>
@@ -11740,31 +11740,31 @@
         <v>3.9</v>
       </c>
       <c r="U70">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V70">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W70">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z70">
-        <v>5.75</v>
+        <v>6.24</v>
       </c>
       <c r="AA70">
         <v>1.34</v>
       </c>
       <c r="AB70">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AC70">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD70">
         <v>1.81</v>
@@ -11792,7 +11792,7 @@
         <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
+        <v>2.99</v>
+      </c>
+      <c r="O71">
         <v>3.4</v>
       </c>
-      <c r="O71">
-        <v>3.7</v>
-      </c>
       <c r="P71">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q71">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="R71">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S71">
         <v>1.28</v>
@@ -11912,7 +11912,7 @@
         <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
         <v>1.16</v>
@@ -11927,16 +11927,16 @@
         <v>2.1</v>
       </c>
       <c r="AC71">
-        <v>2.51</v>
+        <v>2.67</v>
       </c>
       <c r="AD71">
         <v>1.42</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG71">
         <v>2.3</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AK71">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,31 +12045,31 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P72">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="Q72">
-        <v>3.18</v>
+        <v>3.72</v>
       </c>
       <c r="R72">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="S72">
+        <v>1.36</v>
+      </c>
+      <c r="T72">
+        <v>2.75</v>
+      </c>
+      <c r="U72">
+        <v>2.79</v>
+      </c>
+      <c r="V72">
         <v>1.35</v>
-      </c>
-      <c r="T72">
-        <v>2.79</v>
-      </c>
-      <c r="U72">
-        <v>2.75</v>
-      </c>
-      <c r="V72">
-        <v>1.4</v>
       </c>
       <c r="W72">
         <v>1.03</v>
@@ -12078,31 +12078,31 @@
         <v>1.01</v>
       </c>
       <c r="Y72">
+        <v>1.26</v>
+      </c>
+      <c r="Z72">
+        <v>3.2</v>
+      </c>
+      <c r="AA72">
+        <v>1.91</v>
+      </c>
+      <c r="AB72">
+        <v>1.78</v>
+      </c>
+      <c r="AC72">
+        <v>3.28</v>
+      </c>
+      <c r="AD72">
         <v>1.25</v>
-      </c>
-      <c r="Z72">
-        <v>3.28</v>
-      </c>
-      <c r="AA72">
-        <v>1.88</v>
-      </c>
-      <c r="AB72">
-        <v>1.81</v>
-      </c>
-      <c r="AC72">
-        <v>3.2</v>
-      </c>
-      <c r="AD72">
-        <v>1.26</v>
       </c>
       <c r="AE72">
         <v>1.05</v>
       </c>
       <c r="AF72">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG72">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AK72">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O73">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="Q73">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="R73">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S73">
         <v>1.3</v>
@@ -12232,37 +12232,37 @@
         <v>2.63</v>
       </c>
       <c r="V73">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z73">
-        <v>3.72</v>
+        <v>3.48</v>
       </c>
       <c r="AA73">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB73">
         <v>2.05</v>
       </c>
       <c r="AC73">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD73">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE73">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG73">
         <v>2.2</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK73">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,16 +12374,16 @@
         <v>1.22</v>
       </c>
       <c r="O74">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P74">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q74">
         <v>1.65</v>
       </c>
       <c r="R74">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="S74">
         <v>1.31</v>
@@ -12398,10 +12398,10 @@
         <v>1.48</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
         <v>1.21</v>
@@ -12416,7 +12416,7 @@
         <v>2.11</v>
       </c>
       <c r="AC74">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD74">
         <v>1.4</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK74">
         <v>4.15</v>
@@ -12700,13 +12700,13 @@
         <v>1.97</v>
       </c>
       <c r="O76">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="P76">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q76">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="R76">
         <v>1.95</v>
@@ -12718,22 +12718,22 @@
         <v>2.65</v>
       </c>
       <c r="U76">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="V76">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X76">
         <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z76">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA76">
         <v>2.23</v>
@@ -12751,10 +12751,10 @@
         <v>1.02</v>
       </c>
       <c r="AF76">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AG76">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK76">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,28 +12860,28 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="O77">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P77">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q77">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R77">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="S77">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T77">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U77">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="V77">
         <v>1.5</v>
@@ -12896,28 +12896,28 @@
         <v>1.16</v>
       </c>
       <c r="Z77">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="AA77">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB77">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AC77">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD77">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE77">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG77">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.17</v>
       </c>
       <c r="AK77">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13041,7 +13041,7 @@
         <v>1.36</v>
       </c>
       <c r="T78">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="U78">
         <v>2.77</v>
@@ -13053,7 +13053,7 @@
         <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
         <v>1.25</v>
@@ -13065,7 +13065,7 @@
         <v>1.9</v>
       </c>
       <c r="AB78">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC78">
         <v>2.83</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
         <v>1.55</v>
@@ -13192,7 +13192,7 @@
         <v>3.52</v>
       </c>
       <c r="P79">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -13210,7 +13210,7 @@
         <v>2.59</v>
       </c>
       <c r="V79">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W79">
         <v>1.08</v>
@@ -13219,7 +13219,7 @@
         <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z79">
         <v>4.1</v>
@@ -13237,7 +13237,7 @@
         <v>1.4</v>
       </c>
       <c r="AE79">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF79">
         <v>1.57</v>
@@ -13259,7 +13259,7 @@
         <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>1.44</v>
       </c>
       <c r="T82">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="U82">
         <v>3.14</v>
@@ -13732,7 +13732,7 @@
         <v>1.93</v>
       </c>
       <c r="AG82">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13853,19 +13853,19 @@
         <v>2.17</v>
       </c>
       <c r="S83">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T83">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U83">
         <v>2.53</v>
       </c>
       <c r="V83">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W83">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13911,7 +13911,7 @@
         <v>1.21</v>
       </c>
       <c r="AK83">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14019,10 +14019,10 @@
         <v>1.29</v>
       </c>
       <c r="T84">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="U84">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="V84">
         <v>1.45</v>
@@ -14037,13 +14037,13 @@
         <v>1.18</v>
       </c>
       <c r="Z84">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA84">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB84">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC84">
         <v>2.59</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK84">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,13 +14173,13 @@
         <v>0</v>
       </c>
       <c r="Q85">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="R85">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S85">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T85">
         <v>2.88</v>
@@ -14194,34 +14194,34 @@
         <v>1.07</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z85">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA85">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB85">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC85">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD85">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE85">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF85">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG85">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14345,10 +14345,10 @@
         <v>1.45</v>
       </c>
       <c r="T86">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="U86">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="V86">
         <v>1.29</v>
@@ -14369,7 +14369,7 @@
         <v>2.37</v>
       </c>
       <c r="AB86">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC86">
         <v>4.3</v>
@@ -14384,7 +14384,7 @@
         <v>1.91</v>
       </c>
       <c r="AG86">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14656,10 +14656,10 @@
         <v>2.45</v>
       </c>
       <c r="O88">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P88">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q88">
         <v>3.15</v>
@@ -14692,10 +14692,10 @@
         <v>3.94</v>
       </c>
       <c r="AA88">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB88">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC88">
         <v>2.74</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="O89">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P89">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="Q89">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="R89">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="S89">
         <v>1.2</v>
@@ -14837,13 +14837,13 @@
         <v>4</v>
       </c>
       <c r="U89">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V89">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W89">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
         <v>1.02</v>
@@ -14852,7 +14852,7 @@
         <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA89">
         <v>1.5</v>
@@ -14864,16 +14864,16 @@
         <v>2.27</v>
       </c>
       <c r="AD89">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE89">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF89">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG89">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.04</v>
       </c>
       <c r="AK89">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,28 +14982,28 @@
         <v>2.9</v>
       </c>
       <c r="O90">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="P90">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="Q90">
-        <v>3.68</v>
+        <v>3.26</v>
       </c>
       <c r="R90">
         <v>2.04</v>
       </c>
       <c r="S90">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U90">
         <v>3.09</v>
       </c>
       <c r="V90">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W90">
         <v>1.05</v>
@@ -15015,7 +15015,7 @@
         <v>1.33</v>
       </c>
       <c r="Z90">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AA90">
         <v>2.12</v>
@@ -15151,10 +15151,10 @@
         <v>1.75</v>
       </c>
       <c r="Q91">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S91">
         <v>1.44</v>
@@ -15175,10 +15175,10 @@
         <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z91">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AA91">
         <v>2.21</v>
@@ -15193,7 +15193,7 @@
         <v>1.16</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF91">
         <v>2.05</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q92">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R92">
         <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="U92">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V92">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W92">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X92">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z92">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AA92">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB92">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC92">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AD92">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE92">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK92">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O98">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P98">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q98">
         <v>1.86</v>
@@ -16301,13 +16301,13 @@
         <v>1.24</v>
       </c>
       <c r="T98">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U98">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V98">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W98">
         <v>1.14</v>
@@ -16316,7 +16316,7 @@
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z98">
         <v>5</v>
@@ -16325,19 +16325,19 @@
         <v>1.43</v>
       </c>
       <c r="AB98">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC98">
         <v>2.16</v>
       </c>
       <c r="AD98">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE98">
         <v>1.24</v>
       </c>
       <c r="AF98">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG98">
         <v>2.13</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O103">
         <v>3.1</v>
       </c>
       <c r="P103">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P104">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -17276,16 +17276,16 @@
         <v>2.4</v>
       </c>
       <c r="S104">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T104">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U104">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="V104">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W104">
         <v>1.16</v>
@@ -17297,19 +17297,19 @@
         <v>1.15</v>
       </c>
       <c r="Z104">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA104">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB104">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AC104">
         <v>2.22</v>
       </c>
       <c r="AD104">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AE104">
         <v>1.22</v>
@@ -17318,7 +17318,7 @@
         <v>1.4</v>
       </c>
       <c r="AG104">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK104">
         <v>1.62</v>
@@ -17430,7 +17430,7 @@
         <v>3</v>
       </c>
       <c r="P105">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="Q105">
         <v>3.65</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AK105">
         <v>1.39</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O106">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P106">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q106">
         <v>2.36</v>
@@ -17617,19 +17617,19 @@
         <v>1.08</v>
       </c>
       <c r="X106">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA106">
         <v>1.95</v>
       </c>
       <c r="AB106">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC106">
         <v>3.34</v>
@@ -17641,7 +17641,7 @@
         <v>1.05</v>
       </c>
       <c r="AF106">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG106">
         <v>1.84</v>
@@ -17660,7 +17660,7 @@
         <v>1.28</v>
       </c>
       <c r="AK106">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,16 +17750,16 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="O107">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="P107">
         <v>2.37</v>
       </c>
       <c r="Q107">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="R107">
         <v>2.64</v>
@@ -17771,10 +17771,10 @@
         <v>3.98</v>
       </c>
       <c r="U107">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="V107">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W107">
         <v>1.17</v>
@@ -17795,19 +17795,19 @@
         <v>2.72</v>
       </c>
       <c r="AC107">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AD107">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AE107">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AF107">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG107">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.24</v>
       </c>
       <c r="AK107">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,80 +17913,80 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O108">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P108">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q108">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R108">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S108">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T108">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U108">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="V108">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W108">
+        <v>1.02</v>
+      </c>
+      <c r="X108">
         <v>1.03</v>
       </c>
-      <c r="X108">
-        <v>1.05</v>
-      </c>
       <c r="Y108">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z108">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="AA108">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="AB108">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AC108">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD108">
+        <v>1.22</v>
+      </c>
+      <c r="AE108">
+        <v>1.03</v>
+      </c>
+      <c r="AF108">
+        <v>1.65</v>
+      </c>
+      <c r="AG108">
+        <v>1.92</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ108">
         <v>1.28</v>
       </c>
-      <c r="AE108">
-        <v>1.05</v>
-      </c>
-      <c r="AF108">
-        <v>1.69</v>
-      </c>
-      <c r="AG108">
-        <v>2.03</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ108">
-        <v>1.26</v>
-      </c>
       <c r="AK108">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18405,19 +18405,19 @@
         <v>1.48</v>
       </c>
       <c r="O111">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="P111">
-        <v>5.3</v>
+        <v>6.93</v>
       </c>
       <c r="Q111">
         <v>2</v>
       </c>
       <c r="R111">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T111">
         <v>2.65</v>
@@ -18435,19 +18435,19 @@
         <v>1.04</v>
       </c>
       <c r="Y111">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z111">
         <v>2.83</v>
       </c>
       <c r="AA111">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB111">
         <v>1.67</v>
       </c>
       <c r="AC111">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AD111">
         <v>1.19</v>
@@ -18456,10 +18456,10 @@
         <v>1.03</v>
       </c>
       <c r="AF111">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG111">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18574,55 +18574,55 @@
         <v>5.4</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18900,55 +18900,55 @@
         <v>3.4</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O115">
         <v>3.1</v>
@@ -19063,10 +19063,10 @@
         <v>2.22</v>
       </c>
       <c r="Q115">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S115">
         <v>1.4</v>
@@ -19075,7 +19075,7 @@
         <v>2.44</v>
       </c>
       <c r="U115">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="V115">
         <v>1.3</v>
@@ -19084,34 +19084,34 @@
         <v>1.03</v>
       </c>
       <c r="X115">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y115">
         <v>1.38</v>
       </c>
       <c r="Z115">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="AA115">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AB115">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC115">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="AD115">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE115">
         <v>1.07</v>
       </c>
       <c r="AF115">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG115">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK115">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19220,10 +19220,10 @@
         <v>2.37</v>
       </c>
       <c r="O116">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P116">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -19232,7 +19232,7 @@
         <v>2</v>
       </c>
       <c r="S116">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T116">
         <v>2.69</v>
@@ -19250,7 +19250,7 @@
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z116">
         <v>2.88</v>
@@ -19259,16 +19259,16 @@
         <v>2.19</v>
       </c>
       <c r="AB116">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC116">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD116">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE116">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF116">
         <v>1.83</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK116">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19552,55 +19552,55 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19715,55 +19715,55 @@
         <v>2.17</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20056,16 +20056,16 @@
         <v>2.74</v>
       </c>
       <c r="V121">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W121">
         <v>1.08</v>
       </c>
       <c r="X121">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z121">
         <v>3.5</v>
@@ -20086,7 +20086,7 @@
         <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG121">
         <v>1.72</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="O122">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="P122">
-        <v>3.11</v>
+        <v>4.4</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB122">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AC122">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O138">
         <v>3.1</v>
       </c>
       <c r="P138">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -22818,10 +22818,10 @@
         <v>2.1</v>
       </c>
       <c r="S138">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T138">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U138">
         <v>3.3</v>
@@ -22839,7 +22839,7 @@
         <v>1.44</v>
       </c>
       <c r="Z138">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="AA138">
         <v>2.1</v>
@@ -22848,7 +22848,7 @@
         <v>1.63</v>
       </c>
       <c r="AC138">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AD138">
         <v>1.21</v>
@@ -22860,7 +22860,7 @@
         <v>2</v>
       </c>
       <c r="AG138">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK138">
         <v>1.62</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -635,49 +635,49 @@
         </is>
       </c>
       <c r="N2">
+        <v>2.29</v>
+      </c>
+      <c r="O2">
+        <v>3.35</v>
+      </c>
+      <c r="P2">
+        <v>2.6</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>1.6</v>
+      </c>
+      <c r="AB2">
         <v>2.3</v>
-      </c>
-      <c r="O2">
-        <v>3.3</v>
-      </c>
-      <c r="P2">
-        <v>2.62</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>1.57</v>
-      </c>
-      <c r="AB2">
-        <v>2.35</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="R3">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="V3">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA3">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD3">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA4">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="AB4">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC4">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG4">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="O6">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P6">
-        <v>6.12</v>
+        <v>5.6</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R6">
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
         <v>2.62</v>
@@ -1323,16 +1323,16 @@
         <v>1.38</v>
       </c>
       <c r="Z6">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AA6">
         <v>2.13</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC6">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD6">
         <v>1.19</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="O7">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="R7">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.59</v>
+        <v>3.01</v>
       </c>
       <c r="U7">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
+        <v>1.05</v>
+      </c>
+      <c r="X7">
         <v>1.03</v>
       </c>
-      <c r="X7">
-        <v>1.05</v>
-      </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z7">
-        <v>2.85</v>
+        <v>3.76</v>
       </c>
       <c r="AA7">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AB7">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC7">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK7">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="O8">
         <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q8">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="R8">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U8">
+        <v>3.04</v>
+      </c>
+      <c r="V8">
+        <v>1.33</v>
+      </c>
+      <c r="W8">
+        <v>1.03</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>1.33</v>
+      </c>
+      <c r="Z8">
         <v>2.85</v>
       </c>
-      <c r="V8">
-        <v>1.37</v>
-      </c>
-      <c r="W8">
+      <c r="AA8">
+        <v>2.07</v>
+      </c>
+      <c r="AB8">
+        <v>1.7</v>
+      </c>
+      <c r="AC8">
+        <v>3.94</v>
+      </c>
+      <c r="AD8">
+        <v>1.21</v>
+      </c>
+      <c r="AE8">
         <v>1.04</v>
       </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.27</v>
-      </c>
-      <c r="Z8">
-        <v>3.18</v>
-      </c>
-      <c r="AA8">
-        <v>1.93</v>
-      </c>
-      <c r="AB8">
-        <v>1.76</v>
-      </c>
-      <c r="AC8">
-        <v>3.6</v>
-      </c>
-      <c r="AD8">
-        <v>1.25</v>
-      </c>
-      <c r="AE8">
-        <v>1.06</v>
-      </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG8">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O14">
         <v>3.6</v>
@@ -2606,10 +2606,10 @@
         <v>2.4</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U14">
         <v>2.38</v>
@@ -2618,19 +2618,19 @@
         <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
         <v>2.25</v>
@@ -2639,10 +2639,10 @@
         <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
         <v>1.51</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
+        <v>2.7</v>
+      </c>
+      <c r="R27">
+        <v>2.03</v>
+      </c>
+      <c r="S27">
+        <v>1.5</v>
+      </c>
+      <c r="T27">
+        <v>2.45</v>
+      </c>
+      <c r="U27">
+        <v>3.2</v>
+      </c>
+      <c r="V27">
+        <v>1.25</v>
+      </c>
+      <c r="W27">
+        <v>1.06</v>
+      </c>
+      <c r="X27">
+        <v>1.1</v>
+      </c>
+      <c r="Y27">
+        <v>1.44</v>
+      </c>
+      <c r="Z27">
         <v>2.63</v>
       </c>
-      <c r="R27">
-        <v>1.99</v>
-      </c>
-      <c r="S27">
-        <v>1.41</v>
-      </c>
-      <c r="T27">
-        <v>2.8</v>
-      </c>
-      <c r="U27">
-        <v>2.91</v>
-      </c>
-      <c r="V27">
+      <c r="AA27">
+        <v>2.35</v>
+      </c>
+      <c r="AB27">
+        <v>1.53</v>
+      </c>
+      <c r="AC27">
+        <v>4.44</v>
+      </c>
+      <c r="AD27">
+        <v>1.18</v>
+      </c>
+      <c r="AE27">
+        <v>1.01</v>
+      </c>
+      <c r="AF27">
+        <v>2.02</v>
+      </c>
+      <c r="AG27">
+        <v>1.67</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.36</v>
       </c>
-      <c r="W27">
-        <v>1.03</v>
-      </c>
-      <c r="X27">
-        <v>1.06</v>
-      </c>
-      <c r="Y27">
-        <v>1.31</v>
-      </c>
-      <c r="Z27">
-        <v>3.12</v>
-      </c>
-      <c r="AA27">
-        <v>2.04</v>
-      </c>
-      <c r="AB27">
+      <c r="AK27">
         <v>1.7</v>
-      </c>
-      <c r="AC27">
-        <v>3.5</v>
-      </c>
-      <c r="AD27">
-        <v>1.22</v>
-      </c>
-      <c r="AE27">
-        <v>1.08</v>
-      </c>
-      <c r="AF27">
-        <v>1.83</v>
-      </c>
-      <c r="AG27">
-        <v>1.83</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.27</v>
-      </c>
-      <c r="AK27">
-        <v>1.68</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
+        <v>3.3</v>
+      </c>
+      <c r="Q28">
+        <v>2.63</v>
+      </c>
+      <c r="R28">
+        <v>1.99</v>
+      </c>
+      <c r="S28">
+        <v>1.41</v>
+      </c>
+      <c r="T28">
+        <v>2.8</v>
+      </c>
+      <c r="U28">
+        <v>2.91</v>
+      </c>
+      <c r="V28">
+        <v>1.36</v>
+      </c>
+      <c r="W28">
+        <v>1.03</v>
+      </c>
+      <c r="X28">
+        <v>1.06</v>
+      </c>
+      <c r="Y28">
+        <v>1.31</v>
+      </c>
+      <c r="Z28">
+        <v>3.12</v>
+      </c>
+      <c r="AA28">
+        <v>2.04</v>
+      </c>
+      <c r="AB28">
+        <v>1.7</v>
+      </c>
+      <c r="AC28">
         <v>3.5</v>
       </c>
-      <c r="Q28">
-        <v>2.7</v>
-      </c>
-      <c r="R28">
-        <v>2.03</v>
-      </c>
-      <c r="S28">
-        <v>1.5</v>
-      </c>
-      <c r="T28">
-        <v>2.45</v>
-      </c>
-      <c r="U28">
-        <v>3.2</v>
-      </c>
-      <c r="V28">
-        <v>1.25</v>
-      </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1.1</v>
-      </c>
-      <c r="Y28">
-        <v>1.44</v>
-      </c>
-      <c r="Z28">
-        <v>2.63</v>
-      </c>
-      <c r="AA28">
-        <v>2.35</v>
-      </c>
-      <c r="AB28">
-        <v>1.53</v>
-      </c>
-      <c r="AC28">
-        <v>4.44</v>
-      </c>
       <c r="AD28">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="P30">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="R30">
         <v>2.3</v>
@@ -5229,7 +5229,7 @@
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.2</v>
@@ -5253,10 +5253,10 @@
         <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,43 +5362,43 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>4.1</v>
+        <v>3.67</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
         <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA31">
         <v>1.67</v>
@@ -5407,7 +5407,7 @@
         <v>2.15</v>
       </c>
       <c r="AC31">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD31">
         <v>1.45</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="O33">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="P33">
         <v>3.33</v>
       </c>
       <c r="Q33">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="R33">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5712,7 +5712,7 @@
         <v>2.15</v>
       </c>
       <c r="V33">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
         <v>1.15</v>
@@ -5727,7 +5727,7 @@
         <v>4.7</v>
       </c>
       <c r="AA33">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB33">
         <v>2.4</v>
@@ -5736,10 +5736,10 @@
         <v>2.4</v>
       </c>
       <c r="AD33">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF33">
         <v>1.5</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="Q37">
-        <v>3.86</v>
+        <v>2.27</v>
       </c>
       <c r="R37">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
         <v>2.66</v>
       </c>
       <c r="U37">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="V37">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
+        <v>1.06</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>1.3</v>
+      </c>
+      <c r="Z37">
+        <v>3.35</v>
+      </c>
+      <c r="AA37">
+        <v>1.9</v>
+      </c>
+      <c r="AB37">
+        <v>1.85</v>
+      </c>
+      <c r="AC37">
+        <v>3.36</v>
+      </c>
+      <c r="AD37">
+        <v>1.3</v>
+      </c>
+      <c r="AE37">
         <v>1.05</v>
       </c>
-      <c r="X37">
-        <v>1.06</v>
-      </c>
-      <c r="Y37">
-        <v>1.32</v>
-      </c>
-      <c r="Z37">
-        <v>3.2</v>
-      </c>
-      <c r="AA37">
-        <v>2.05</v>
-      </c>
-      <c r="AB37">
-        <v>1.75</v>
-      </c>
-      <c r="AC37">
-        <v>3.42</v>
-      </c>
-      <c r="AD37">
-        <v>1.25</v>
-      </c>
-      <c r="AE37">
-        <v>1.07</v>
-      </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG37">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q38">
-        <v>2.27</v>
+        <v>3.86</v>
       </c>
       <c r="R38">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T38">
         <v>2.66</v>
       </c>
       <c r="U38">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W38">
+        <v>1.05</v>
+      </c>
+      <c r="X38">
         <v>1.06</v>
       </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
       <c r="Y38">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z38">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA38">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC38">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.48</v>
+        <v>2.46</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P39">
-        <v>6.55</v>
+        <v>2.78</v>
       </c>
       <c r="Q39">
+        <v>3.26</v>
+      </c>
+      <c r="R39">
+        <v>2</v>
+      </c>
+      <c r="S39">
+        <v>1.49</v>
+      </c>
+      <c r="T39">
+        <v>2.53</v>
+      </c>
+      <c r="U39">
+        <v>3.17</v>
+      </c>
+      <c r="V39">
+        <v>1.26</v>
+      </c>
+      <c r="W39">
+        <v>1.03</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
+        <v>1.43</v>
+      </c>
+      <c r="Z39">
+        <v>2.74</v>
+      </c>
+      <c r="AA39">
+        <v>2.35</v>
+      </c>
+      <c r="AB39">
+        <v>1.54</v>
+      </c>
+      <c r="AC39">
+        <v>4.33</v>
+      </c>
+      <c r="AD39">
+        <v>1.14</v>
+      </c>
+      <c r="AE39">
+        <v>1.03</v>
+      </c>
+      <c r="AF39">
         <v>1.95</v>
       </c>
-      <c r="R39">
-        <v>2.2</v>
-      </c>
-      <c r="S39">
-        <v>1.35</v>
-      </c>
-      <c r="T39">
-        <v>2.82</v>
-      </c>
-      <c r="U39">
-        <v>2.78</v>
-      </c>
-      <c r="V39">
-        <v>1.36</v>
-      </c>
-      <c r="W39">
-        <v>1.04</v>
-      </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.24</v>
-      </c>
-      <c r="Z39">
-        <v>3.34</v>
-      </c>
-      <c r="AA39">
-        <v>1.95</v>
-      </c>
-      <c r="AB39">
-        <v>1.83</v>
-      </c>
-      <c r="AC39">
-        <v>3.14</v>
-      </c>
-      <c r="AD39">
-        <v>1.27</v>
-      </c>
-      <c r="AE39">
-        <v>1.11</v>
-      </c>
-      <c r="AF39">
-        <v>2.04</v>
-      </c>
       <c r="AG39">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AK39">
-        <v>2.53</v>
+        <v>1.43</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.46</v>
+        <v>4.65</v>
       </c>
       <c r="O40">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>2.78</v>
+        <v>1.51</v>
       </c>
       <c r="Q40">
-        <v>3.26</v>
+        <v>5</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>2.53</v>
+        <v>3.23</v>
       </c>
       <c r="U40">
-        <v>3.17</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA40">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>4.33</v>
+        <v>2.81</v>
       </c>
       <c r="AD40">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>4.65</v>
+        <v>1.63</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>1.51</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
-        <v>5</v>
+        <v>2.21</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="T41">
-        <v>3.23</v>
+        <v>2.53</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
+        <v>1.33</v>
+      </c>
+      <c r="Z41">
+        <v>2.83</v>
+      </c>
+      <c r="AA41">
+        <v>2.15</v>
+      </c>
+      <c r="AB41">
+        <v>1.66</v>
+      </c>
+      <c r="AC41">
+        <v>3.72</v>
+      </c>
+      <c r="AD41">
         <v>1.2</v>
       </c>
-      <c r="Z41">
-        <v>3.9</v>
-      </c>
-      <c r="AA41">
-        <v>1.71</v>
-      </c>
-      <c r="AB41">
+      <c r="AE41">
+        <v>1.03</v>
+      </c>
+      <c r="AF41">
+        <v>2.05</v>
+      </c>
+      <c r="AG41">
+        <v>1.67</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.22</v>
+      </c>
+      <c r="AK41">
         <v>2.1</v>
-      </c>
-      <c r="AC41">
-        <v>2.81</v>
-      </c>
-      <c r="AD41">
-        <v>1.36</v>
-      </c>
-      <c r="AE41">
-        <v>1.13</v>
-      </c>
-      <c r="AF41">
-        <v>1.8</v>
-      </c>
-      <c r="AG41">
-        <v>1.93</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.21</v>
-      </c>
-      <c r="AK41">
-        <v>1.08</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P42">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q42">
-        <v>2.21</v>
+        <v>3.3</v>
       </c>
       <c r="R42">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="S42">
         <v>1.43</v>
@@ -7176,43 +7176,43 @@
         <v>2.53</v>
       </c>
       <c r="U42">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="V42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z42">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA42">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB42">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC42">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="AD42">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE42">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG42">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK42">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="O43">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>2.6</v>
+        <v>6.55</v>
       </c>
       <c r="Q43">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="R43">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="U43">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
         <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z43">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AA43">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB43">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC43">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="AG43">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK43">
-        <v>1.4</v>
+        <v>2.53</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="O44">
         <v>3.5</v>
@@ -7502,10 +7502,10 @@
         <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V44">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
         <v>1.08</v>
@@ -7517,7 +7517,7 @@
         <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>3.9</v>
+        <v>4.24</v>
       </c>
       <c r="AA44">
         <v>1.76</v>
@@ -7526,7 +7526,7 @@
         <v>2.12</v>
       </c>
       <c r="AC44">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="AD44">
         <v>1.42</v>
@@ -7535,7 +7535,7 @@
         <v>1.11</v>
       </c>
       <c r="AF44">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
         <v>2.28</v>
@@ -8951,31 +8951,31 @@
         <v>2.3</v>
       </c>
       <c r="O53">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q53">
         <v>2.89</v>
       </c>
       <c r="R53">
-        <v>2.39</v>
+        <v>2.22</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U53">
         <v>2.4</v>
       </c>
       <c r="V53">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X53">
         <v>1.02</v>
@@ -8990,16 +8990,16 @@
         <v>1.61</v>
       </c>
       <c r="AB53">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC53">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AD53">
         <v>1.45</v>
       </c>
       <c r="AE53">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF53">
         <v>1.51</v>
@@ -9123,22 +9123,22 @@
         <v>2</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S54">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T54">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V54">
         <v>1.64</v>
       </c>
       <c r="W54">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X54">
         <v>1.02</v>
@@ -9147,10 +9147,10 @@
         <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA54">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB54">
         <v>2.49</v>
@@ -9162,13 +9162,13 @@
         <v>1.66</v>
       </c>
       <c r="AE54">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF54">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG54">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="O56">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P56">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Q56">
         <v>3.64</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O69">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P69">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q69">
         <v>4.8</v>
@@ -11577,7 +11577,7 @@
         <v>3.58</v>
       </c>
       <c r="U69">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V69">
         <v>1.67</v>
@@ -11592,19 +11592,19 @@
         <v>1.11</v>
       </c>
       <c r="Z69">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA69">
         <v>1.5</v>
       </c>
       <c r="AB69">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC69">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AD69">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE69">
         <v>1.22</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AK69">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="P75">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q75">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R75">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S75">
         <v>1.36</v>
@@ -12561,16 +12561,16 @@
         <v>1.39</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z75">
-        <v>3.3</v>
+        <v>3.57</v>
       </c>
       <c r="AA75">
         <v>1.95</v>
@@ -12579,10 +12579,10 @@
         <v>1.85</v>
       </c>
       <c r="AC75">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="AD75">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE75">
         <v>1.09</v>
@@ -12591,7 +12591,7 @@
         <v>1.7</v>
       </c>
       <c r="AG75">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="O83">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="P83">
-        <v>4.17</v>
+        <v>6.35</v>
       </c>
       <c r="Q83">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="R83">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S83">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T83">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U83">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="V83">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W83">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z83">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AA83">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB83">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC83">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AD83">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE83">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG83">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK83">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="R84">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="S84">
+        <v>1.45</v>
+      </c>
+      <c r="T84">
+        <v>2.55</v>
+      </c>
+      <c r="U84">
+        <v>3.28</v>
+      </c>
+      <c r="V84">
         <v>1.29</v>
       </c>
-      <c r="T84">
-        <v>2.97</v>
-      </c>
-      <c r="U84">
-        <v>2.46</v>
-      </c>
-      <c r="V84">
-        <v>1.45</v>
-      </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="Z84">
-        <v>3.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA84">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="AB84">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC84">
-        <v>2.59</v>
+        <v>4.3</v>
       </c>
       <c r="AD84">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AE84">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AF84">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG84">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK84">
-        <v>2.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q85">
-        <v>2.72</v>
+        <v>2.25</v>
       </c>
       <c r="R85">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S85">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
         <v>2.88</v>
       </c>
       <c r="U85">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="V85">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W85">
         <v>1.07</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA85">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AB85">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC85">
-        <v>3.28</v>
+        <v>2.81</v>
       </c>
       <c r="AD85">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE85">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF85">
         <v>1.7</v>
       </c>
       <c r="AG85">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G86">
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
+        <v>2.72</v>
+      </c>
+      <c r="R86">
+        <v>2.13</v>
+      </c>
+      <c r="S86">
+        <v>1.33</v>
+      </c>
+      <c r="T86">
         <v>2.88</v>
       </c>
-      <c r="R86">
-        <v>1.91</v>
-      </c>
-      <c r="S86">
-        <v>1.45</v>
-      </c>
-      <c r="T86">
-        <v>2.55</v>
-      </c>
       <c r="U86">
+        <v>2.75</v>
+      </c>
+      <c r="V86">
+        <v>1.36</v>
+      </c>
+      <c r="W86">
+        <v>1.07</v>
+      </c>
+      <c r="X86">
+        <v>1</v>
+      </c>
+      <c r="Y86">
+        <v>1.24</v>
+      </c>
+      <c r="Z86">
+        <v>3.34</v>
+      </c>
+      <c r="AA86">
+        <v>1.88</v>
+      </c>
+      <c r="AB86">
+        <v>1.81</v>
+      </c>
+      <c r="AC86">
         <v>3.28</v>
       </c>
-      <c r="V86">
-        <v>1.29</v>
-      </c>
-      <c r="W86">
-        <v>1.03</v>
-      </c>
-      <c r="X86">
-        <v>1.02</v>
-      </c>
-      <c r="Y86">
-        <v>1.37</v>
-      </c>
-      <c r="Z86">
-        <v>2.66</v>
-      </c>
-      <c r="AA86">
-        <v>2.37</v>
-      </c>
-      <c r="AB86">
-        <v>1.53</v>
-      </c>
-      <c r="AC86">
-        <v>4.3</v>
-      </c>
       <c r="AD86">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE86">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF86">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG86">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O87">
         <v>2.5</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK87">
         <v>1.36</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="O93">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="P93">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -15492,7 +15492,7 @@
         <v>4.33</v>
       </c>
       <c r="V93">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W93">
         <v>1.02</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AK93">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,22 +15631,22 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O94">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="P94">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q94">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="R94">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="S94">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T94">
         <v>2.25</v>
@@ -15655,10 +15655,10 @@
         <v>3.78</v>
       </c>
       <c r="V94">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W94">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
         <v>1.09</v>
@@ -15673,13 +15673,13 @@
         <v>2.69</v>
       </c>
       <c r="AB94">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC94">
         <v>5.25</v>
       </c>
       <c r="AD94">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE94">
         <v>1.03</v>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O95">
         <v>2.8</v>
@@ -15818,31 +15818,31 @@
         <v>3.82</v>
       </c>
       <c r="V95">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W95">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X95">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y95">
         <v>1.53</v>
       </c>
       <c r="Z95">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AA95">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AB95">
         <v>1.38</v>
       </c>
       <c r="AC95">
-        <v>5.45</v>
+        <v>5.65</v>
       </c>
       <c r="AD95">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE95">
         <v>1.04</v>
@@ -15851,7 +15851,7 @@
         <v>2.16</v>
       </c>
       <c r="AG95">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15957,22 +15957,22 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.01</v>
+        <v>3.4</v>
       </c>
       <c r="O96">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="P96">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q96">
         <v>5.2</v>
       </c>
       <c r="R96">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="S96">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="T96">
         <v>2.45</v>
@@ -15996,7 +15996,7 @@
         <v>2.36</v>
       </c>
       <c r="AA96">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AB96">
         <v>1.41</v>
@@ -16014,7 +16014,7 @@
         <v>2.17</v>
       </c>
       <c r="AG96">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16129,10 +16129,10 @@
         <v>2.7</v>
       </c>
       <c r="Q97">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="R97">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S97">
         <v>1.69</v>
@@ -16141,7 +16141,7 @@
         <v>2.04</v>
       </c>
       <c r="U97">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="V97">
         <v>1.15</v>
@@ -16156,7 +16156,7 @@
         <v>1.5</v>
       </c>
       <c r="Z97">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AA97">
         <v>2.97</v>
@@ -16174,7 +16174,7 @@
         <v>1.02</v>
       </c>
       <c r="AF97">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="AG97">
         <v>1.5</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AK97">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -18076,22 +18076,22 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O109">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P109">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="Q109">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R109">
         <v>2</v>
       </c>
       <c r="S109">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="T109">
         <v>2.1</v>
@@ -18115,7 +18115,7 @@
         <v>2.13</v>
       </c>
       <c r="AA109">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="AB109">
         <v>1.34</v>
@@ -18133,7 +18133,7 @@
         <v>2.78</v>
       </c>
       <c r="AG109">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18239,16 +18239,16 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="O110">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="P110">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q110">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="R110">
         <v>1.93</v>
@@ -18257,46 +18257,46 @@
         <v>1.64</v>
       </c>
       <c r="T110">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U110">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="V110">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W110">
         <v>1.03</v>
       </c>
       <c r="X110">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y110">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z110">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AA110">
         <v>2.87</v>
       </c>
       <c r="AB110">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC110">
         <v>5.2</v>
       </c>
       <c r="AD110">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE110">
         <v>1.03</v>
       </c>
       <c r="AF110">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AG110">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.36</v>
       </c>
       <c r="AK110">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="O113">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P113">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q113">
         <v>4</v>
@@ -18758,28 +18758,28 @@
         <v>1.07</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z113">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="AA113">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB113">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC113">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD113">
         <v>1.37</v>
       </c>
       <c r="AE113">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF113">
         <v>1.7</v>
@@ -19380,58 +19380,58 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O117">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P117">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="Q117">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="R117">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S117">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T117">
         <v>3.6</v>
       </c>
       <c r="U117">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="V117">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="W117">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X117">
         <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z117">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AA117">
         <v>1.46</v>
       </c>
       <c r="AB117">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AC117">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AD117">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AE117">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF117">
         <v>1.49</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK117">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O120">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="P120">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="Q120">
         <v>3.3</v>
@@ -19884,40 +19884,40 @@
         <v>1.95</v>
       </c>
       <c r="S120">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T120">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U120">
         <v>3.2</v>
       </c>
       <c r="V120">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W120">
         <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y120">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z120">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA120">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB120">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC120">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD120">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE120">
         <v>1.04</v>
@@ -19926,7 +19926,7 @@
         <v>1.85</v>
       </c>
       <c r="AG120">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20361,28 +20361,28 @@
         <v>2.08</v>
       </c>
       <c r="O123">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P123">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="Q123">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="R123">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S123">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T123">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U123">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="V123">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W123">
         <v>1.07</v>
@@ -20391,28 +20391,28 @@
         <v>1</v>
       </c>
       <c r="Y123">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z123">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA123">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB123">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC123">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="AD123">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE123">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG123">
         <v>2</v>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK123">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="O124">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P124">
-        <v>5.11</v>
+        <v>4.65</v>
       </c>
       <c r="Q124">
         <v>2.08</v>
@@ -20560,7 +20560,7 @@
         <v>3.8</v>
       </c>
       <c r="AA124">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB124">
         <v>2.07</v>
@@ -20569,7 +20569,7 @@
         <v>2.7</v>
       </c>
       <c r="AD124">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE124">
         <v>1.14</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK124">
         <v>2.2</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="O125">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P125">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q125">
         <v>4</v>
@@ -20726,7 +20726,7 @@
         <v>1.9</v>
       </c>
       <c r="AB125">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC125">
         <v>3.14</v>
@@ -20735,7 +20735,7 @@
         <v>1.31</v>
       </c>
       <c r="AE125">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF125">
         <v>1.75</v>
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O126">
         <v>3.19</v>
@@ -20856,25 +20856,25 @@
         <v>2.7</v>
       </c>
       <c r="Q126">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R126">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="S126">
         <v>1.33</v>
       </c>
       <c r="T126">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U126">
         <v>2.56</v>
       </c>
       <c r="V126">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W126">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X126">
         <v>1.01</v>
@@ -20886,13 +20886,13 @@
         <v>3.8</v>
       </c>
       <c r="AA126">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB126">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC126">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AD126">
         <v>1.33</v>
@@ -20901,10 +20901,10 @@
         <v>1.09</v>
       </c>
       <c r="AF126">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG126">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK126">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21013,10 +21013,10 @@
         <v>1.33</v>
       </c>
       <c r="O127">
-        <v>4.9</v>
+        <v>4.35</v>
       </c>
       <c r="P127">
-        <v>6.8</v>
+        <v>5.15</v>
       </c>
       <c r="Q127">
         <v>1.8</v>
@@ -21028,7 +21028,7 @@
         <v>1.2</v>
       </c>
       <c r="T127">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="U127">
         <v>2.1</v>
@@ -21037,16 +21037,16 @@
         <v>1.67</v>
       </c>
       <c r="W127">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X127">
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z127">
-        <v>5.45</v>
+        <v>5.19</v>
       </c>
       <c r="AA127">
         <v>1.4</v>
@@ -21176,10 +21176,10 @@
         <v>2.15</v>
       </c>
       <c r="O128">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P128">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB128">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -21339,7 +21339,7 @@
         <v>1.72</v>
       </c>
       <c r="O129">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P129">
         <v>4.33</v>
@@ -21363,10 +21363,10 @@
         <v>1.55</v>
       </c>
       <c r="W129">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X129">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
         <v>1.18</v>
@@ -21387,7 +21387,7 @@
         <v>1.55</v>
       </c>
       <c r="AE129">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF129">
         <v>1.55</v>
@@ -21409,7 +21409,7 @@
         <v>1.22</v>
       </c>
       <c r="AK129">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,31 +21499,31 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O130">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="P130">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q130">
         <v>3.35</v>
       </c>
       <c r="R130">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S130">
         <v>1.36</v>
       </c>
       <c r="T130">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="U130">
         <v>2.62</v>
       </c>
       <c r="V130">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W130">
         <v>1.08</v>
@@ -21535,28 +21535,28 @@
         <v>1.28</v>
       </c>
       <c r="Z130">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AA130">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB130">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC130">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD130">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE130">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF130">
         <v>1.65</v>
       </c>
       <c r="AG130">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21662,19 +21662,19 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O131">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P131">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="Q131">
         <v>2.25</v>
       </c>
       <c r="R131">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S131">
         <v>1.23</v>
@@ -21698,10 +21698,10 @@
         <v>1.13</v>
       </c>
       <c r="Z131">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA131">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AB131">
         <v>2.32</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK131">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O132">
         <v>3.9</v>
@@ -21846,13 +21846,13 @@
         <v>4.6</v>
       </c>
       <c r="U132">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V132">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W132">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X132">
         <v>0</v>
@@ -21870,19 +21870,19 @@
         <v>3.4</v>
       </c>
       <c r="AC132">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AD132">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AE132">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AF132">
         <v>1.29</v>
       </c>
       <c r="AG132">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK132">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O133">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P133">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="Q133">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="R133">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="S133">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T133">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U133">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V133">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W133">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X133">
         <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z133">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA133">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AB133">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AC133">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD133">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AE133">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF133">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AG133">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK133">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="O134">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P134">
-        <v>3.95</v>
+        <v>2.81</v>
       </c>
       <c r="Q134">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="R134">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="S134">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T134">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="U134">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="V134">
+        <v>1.88</v>
+      </c>
+      <c r="W134">
+        <v>1.22</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>1.03</v>
+      </c>
+      <c r="Z134">
+        <v>7.5</v>
+      </c>
+      <c r="AA134">
+        <v>1.32</v>
+      </c>
+      <c r="AB134">
+        <v>3.4</v>
+      </c>
+      <c r="AC134">
         <v>1.8</v>
       </c>
-      <c r="W134">
-        <v>1.19</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>1.11</v>
-      </c>
-      <c r="Z134">
-        <v>6.8</v>
-      </c>
-      <c r="AA134">
-        <v>1.38</v>
-      </c>
-      <c r="AB134">
-        <v>3.1</v>
-      </c>
-      <c r="AC134">
-        <v>1.85</v>
-      </c>
       <c r="AD134">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AE134">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AF134">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AG134">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK134">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="O135">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P135">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="Q135">
         <v>2.48</v>
@@ -22329,7 +22329,7 @@
         <v>2.22</v>
       </c>
       <c r="S135">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
         <v>3.2</v>
@@ -22341,7 +22341,7 @@
         <v>1.48</v>
       </c>
       <c r="W135">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
         <v>1.03</v>
@@ -22353,10 +22353,10 @@
         <v>3.98</v>
       </c>
       <c r="AA135">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB135">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AC135">
         <v>2.59</v>
@@ -22365,13 +22365,13 @@
         <v>1.39</v>
       </c>
       <c r="AE135">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF135">
         <v>1.57</v>
       </c>
       <c r="AG135">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22489,10 +22489,10 @@
         <v>3.6</v>
       </c>
       <c r="R136">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T136">
         <v>2.96</v>
@@ -22504,13 +22504,13 @@
         <v>1.43</v>
       </c>
       <c r="W136">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
         <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z136">
         <v>3.5</v>
@@ -22547,7 +22547,7 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
         <v>1.3</v>
@@ -22643,7 +22643,7 @@
         <v>2.05</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P137">
         <v>2.93</v>
@@ -22652,7 +22652,7 @@
         <v>2.57</v>
       </c>
       <c r="R137">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S137">
         <v>1.34</v>
@@ -22667,16 +22667,16 @@
         <v>1.44</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X137">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
         <v>1.28</v>
       </c>
       <c r="Z137">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA137">
         <v>1.9</v>
@@ -22694,7 +22694,7 @@
         <v>1.07</v>
       </c>
       <c r="AF137">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG137">
         <v>2</v>
@@ -22975,55 +22975,55 @@
         <v>1.45</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA139">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AB139">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23129,19 +23129,19 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="O140">
-        <v>3.4</v>
+        <v>4.12</v>
       </c>
       <c r="P140">
         <v>2.1</v>
       </c>
       <c r="Q140">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="R140">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S140">
         <v>1.29</v>
@@ -23202,7 +23202,7 @@
         <v>1.21</v>
       </c>
       <c r="AK140">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23307,16 +23307,16 @@
         <v>2.55</v>
       </c>
       <c r="S141">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T141">
         <v>3.7</v>
       </c>
       <c r="U141">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V141">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W141">
         <v>1.18</v>
@@ -23325,7 +23325,7 @@
         <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z141">
         <v>5.36</v>
@@ -23334,7 +23334,7 @@
         <v>1.5</v>
       </c>
       <c r="AB141">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AC141">
         <v>2.18</v>
@@ -23343,7 +23343,7 @@
         <v>1.62</v>
       </c>
       <c r="AE141">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF141">
         <v>1.44</v>
@@ -23458,10 +23458,10 @@
         <v>2.05</v>
       </c>
       <c r="O142">
-        <v>3.7</v>
+        <v>4.12</v>
       </c>
       <c r="P142">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q142">
         <v>2.5</v>
@@ -23473,7 +23473,7 @@
         <v>1.25</v>
       </c>
       <c r="T142">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U142">
         <v>2.21</v>
@@ -23503,10 +23503,10 @@
         <v>2.33</v>
       </c>
       <c r="AD142">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE142">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF142">
         <v>1.44</v>
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="O143">
         <v>4.4</v>
@@ -23633,16 +23633,16 @@
         <v>2.62</v>
       </c>
       <c r="S143">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T143">
         <v>4.2</v>
       </c>
       <c r="U143">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V143">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W143">
         <v>1.17</v>
@@ -23657,16 +23657,16 @@
         <v>6</v>
       </c>
       <c r="AA143">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB143">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AC143">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD143">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE143">
         <v>1.26</v>
@@ -23675,7 +23675,7 @@
         <v>1.5</v>
       </c>
       <c r="AG143">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK143">
         <v>2.4</v>
@@ -23790,55 +23790,55 @@
         <v>0</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24107,19 +24107,19 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="O146">
         <v>3.45</v>
       </c>
       <c r="P146">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q146">
         <v>3.3</v>
       </c>
       <c r="R146">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S146">
         <v>1.31</v>
@@ -24128,7 +24128,7 @@
         <v>3.02</v>
       </c>
       <c r="U146">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V146">
         <v>1.43</v>
@@ -24140,31 +24140,31 @@
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z146">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA146">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB146">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC146">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD146">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE146">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF146">
         <v>1.58</v>
       </c>
       <c r="AG146">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK146">
         <v>1.37</v>
@@ -24273,10 +24273,10 @@
         <v>1.7</v>
       </c>
       <c r="O147">
-        <v>4.36</v>
+        <v>4.26</v>
       </c>
       <c r="P147">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="Q147">
         <v>2.2</v>
@@ -24285,7 +24285,7 @@
         <v>2.35</v>
       </c>
       <c r="S147">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T147">
         <v>3.4</v>
@@ -24324,10 +24324,10 @@
         <v>1.2</v>
       </c>
       <c r="AF147">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG147">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O148">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P148">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q148">
         <v>2.9</v>
@@ -24454,22 +24454,22 @@
         <v>2.88</v>
       </c>
       <c r="U148">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="V148">
         <v>1.35</v>
       </c>
       <c r="W148">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X148">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y148">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z148">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA148">
         <v>2</v>
@@ -24478,16 +24478,16 @@
         <v>1.76</v>
       </c>
       <c r="AC148">
-        <v>3.57</v>
+        <v>3.34</v>
       </c>
       <c r="AD148">
         <v>1.27</v>
       </c>
       <c r="AE148">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF148">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG148">
         <v>2</v>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK148">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24611,16 +24611,16 @@
         <v>2.19</v>
       </c>
       <c r="S149">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T149">
         <v>3.12</v>
       </c>
       <c r="U149">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="V149">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W149">
         <v>1.11</v>
@@ -24641,7 +24641,7 @@
         <v>1.96</v>
       </c>
       <c r="AC149">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD149">
         <v>1.34</v>
@@ -24653,7 +24653,7 @@
         <v>1.61</v>
       </c>
       <c r="AG149">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24759,19 +24759,19 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O150">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P150">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="Q150">
         <v>3.08</v>
       </c>
       <c r="R150">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S150">
         <v>1.3</v>
@@ -24792,28 +24792,28 @@
         <v>1</v>
       </c>
       <c r="Y150">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z150">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="AA150">
         <v>1.72</v>
       </c>
       <c r="AB150">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AC150">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="AD150">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE150">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF150">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG150">
         <v>2.3</v>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK150">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24928,10 +24928,10 @@
         <v>3.7</v>
       </c>
       <c r="P151">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="Q151">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="R151">
         <v>2.45</v>
@@ -24955,7 +24955,7 @@
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z151">
         <v>5</v>
@@ -24964,13 +24964,13 @@
         <v>1.5</v>
       </c>
       <c r="AB151">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AC151">
         <v>2.31</v>
       </c>
       <c r="AD151">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE151">
         <v>1.2</v>
@@ -25085,16 +25085,16 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O152">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P152">
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="Q152">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R152">
         <v>2.45</v>
@@ -25112,7 +25112,7 @@
         <v>1.7</v>
       </c>
       <c r="W152">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X152">
         <v>1.01</v>
@@ -25121,7 +25121,7 @@
         <v>1.13</v>
       </c>
       <c r="Z152">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA152">
         <v>1.41</v>
@@ -25136,7 +25136,7 @@
         <v>1.64</v>
       </c>
       <c r="AE152">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF152">
         <v>1.4</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
+        <v>3.3</v>
+      </c>
+      <c r="Q27">
+        <v>2.63</v>
+      </c>
+      <c r="R27">
+        <v>1.99</v>
+      </c>
+      <c r="S27">
+        <v>1.41</v>
+      </c>
+      <c r="T27">
+        <v>2.8</v>
+      </c>
+      <c r="U27">
+        <v>2.91</v>
+      </c>
+      <c r="V27">
+        <v>1.36</v>
+      </c>
+      <c r="W27">
+        <v>1.03</v>
+      </c>
+      <c r="X27">
+        <v>1.06</v>
+      </c>
+      <c r="Y27">
+        <v>1.31</v>
+      </c>
+      <c r="Z27">
+        <v>3.12</v>
+      </c>
+      <c r="AA27">
+        <v>2.04</v>
+      </c>
+      <c r="AB27">
+        <v>1.7</v>
+      </c>
+      <c r="AC27">
         <v>3.5</v>
       </c>
-      <c r="Q27">
-        <v>2.7</v>
-      </c>
-      <c r="R27">
-        <v>2.03</v>
-      </c>
-      <c r="S27">
-        <v>1.5</v>
-      </c>
-      <c r="T27">
-        <v>2.45</v>
-      </c>
-      <c r="U27">
-        <v>3.2</v>
-      </c>
-      <c r="V27">
-        <v>1.25</v>
-      </c>
-      <c r="W27">
-        <v>1.06</v>
-      </c>
-      <c r="X27">
-        <v>1.1</v>
-      </c>
-      <c r="Y27">
-        <v>1.44</v>
-      </c>
-      <c r="Z27">
-        <v>2.63</v>
-      </c>
-      <c r="AA27">
-        <v>2.35</v>
-      </c>
-      <c r="AB27">
-        <v>1.53</v>
-      </c>
-      <c r="AC27">
-        <v>4.44</v>
-      </c>
       <c r="AD27">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P28">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q28">
+        <v>2.7</v>
+      </c>
+      <c r="R28">
+        <v>2.03</v>
+      </c>
+      <c r="S28">
+        <v>1.5</v>
+      </c>
+      <c r="T28">
+        <v>2.45</v>
+      </c>
+      <c r="U28">
+        <v>3.2</v>
+      </c>
+      <c r="V28">
+        <v>1.25</v>
+      </c>
+      <c r="W28">
+        <v>1.06</v>
+      </c>
+      <c r="X28">
+        <v>1.1</v>
+      </c>
+      <c r="Y28">
+        <v>1.44</v>
+      </c>
+      <c r="Z28">
         <v>2.63</v>
       </c>
-      <c r="R28">
-        <v>1.99</v>
-      </c>
-      <c r="S28">
-        <v>1.41</v>
-      </c>
-      <c r="T28">
-        <v>2.8</v>
-      </c>
-      <c r="U28">
-        <v>2.91</v>
-      </c>
-      <c r="V28">
+      <c r="AA28">
+        <v>2.35</v>
+      </c>
+      <c r="AB28">
+        <v>1.53</v>
+      </c>
+      <c r="AC28">
+        <v>4.44</v>
+      </c>
+      <c r="AD28">
+        <v>1.18</v>
+      </c>
+      <c r="AE28">
+        <v>1.01</v>
+      </c>
+      <c r="AF28">
+        <v>2.02</v>
+      </c>
+      <c r="AG28">
+        <v>1.67</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.36</v>
       </c>
-      <c r="W28">
-        <v>1.03</v>
-      </c>
-      <c r="X28">
-        <v>1.06</v>
-      </c>
-      <c r="Y28">
-        <v>1.31</v>
-      </c>
-      <c r="Z28">
-        <v>3.12</v>
-      </c>
-      <c r="AA28">
-        <v>2.04</v>
-      </c>
-      <c r="AB28">
+      <c r="AK28">
         <v>1.7</v>
-      </c>
-      <c r="AC28">
-        <v>3.5</v>
-      </c>
-      <c r="AD28">
-        <v>1.22</v>
-      </c>
-      <c r="AE28">
-        <v>1.08</v>
-      </c>
-      <c r="AF28">
-        <v>1.83</v>
-      </c>
-      <c r="AG28">
-        <v>1.83</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.27</v>
-      </c>
-      <c r="AK28">
-        <v>1.68</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q37">
-        <v>2.27</v>
+        <v>3.86</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T37">
         <v>2.66</v>
       </c>
       <c r="U37">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W37">
+        <v>1.05</v>
+      </c>
+      <c r="X37">
         <v>1.06</v>
       </c>
-      <c r="X37">
-        <v>1.03</v>
-      </c>
       <c r="Y37">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA37">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC37">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="AD37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="O38">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="Q38">
-        <v>3.86</v>
+        <v>2.27</v>
       </c>
       <c r="R38">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S38">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
         <v>2.66</v>
       </c>
       <c r="U38">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="V38">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.3</v>
+      </c>
+      <c r="Z38">
+        <v>3.35</v>
+      </c>
+      <c r="AA38">
+        <v>1.9</v>
+      </c>
+      <c r="AB38">
+        <v>1.85</v>
+      </c>
+      <c r="AC38">
+        <v>3.36</v>
+      </c>
+      <c r="AD38">
+        <v>1.3</v>
+      </c>
+      <c r="AE38">
         <v>1.05</v>
       </c>
-      <c r="X38">
-        <v>1.06</v>
-      </c>
-      <c r="Y38">
-        <v>1.32</v>
-      </c>
-      <c r="Z38">
-        <v>3.2</v>
-      </c>
-      <c r="AA38">
-        <v>2.05</v>
-      </c>
-      <c r="AB38">
-        <v>1.75</v>
-      </c>
-      <c r="AC38">
-        <v>3.42</v>
-      </c>
-      <c r="AD38">
-        <v>1.25</v>
-      </c>
-      <c r="AE38">
-        <v>1.07</v>
-      </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG38">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK38">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="O42">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>2.6</v>
+        <v>6.55</v>
       </c>
       <c r="Q42">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="R42">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="U42">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
         <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z42">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AA42">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB42">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC42">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD42">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="AG42">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>1.4</v>
+        <v>2.53</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="P43">
-        <v>6.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q43">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T43">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="U43">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
         <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AA43">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB43">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC43">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AG43">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>2.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="O96">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="P96">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q96">
-        <v>5.2</v>
+        <v>3.74</v>
       </c>
       <c r="R96">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="S96">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="T96">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="U96">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="V96">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W96">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X96">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y96">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z96">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AA96">
-        <v>2.48</v>
+        <v>2.97</v>
       </c>
       <c r="AB96">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AC96">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD96">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AE96">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF96">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AG96">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AK96">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O97">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="P97">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q97">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="R97">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="S97">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="T97">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="U97">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="V97">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W97">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y97">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z97">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AA97">
-        <v>2.97</v>
+        <v>2.48</v>
       </c>
       <c r="AB97">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AC97">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD97">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AE97">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF97">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AG97">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="O129">
-        <v>3.9</v>
+        <v>3.41</v>
       </c>
       <c r="P129">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q129">
-        <v>2.15</v>
+        <v>3.35</v>
       </c>
       <c r="R129">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S129">
+        <v>1.36</v>
+      </c>
+      <c r="T129">
+        <v>2.77</v>
+      </c>
+      <c r="U129">
+        <v>2.62</v>
+      </c>
+      <c r="V129">
+        <v>1.4</v>
+      </c>
+      <c r="W129">
+        <v>1.08</v>
+      </c>
+      <c r="X129">
+        <v>1.03</v>
+      </c>
+      <c r="Y129">
+        <v>1.28</v>
+      </c>
+      <c r="Z129">
+        <v>3.7</v>
+      </c>
+      <c r="AA129">
+        <v>1.89</v>
+      </c>
+      <c r="AB129">
+        <v>1.94</v>
+      </c>
+      <c r="AC129">
+        <v>3.05</v>
+      </c>
+      <c r="AD129">
         <v>1.29</v>
       </c>
-      <c r="T129">
-        <v>3.6</v>
-      </c>
-      <c r="U129">
-        <v>2.3</v>
-      </c>
-      <c r="V129">
-        <v>1.55</v>
-      </c>
-      <c r="W129">
-        <v>1.14</v>
-      </c>
-      <c r="X129">
-        <v>1.01</v>
-      </c>
-      <c r="Y129">
-        <v>1.18</v>
-      </c>
-      <c r="Z129">
-        <v>4.5</v>
-      </c>
-      <c r="AA129">
-        <v>1.58</v>
-      </c>
-      <c r="AB129">
-        <v>2.17</v>
-      </c>
-      <c r="AC129">
-        <v>2.6</v>
-      </c>
-      <c r="AD129">
-        <v>1.55</v>
-      </c>
       <c r="AE129">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF129">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG129">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK129">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="O130">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="P130">
-        <v>2.2</v>
+        <v>3.98</v>
       </c>
       <c r="Q130">
-        <v>3.35</v>
+        <v>2.25</v>
       </c>
       <c r="R130">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="S130">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T130">
-        <v>2.77</v>
+        <v>3.58</v>
       </c>
       <c r="U130">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="V130">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W130">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X130">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y130">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>3.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA130">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AB130">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="AC130">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD130">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AE130">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF130">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG130">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK130">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,80 +21662,80 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O131">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P131">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="Q131">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="R131">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="S131">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="T131">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="U131">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="V131">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="W131">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X131">
         <v>0</v>
       </c>
       <c r="Y131">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z131">
-        <v>4.65</v>
+        <v>8</v>
       </c>
       <c r="AA131">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AB131">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="AC131">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AD131">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="AE131">
+        <v>1.46</v>
+      </c>
+      <c r="AF131">
+        <v>1.29</v>
+      </c>
+      <c r="AG131">
+        <v>3.2</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
         <v>1.2</v>
       </c>
-      <c r="AF131">
-        <v>1.5</v>
-      </c>
-      <c r="AG131">
-        <v>2.4</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>1.23</v>
-      </c>
       <c r="AK131">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G132">
@@ -21828,61 +21828,61 @@
         <v>2</v>
       </c>
       <c r="O132">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P132">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="Q132">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="R132">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="S132">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T132">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="U132">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V132">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W132">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X132">
         <v>0</v>
       </c>
       <c r="Y132">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z132">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA132">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AB132">
         <v>3.4</v>
       </c>
       <c r="AC132">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AD132">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AE132">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AF132">
         <v>1.29</v>
       </c>
       <c r="AG132">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK132">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O133">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P133">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q133">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="R133">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S133">
+        <v>1.29</v>
+      </c>
+      <c r="T133">
+        <v>3.6</v>
+      </c>
+      <c r="U133">
+        <v>2.3</v>
+      </c>
+      <c r="V133">
+        <v>1.55</v>
+      </c>
+      <c r="W133">
+        <v>1.14</v>
+      </c>
+      <c r="X133">
+        <v>1.01</v>
+      </c>
+      <c r="Y133">
         <v>1.18</v>
       </c>
-      <c r="T133">
-        <v>4.6</v>
-      </c>
-      <c r="U133">
-        <v>1.91</v>
-      </c>
-      <c r="V133">
-        <v>1.8</v>
-      </c>
-      <c r="W133">
-        <v>1.19</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>1.07</v>
-      </c>
       <c r="Z133">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA133">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AB133">
-        <v>3.04</v>
+        <v>2.17</v>
       </c>
       <c r="AC133">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AD133">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AE133">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AF133">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AG133">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK133">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O134">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P134">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="Q134">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="R134">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="S134">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T134">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U134">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V134">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W134">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X134">
         <v>0</v>
       </c>
       <c r="Y134">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z134">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA134">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AB134">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AC134">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD134">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AE134">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF134">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AG134">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK134">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AL134">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="R7">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>3.01</v>
+        <v>2.59</v>
       </c>
       <c r="U7">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
+        <v>1.03</v>
+      </c>
+      <c r="X7">
         <v>1.05</v>
       </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z7">
-        <v>3.76</v>
+        <v>2.85</v>
       </c>
       <c r="AA7">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AB7">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AG7">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="P8">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q8">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>2.59</v>
+        <v>3.01</v>
       </c>
       <c r="U8">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
         <v>1.03</v>
       </c>
-      <c r="X8">
-        <v>1.05</v>
-      </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>2.85</v>
+        <v>3.76</v>
       </c>
       <c r="AA8">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC8">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="AD8">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK8">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="O15">
-        <v>2.98</v>
+        <v>3.26</v>
       </c>
       <c r="P15">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="R15">
         <v>2.02</v>
       </c>
       <c r="S15">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T15">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
         <v>1.03</v>
@@ -2790,10 +2790,10 @@
         <v>1.35</v>
       </c>
       <c r="Z15">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="AA15">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB15">
         <v>1.75</v>
@@ -2802,7 +2802,7 @@
         <v>3.94</v>
       </c>
       <c r="AD15">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
+        <v>1.92</v>
+      </c>
+      <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26">
+        <v>3.5</v>
+      </c>
+      <c r="Q26">
+        <v>2.7</v>
+      </c>
+      <c r="R26">
+        <v>2.03</v>
+      </c>
+      <c r="S26">
+        <v>1.5</v>
+      </c>
+      <c r="T26">
+        <v>2.45</v>
+      </c>
+      <c r="U26">
+        <v>3.2</v>
+      </c>
+      <c r="V26">
         <v>1.25</v>
       </c>
-      <c r="O26">
-        <v>5</v>
-      </c>
-      <c r="P26">
-        <v>10</v>
-      </c>
-      <c r="Q26">
-        <v>1.65</v>
-      </c>
-      <c r="R26">
-        <v>2.36</v>
-      </c>
-      <c r="S26">
-        <v>1.34</v>
-      </c>
-      <c r="T26">
-        <v>2.88</v>
-      </c>
-      <c r="U26">
-        <v>2.62</v>
-      </c>
-      <c r="V26">
-        <v>1.4</v>
-      </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
+        <v>1.1</v>
+      </c>
+      <c r="Y26">
+        <v>1.44</v>
+      </c>
+      <c r="Z26">
+        <v>2.63</v>
+      </c>
+      <c r="AA26">
+        <v>2.35</v>
+      </c>
+      <c r="AB26">
+        <v>1.53</v>
+      </c>
+      <c r="AC26">
+        <v>4.44</v>
+      </c>
+      <c r="AD26">
+        <v>1.18</v>
+      </c>
+      <c r="AE26">
         <v>1.01</v>
       </c>
-      <c r="Y26">
-        <v>1.22</v>
-      </c>
-      <c r="Z26">
-        <v>3.56</v>
-      </c>
-      <c r="AA26">
-        <v>1.8</v>
-      </c>
-      <c r="AB26">
-        <v>1.95</v>
-      </c>
-      <c r="AC26">
-        <v>3.08</v>
-      </c>
-      <c r="AD26">
-        <v>1.31</v>
-      </c>
-      <c r="AE26">
-        <v>1.08</v>
-      </c>
       <c r="AF26">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AG26">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AK26">
-        <v>3.54</v>
+        <v>1.7</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
+        <v>1.25</v>
+      </c>
+      <c r="O27">
+        <v>5</v>
+      </c>
+      <c r="P27">
+        <v>10</v>
+      </c>
+      <c r="Q27">
+        <v>1.65</v>
+      </c>
+      <c r="R27">
+        <v>2.36</v>
+      </c>
+      <c r="S27">
+        <v>1.34</v>
+      </c>
+      <c r="T27">
+        <v>2.88</v>
+      </c>
+      <c r="U27">
+        <v>2.62</v>
+      </c>
+      <c r="V27">
+        <v>1.4</v>
+      </c>
+      <c r="W27">
+        <v>1.05</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.22</v>
+      </c>
+      <c r="Z27">
+        <v>3.56</v>
+      </c>
+      <c r="AA27">
+        <v>1.8</v>
+      </c>
+      <c r="AB27">
         <v>1.95</v>
       </c>
-      <c r="O27">
-        <v>3.25</v>
-      </c>
-      <c r="P27">
-        <v>3.3</v>
-      </c>
-      <c r="Q27">
-        <v>2.63</v>
-      </c>
-      <c r="R27">
-        <v>1.99</v>
-      </c>
-      <c r="S27">
-        <v>1.41</v>
-      </c>
-      <c r="T27">
-        <v>2.8</v>
-      </c>
-      <c r="U27">
-        <v>2.91</v>
-      </c>
-      <c r="V27">
-        <v>1.36</v>
-      </c>
-      <c r="W27">
-        <v>1.03</v>
-      </c>
-      <c r="X27">
-        <v>1.06</v>
-      </c>
-      <c r="Y27">
+      <c r="AC27">
+        <v>3.08</v>
+      </c>
+      <c r="AD27">
         <v>1.31</v>
-      </c>
-      <c r="Z27">
-        <v>3.12</v>
-      </c>
-      <c r="AA27">
-        <v>2.04</v>
-      </c>
-      <c r="AB27">
-        <v>1.7</v>
-      </c>
-      <c r="AC27">
-        <v>3.5</v>
-      </c>
-      <c r="AD27">
-        <v>1.22</v>
       </c>
       <c r="AE27">
         <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AG27">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AK27">
-        <v>1.68</v>
+        <v>3.54</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
+        <v>3.3</v>
+      </c>
+      <c r="Q28">
+        <v>2.63</v>
+      </c>
+      <c r="R28">
+        <v>1.99</v>
+      </c>
+      <c r="S28">
+        <v>1.41</v>
+      </c>
+      <c r="T28">
+        <v>2.8</v>
+      </c>
+      <c r="U28">
+        <v>2.91</v>
+      </c>
+      <c r="V28">
+        <v>1.36</v>
+      </c>
+      <c r="W28">
+        <v>1.03</v>
+      </c>
+      <c r="X28">
+        <v>1.06</v>
+      </c>
+      <c r="Y28">
+        <v>1.31</v>
+      </c>
+      <c r="Z28">
+        <v>3.12</v>
+      </c>
+      <c r="AA28">
+        <v>2.04</v>
+      </c>
+      <c r="AB28">
+        <v>1.7</v>
+      </c>
+      <c r="AC28">
         <v>3.5</v>
       </c>
-      <c r="Q28">
-        <v>2.7</v>
-      </c>
-      <c r="R28">
-        <v>2.03</v>
-      </c>
-      <c r="S28">
-        <v>1.5</v>
-      </c>
-      <c r="T28">
-        <v>2.45</v>
-      </c>
-      <c r="U28">
-        <v>3.2</v>
-      </c>
-      <c r="V28">
-        <v>1.25</v>
-      </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1.1</v>
-      </c>
-      <c r="Y28">
-        <v>1.44</v>
-      </c>
-      <c r="Z28">
-        <v>2.63</v>
-      </c>
-      <c r="AA28">
-        <v>2.35</v>
-      </c>
-      <c r="AB28">
-        <v>1.53</v>
-      </c>
-      <c r="AC28">
-        <v>4.44</v>
-      </c>
       <c r="AD28">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P35">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q35">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="R35">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
         <v>1.31</v>
@@ -6035,10 +6035,10 @@
         <v>3.32</v>
       </c>
       <c r="U35">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6050,19 +6050,19 @@
         <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB35">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
         <v>2.74</v>
       </c>
       <c r="AD35">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
         <v>1.11</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
         <v>2.58</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="Q37">
-        <v>3.86</v>
+        <v>2.27</v>
       </c>
       <c r="R37">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
         <v>2.66</v>
       </c>
       <c r="U37">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="V37">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
+        <v>1.06</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>1.3</v>
+      </c>
+      <c r="Z37">
+        <v>3.35</v>
+      </c>
+      <c r="AA37">
+        <v>1.9</v>
+      </c>
+      <c r="AB37">
+        <v>1.85</v>
+      </c>
+      <c r="AC37">
+        <v>3.36</v>
+      </c>
+      <c r="AD37">
+        <v>1.3</v>
+      </c>
+      <c r="AE37">
         <v>1.05</v>
       </c>
-      <c r="X37">
-        <v>1.06</v>
-      </c>
-      <c r="Y37">
-        <v>1.32</v>
-      </c>
-      <c r="Z37">
-        <v>3.2</v>
-      </c>
-      <c r="AA37">
-        <v>2.05</v>
-      </c>
-      <c r="AB37">
-        <v>1.75</v>
-      </c>
-      <c r="AC37">
-        <v>3.42</v>
-      </c>
-      <c r="AD37">
-        <v>1.25</v>
-      </c>
-      <c r="AE37">
-        <v>1.07</v>
-      </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG37">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q38">
-        <v>2.27</v>
+        <v>3.86</v>
       </c>
       <c r="R38">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T38">
         <v>2.66</v>
       </c>
       <c r="U38">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W38">
+        <v>1.05</v>
+      </c>
+      <c r="X38">
         <v>1.06</v>
       </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
       <c r="Y38">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z38">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA38">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC38">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="O62">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="P62">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q62">
         <v>4.2</v>
@@ -10430,10 +10430,10 @@
         <v>2.17</v>
       </c>
       <c r="S62">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T62">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U62">
         <v>3.08</v>
@@ -10448,13 +10448,13 @@
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z62">
         <v>3.05</v>
       </c>
       <c r="AA62">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB62">
         <v>1.74</v>
@@ -10472,7 +10472,7 @@
         <v>1.83</v>
       </c>
       <c r="AG62">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AK62">
         <v>1.33</v>
@@ -14982,16 +14982,16 @@
         <v>2.9</v>
       </c>
       <c r="O90">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="P90">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="Q90">
-        <v>3.26</v>
+        <v>3.64</v>
       </c>
       <c r="R90">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="S90">
         <v>1.46</v>
@@ -15000,7 +15000,7 @@
         <v>2.62</v>
       </c>
       <c r="U90">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="V90">
         <v>1.36</v>
@@ -15015,16 +15015,16 @@
         <v>1.33</v>
       </c>
       <c r="Z90">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="AA90">
         <v>2.12</v>
       </c>
       <c r="AB90">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC90">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AD90">
         <v>1.25</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="AK90">
         <v>1.43</v>
@@ -19392,13 +19392,13 @@
         <v>1.95</v>
       </c>
       <c r="R117">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S117">
         <v>1.22</v>
       </c>
       <c r="T117">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="U117">
         <v>1.94</v>
@@ -19407,37 +19407,37 @@
         <v>1.46</v>
       </c>
       <c r="W117">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X117">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z117">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA117">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AB117">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AC117">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD117">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE117">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF117">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AG117">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK117">
         <v>2.15</v>
@@ -20358,31 +20358,31 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O123">
         <v>3.25</v>
       </c>
       <c r="P123">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q123">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="R123">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S123">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T123">
         <v>2.92</v>
       </c>
       <c r="U123">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="V123">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W123">
         <v>1.07</v>
@@ -20391,31 +20391,31 @@
         <v>1</v>
       </c>
       <c r="Y123">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z123">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA123">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB123">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AC123">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD123">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE123">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF123">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG123">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.23</v>
       </c>
       <c r="AK123">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,10 +20521,10 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="O124">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P124">
         <v>4.65</v>
@@ -20536,19 +20536,19 @@
         <v>2.3</v>
       </c>
       <c r="S124">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T124">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U124">
         <v>2.47</v>
       </c>
       <c r="V124">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W124">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X124">
         <v>1.03</v>
@@ -20572,7 +20572,7 @@
         <v>1.36</v>
       </c>
       <c r="AE124">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF124">
         <v>1.75</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK124">
         <v>2.2</v>
@@ -20684,7 +20684,7 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="O125">
         <v>3.18</v>
@@ -20693,16 +20693,16 @@
         <v>1.86</v>
       </c>
       <c r="Q125">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="R125">
         <v>2.2</v>
       </c>
       <c r="S125">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T125">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="U125">
         <v>2.87</v>
@@ -20711,7 +20711,7 @@
         <v>1.4</v>
       </c>
       <c r="W125">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X125">
         <v>1.01</v>
@@ -20720,19 +20720,19 @@
         <v>1.29</v>
       </c>
       <c r="Z125">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="AA125">
         <v>1.9</v>
       </c>
       <c r="AB125">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC125">
         <v>3.14</v>
       </c>
       <c r="AD125">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE125">
         <v>1.06</v>
@@ -20850,10 +20850,10 @@
         <v>2.2</v>
       </c>
       <c r="O126">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="P126">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q126">
         <v>2.8</v>
@@ -20865,10 +20865,10 @@
         <v>1.33</v>
       </c>
       <c r="T126">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U126">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="V126">
         <v>1.44</v>
@@ -20883,10 +20883,10 @@
         <v>1.21</v>
       </c>
       <c r="Z126">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA126">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB126">
         <v>1.93</v>
@@ -20898,13 +20898,13 @@
         <v>1.33</v>
       </c>
       <c r="AE126">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF126">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG126">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
         <v>1.53</v>
@@ -21016,7 +21016,7 @@
         <v>4.35</v>
       </c>
       <c r="P127">
-        <v>5.15</v>
+        <v>6.8</v>
       </c>
       <c r="Q127">
         <v>1.8</v>
@@ -21031,10 +21031,10 @@
         <v>3.96</v>
       </c>
       <c r="U127">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V127">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W127">
         <v>1.17</v>
@@ -21049,7 +21049,7 @@
         <v>5.19</v>
       </c>
       <c r="AA127">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB127">
         <v>2.5</v>
@@ -21058,16 +21058,16 @@
         <v>2.14</v>
       </c>
       <c r="AD127">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE127">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF127">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG127">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,80 +21825,80 @@
         </is>
       </c>
       <c r="N132">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="O132">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P132">
-        <v>2.81</v>
+        <v>4.33</v>
       </c>
       <c r="Q132">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="R132">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="S132">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T132">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="U132">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="V132">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="W132">
+        <v>1.14</v>
+      </c>
+      <c r="X132">
+        <v>1.01</v>
+      </c>
+      <c r="Y132">
+        <v>1.18</v>
+      </c>
+      <c r="Z132">
+        <v>4.5</v>
+      </c>
+      <c r="AA132">
+        <v>1.58</v>
+      </c>
+      <c r="AB132">
+        <v>2.17</v>
+      </c>
+      <c r="AC132">
+        <v>2.6</v>
+      </c>
+      <c r="AD132">
+        <v>1.55</v>
+      </c>
+      <c r="AE132">
+        <v>1.21</v>
+      </c>
+      <c r="AF132">
+        <v>1.55</v>
+      </c>
+      <c r="AG132">
+        <v>2.25</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
         <v>1.22</v>
       </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>1.03</v>
-      </c>
-      <c r="Z132">
-        <v>7.5</v>
-      </c>
-      <c r="AA132">
-        <v>1.32</v>
-      </c>
-      <c r="AB132">
-        <v>3.4</v>
-      </c>
-      <c r="AC132">
-        <v>1.8</v>
-      </c>
-      <c r="AD132">
-        <v>2.01</v>
-      </c>
-      <c r="AE132">
-        <v>1.4</v>
-      </c>
-      <c r="AF132">
-        <v>1.29</v>
-      </c>
-      <c r="AG132">
-        <v>3.3</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>1.36</v>
-      </c>
       <c r="AK132">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="O133">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P133">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="Q133">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="R133">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S133">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T133">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="U133">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="V133">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="W133">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z133">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA133">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AB133">
-        <v>2.17</v>
+        <v>3.04</v>
       </c>
       <c r="AC133">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AD133">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AE133">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AF133">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AG133">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK133">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O134">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P134">
-        <v>3.8</v>
+        <v>2.81</v>
       </c>
       <c r="Q134">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="R134">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="S134">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T134">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="U134">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="V134">
+        <v>1.88</v>
+      </c>
+      <c r="W134">
+        <v>1.22</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>1.03</v>
+      </c>
+      <c r="Z134">
+        <v>7.5</v>
+      </c>
+      <c r="AA134">
+        <v>1.32</v>
+      </c>
+      <c r="AB134">
+        <v>3.4</v>
+      </c>
+      <c r="AC134">
         <v>1.8</v>
       </c>
-      <c r="W134">
-        <v>1.19</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>1.07</v>
-      </c>
-      <c r="Z134">
-        <v>6.8</v>
-      </c>
-      <c r="AA134">
-        <v>1.38</v>
-      </c>
-      <c r="AB134">
-        <v>3.04</v>
-      </c>
-      <c r="AC134">
-        <v>1.91</v>
-      </c>
       <c r="AD134">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AE134">
+        <v>1.4</v>
+      </c>
+      <c r="AF134">
+        <v>1.29</v>
+      </c>
+      <c r="AG134">
+        <v>3.3</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
         <v>1.36</v>
       </c>
-      <c r="AF134">
-        <v>1.38</v>
-      </c>
-      <c r="AG134">
-        <v>2.85</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.16</v>
-      </c>
       <c r="AK134">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22314,16 +22314,16 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O135">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P135">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="Q135">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R135">
         <v>2.22</v>
@@ -22332,7 +22332,7 @@
         <v>1.3</v>
       </c>
       <c r="T135">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U135">
         <v>2.38</v>
@@ -22353,25 +22353,25 @@
         <v>3.98</v>
       </c>
       <c r="AA135">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB135">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC135">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="AD135">
         <v>1.39</v>
       </c>
       <c r="AE135">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF135">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG135">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22477,40 +22477,40 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="O136">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
       </c>
       <c r="R136">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S136">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U136">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="V136">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X136">
         <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z136">
         <v>3.5</v>
@@ -22519,13 +22519,13 @@
         <v>1.9</v>
       </c>
       <c r="AB136">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC136">
         <v>2.83</v>
       </c>
       <c r="AD136">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE136">
         <v>1.1</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22975,28 +22975,28 @@
         <v>1.45</v>
       </c>
       <c r="Q139">
-        <v>5.66</v>
+        <v>5.5</v>
       </c>
       <c r="R139">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S139">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T139">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U139">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="V139">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W139">
         <v>1.08</v>
       </c>
       <c r="X139">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y139">
         <v>1.21</v>
@@ -23008,22 +23008,22 @@
         <v>1.7</v>
       </c>
       <c r="AB139">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AC139">
         <v>2.7</v>
       </c>
       <c r="AD139">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE139">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF139">
         <v>1.78</v>
       </c>
       <c r="AG139">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23790,34 +23790,34 @@
         <v>0</v>
       </c>
       <c r="Q144">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="R144">
         <v>2.16</v>
       </c>
       <c r="S144">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
         <v>3.04</v>
       </c>
       <c r="U144">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="V144">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W144">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X144">
         <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z144">
-        <v>3.68</v>
+        <v>2.9</v>
       </c>
       <c r="AA144">
         <v>1.59</v>
@@ -23832,10 +23832,10 @@
         <v>1.29</v>
       </c>
       <c r="AE144">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF144">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AG144">
         <v>1.93</v>
@@ -23854,7 +23854,7 @@
         <v>1.23</v>
       </c>
       <c r="AK144">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24113,13 +24113,13 @@
         <v>3.45</v>
       </c>
       <c r="P146">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q146">
         <v>3.3</v>
       </c>
       <c r="R146">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S146">
         <v>1.31</v>
@@ -24131,34 +24131,34 @@
         <v>2.48</v>
       </c>
       <c r="V146">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z146">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AA146">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB146">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC146">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="AD146">
         <v>1.4</v>
       </c>
       <c r="AE146">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF146">
         <v>1.58</v>
@@ -24439,34 +24439,34 @@
         <v>3.15</v>
       </c>
       <c r="P148">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="Q148">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R148">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S148">
         <v>1.36</v>
       </c>
       <c r="T148">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U148">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="V148">
         <v>1.35</v>
       </c>
       <c r="W148">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X148">
         <v>1.02</v>
       </c>
       <c r="Y148">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z148">
         <v>3.04</v>
@@ -24475,10 +24475,10 @@
         <v>2</v>
       </c>
       <c r="AB148">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC148">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD148">
         <v>1.27</v>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK148">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24605,25 +24605,25 @@
         <v>2.59</v>
       </c>
       <c r="Q149">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R149">
         <v>2.19</v>
       </c>
       <c r="S149">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T149">
         <v>3.12</v>
       </c>
       <c r="U149">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="V149">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W149">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X149">
         <v>1.03</v>
@@ -24632,7 +24632,7 @@
         <v>1.19</v>
       </c>
       <c r="Z149">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA149">
         <v>1.75</v>
@@ -24647,13 +24647,13 @@
         <v>1.34</v>
       </c>
       <c r="AE149">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF149">
         <v>1.61</v>
       </c>
       <c r="AG149">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK149">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24759,7 +24759,7 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="O150">
         <v>3.32</v>
@@ -24777,7 +24777,7 @@
         <v>1.3</v>
       </c>
       <c r="T150">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U150">
         <v>2.41</v>
@@ -24786,7 +24786,7 @@
         <v>1.47</v>
       </c>
       <c r="W150">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X150">
         <v>1</v>
@@ -24801,10 +24801,10 @@
         <v>1.72</v>
       </c>
       <c r="AB150">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AC150">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="AD150">
         <v>1.39</v>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AK150">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL150">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -1791,10 +1791,10 @@
         <v>2.32</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U9">
         <v>2.5</v>
@@ -1809,7 +1809,7 @@
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z9">
         <v>4</v>
@@ -1818,22 +1818,22 @@
         <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AC9">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
         <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         <v>2.17</v>
       </c>
       <c r="O10">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="P10">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
         <v>3.04</v>
@@ -1960,10 +1960,10 @@
         <v>2.82</v>
       </c>
       <c r="U10">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
         <v>1.04</v>
@@ -1975,19 +1975,19 @@
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
         <v>1.87</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC10">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD10">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
         <v>1.07</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="O11">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q11">
         <v>3.3</v>
@@ -2120,19 +2120,19 @@
         <v>1.42</v>
       </c>
       <c r="T11">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
         <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.3</v>
@@ -2144,22 +2144,22 @@
         <v>1.98</v>
       </c>
       <c r="AB11">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="AD11">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.45</v>
+        <v>5.01</v>
       </c>
       <c r="O12">
         <v>3.7</v>
       </c>
       <c r="P12">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q12">
         <v>5.5</v>
       </c>
       <c r="R12">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2292,37 +2292,37 @@
         <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
         <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
         <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,43 +2428,43 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q13">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
         <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
         <v>2.33</v>
       </c>
       <c r="V13">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA13">
         <v>1.64</v>
@@ -2485,7 +2485,7 @@
         <v>1.51</v>
       </c>
       <c r="AG13">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK13">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>2.25</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15">
         <v>3.94</v>
@@ -3572,19 +3572,19 @@
         <v>1.57</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="P20">
-        <v>4.4</v>
+        <v>4.92</v>
       </c>
       <c r="Q20">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R20">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="S20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
         <v>4.3</v>
@@ -3611,16 +3611,16 @@
         <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AC20">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AD20">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE20">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF20">
         <v>1.36</v>
@@ -3642,7 +3642,7 @@
         <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,28 +3732,28 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O21">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="R21">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="S21">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="U21">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
         <v>1.8</v>
@@ -3765,19 +3765,19 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z21">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA21">
         <v>1.33</v>
       </c>
       <c r="AB21">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AC21">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD21">
         <v>1.9</v>
@@ -3786,10 +3786,10 @@
         <v>1.33</v>
       </c>
       <c r="AF21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG21">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O22">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P22">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Q22">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R22">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="S22">
         <v>1.23</v>
@@ -3916,16 +3916,16 @@
         <v>4.5</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V22">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.12</v>
@@ -3934,22 +3934,22 @@
         <v>6.5</v>
       </c>
       <c r="AA22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB22">
         <v>2.7</v>
       </c>
       <c r="AC22">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AD22">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG22">
         <v>2.15</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AK22">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         <v>2.13</v>
       </c>
       <c r="Q24">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="R24">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S24">
         <v>1.36</v>
@@ -4275,7 +4275,7 @@
         <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AG24">
         <v>2</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R25">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.33</v>
@@ -4405,28 +4405,28 @@
         <v>3</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z25">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA25">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC25">
         <v>2.75</v>
@@ -4438,10 +4438,10 @@
         <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O26">
         <v>3</v>
@@ -4556,43 +4556,43 @@
         <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
         <v>2.03</v>
       </c>
       <c r="S26">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T26">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U26">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V26">
         <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y26">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z26">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AA26">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB26">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC26">
-        <v>4.44</v>
+        <v>4.33</v>
       </c>
       <c r="AD26">
         <v>1.18</v>
@@ -4604,7 +4604,7 @@
         <v>2.02</v>
       </c>
       <c r="AG26">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O27">
         <v>5</v>
@@ -4719,49 +4719,49 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R27">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="AA27">
         <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
         <v>2.25</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK27">
         <v>3.54</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
         <v>3.3</v>
       </c>
       <c r="Q28">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
         <v>1.99</v>
@@ -4891,10 +4891,10 @@
         <v>1.41</v>
       </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V28">
         <v>1.36</v>
@@ -4903,34 +4903,34 @@
         <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="AA28">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB28">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC28">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
         <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
         <v>1.68</v>
@@ -5109,7 +5109,7 @@
         <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q34">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="R34">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
         <v>1.31</v>
@@ -5872,10 +5872,10 @@
         <v>2.97</v>
       </c>
       <c r="U34">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
         <v>1.07</v>
@@ -5884,19 +5884,19 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC34">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AD34">
         <v>1.36</v>
@@ -5905,7 +5905,7 @@
         <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
         <v>2.1</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O35">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
         <v>5.9</v>
@@ -6053,10 +6053,10 @@
         <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC35">
         <v>2.74</v>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P36">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q36">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R36">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>1.24</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W36">
         <v>1.14</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="AA36">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC36">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AD36">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE36">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG36">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,62 +6343,62 @@
         <v>1.73</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q37">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
         <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA37">
+        <v>1.91</v>
+      </c>
+      <c r="AB37">
+        <v>1.84</v>
+      </c>
+      <c r="AC37">
+        <v>3.2</v>
+      </c>
+      <c r="AD37">
+        <v>1.26</v>
+      </c>
+      <c r="AE37">
+        <v>1.06</v>
+      </c>
+      <c r="AF37">
+        <v>1.8</v>
+      </c>
+      <c r="AG37">
         <v>1.9</v>
       </c>
-      <c r="AB37">
-        <v>1.85</v>
-      </c>
-      <c r="AC37">
-        <v>3.36</v>
-      </c>
-      <c r="AD37">
-        <v>1.3</v>
-      </c>
-      <c r="AE37">
-        <v>1.05</v>
-      </c>
-      <c r="AF37">
-        <v>1.82</v>
-      </c>
-      <c r="AG37">
-        <v>1.87</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,61 +6503,61 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
         <v>3.2</v>
       </c>
       <c r="P38">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q38">
-        <v>3.86</v>
+        <v>3.39</v>
       </c>
       <c r="R38">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="S38">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="U38">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="V38">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
         <v>1.32</v>
       </c>
       <c r="Z38">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AA38">
         <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC38">
         <v>3.42</v>
       </c>
       <c r="AD38">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE38">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
         <v>1.91</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P39">
         <v>2.78</v>
@@ -6678,49 +6678,49 @@
         <v>3.26</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S39">
         <v>1.49</v>
       </c>
       <c r="T39">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="U39">
-        <v>3.17</v>
+        <v>3.32</v>
       </c>
       <c r="V39">
         <v>1.26</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y39">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z39">
-        <v>2.74</v>
+        <v>2.53</v>
       </c>
       <c r="AA39">
         <v>2.35</v>
       </c>
       <c r="AB39">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC39">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD39">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE39">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG39">
         <v>1.75</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
         <v>1.51</v>
@@ -6844,43 +6844,43 @@
         <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
         <v>3.23</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC40">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
         <v>1.8</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,52 +6992,52 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="O41">
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="R41">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="U41">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="V41">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z41">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB41">
         <v>1.66</v>
       </c>
       <c r="AC41">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="AD41">
         <v>1.2</v>
@@ -7046,10 +7046,10 @@
         <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG41">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK41">
         <v>2.1</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
@@ -7173,10 +7173,10 @@
         <v>1.35</v>
       </c>
       <c r="T42">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="U42">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="V42">
         <v>1.36</v>
@@ -7188,13 +7188,13 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA42">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB42">
         <v>1.83</v>
@@ -7206,13 +7206,13 @@
         <v>1.27</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK42">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,7 +7321,7 @@
         <v>2.6</v>
       </c>
       <c r="O43">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P43">
         <v>2.6</v>
@@ -7330,52 +7330,52 @@
         <v>3.3</v>
       </c>
       <c r="R43">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T43">
         <v>2.53</v>
       </c>
       <c r="U43">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V43">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W43">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y43">
         <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="AA43">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AB43">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC43">
         <v>3.42</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
         <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG43">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.81</v>
+        <v>3.9</v>
       </c>
       <c r="O46">
-        <v>3.53</v>
+        <v>4.05</v>
       </c>
       <c r="P46">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Q46">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="R46">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="S46">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="U46">
         <v>2.01</v>
       </c>
       <c r="V46">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z46">
-        <v>5.8</v>
+        <v>6.17</v>
       </c>
       <c r="AA46">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB46">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC46">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD46">
         <v>1.8</v>
       </c>
       <c r="AE46">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF46">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG46">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P47">
         <v>3.25</v>
@@ -7988,16 +7988,16 @@
         <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="U47">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
         <v>1.48</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8006,13 +8006,13 @@
         <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA47">
         <v>1.8</v>
       </c>
       <c r="AB47">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC47">
         <v>2.8</v>
@@ -8021,13 +8021,13 @@
         <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF47">
         <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK47">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8462,22 +8462,22 @@
         <v>1.67</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="P50">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S50">
         <v>1.36</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="U50">
         <v>2.7</v>
@@ -8489,7 +8489,7 @@
         <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
         <v>1.25</v>
@@ -8498,10 +8498,10 @@
         <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB50">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC50">
         <v>2.92</v>
@@ -8510,13 +8510,13 @@
         <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG50">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.23</v>
       </c>
       <c r="AK50">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="O51">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P51">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q51">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R51">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.16</v>
+        <v>2.91</v>
       </c>
       <c r="U51">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V51">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
         <v>1.08</v>
@@ -8655,31 +8655,31 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC51">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
         <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O52">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
         <v>1.6</v>
       </c>
       <c r="Q52">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="R52">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T52">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="U52">
         <v>2.41</v>
       </c>
       <c r="V52">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W52">
         <v>1.09</v>
@@ -8818,31 +8818,31 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
         <v>3.96</v>
       </c>
       <c r="AA52">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB52">
         <v>2.15</v>
       </c>
       <c r="AC52">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AD52">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE52">
         <v>1.16</v>
       </c>
       <c r="AF52">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>2.18</v>
       </c>
       <c r="AK52">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O55">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="P55">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q55">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R55">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="S55">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T55">
         <v>3.25</v>
       </c>
       <c r="U55">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V55">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W55">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA55">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB55">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC55">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="AD55">
         <v>1.41</v>
       </c>
       <c r="AE55">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF55">
         <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AK55">
         <v>1.25</v>
@@ -9458,28 +9458,28 @@
         <v>4</v>
       </c>
       <c r="U56">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V56">
         <v>1.7</v>
       </c>
       <c r="W56">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z56">
-        <v>5.55</v>
+        <v>6.23</v>
       </c>
       <c r="AA56">
         <v>1.42</v>
       </c>
       <c r="AB56">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC56">
         <v>2.02</v>
@@ -9618,7 +9618,7 @@
         <v>1.4</v>
       </c>
       <c r="T57">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U57">
         <v>3</v>
@@ -9630,31 +9630,31 @@
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y57">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z57">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA57">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB57">
         <v>1.65</v>
       </c>
       <c r="AC57">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AD57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
         <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG57">
         <v>1.81</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
         <v>1.5</v>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O60">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P60">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="Q60">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R60">
         <v>1.88</v>
@@ -10110,7 +10110,7 @@
         <v>2.28</v>
       </c>
       <c r="U60">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V60">
         <v>1.23</v>
@@ -10119,34 +10119,34 @@
         <v>1.01</v>
       </c>
       <c r="X60">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y60">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z60">
         <v>2.41</v>
       </c>
       <c r="AA60">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AB60">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC60">
         <v>5.25</v>
       </c>
       <c r="AD60">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE60">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF60">
         <v>2.25</v>
       </c>
       <c r="AG60">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK60">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10258,22 +10258,22 @@
         <v>3.37</v>
       </c>
       <c r="P61">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="Q61">
-        <v>4.11</v>
+        <v>3.7</v>
       </c>
       <c r="R61">
         <v>2.27</v>
       </c>
       <c r="S61">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T61">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
         <v>1.53</v>
@@ -10282,19 +10282,19 @@
         <v>1.1</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z61">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA61">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB61">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC61">
         <v>2.43</v>
@@ -10306,7 +10306,7 @@
         <v>1.15</v>
       </c>
       <c r="AF61">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
         <v>2.3</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="AK61">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10584,19 +10584,19 @@
         <v>3.1</v>
       </c>
       <c r="P63">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q63">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R63">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S63">
         <v>1.46</v>
       </c>
       <c r="T63">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U63">
         <v>3.25</v>
@@ -10611,10 +10611,10 @@
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z63">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA63">
         <v>2.25</v>
@@ -10623,7 +10623,7 @@
         <v>1.61</v>
       </c>
       <c r="AC63">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AD63">
         <v>1.16</v>
@@ -10632,10 +10632,10 @@
         <v>1.02</v>
       </c>
       <c r="AF63">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG63">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AK63">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="Q65">
         <v>3.15</v>
       </c>
       <c r="R65">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S65">
         <v>1.32</v>
       </c>
       <c r="T65">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U65">
         <v>2.71</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
         <v>1.41</v>
@@ -11067,37 +11067,37 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q66">
         <v>3.8</v>
       </c>
       <c r="R66">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U66">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V66">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
         <v>1.12</v>
@@ -11109,22 +11109,22 @@
         <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AC66">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD66">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE66">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG66">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AK66">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,58 +11230,58 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O67">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="P67">
-        <v>3.05</v>
+        <v>3.41</v>
       </c>
       <c r="Q67">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="R67">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T67">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U67">
         <v>2.15</v>
       </c>
       <c r="V67">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W67">
         <v>1.14</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA67">
         <v>1.49</v>
       </c>
       <c r="AB67">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AC67">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AD67">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE67">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF67">
         <v>1.44</v>
@@ -11411,13 +11411,13 @@
         <v>1.35</v>
       </c>
       <c r="T68">
-        <v>3.07</v>
+        <v>2.82</v>
       </c>
       <c r="U68">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V68">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
         <v>1.07</v>
@@ -11426,31 +11426,31 @@
         <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.42</v>
+        <v>3.62</v>
       </c>
       <c r="AA68">
+        <v>1.88</v>
+      </c>
+      <c r="AB68">
         <v>1.9</v>
       </c>
-      <c r="AB68">
-        <v>1.85</v>
-      </c>
       <c r="AC68">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AD68">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF68">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG68">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O70">
         <v>3.55</v>
@@ -11728,7 +11728,7 @@
         <v>3</v>
       </c>
       <c r="Q70">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="R70">
         <v>2.47</v>
@@ -11737,13 +11737,13 @@
         <v>1.18</v>
       </c>
       <c r="T70">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V70">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W70">
         <v>1.17</v>
@@ -11752,22 +11752,22 @@
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z70">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="AA70">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB70">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC70">
         <v>1.99</v>
       </c>
       <c r="AD70">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE70">
         <v>1.3</v>
@@ -11776,7 +11776,7 @@
         <v>1.36</v>
       </c>
       <c r="AG70">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,25 +11882,25 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="O71">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P71">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q71">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="R71">
         <v>2.27</v>
       </c>
       <c r="S71">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U71">
         <v>2.3</v>
@@ -11912,7 +11912,7 @@
         <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
         <v>1.16</v>
@@ -11921,25 +11921,25 @@
         <v>4.4</v>
       </c>
       <c r="AA71">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB71">
         <v>2.1</v>
       </c>
       <c r="AC71">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AD71">
         <v>1.42</v>
       </c>
       <c r="AE71">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG71">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.68</v>
       </c>
       <c r="AK71">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,25 +12045,25 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="O72">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="Q72">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R72">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S72">
         <v>1.36</v>
       </c>
       <c r="T72">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="U72">
         <v>2.79</v>
@@ -12075,31 +12075,31 @@
         <v>1.03</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA72">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB72">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC72">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD72">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE72">
         <v>1.05</v>
       </c>
       <c r="AF72">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
         <v>1.98</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AK72">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,22 +12208,22 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="Q73">
         <v>2.85</v>
       </c>
       <c r="R73">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T73">
         <v>3.2</v>
@@ -12232,7 +12232,7 @@
         <v>2.63</v>
       </c>
       <c r="V73">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
         <v>1.1</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="O74">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="P74">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Q74">
         <v>1.65</v>
@@ -12386,49 +12386,49 @@
         <v>2.6</v>
       </c>
       <c r="S74">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T74">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="U74">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V74">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
         <v>1.21</v>
       </c>
       <c r="Z74">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="AA74">
         <v>1.7</v>
       </c>
       <c r="AB74">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC74">
         <v>2.75</v>
       </c>
       <c r="AD74">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE74">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
         <v>2.4</v>
       </c>
       <c r="AG74">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12706,10 +12706,10 @@
         <v>3.6</v>
       </c>
       <c r="Q76">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="R76">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="S76">
         <v>1.45</v>
@@ -12745,7 +12745,7 @@
         <v>4.07</v>
       </c>
       <c r="AD76">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE76">
         <v>1.02</v>
@@ -12860,49 +12860,49 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="O77">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P77">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q77">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R77">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T77">
         <v>3.25</v>
       </c>
       <c r="U77">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V77">
         <v>1.5</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="AA77">
         <v>1.67</v>
       </c>
       <c r="AB77">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC77">
         <v>2.59</v>
@@ -12911,13 +12911,13 @@
         <v>1.39</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF77">
         <v>1.64</v>
       </c>
       <c r="AG77">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.17</v>
       </c>
       <c r="AK77">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,31 +13023,31 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O78">
         <v>3.3</v>
       </c>
       <c r="P78">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q78">
         <v>2.7</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
         <v>1.36</v>
       </c>
       <c r="T78">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="U78">
         <v>2.77</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W78">
         <v>1.07</v>
@@ -13056,13 +13056,13 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
         <v>3.5</v>
       </c>
       <c r="AA78">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB78">
         <v>1.96</v>
@@ -13074,7 +13074,7 @@
         <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF78">
         <v>1.7</v>
@@ -13189,16 +13189,16 @@
         <v>3</v>
       </c>
       <c r="O79">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="P79">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q79">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R79">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
         <v>1.3</v>
@@ -13216,7 +13216,7 @@
         <v>1.08</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y79">
         <v>1.2</v>
@@ -13237,13 +13237,13 @@
         <v>1.4</v>
       </c>
       <c r="AE79">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF79">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG79">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
         <v>1.35</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="O82">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P82">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -13693,7 +13693,7 @@
         <v>1.44</v>
       </c>
       <c r="T82">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U82">
         <v>3.14</v>
@@ -13714,7 +13714,7 @@
         <v>2.7</v>
       </c>
       <c r="AA82">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB82">
         <v>1.58</v>
@@ -13732,7 +13732,7 @@
         <v>1.93</v>
       </c>
       <c r="AG82">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13838,28 +13838,28 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="O83">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P83">
         <v>6.35</v>
       </c>
       <c r="Q83">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R83">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="S83">
         <v>1.29</v>
       </c>
       <c r="T83">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="U83">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V83">
         <v>1.45</v>
@@ -13874,19 +13874,19 @@
         <v>1.18</v>
       </c>
       <c r="Z83">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="AA83">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB83">
         <v>2.1</v>
       </c>
       <c r="AC83">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD83">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE83">
         <v>1.12</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q84">
         <v>2.88</v>
@@ -14025,7 +14025,7 @@
         <v>3.28</v>
       </c>
       <c r="V84">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W84">
         <v>1.03</v>
@@ -14055,10 +14055,10 @@
         <v>1</v>
       </c>
       <c r="AF84">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG84">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O85">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P85">
-        <v>4.17</v>
+        <v>4.06</v>
       </c>
       <c r="Q85">
         <v>2.25</v>
@@ -14221,7 +14221,7 @@
         <v>1.7</v>
       </c>
       <c r="AG85">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,10 +14336,10 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="R86">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S86">
         <v>1.33</v>
@@ -14351,13 +14351,13 @@
         <v>2.75</v>
       </c>
       <c r="V86">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
         <v>1.07</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
         <v>1.24</v>
@@ -14384,7 +14384,7 @@
         <v>1.7</v>
       </c>
       <c r="AG86">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK86">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14662,10 +14662,10 @@
         <v>2.37</v>
       </c>
       <c r="Q88">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R88">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S88">
         <v>1.3</v>
@@ -14674,28 +14674,28 @@
         <v>3.1</v>
       </c>
       <c r="U88">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V88">
         <v>1.44</v>
       </c>
       <c r="W88">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z88">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="AA88">
         <v>1.73</v>
       </c>
       <c r="AB88">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC88">
         <v>2.74</v>
@@ -14704,10 +14704,10 @@
         <v>1.35</v>
       </c>
       <c r="AE88">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF88">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG88">
         <v>2.19</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O89">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="P89">
-        <v>7.7</v>
+        <v>9.25</v>
       </c>
       <c r="Q89">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R89">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U89">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="V89">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W89">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z89">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AA89">
         <v>1.5</v>
       </c>
       <c r="AB89">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AC89">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AD89">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE89">
         <v>1.2</v>
       </c>
       <c r="AF89">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG89">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="O91">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P91">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q91">
+        <v>5.75</v>
+      </c>
+      <c r="R91">
+        <v>2.08</v>
+      </c>
+      <c r="S91">
+        <v>1.52</v>
+      </c>
+      <c r="T91">
+        <v>2.32</v>
+      </c>
+      <c r="U91">
+        <v>3.6</v>
+      </c>
+      <c r="V91">
+        <v>1.25</v>
+      </c>
+      <c r="W91">
+        <v>1.04</v>
+      </c>
+      <c r="X91">
+        <v>1.1</v>
+      </c>
+      <c r="Y91">
+        <v>1.5</v>
+      </c>
+      <c r="Z91">
+        <v>2.7</v>
+      </c>
+      <c r="AA91">
+        <v>2.25</v>
+      </c>
+      <c r="AB91">
+        <v>1.61</v>
+      </c>
+      <c r="AC91">
         <v>4.5</v>
       </c>
-      <c r="R91">
-        <v>2.01</v>
-      </c>
-      <c r="S91">
-        <v>1.44</v>
-      </c>
-      <c r="T91">
-        <v>2.63</v>
-      </c>
-      <c r="U91">
-        <v>3.15</v>
-      </c>
-      <c r="V91">
-        <v>1.28</v>
-      </c>
-      <c r="W91">
+      <c r="AD91">
+        <v>1.13</v>
+      </c>
+      <c r="AE91">
         <v>1.05</v>
       </c>
-      <c r="X91">
-        <v>1.03</v>
-      </c>
-      <c r="Y91">
-        <v>1.42</v>
-      </c>
-      <c r="Z91">
-        <v>2.85</v>
-      </c>
-      <c r="AA91">
+      <c r="AF91">
         <v>2.21</v>
       </c>
-      <c r="AB91">
-        <v>1.59</v>
-      </c>
-      <c r="AC91">
-        <v>4.05</v>
-      </c>
-      <c r="AD91">
-        <v>1.16</v>
-      </c>
-      <c r="AE91">
-        <v>1.02</v>
-      </c>
-      <c r="AF91">
-        <v>2.05</v>
-      </c>
       <c r="AG91">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,31 +15305,31 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="O92">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P92">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="Q92">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R92">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S92">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="U92">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="V92">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W92">
         <v>1.05</v>
@@ -15338,31 +15338,31 @@
         <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z92">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA92">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB92">
         <v>1.95</v>
       </c>
       <c r="AC92">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="AD92">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF92">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK92">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -16286,58 +16286,58 @@
         <v>1.4</v>
       </c>
       <c r="O98">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P98">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q98">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R98">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S98">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T98">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U98">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V98">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W98">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z98">
         <v>5</v>
       </c>
       <c r="AA98">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC98">
         <v>2.16</v>
       </c>
       <c r="AD98">
+        <v>1.66</v>
+      </c>
+      <c r="AE98">
+        <v>1.21</v>
+      </c>
+      <c r="AF98">
         <v>1.62</v>
-      </c>
-      <c r="AE98">
-        <v>1.24</v>
-      </c>
-      <c r="AF98">
-        <v>1.64</v>
       </c>
       <c r="AG98">
         <v>2.13</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AK98">
-        <v>2.79</v>
+        <v>2.61</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O103">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P103">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA103">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AB103">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O104">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q104">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R104">
         <v>2.4</v>
       </c>
       <c r="S104">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T104">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U104">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="V104">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W104">
         <v>1.16</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z104">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="AA104">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AB104">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AC104">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AD104">
         <v>1.61</v>
       </c>
       <c r="AE104">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF104">
+        <v>1.41</v>
+      </c>
+      <c r="AG104">
+        <v>2.75</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.4</v>
       </c>
-      <c r="AG104">
-        <v>2.66</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.44</v>
-      </c>
       <c r="AK104">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="O105">
         <v>3</v>
@@ -17445,10 +17445,10 @@
         <v>2.34</v>
       </c>
       <c r="U105">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="V105">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W105">
         <v>1.01</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AK105">
         <v>1.39</v>
@@ -17590,55 +17590,55 @@
         <v>1.75</v>
       </c>
       <c r="O106">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
         <v>3.7</v>
       </c>
       <c r="Q106">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="R106">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S106">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="U106">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="V106">
         <v>1.37</v>
       </c>
       <c r="W106">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z106">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA106">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB106">
         <v>1.75</v>
       </c>
       <c r="AC106">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AD106">
         <v>1.24</v>
       </c>
       <c r="AE106">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF106">
         <v>1.83</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="O107">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="P107">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q107">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="R107">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="S107">
         <v>1.19</v>
@@ -17771,7 +17771,7 @@
         <v>3.98</v>
       </c>
       <c r="U107">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V107">
         <v>1.75</v>
@@ -17786,22 +17786,22 @@
         <v>1.07</v>
       </c>
       <c r="Z107">
-        <v>5.8</v>
+        <v>6.23</v>
       </c>
       <c r="AA107">
         <v>1.4</v>
       </c>
       <c r="AB107">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AC107">
         <v>2.01</v>
       </c>
       <c r="AD107">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AE107">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AF107">
         <v>1.33</v>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
         <v>1.49</v>
@@ -17922,19 +17922,19 @@
         <v>2.5</v>
       </c>
       <c r="Q108">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R108">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S108">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="U108">
-        <v>2.96</v>
+        <v>2.39</v>
       </c>
       <c r="V108">
         <v>1.32</v>
@@ -17943,16 +17943,16 @@
         <v>1.02</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z108">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AA108">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AB108">
         <v>1.69</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18402,25 +18402,25 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O111">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P111">
-        <v>6.93</v>
+        <v>5.75</v>
       </c>
       <c r="Q111">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="R111">
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T111">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U111">
         <v>3.1</v>
@@ -18429,22 +18429,22 @@
         <v>1.31</v>
       </c>
       <c r="W111">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y111">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z111">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA111">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AB111">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC111">
         <v>3.65</v>
@@ -18453,13 +18453,13 @@
         <v>1.19</v>
       </c>
       <c r="AE111">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG111">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK111">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,61 +18565,61 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="O112">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P112">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q112">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="R112">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S112">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T112">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U112">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V112">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W112">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z112">
         <v>4.3</v>
       </c>
       <c r="AA112">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB112">
         <v>2.2</v>
       </c>
       <c r="AC112">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AD112">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE112">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF112">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG112">
         <v>2.05</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK112">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18891,19 +18891,19 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="O114">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P114">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q114">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="R114">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="S114">
         <v>1.14</v>
@@ -18912,40 +18912,40 @@
         <v>4.9</v>
       </c>
       <c r="U114">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V114">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W114">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z114">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA114">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB114">
         <v>3.28</v>
       </c>
       <c r="AC114">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AD114">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE114">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF114">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG114">
         <v>3</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK114">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,58 +19054,58 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="O115">
         <v>3.1</v>
       </c>
       <c r="P115">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q115">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="R115">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="S115">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T115">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="U115">
         <v>3.12</v>
       </c>
       <c r="V115">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W115">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y115">
         <v>1.38</v>
       </c>
       <c r="Z115">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AA115">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB115">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC115">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="AD115">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE115">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF115">
         <v>1.83</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK115">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="O116">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="P116">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="Q116">
         <v>3</v>
       </c>
       <c r="R116">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S116">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T116">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U116">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="V116">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W116">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z116">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA116">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AB116">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC116">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD116">
         <v>1.2</v>
       </c>
       <c r="AE116">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG116">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19425,7 +19425,7 @@
         <v>2.25</v>
       </c>
       <c r="AC117">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD117">
         <v>1.56</v>
@@ -19543,31 +19543,31 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q118">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="R118">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S118">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T118">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U118">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V118">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W118">
         <v>1.17</v>
@@ -19582,16 +19582,16 @@
         <v>5.3</v>
       </c>
       <c r="AA118">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB118">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC118">
         <v>2.09</v>
       </c>
       <c r="AD118">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE118">
         <v>1.24</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK118">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O119">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P119">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="Q119">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="R119">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S119">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T119">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U119">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V119">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W119">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
         <v>1.03</v>
       </c>
       <c r="Y119">
+        <v>1.29</v>
+      </c>
+      <c r="Z119">
+        <v>3.04</v>
+      </c>
+      <c r="AA119">
+        <v>2.01</v>
+      </c>
+      <c r="AB119">
+        <v>1.74</v>
+      </c>
+      <c r="AC119">
+        <v>3.28</v>
+      </c>
+      <c r="AD119">
         <v>1.25</v>
       </c>
-      <c r="Z119">
-        <v>3.5</v>
-      </c>
-      <c r="AA119">
-        <v>1.92</v>
-      </c>
-      <c r="AB119">
-        <v>1.78</v>
-      </c>
-      <c r="AC119">
-        <v>3.05</v>
-      </c>
-      <c r="AD119">
-        <v>1.33</v>
-      </c>
       <c r="AE119">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF119">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG119">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK119">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O121">
         <v>4</v>
@@ -20041,7 +20041,7 @@
         <v>5.75</v>
       </c>
       <c r="Q121">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R121">
         <v>2.25</v>
@@ -20056,16 +20056,16 @@
         <v>2.74</v>
       </c>
       <c r="V121">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
         <v>1.08</v>
       </c>
       <c r="X121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z121">
         <v>3.5</v>
@@ -20074,19 +20074,19 @@
         <v>1.82</v>
       </c>
       <c r="AB121">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC121">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD121">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE121">
         <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG121">
         <v>1.72</v>
@@ -20105,7 +20105,7 @@
         <v>1.19</v>
       </c>
       <c r="AK121">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O122">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="P122">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA122">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB122">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20400,7 +20400,7 @@
         <v>1.65</v>
       </c>
       <c r="AB123">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC123">
         <v>3.05</v>
@@ -20431,7 +20431,7 @@
         <v>1.23</v>
       </c>
       <c r="AK123">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,80 +21988,80 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O133">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P133">
-        <v>3.8</v>
+        <v>2.81</v>
       </c>
       <c r="Q133">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="R133">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="S133">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T133">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="U133">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="V133">
+        <v>1.88</v>
+      </c>
+      <c r="W133">
+        <v>1.22</v>
+      </c>
+      <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133">
+        <v>1.03</v>
+      </c>
+      <c r="Z133">
+        <v>7.5</v>
+      </c>
+      <c r="AA133">
+        <v>1.32</v>
+      </c>
+      <c r="AB133">
+        <v>3.4</v>
+      </c>
+      <c r="AC133">
         <v>1.8</v>
       </c>
-      <c r="W133">
-        <v>1.19</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>1.07</v>
-      </c>
-      <c r="Z133">
-        <v>6.8</v>
-      </c>
-      <c r="AA133">
-        <v>1.38</v>
-      </c>
-      <c r="AB133">
-        <v>3.04</v>
-      </c>
-      <c r="AC133">
-        <v>1.91</v>
-      </c>
       <c r="AD133">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AE133">
+        <v>1.4</v>
+      </c>
+      <c r="AF133">
+        <v>1.29</v>
+      </c>
+      <c r="AG133">
+        <v>3.3</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ133">
         <v>1.36</v>
       </c>
-      <c r="AF133">
-        <v>1.38</v>
-      </c>
-      <c r="AG133">
-        <v>2.85</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>1.16</v>
-      </c>
       <c r="AK133">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O134">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P134">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="Q134">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="R134">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="S134">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T134">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U134">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V134">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W134">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X134">
         <v>0</v>
       </c>
       <c r="Y134">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z134">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA134">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AB134">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AC134">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD134">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AE134">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF134">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AG134">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK134">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O138">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P138">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -22821,10 +22821,10 @@
         <v>1.49</v>
       </c>
       <c r="T138">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U138">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="V138">
         <v>1.26</v>
@@ -22836,31 +22836,31 @@
         <v>1.04</v>
       </c>
       <c r="Y138">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z138">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="AA138">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB138">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AC138">
         <v>4.3</v>
       </c>
       <c r="AD138">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE138">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF138">
         <v>2</v>
       </c>
       <c r="AG138">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>1.33</v>
       </c>
       <c r="AK138">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23851,7 +23851,7 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK144">
         <v>1.57</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.22</v>
+        <v>1.97</v>
       </c>
       <c r="O26">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U26">
-        <v>2.77</v>
+        <v>3.12</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
+        <v>1.36</v>
+      </c>
+      <c r="Z26">
+        <v>3.1</v>
+      </c>
+      <c r="AA26">
+        <v>2.04</v>
+      </c>
+      <c r="AB26">
+        <v>1.69</v>
+      </c>
+      <c r="AC26">
+        <v>3.45</v>
+      </c>
+      <c r="AD26">
         <v>1.22</v>
       </c>
-      <c r="Z26">
-        <v>4.1</v>
-      </c>
-      <c r="AA26">
-        <v>1.8</v>
-      </c>
-      <c r="AB26">
-        <v>1.9</v>
-      </c>
-      <c r="AC26">
-        <v>3.1</v>
-      </c>
-      <c r="AD26">
-        <v>1.36</v>
-      </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>3.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>11</v>
       </c>
       <c r="Q27">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="R27">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK27">
-        <v>1.68</v>
+        <v>3.54</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4888,16 +4888,16 @@
         <v>2.03</v>
       </c>
       <c r="S28">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T28">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="U28">
         <v>3.3</v>
       </c>
       <c r="V28">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
         <v>1.03</v>
@@ -4918,7 +4918,7 @@
         <v>1.54</v>
       </c>
       <c r="AC28">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD28">
         <v>1.18</v>
@@ -10258,10 +10258,10 @@
         <v>3.1</v>
       </c>
       <c r="P61">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q61">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R61">
         <v>1.88</v>
@@ -10297,7 +10297,7 @@
         <v>1.5</v>
       </c>
       <c r="AC61">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="AD61">
         <v>1.13</v>
@@ -10309,7 +10309,7 @@
         <v>2.25</v>
       </c>
       <c r="AG61">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -15314,16 +15314,16 @@
         <v>1.69</v>
       </c>
       <c r="Q92">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="R92">
         <v>2.08</v>
       </c>
       <c r="S92">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T92">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="U92">
         <v>3.6</v>
@@ -15335,7 +15335,7 @@
         <v>1.04</v>
       </c>
       <c r="X92">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y92">
         <v>1.5</v>
@@ -15344,10 +15344,10 @@
         <v>2.7</v>
       </c>
       <c r="AA92">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AB92">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AC92">
         <v>4.5</v>
@@ -15359,7 +15359,7 @@
         <v>1.05</v>
       </c>
       <c r="AF92">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG92">
         <v>1.6</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="O134">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="P134">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="Q134">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="R134">
-        <v>2.79</v>
+        <v>2.61</v>
       </c>
       <c r="S134">
+        <v>1.18</v>
+      </c>
+      <c r="T134">
+        <v>4.6</v>
+      </c>
+      <c r="U134">
+        <v>1.9</v>
+      </c>
+      <c r="V134">
+        <v>1.8</v>
+      </c>
+      <c r="W134">
+        <v>1.2</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>1.11</v>
+      </c>
+      <c r="Z134">
+        <v>6.81</v>
+      </c>
+      <c r="AA134">
+        <v>1.35</v>
+      </c>
+      <c r="AB134">
+        <v>3.04</v>
+      </c>
+      <c r="AC134">
+        <v>1.95</v>
+      </c>
+      <c r="AD134">
+        <v>1.88</v>
+      </c>
+      <c r="AE134">
+        <v>1.36</v>
+      </c>
+      <c r="AF134">
+        <v>1.36</v>
+      </c>
+      <c r="AG134">
+        <v>2.88</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
         <v>1.17</v>
       </c>
-      <c r="T134">
-        <v>5.2</v>
-      </c>
-      <c r="U134">
-        <v>1.85</v>
-      </c>
-      <c r="V134">
-        <v>1.81</v>
-      </c>
-      <c r="W134">
-        <v>1.22</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>1.06</v>
-      </c>
-      <c r="Z134">
-        <v>7.5</v>
-      </c>
-      <c r="AA134">
-        <v>1.33</v>
-      </c>
-      <c r="AB134">
-        <v>3.4</v>
-      </c>
-      <c r="AC134">
-        <v>1.75</v>
-      </c>
-      <c r="AD134">
-        <v>1.99</v>
-      </c>
-      <c r="AE134">
-        <v>1.45</v>
-      </c>
-      <c r="AF134">
-        <v>1.3</v>
-      </c>
-      <c r="AG134">
-        <v>3.4</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.18</v>
-      </c>
       <c r="AK134">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
+        <v>2.03</v>
+      </c>
+      <c r="O135">
+        <v>3.93</v>
+      </c>
+      <c r="P135">
+        <v>2.63</v>
+      </c>
+      <c r="Q135">
+        <v>2.5</v>
+      </c>
+      <c r="R135">
+        <v>2.79</v>
+      </c>
+      <c r="S135">
+        <v>1.17</v>
+      </c>
+      <c r="T135">
+        <v>5.2</v>
+      </c>
+      <c r="U135">
+        <v>1.85</v>
+      </c>
+      <c r="V135">
+        <v>1.81</v>
+      </c>
+      <c r="W135">
+        <v>1.22</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>1.06</v>
+      </c>
+      <c r="Z135">
+        <v>7.5</v>
+      </c>
+      <c r="AA135">
+        <v>1.33</v>
+      </c>
+      <c r="AB135">
+        <v>3.4</v>
+      </c>
+      <c r="AC135">
+        <v>1.75</v>
+      </c>
+      <c r="AD135">
+        <v>1.99</v>
+      </c>
+      <c r="AE135">
+        <v>1.45</v>
+      </c>
+      <c r="AF135">
+        <v>1.3</v>
+      </c>
+      <c r="AG135">
+        <v>3.4</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>1.18</v>
+      </c>
+      <c r="AK135">
         <v>1.67</v>
-      </c>
-      <c r="O135">
-        <v>4</v>
-      </c>
-      <c r="P135">
-        <v>4.2</v>
-      </c>
-      <c r="Q135">
-        <v>2.16</v>
-      </c>
-      <c r="R135">
-        <v>2.61</v>
-      </c>
-      <c r="S135">
-        <v>1.18</v>
-      </c>
-      <c r="T135">
-        <v>4.6</v>
-      </c>
-      <c r="U135">
-        <v>1.9</v>
-      </c>
-      <c r="V135">
-        <v>1.8</v>
-      </c>
-      <c r="W135">
-        <v>1.2</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>1.11</v>
-      </c>
-      <c r="Z135">
-        <v>6.81</v>
-      </c>
-      <c r="AA135">
-        <v>1.35</v>
-      </c>
-      <c r="AB135">
-        <v>3.04</v>
-      </c>
-      <c r="AC135">
-        <v>1.95</v>
-      </c>
-      <c r="AD135">
-        <v>1.88</v>
-      </c>
-      <c r="AE135">
-        <v>1.36</v>
-      </c>
-      <c r="AF135">
-        <v>1.36</v>
-      </c>
-      <c r="AG135">
-        <v>2.88</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.17</v>
-      </c>
-      <c r="AK135">
-        <v>2.08</v>
       </c>
       <c r="AL135">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="Q7">
-        <v>3.18</v>
+        <v>2.51</v>
       </c>
       <c r="R7">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
+        <v>2.59</v>
+      </c>
+      <c r="U7">
         <v>3</v>
       </c>
-      <c r="U7">
-        <v>2.65</v>
-      </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
         <v>1.05</v>
       </c>
       <c r="X7">
+        <v>1.05</v>
+      </c>
+      <c r="Y7">
+        <v>1.37</v>
+      </c>
+      <c r="Z7">
+        <v>2.85</v>
+      </c>
+      <c r="AA7">
+        <v>2.13</v>
+      </c>
+      <c r="AB7">
+        <v>1.71</v>
+      </c>
+      <c r="AC7">
+        <v>3.62</v>
+      </c>
+      <c r="AD7">
+        <v>1.21</v>
+      </c>
+      <c r="AE7">
         <v>1.04</v>
       </c>
-      <c r="Y7">
-        <v>1.29</v>
-      </c>
-      <c r="Z7">
-        <v>3.38</v>
-      </c>
-      <c r="AA7">
-        <v>1.9</v>
-      </c>
-      <c r="AB7">
-        <v>1.9</v>
-      </c>
-      <c r="AC7">
-        <v>3.16</v>
-      </c>
-      <c r="AD7">
+      <c r="AF7">
+        <v>1.86</v>
+      </c>
+      <c r="AG7">
+        <v>1.85</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.33</v>
       </c>
-      <c r="AE7">
-        <v>1.11</v>
-      </c>
-      <c r="AF7">
-        <v>1.64</v>
-      </c>
-      <c r="AG7">
-        <v>2.1</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.35</v>
-      </c>
       <c r="AK7">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q8">
-        <v>2.51</v>
+        <v>3.18</v>
       </c>
       <c r="R8">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
         <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>2.85</v>
+        <v>3.38</v>
       </c>
       <c r="AA8">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AB8">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AC8">
-        <v>3.62</v>
+        <v>3.16</v>
       </c>
       <c r="AD8">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK8">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
         <v>2.6</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R13">
         <v>2.3</v>
@@ -2446,25 +2446,25 @@
         <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
         <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
         <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="AA13">
         <v>1.64</v>
@@ -2501,7 +2501,7 @@
         <v>1.44</v>
       </c>
       <c r="AK13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O20">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P20">
-        <v>4.92</v>
+        <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R20">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="S20">
         <v>1.16</v>
@@ -3590,10 +3590,10 @@
         <v>4.3</v>
       </c>
       <c r="U20">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V20">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
         <v>1.22</v>
@@ -3608,7 +3608,7 @@
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
         <v>3.04</v>
@@ -3623,10 +3623,10 @@
         <v>1.4</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG20">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,22 +3732,22 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q21">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R21">
         <v>2.6</v>
       </c>
       <c r="S21">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T21">
         <v>4.15</v>
@@ -3765,25 +3765,25 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB21">
         <v>3.13</v>
       </c>
       <c r="AC21">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AD21">
         <v>1.9</v>
       </c>
       <c r="AE21">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF21">
         <v>1.33</v>
@@ -3895,40 +3895,40 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O22">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P22">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R22">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="S22">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T22">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V22">
         <v>1.69</v>
       </c>
       <c r="W22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z22">
         <v>6.5</v>
@@ -3940,19 +3940,19 @@
         <v>2.7</v>
       </c>
       <c r="AC22">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AD22">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF22">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK22">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26">
+        <v>3.5</v>
+      </c>
+      <c r="Q26">
+        <v>2.75</v>
+      </c>
+      <c r="R26">
+        <v>2.03</v>
+      </c>
+      <c r="S26">
+        <v>1.51</v>
+      </c>
+      <c r="T26">
+        <v>2.52</v>
+      </c>
+      <c r="U26">
         <v>3.3</v>
       </c>
-      <c r="P26">
-        <v>3.4</v>
-      </c>
-      <c r="Q26">
-        <v>2.62</v>
-      </c>
-      <c r="R26">
-        <v>1.99</v>
-      </c>
-      <c r="S26">
-        <v>1.41</v>
-      </c>
-      <c r="T26">
-        <v>2.75</v>
-      </c>
-      <c r="U26">
-        <v>3.12</v>
-      </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
         <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y26">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z26">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="AA26">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AB26">
+        <v>1.54</v>
+      </c>
+      <c r="AC26">
+        <v>4.2</v>
+      </c>
+      <c r="AD26">
+        <v>1.18</v>
+      </c>
+      <c r="AE26">
+        <v>1.01</v>
+      </c>
+      <c r="AF26">
+        <v>2.02</v>
+      </c>
+      <c r="AG26">
         <v>1.69</v>
-      </c>
-      <c r="AC26">
-        <v>3.45</v>
-      </c>
-      <c r="AD26">
-        <v>1.22</v>
-      </c>
-      <c r="AE26">
-        <v>1.07</v>
-      </c>
-      <c r="AF26">
-        <v>1.83</v>
-      </c>
-      <c r="AG26">
-        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q28">
+        <v>2.62</v>
+      </c>
+      <c r="R28">
+        <v>1.99</v>
+      </c>
+      <c r="S28">
+        <v>1.41</v>
+      </c>
+      <c r="T28">
         <v>2.75</v>
       </c>
-      <c r="R28">
-        <v>2.03</v>
-      </c>
-      <c r="S28">
-        <v>1.51</v>
-      </c>
-      <c r="T28">
-        <v>2.52</v>
-      </c>
       <c r="U28">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
         <v>1.03</v>
       </c>
       <c r="X28">
+        <v>1.02</v>
+      </c>
+      <c r="Y28">
+        <v>1.36</v>
+      </c>
+      <c r="Z28">
+        <v>3.1</v>
+      </c>
+      <c r="AA28">
+        <v>2.04</v>
+      </c>
+      <c r="AB28">
+        <v>1.69</v>
+      </c>
+      <c r="AC28">
+        <v>3.45</v>
+      </c>
+      <c r="AD28">
+        <v>1.22</v>
+      </c>
+      <c r="AE28">
         <v>1.07</v>
       </c>
-      <c r="Y28">
-        <v>1.41</v>
-      </c>
-      <c r="Z28">
-        <v>2.52</v>
-      </c>
-      <c r="AA28">
-        <v>2.27</v>
-      </c>
-      <c r="AB28">
-        <v>1.54</v>
-      </c>
-      <c r="AC28">
-        <v>4.2</v>
-      </c>
-      <c r="AD28">
-        <v>1.18</v>
-      </c>
-      <c r="AE28">
-        <v>1.01</v>
-      </c>
       <c r="AF28">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL28">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O5">
+        <v>2.95</v>
+      </c>
+      <c r="P5">
         <v>3.2</v>
       </c>
-      <c r="P5">
-        <v>3.4</v>
-      </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="O9">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
         <v>1.96</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="R9">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
         <v>3.08</v>
@@ -1803,16 +1803,16 @@
         <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z9">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="AA9">
         <v>1.71</v>
@@ -1821,10 +1821,10 @@
         <v>2.07</v>
       </c>
       <c r="AC9">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
         <v>1.1</v>
@@ -1833,7 +1833,7 @@
         <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,13 +1942,13 @@
         <v>2.17</v>
       </c>
       <c r="O10">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="P10">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q10">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="R10">
         <v>2.06</v>
@@ -1960,40 +1960,40 @@
         <v>2.82</v>
       </c>
       <c r="U10">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
         <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB10">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD10">
         <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
         <v>2.15</v>
@@ -2012,7 +2012,7 @@
         <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.01</v>
+        <v>2.35</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="Q11">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S11">
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
+        <v>3.4</v>
+      </c>
+      <c r="AA11">
+        <v>1.96</v>
+      </c>
+      <c r="AB11">
+        <v>1.8</v>
+      </c>
+      <c r="AC11">
         <v>3.42</v>
       </c>
-      <c r="AA11">
-        <v>1.8</v>
-      </c>
-      <c r="AB11">
-        <v>1.88</v>
-      </c>
-      <c r="AC11">
-        <v>3.1</v>
-      </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.37</v>
+        <v>4.45</v>
       </c>
       <c r="O12">
+        <v>3.75</v>
+      </c>
+      <c r="P12">
+        <v>1.47</v>
+      </c>
+      <c r="Q12">
+        <v>5</v>
+      </c>
+      <c r="R12">
+        <v>2.25</v>
+      </c>
+      <c r="S12">
+        <v>1.35</v>
+      </c>
+      <c r="T12">
+        <v>2.95</v>
+      </c>
+      <c r="U12">
+        <v>2.66</v>
+      </c>
+      <c r="V12">
+        <v>1.42</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.23</v>
+      </c>
+      <c r="Z12">
+        <v>3.61</v>
+      </c>
+      <c r="AA12">
+        <v>1.8</v>
+      </c>
+      <c r="AB12">
+        <v>1.88</v>
+      </c>
+      <c r="AC12">
         <v>3.25</v>
       </c>
-      <c r="P12">
-        <v>2.55</v>
-      </c>
-      <c r="Q12">
-        <v>3.3</v>
-      </c>
-      <c r="R12">
-        <v>2.15</v>
-      </c>
-      <c r="S12">
-        <v>1.42</v>
-      </c>
-      <c r="T12">
-        <v>2.7</v>
-      </c>
-      <c r="U12">
-        <v>2.73</v>
-      </c>
-      <c r="V12">
+      <c r="AD12">
         <v>1.33</v>
       </c>
-      <c r="W12">
-        <v>1.02</v>
-      </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
-      <c r="Y12">
-        <v>1.3</v>
-      </c>
-      <c r="Z12">
-        <v>3.25</v>
-      </c>
-      <c r="AA12">
-        <v>1.98</v>
-      </c>
-      <c r="AB12">
-        <v>1.8</v>
-      </c>
-      <c r="AC12">
-        <v>3.59</v>
-      </c>
-      <c r="AD12">
-        <v>1.29</v>
-      </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG12">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AK12">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>2.3</v>
       </c>
       <c r="O13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q13">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R13">
         <v>2.3</v>
@@ -2446,25 +2446,25 @@
         <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
         <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="AA13">
         <v>1.64</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q15">
         <v>3.62</v>
@@ -2769,16 +2769,16 @@
         <v>2.02</v>
       </c>
       <c r="S15">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
         <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
         <v>1.03</v>
@@ -2790,7 +2790,7 @@
         <v>1.35</v>
       </c>
       <c r="Z15">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="AA15">
         <v>2.25</v>
@@ -2799,7 +2799,7 @@
         <v>1.7</v>
       </c>
       <c r="AC15">
-        <v>3.94</v>
+        <v>4.03</v>
       </c>
       <c r="AD15">
         <v>1.21</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK15">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="O16">
+        <v>3.08</v>
+      </c>
+      <c r="P16">
+        <v>2.03</v>
+      </c>
+      <c r="Q16">
+        <v>3.6</v>
+      </c>
+      <c r="R16">
+        <v>2.15</v>
+      </c>
+      <c r="S16">
+        <v>1.37</v>
+      </c>
+      <c r="T16">
+        <v>2.71</v>
+      </c>
+      <c r="U16">
+        <v>2.78</v>
+      </c>
+      <c r="V16">
+        <v>1.4</v>
+      </c>
+      <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
+        <v>1.04</v>
+      </c>
+      <c r="Y16">
+        <v>1.32</v>
+      </c>
+      <c r="Z16">
+        <v>3.28</v>
+      </c>
+      <c r="AA16">
+        <v>1.89</v>
+      </c>
+      <c r="AB16">
+        <v>1.79</v>
+      </c>
+      <c r="AC16">
         <v>3.2</v>
       </c>
-      <c r="P16">
-        <v>2.28</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O17">
+        <v>3.13</v>
+      </c>
+      <c r="P17">
+        <v>2.33</v>
+      </c>
+      <c r="Q17">
+        <v>3.12</v>
+      </c>
+      <c r="R17">
+        <v>2.05</v>
+      </c>
+      <c r="S17">
+        <v>1.38</v>
+      </c>
+      <c r="T17">
+        <v>2.75</v>
+      </c>
+      <c r="U17">
+        <v>2.79</v>
+      </c>
+      <c r="V17">
+        <v>1.4</v>
+      </c>
+      <c r="W17">
+        <v>1.07</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1.25</v>
+      </c>
+      <c r="Z17">
+        <v>3.28</v>
+      </c>
+      <c r="AA17">
+        <v>1.96</v>
+      </c>
+      <c r="AB17">
+        <v>1.8</v>
+      </c>
+      <c r="AC17">
         <v>3.2</v>
       </c>
-      <c r="P17">
-        <v>2.65</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O18">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="O19">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P19">
         <v>7.5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="O20">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="Q20">
         <v>1.96</v>
       </c>
       <c r="R20">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="S20">
         <v>1.16</v>
@@ -3590,7 +3590,7 @@
         <v>4.3</v>
       </c>
       <c r="U20">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V20">
         <v>1.85</v>
@@ -3608,25 +3608,25 @@
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
         <v>3.04</v>
       </c>
       <c r="AC20">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD20">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AE20">
         <v>1.4</v>
       </c>
       <c r="AF20">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="O21">
         <v>4</v>
       </c>
       <c r="P21">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -3774,13 +3774,13 @@
         <v>1.36</v>
       </c>
       <c r="AB21">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="AC21">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AD21">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE21">
         <v>1.4</v>
@@ -3895,37 +3895,37 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="O22">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="P22">
-        <v>8</v>
+        <v>9.15</v>
       </c>
       <c r="Q22">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R22">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="S22">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V22">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.1</v>
@@ -3940,19 +3940,19 @@
         <v>2.7</v>
       </c>
       <c r="AC22">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AD22">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE22">
         <v>1.3</v>
       </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG22">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK22">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,37 +4221,37 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.41</v>
+        <v>1.95</v>
       </c>
       <c r="O24">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>2.13</v>
+        <v>3.8</v>
       </c>
       <c r="Q24">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
         <v>1.3</v>
@@ -4260,7 +4260,7 @@
         <v>3.4</v>
       </c>
       <c r="AA24">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB24">
         <v>1.8</v>
@@ -4269,16 +4269,16 @@
         <v>3.4</v>
       </c>
       <c r="AD24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
         <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,37 +4384,37 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
+        <v>2.5</v>
+      </c>
+      <c r="Q25">
         <v>2.75</v>
-      </c>
-      <c r="Q25">
-        <v>3</v>
       </c>
       <c r="R25">
         <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U25">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W25">
         <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.24</v>
@@ -4423,10 +4423,10 @@
         <v>3.34</v>
       </c>
       <c r="AA25">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
         <v>2.75</v>
@@ -4438,7 +4438,7 @@
         <v>1.07</v>
       </c>
       <c r="AF25">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
         <v>2.23</v>
@@ -4457,7 +4457,7 @@
         <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
       </c>
       <c r="R26">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="S26">
         <v>1.51</v>
       </c>
       <c r="T26">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="U26">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W26">
         <v>1.03</v>
@@ -4580,7 +4580,7 @@
         <v>1.07</v>
       </c>
       <c r="Y26">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z26">
         <v>2.52</v>
@@ -4598,7 +4598,7 @@
         <v>1.18</v>
       </c>
       <c r="AE26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF26">
         <v>2.02</v>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4713,13 +4713,13 @@
         <v>1.22</v>
       </c>
       <c r="O27">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P27">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="Q27">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="R27">
         <v>2.5</v>
@@ -4728,13 +4728,13 @@
         <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
         <v>1.1</v>
@@ -4752,7 +4752,7 @@
         <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AC27">
         <v>3.1</v>
@@ -4761,10 +4761,10 @@
         <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG27">
         <v>1.57</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O28">
         <v>3.3</v>
       </c>
       <c r="P28">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q28">
         <v>2.62</v>
@@ -4891,10 +4891,10 @@
         <v>1.41</v>
       </c>
       <c r="T28">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U28">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="V28">
         <v>1.36</v>
@@ -4903,7 +4903,7 @@
         <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
         <v>1.36</v>
@@ -4924,7 +4924,7 @@
         <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
         <v>1.83</v>
@@ -5109,7 +5109,7 @@
         <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O34">
         <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q34">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S34">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB34">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AC34">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD34">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK34">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>4.46</v>
       </c>
       <c r="P35">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S35">
         <v>1.31</v>
@@ -6038,7 +6038,7 @@
         <v>2.54</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6053,10 +6053,10 @@
         <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB35">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AC35">
         <v>2.74</v>
@@ -6071,7 +6071,7 @@
         <v>1.78</v>
       </c>
       <c r="AG35">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
         <v>2.58</v>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q36">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S36">
         <v>1.24</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U36">
         <v>2.15</v>
       </c>
       <c r="V36">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
         <v>1.14</v>
@@ -6213,13 +6213,13 @@
         <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>4.98</v>
+        <v>4.65</v>
       </c>
       <c r="AA36">
         <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC36">
         <v>2.27</v>
@@ -6234,7 +6234,7 @@
         <v>1.52</v>
       </c>
       <c r="AG36">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6349,55 +6349,55 @@
         <v>4</v>
       </c>
       <c r="Q37">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U37">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V37">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z37">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA37">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB37">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD37">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="O38">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
         <v>2.15</v>
@@ -6515,52 +6515,52 @@
         <v>3.39</v>
       </c>
       <c r="R38">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="U38">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="V38">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.31</v>
+      </c>
+      <c r="Z38">
+        <v>3.05</v>
+      </c>
+      <c r="AA38">
+        <v>1.96</v>
+      </c>
+      <c r="AB38">
+        <v>1.8</v>
+      </c>
+      <c r="AC38">
+        <v>3.28</v>
+      </c>
+      <c r="AD38">
+        <v>1.25</v>
+      </c>
+      <c r="AE38">
         <v>1.07</v>
-      </c>
-      <c r="X38">
-        <v>1.04</v>
-      </c>
-      <c r="Y38">
-        <v>1.32</v>
-      </c>
-      <c r="Z38">
-        <v>3.24</v>
-      </c>
-      <c r="AA38">
-        <v>2.05</v>
-      </c>
-      <c r="AB38">
-        <v>1.72</v>
-      </c>
-      <c r="AC38">
-        <v>3.42</v>
-      </c>
-      <c r="AD38">
-        <v>1.23</v>
-      </c>
-      <c r="AE38">
-        <v>1.06</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="AK38">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O39">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="P39">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="Q39">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="R39">
         <v>1.91</v>
@@ -6693,34 +6693,34 @@
         <v>1.26</v>
       </c>
       <c r="W39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
         <v>1.06</v>
       </c>
       <c r="Y39">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Z39">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AA39">
         <v>2.35</v>
       </c>
       <c r="AB39">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC39">
         <v>4.5</v>
       </c>
       <c r="AD39">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF39">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG39">
         <v>1.75</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK39">
         <v>1.47</v>
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="Q40">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="R40">
         <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T40">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="U40">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W40">
         <v>1.11</v>
@@ -6862,31 +6862,31 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA40">
         <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC40">
         <v>2.88</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
         <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q41">
         <v>2.17</v>
@@ -7007,16 +7007,16 @@
         <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T41">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="U41">
-        <v>2.87</v>
+        <v>3.13</v>
       </c>
       <c r="V41">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W41">
         <v>1.05</v>
@@ -7025,47 +7025,47 @@
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA41">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB41">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC41">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AD41">
+        <v>1.22</v>
+      </c>
+      <c r="AE41">
+        <v>1.07</v>
+      </c>
+      <c r="AF41">
+        <v>1.95</v>
+      </c>
+      <c r="AG41">
+        <v>1.63</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.2</v>
       </c>
-      <c r="AE41">
-        <v>1.03</v>
-      </c>
-      <c r="AF41">
-        <v>2.1</v>
-      </c>
-      <c r="AG41">
-        <v>1.66</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.09</v>
-      </c>
       <c r="AK41">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,7 +7164,7 @@
         <v>6</v>
       </c>
       <c r="Q42">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R42">
         <v>2.2</v>
@@ -7173,37 +7173,37 @@
         <v>1.35</v>
       </c>
       <c r="T42">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="U42">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W42">
         <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
         <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA42">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB42">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC42">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD42">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE42">
         <v>1.06</v>
@@ -7212,7 +7212,7 @@
         <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O43">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R43">
         <v>2.1</v>
@@ -7342,10 +7342,10 @@
         <v>3</v>
       </c>
       <c r="V43">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
         <v>1.06</v>
@@ -7354,13 +7354,13 @@
         <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AA43">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB43">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC43">
         <v>3.42</v>
@@ -7369,13 +7369,13 @@
         <v>1.25</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
         <v>1.8</v>
       </c>
       <c r="AG43">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK43">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>3.53</v>
       </c>
       <c r="P46">
         <v>1.75</v>
       </c>
       <c r="Q46">
-        <v>4.16</v>
+        <v>4.01</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S46">
         <v>1.19</v>
       </c>
       <c r="T46">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="U46">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="V46">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W46">
         <v>1.17</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
         <v>1.07</v>
       </c>
       <c r="Z46">
-        <v>6.13</v>
+        <v>6.2</v>
       </c>
       <c r="AA46">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB46">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AC46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD46">
         <v>1.8</v>
       </c>
       <c r="AE46">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG46">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.91</v>
       </c>
       <c r="AK46">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="O47">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7988,10 +7988,10 @@
         <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V47">
         <v>1.48</v>
@@ -8000,10 +8000,10 @@
         <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z47">
         <v>3.8</v>
@@ -8012,7 +8012,7 @@
         <v>1.8</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC47">
         <v>2.8</v>
@@ -8027,7 +8027,7 @@
         <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.72</v>
+        <v>3.23</v>
       </c>
       <c r="O48">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="P48">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="Q48">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="R48">
         <v>2.04</v>
       </c>
       <c r="S48">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T48">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U48">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V48">
+        <v>1.32</v>
+      </c>
+      <c r="W48">
+        <v>1.01</v>
+      </c>
+      <c r="X48">
+        <v>1.01</v>
+      </c>
+      <c r="Y48">
         <v>1.35</v>
       </c>
-      <c r="W48">
-        <v>1.04</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.36</v>
-      </c>
       <c r="Z48">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA48">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AB48">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC48">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AD48">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF48">
         <v>1.83</v>
       </c>
       <c r="AG48">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8326,34 +8326,34 @@
         <v>0</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE49">
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>1.97</v>
       </c>
       <c r="AG50">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8625,16 +8625,16 @@
         <v>1.67</v>
       </c>
       <c r="O51">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
         <v>4.67</v>
       </c>
       <c r="Q51">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
         <v>1.36</v>
@@ -8649,22 +8649,22 @@
         <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA51">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
         <v>2.92</v>
@@ -8673,7 +8673,7 @@
         <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
         <v>1.83</v>
@@ -8695,7 +8695,7 @@
         <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,37 +8785,37 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="O52">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P52">
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="Q52">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
-        <v>2.91</v>
+        <v>3.16</v>
       </c>
       <c r="U52">
         <v>2.45</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.22</v>
@@ -8827,7 +8827,7 @@
         <v>1.7</v>
       </c>
       <c r="AB52">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC52">
         <v>2.88</v>
@@ -8836,13 +8836,13 @@
         <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK52">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,31 +8948,31 @@
         </is>
       </c>
       <c r="N53">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q53">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S53">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T53">
-        <v>3.21</v>
+        <v>2.91</v>
       </c>
       <c r="U53">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V53">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W53">
         <v>1.09</v>
@@ -8981,19 +8981,19 @@
         <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z53">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AA53">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB53">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC53">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD53">
         <v>1.42</v>
@@ -9002,10 +9002,10 @@
         <v>1.16</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>2.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O56">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q56">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R56">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="S56">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
         <v>2.5</v>
       </c>
       <c r="V56">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W56">
         <v>1.06</v>
@@ -9470,28 +9470,28 @@
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z56">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA56">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB56">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC56">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD56">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE56">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG56">
         <v>2.15</v>
@@ -9600,16 +9600,16 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q57">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="R57">
         <v>2.5</v>
@@ -9621,13 +9621,13 @@
         <v>4</v>
       </c>
       <c r="U57">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V57">
         <v>1.7</v>
       </c>
       <c r="W57">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9636,13 +9636,13 @@
         <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>6.23</v>
+        <v>6.3</v>
       </c>
       <c r="AA57">
         <v>1.42</v>
       </c>
       <c r="AB57">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
         <v>2.02</v>
@@ -9651,13 +9651,13 @@
         <v>1.75</v>
       </c>
       <c r="AE57">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF57">
         <v>1.37</v>
       </c>
       <c r="AG57">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O58">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>3.23</v>
+        <v>2.93</v>
       </c>
       <c r="Q58">
         <v>2.95</v>
@@ -9790,22 +9790,22 @@
         <v>1.36</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
         <v>1.06</v>
       </c>
       <c r="Y58">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z58">
         <v>2.85</v>
       </c>
       <c r="AA58">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB58">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC58">
         <v>4.2</v>
@@ -9814,13 +9814,13 @@
         <v>1.22</v>
       </c>
       <c r="AE58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG58">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="O61">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="P61">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="Q61">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="R61">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S61">
         <v>1.55</v>
@@ -10273,7 +10273,7 @@
         <v>2.28</v>
       </c>
       <c r="U61">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V61">
         <v>1.23</v>
@@ -10291,13 +10291,13 @@
         <v>2.41</v>
       </c>
       <c r="AA61">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AB61">
         <v>1.5</v>
       </c>
       <c r="AC61">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD61">
         <v>1.13</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="O62">
-        <v>3.65</v>
+        <v>3.37</v>
       </c>
       <c r="P62">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="Q62">
         <v>3.7</v>
@@ -10457,16 +10457,16 @@
         <v>1.6</v>
       </c>
       <c r="AB62">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC62">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD62">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE62">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
         <v>1.57</v>
@@ -10584,19 +10584,19 @@
         <v>3.12</v>
       </c>
       <c r="P63">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
       </c>
       <c r="R63">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S63">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T63">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U63">
         <v>3.08</v>
@@ -10620,7 +10620,7 @@
         <v>2.12</v>
       </c>
       <c r="AB63">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC63">
         <v>3.65</v>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AK63">
         <v>1.33</v>
@@ -10750,16 +10750,16 @@
         <v>2.45</v>
       </c>
       <c r="Q64">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R64">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S64">
         <v>1.46</v>
       </c>
       <c r="T64">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U64">
         <v>3.25</v>
@@ -10774,13 +10774,13 @@
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z64">
         <v>2.7</v>
       </c>
       <c r="AA64">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB64">
         <v>1.61</v>
@@ -10814,7 +10814,7 @@
         <v>1.45</v>
       </c>
       <c r="AK64">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,7 +11076,7 @@
         <v>2.38</v>
       </c>
       <c r="Q66">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R66">
         <v>2.1</v>
@@ -11085,7 +11085,7 @@
         <v>1.32</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="U66">
         <v>2.71</v>
@@ -11094,22 +11094,22 @@
         <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
         <v>1</v>
       </c>
       <c r="Y66">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="AA66">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AB66">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC66">
         <v>3.14</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK66">
         <v>1.41</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
+        <v>3.3</v>
+      </c>
+      <c r="O67">
         <v>3.5</v>
       </c>
-      <c r="O67">
-        <v>3.7</v>
-      </c>
       <c r="P67">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q67">
         <v>3.8</v>
@@ -11251,13 +11251,13 @@
         <v>3.58</v>
       </c>
       <c r="U67">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="V67">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W67">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11266,13 +11266,13 @@
         <v>1.12</v>
       </c>
       <c r="Z67">
-        <v>4.7</v>
+        <v>5.01</v>
       </c>
       <c r="AA67">
         <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC67">
         <v>2.4</v>
@@ -11281,13 +11281,13 @@
         <v>1.56</v>
       </c>
       <c r="AE67">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG67">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AK67">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O68">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P68">
-        <v>3.41</v>
+        <v>3.05</v>
       </c>
       <c r="Q68">
         <v>2.38</v>
       </c>
       <c r="R68">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S68">
         <v>1.2</v>
       </c>
       <c r="T68">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="U68">
         <v>2.15</v>
@@ -11432,13 +11432,13 @@
         <v>5.5</v>
       </c>
       <c r="AA68">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB68">
         <v>2.63</v>
       </c>
       <c r="AC68">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD68">
         <v>1.56</v>
@@ -11450,7 +11450,7 @@
         <v>1.44</v>
       </c>
       <c r="AG68">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK68">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="O69">
         <v>3.2</v>
@@ -11565,7 +11565,7 @@
         <v>2.62</v>
       </c>
       <c r="Q69">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="R69">
         <v>2.06</v>
@@ -11577,10 +11577,10 @@
         <v>2.82</v>
       </c>
       <c r="U69">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W69">
         <v>1.07</v>
@@ -11589,31 +11589,31 @@
         <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z69">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="AA69">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB69">
         <v>1.9</v>
       </c>
       <c r="AC69">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE69">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF69">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG69">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK69">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11882,16 +11882,16 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O71">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="P71">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="Q71">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R71">
         <v>2.47</v>
@@ -11900,13 +11900,13 @@
         <v>1.18</v>
       </c>
       <c r="T71">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="U71">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="W71">
         <v>1.17</v>
@@ -11915,25 +11915,25 @@
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>6.23</v>
+        <v>5.7</v>
       </c>
       <c r="AA71">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB71">
         <v>2.75</v>
       </c>
       <c r="AC71">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AD71">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE71">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF71">
         <v>1.36</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
         <v>1.73</v>
@@ -12048,58 +12048,58 @@
         <v>3.2</v>
       </c>
       <c r="O72">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q72">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R72">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="S72">
         <v>1.3</v>
       </c>
       <c r="T72">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U72">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V72">
+        <v>1.5</v>
+      </c>
+      <c r="W72">
+        <v>1.07</v>
+      </c>
+      <c r="X72">
+        <v>1.04</v>
+      </c>
+      <c r="Y72">
+        <v>1.18</v>
+      </c>
+      <c r="Z72">
+        <v>4.1</v>
+      </c>
+      <c r="AA72">
+        <v>1.66</v>
+      </c>
+      <c r="AB72">
+        <v>2.15</v>
+      </c>
+      <c r="AC72">
+        <v>2.68</v>
+      </c>
+      <c r="AD72">
+        <v>1.37</v>
+      </c>
+      <c r="AE72">
+        <v>1.11</v>
+      </c>
+      <c r="AF72">
         <v>1.55</v>
-      </c>
-      <c r="W72">
-        <v>1.11</v>
-      </c>
-      <c r="X72">
-        <v>1.02</v>
-      </c>
-      <c r="Y72">
-        <v>1.16</v>
-      </c>
-      <c r="Z72">
-        <v>4.4</v>
-      </c>
-      <c r="AA72">
-        <v>1.65</v>
-      </c>
-      <c r="AB72">
-        <v>2.1</v>
-      </c>
-      <c r="AC72">
-        <v>2.65</v>
-      </c>
-      <c r="AD72">
-        <v>1.42</v>
-      </c>
-      <c r="AE72">
-        <v>1.13</v>
-      </c>
-      <c r="AF72">
-        <v>1.57</v>
       </c>
       <c r="AG72">
         <v>2.25</v>
@@ -12118,7 +12118,7 @@
         <v>1.68</v>
       </c>
       <c r="AK72">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,13 +12211,13 @@
         <v>2.78</v>
       </c>
       <c r="O73">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="Q73">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R73">
         <v>2.05</v>
@@ -12226,7 +12226,7 @@
         <v>1.36</v>
       </c>
       <c r="T73">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U73">
         <v>2.79</v>
@@ -12238,25 +12238,25 @@
         <v>1.03</v>
       </c>
       <c r="X73">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z73">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA73">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB73">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AC73">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD73">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
         <v>1.05</v>
@@ -12265,7 +12265,7 @@
         <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O74">
         <v>3.3</v>
@@ -12389,10 +12389,10 @@
         <v>1.35</v>
       </c>
       <c r="T74">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="U74">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V74">
         <v>1.44</v>
@@ -12401,13 +12401,13 @@
         <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
         <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="AA74">
         <v>1.75</v>
@@ -12428,7 +12428,7 @@
         <v>1.62</v>
       </c>
       <c r="AG74">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12537,31 +12537,31 @@
         <v>1.18</v>
       </c>
       <c r="O75">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="P75">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="Q75">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R75">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="S75">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
         <v>3.25</v>
       </c>
       <c r="U75">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V75">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12570,19 +12570,19 @@
         <v>1.21</v>
       </c>
       <c r="Z75">
-        <v>3.9</v>
+        <v>4.11</v>
       </c>
       <c r="AA75">
         <v>1.7</v>
       </c>
       <c r="AB75">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AC75">
         <v>2.75</v>
       </c>
       <c r="AD75">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE75">
         <v>1.13</v>
@@ -12591,7 +12591,7 @@
         <v>2.4</v>
       </c>
       <c r="AG75">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AK75">
         <v>4.15</v>
@@ -12860,25 +12860,25 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="O77">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="P77">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q77">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="R77">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="S77">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T77">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="U77">
         <v>3.16</v>
@@ -12899,16 +12899,16 @@
         <v>2.74</v>
       </c>
       <c r="AA77">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AB77">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC77">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="AD77">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE77">
         <v>1.02</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O78">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P78">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q78">
         <v>2.24</v>
@@ -13047,34 +13047,34 @@
         <v>2.5</v>
       </c>
       <c r="V78">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W78">
         <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="AA78">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB78">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC78">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD78">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
         <v>1.64</v>
@@ -13186,49 +13186,49 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="O79">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P79">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
         <v>2.7</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
         <v>1.36</v>
       </c>
       <c r="T79">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="U79">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="V79">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
         <v>1.07</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z79">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA79">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB79">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AC79">
         <v>2.83</v>
@@ -13237,7 +13237,7 @@
         <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF79">
         <v>1.7</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13352,25 +13352,25 @@
         <v>3</v>
       </c>
       <c r="O80">
+        <v>3.5</v>
+      </c>
+      <c r="P80">
+        <v>2.16</v>
+      </c>
+      <c r="Q80">
         <v>3.7</v>
       </c>
-      <c r="P80">
-        <v>2.2</v>
-      </c>
-      <c r="Q80">
-        <v>3.45</v>
-      </c>
       <c r="R80">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S80">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T80">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U80">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V80">
         <v>1.46</v>
@@ -13379,7 +13379,7 @@
         <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y80">
         <v>1.2</v>
@@ -13388,10 +13388,10 @@
         <v>4.1</v>
       </c>
       <c r="AA80">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB80">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC80">
         <v>2.8</v>
@@ -13400,13 +13400,13 @@
         <v>1.4</v>
       </c>
       <c r="AE80">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF80">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG80">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK80">
         <v>1.35</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13856,7 +13856,7 @@
         <v>1.44</v>
       </c>
       <c r="T83">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="U83">
         <v>3.14</v>
@@ -13877,7 +13877,7 @@
         <v>2.7</v>
       </c>
       <c r="AA83">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AB83">
         <v>1.58</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
         <v>1.67</v>
@@ -14010,28 +14010,28 @@
         <v>6.35</v>
       </c>
       <c r="Q84">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="R84">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S84">
         <v>1.29</v>
       </c>
       <c r="T84">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="U84">
         <v>2.47</v>
       </c>
       <c r="V84">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
         <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y84">
         <v>1.18</v>
@@ -14043,22 +14043,22 @@
         <v>1.68</v>
       </c>
       <c r="AB84">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC84">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD84">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE84">
         <v>1.12</v>
       </c>
       <c r="AF84">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG84">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK84">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14185,7 +14185,7 @@
         <v>2.55</v>
       </c>
       <c r="U85">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V85">
         <v>1.26</v>
@@ -14203,7 +14203,7 @@
         <v>2.66</v>
       </c>
       <c r="AA85">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AB85">
         <v>1.53</v>
@@ -14218,10 +14218,10 @@
         <v>1</v>
       </c>
       <c r="AF85">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG85">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14336,46 +14336,46 @@
         <v>4.06</v>
       </c>
       <c r="Q86">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R86">
         <v>2.17</v>
       </c>
       <c r="S86">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T86">
         <v>2.88</v>
       </c>
       <c r="U86">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="V86">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W86">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z86">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA86">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB86">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC86">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AD86">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE86">
         <v>1.1</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,10 +14499,10 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R87">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S87">
         <v>1.33</v>
@@ -14514,34 +14514,34 @@
         <v>2.75</v>
       </c>
       <c r="V87">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z87">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA87">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB87">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC87">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AD87">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE87">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF87">
         <v>1.7</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
         <v>1.73</v>
@@ -14819,13 +14819,13 @@
         <v>2.45</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P89">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q89">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R89">
         <v>2.17</v>
@@ -14867,13 +14867,13 @@
         <v>1.35</v>
       </c>
       <c r="AE89">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF89">
         <v>1.57</v>
       </c>
       <c r="AG89">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14982,10 +14982,10 @@
         <v>1.25</v>
       </c>
       <c r="O90">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="P90">
-        <v>9.25</v>
+        <v>8.4</v>
       </c>
       <c r="Q90">
         <v>1.7</v>
@@ -15000,40 +15000,40 @@
         <v>3.55</v>
       </c>
       <c r="U90">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="V90">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X90">
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA90">
         <v>1.5</v>
       </c>
       <c r="AB90">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AC90">
         <v>2.26</v>
       </c>
       <c r="AD90">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE90">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG90">
         <v>1.9</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O91">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="P91">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="Q91">
         <v>3.64</v>
@@ -15163,7 +15163,7 @@
         <v>2.62</v>
       </c>
       <c r="U91">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="V91">
         <v>1.36</v>
@@ -15178,16 +15178,16 @@
         <v>1.33</v>
       </c>
       <c r="Z91">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AA91">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AB91">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD91">
         <v>1.25</v>
@@ -15305,19 +15305,19 @@
         </is>
       </c>
       <c r="N92">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="O92">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P92">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q92">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R92">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="S92">
         <v>1.53</v>
@@ -15326,13 +15326,13 @@
         <v>2.29</v>
       </c>
       <c r="U92">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="V92">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W92">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X92">
         <v>1.11</v>
@@ -15341,7 +15341,7 @@
         <v>1.5</v>
       </c>
       <c r="Z92">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AA92">
         <v>2.41</v>
@@ -15350,19 +15350,19 @@
         <v>1.5</v>
       </c>
       <c r="AC92">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD92">
         <v>1.13</v>
       </c>
       <c r="AE92">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF92">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG92">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AK92">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="O93">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="P93">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="Q93">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R93">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S93">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T93">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="U93">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="V93">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W93">
+        <v>1.03</v>
+      </c>
+      <c r="X93">
+        <v>1.06</v>
+      </c>
+      <c r="Y93">
+        <v>1.25</v>
+      </c>
+      <c r="Z93">
+        <v>3.28</v>
+      </c>
+      <c r="AA93">
+        <v>2.05</v>
+      </c>
+      <c r="AB93">
+        <v>1.75</v>
+      </c>
+      <c r="AC93">
+        <v>2.75</v>
+      </c>
+      <c r="AD93">
+        <v>1.2</v>
+      </c>
+      <c r="AE93">
         <v>1.05</v>
       </c>
-      <c r="X93">
-        <v>1.05</v>
-      </c>
-      <c r="Y93">
-        <v>1.19</v>
-      </c>
-      <c r="Z93">
-        <v>3.76</v>
-      </c>
-      <c r="AA93">
-        <v>1.75</v>
-      </c>
-      <c r="AB93">
-        <v>1.95</v>
-      </c>
-      <c r="AC93">
-        <v>2.5</v>
-      </c>
-      <c r="AD93">
-        <v>1.25</v>
-      </c>
-      <c r="AE93">
-        <v>1.06</v>
-      </c>
       <c r="AF93">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG93">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK93">
         <v>1.8</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O99">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P99">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q99">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R99">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T99">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="U99">
         <v>2.14</v>
       </c>
       <c r="V99">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W99">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X99">
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z99">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA99">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB99">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AC99">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD99">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE99">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF99">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG99">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X100">
         <v>0</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,22 +17270,22 @@
         <v>4.15</v>
       </c>
       <c r="Q104">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R104">
         <v>1.91</v>
       </c>
       <c r="S104">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T104">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="U104">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="V104">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W104">
         <v>1.05</v>
@@ -17294,31 +17294,31 @@
         <v>1.07</v>
       </c>
       <c r="Y104">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Z104">
         <v>2.49</v>
       </c>
       <c r="AA104">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="AB104">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC104">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AD104">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE104">
         <v>1.01</v>
       </c>
       <c r="AF104">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AG104">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.27</v>
       </c>
       <c r="AK104">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O105">
         <v>3.5</v>
       </c>
       <c r="P105">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q105">
         <v>2.4</v>
@@ -17442,7 +17442,7 @@
         <v>1.22</v>
       </c>
       <c r="T105">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U105">
         <v>2.1</v>
@@ -17460,28 +17460,28 @@
         <v>1.13</v>
       </c>
       <c r="Z105">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA105">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB105">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AC105">
         <v>2.26</v>
       </c>
       <c r="AD105">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE105">
         <v>1.25</v>
       </c>
       <c r="AF105">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG105">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="O106">
         <v>3</v>
       </c>
       <c r="P106">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="Q106">
         <v>3.65</v>
@@ -17602,19 +17602,19 @@
         <v>1.84</v>
       </c>
       <c r="S106">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="T106">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="U106">
         <v>3.22</v>
       </c>
       <c r="V106">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W106">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
         <v>1.05</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AK106">
         <v>1.39</v>
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O107">
         <v>3.4</v>
       </c>
       <c r="P107">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q107">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="R107">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S107">
         <v>1.36</v>
@@ -17771,7 +17771,7 @@
         <v>2.84</v>
       </c>
       <c r="U107">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="V107">
         <v>1.37</v>
@@ -17780,7 +17780,7 @@
         <v>1.04</v>
       </c>
       <c r="X107">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
         <v>1.33</v>
@@ -17789,13 +17789,13 @@
         <v>3.25</v>
       </c>
       <c r="AA107">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB107">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC107">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AD107">
         <v>1.24</v>
@@ -17804,7 +17804,7 @@
         <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG107">
         <v>1.84</v>
@@ -17913,16 +17913,16 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O108">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P108">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q108">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="R108">
         <v>2.45</v>
@@ -17946,10 +17946,10 @@
         <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z108">
-        <v>6.23</v>
+        <v>6.3</v>
       </c>
       <c r="AA108">
         <v>1.4</v>
@@ -17964,7 +17964,7 @@
         <v>1.77</v>
       </c>
       <c r="AE108">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF108">
         <v>1.33</v>
@@ -18076,28 +18076,28 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O109">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P109">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="Q109">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R109">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S109">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T109">
-        <v>2.14</v>
+        <v>2.65</v>
       </c>
       <c r="U109">
-        <v>2.39</v>
+        <v>2.96</v>
       </c>
       <c r="V109">
         <v>1.32</v>
@@ -18106,13 +18106,13 @@
         <v>1.02</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z109">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA109">
         <v>2.04</v>
@@ -18121,7 +18121,7 @@
         <v>1.69</v>
       </c>
       <c r="AC109">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD109">
         <v>1.22</v>
@@ -18130,10 +18130,10 @@
         <v>1.03</v>
       </c>
       <c r="AF109">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG109">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18586,7 +18586,7 @@
         <v>2.75</v>
       </c>
       <c r="U112">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V112">
         <v>1.31</v>
@@ -18595,34 +18595,34 @@
         <v>1.05</v>
       </c>
       <c r="X112">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA112">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB112">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC112">
-        <v>3.65</v>
+        <v>3.99</v>
       </c>
       <c r="AD112">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE112">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF112">
         <v>2.2</v>
       </c>
       <c r="AG112">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK112">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,19 +18728,19 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O113">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P113">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q113">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R113">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S113">
         <v>1.25</v>
@@ -18749,43 +18749,43 @@
         <v>3.5</v>
       </c>
       <c r="U113">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V113">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W113">
         <v>1.13</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z113">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA113">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB113">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC113">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AD113">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE113">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF113">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG113">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -19054,19 +19054,19 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O115">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P115">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q115">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="R115">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="S115">
         <v>1.14</v>
@@ -19075,43 +19075,43 @@
         <v>4.9</v>
       </c>
       <c r="U115">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V115">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W115">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X115">
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z115">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA115">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AB115">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AC115">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AD115">
         <v>2</v>
       </c>
       <c r="AE115">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AF115">
         <v>1.3</v>
       </c>
       <c r="AG115">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK115">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19226,25 +19226,25 @@
         <v>2.3</v>
       </c>
       <c r="Q116">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R116">
         <v>1.94</v>
       </c>
       <c r="S116">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T116">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U116">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V116">
         <v>1.29</v>
       </c>
       <c r="W116">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X116">
         <v>1.04</v>
@@ -19253,7 +19253,7 @@
         <v>1.38</v>
       </c>
       <c r="Z116">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AA116">
         <v>2.19</v>
@@ -19262,7 +19262,7 @@
         <v>1.65</v>
       </c>
       <c r="AC116">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AD116">
         <v>1.18</v>
@@ -19271,10 +19271,10 @@
         <v>1.03</v>
       </c>
       <c r="AF116">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG116">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK116">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="O117">
         <v>2.83</v>
       </c>
       <c r="P117">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -19395,10 +19395,10 @@
         <v>1.95</v>
       </c>
       <c r="S117">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T117">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U117">
         <v>2.87</v>
@@ -19407,13 +19407,13 @@
         <v>1.36</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X117">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z117">
         <v>2.92</v>
@@ -19428,7 +19428,7 @@
         <v>4.1</v>
       </c>
       <c r="AD117">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE117">
         <v>1.04</v>
@@ -19437,7 +19437,7 @@
         <v>1.79</v>
       </c>
       <c r="AG117">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK117">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19709,61 +19709,61 @@
         <v>2.14</v>
       </c>
       <c r="O119">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P119">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q119">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R119">
         <v>2.4</v>
       </c>
       <c r="S119">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T119">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U119">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V119">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W119">
         <v>1.17</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z119">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA119">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB119">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC119">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AD119">
         <v>1.64</v>
       </c>
       <c r="AE119">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF119">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AG119">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK119">
         <v>1.6</v>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O120">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P120">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q120">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="R120">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S120">
         <v>1.39</v>
@@ -19893,7 +19893,7 @@
         <v>2.88</v>
       </c>
       <c r="V120">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W120">
         <v>1.05</v>
@@ -19920,7 +19920,7 @@
         <v>1.25</v>
       </c>
       <c r="AE120">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
         <v>1.74</v>
@@ -20198,46 +20198,46 @@
         <v>1.44</v>
       </c>
       <c r="O122">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P122">
         <v>5.75</v>
       </c>
       <c r="Q122">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S122">
         <v>1.33</v>
       </c>
       <c r="T122">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="U122">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V122">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W122">
         <v>1.08</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
         <v>1.25</v>
       </c>
       <c r="Z122">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA122">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB122">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC122">
         <v>3.1</v>
@@ -20246,13 +20246,13 @@
         <v>1.36</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF122">
         <v>2</v>
       </c>
       <c r="AG122">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK122">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O123">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P123">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="Q123">
         <v>2</v>
       </c>
       <c r="R123">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S123">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T123">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U123">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="V123">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W123">
+        <v>1.11</v>
+      </c>
+      <c r="X123">
+        <v>1.01</v>
+      </c>
+      <c r="Y123">
         <v>1.14</v>
       </c>
-      <c r="X123">
-        <v>1.03</v>
-      </c>
-      <c r="Y123">
-        <v>1.12</v>
-      </c>
       <c r="Z123">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA123">
         <v>1.53</v>
       </c>
       <c r="AB123">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC123">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD123">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AE123">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF123">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG123">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
+        <v>2.03</v>
+      </c>
+      <c r="O134">
+        <v>3.93</v>
+      </c>
+      <c r="P134">
+        <v>2.63</v>
+      </c>
+      <c r="Q134">
+        <v>2.5</v>
+      </c>
+      <c r="R134">
+        <v>2.79</v>
+      </c>
+      <c r="S134">
+        <v>1.17</v>
+      </c>
+      <c r="T134">
+        <v>5.2</v>
+      </c>
+      <c r="U134">
+        <v>1.85</v>
+      </c>
+      <c r="V134">
+        <v>1.81</v>
+      </c>
+      <c r="W134">
+        <v>1.22</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>1.06</v>
+      </c>
+      <c r="Z134">
+        <v>7.5</v>
+      </c>
+      <c r="AA134">
+        <v>1.33</v>
+      </c>
+      <c r="AB134">
+        <v>3.4</v>
+      </c>
+      <c r="AC134">
+        <v>1.75</v>
+      </c>
+      <c r="AD134">
+        <v>1.99</v>
+      </c>
+      <c r="AE134">
+        <v>1.45</v>
+      </c>
+      <c r="AF134">
+        <v>1.3</v>
+      </c>
+      <c r="AG134">
+        <v>3.4</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
+        <v>1.18</v>
+      </c>
+      <c r="AK134">
         <v>1.67</v>
-      </c>
-      <c r="O134">
-        <v>4</v>
-      </c>
-      <c r="P134">
-        <v>4.2</v>
-      </c>
-      <c r="Q134">
-        <v>2.16</v>
-      </c>
-      <c r="R134">
-        <v>2.61</v>
-      </c>
-      <c r="S134">
-        <v>1.18</v>
-      </c>
-      <c r="T134">
-        <v>4.6</v>
-      </c>
-      <c r="U134">
-        <v>1.9</v>
-      </c>
-      <c r="V134">
-        <v>1.8</v>
-      </c>
-      <c r="W134">
-        <v>1.2</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>1.11</v>
-      </c>
-      <c r="Z134">
-        <v>6.81</v>
-      </c>
-      <c r="AA134">
-        <v>1.35</v>
-      </c>
-      <c r="AB134">
-        <v>3.04</v>
-      </c>
-      <c r="AC134">
-        <v>1.95</v>
-      </c>
-      <c r="AD134">
-        <v>1.88</v>
-      </c>
-      <c r="AE134">
-        <v>1.36</v>
-      </c>
-      <c r="AF134">
-        <v>1.36</v>
-      </c>
-      <c r="AG134">
-        <v>2.88</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.17</v>
-      </c>
-      <c r="AK134">
-        <v>2.08</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="O135">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="P135">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="Q135">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="R135">
-        <v>2.79</v>
+        <v>2.61</v>
       </c>
       <c r="S135">
+        <v>1.18</v>
+      </c>
+      <c r="T135">
+        <v>4.6</v>
+      </c>
+      <c r="U135">
+        <v>1.9</v>
+      </c>
+      <c r="V135">
+        <v>1.8</v>
+      </c>
+      <c r="W135">
+        <v>1.2</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>1.11</v>
+      </c>
+      <c r="Z135">
+        <v>6.81</v>
+      </c>
+      <c r="AA135">
+        <v>1.35</v>
+      </c>
+      <c r="AB135">
+        <v>3.04</v>
+      </c>
+      <c r="AC135">
+        <v>1.95</v>
+      </c>
+      <c r="AD135">
+        <v>1.88</v>
+      </c>
+      <c r="AE135">
+        <v>1.36</v>
+      </c>
+      <c r="AF135">
+        <v>1.36</v>
+      </c>
+      <c r="AG135">
+        <v>2.88</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
         <v>1.17</v>
       </c>
-      <c r="T135">
-        <v>5.2</v>
-      </c>
-      <c r="U135">
-        <v>1.85</v>
-      </c>
-      <c r="V135">
-        <v>1.81</v>
-      </c>
-      <c r="W135">
-        <v>1.22</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>1.06</v>
-      </c>
-      <c r="Z135">
-        <v>7.5</v>
-      </c>
-      <c r="AA135">
-        <v>1.33</v>
-      </c>
-      <c r="AB135">
-        <v>3.4</v>
-      </c>
-      <c r="AC135">
-        <v>1.75</v>
-      </c>
-      <c r="AD135">
-        <v>1.99</v>
-      </c>
-      <c r="AE135">
-        <v>1.45</v>
-      </c>
-      <c r="AF135">
-        <v>1.3</v>
-      </c>
-      <c r="AG135">
-        <v>3.4</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.18</v>
-      </c>
       <c r="AK135">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22966,16 +22966,16 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O139">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P139">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q139">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="R139">
         <v>2.1</v>
@@ -23002,22 +23002,22 @@
         <v>1.36</v>
       </c>
       <c r="Z139">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="AA139">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB139">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC139">
-        <v>4.51</v>
+        <v>3.2</v>
       </c>
       <c r="AD139">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE139">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF139">
         <v>2</v>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK139">
         <v>1.56</v>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC146">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
         <v>2.58</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O3">
         <v>3.6</v>
@@ -816,16 +816,16 @@
         <v>1.29</v>
       </c>
       <c r="T3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -964,58 +964,58 @@
         <v>2.42</v>
       </c>
       <c r="O4">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R4">
         <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
         <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
         <v>4</v>
       </c>
       <c r="AA4">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB4">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AC4">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AD4">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
         <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG4">
         <v>2.26</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AK4">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P6">
-        <v>6.25</v>
+        <v>6.12</v>
       </c>
       <c r="Q6">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="R6">
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V6">
         <v>1.33</v>
@@ -1320,22 +1320,22 @@
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="Z6">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA6">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC6">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AD6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
         <v>1.02</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P7">
         <v>3.17</v>
@@ -1462,7 +1462,7 @@
         <v>2.51</v>
       </c>
       <c r="R7">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
         <v>1.44</v>
@@ -1474,37 +1474,37 @@
         <v>3</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z7">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AA7">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB7">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC7">
-        <v>3.62</v>
+        <v>3.88</v>
       </c>
       <c r="AD7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE7">
         <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
         <v>1.85</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P8">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
         <v>1.33</v>
@@ -1637,40 +1637,40 @@
         <v>2.65</v>
       </c>
       <c r="V8">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
         <v>1.05</v>
       </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
       <c r="Y8">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z8">
         <v>3.38</v>
       </c>
       <c r="AA8">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB8">
         <v>1.9</v>
       </c>
       <c r="AC8">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="O10">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Q10">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="R10">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U10">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA10">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC10">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AD10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AG10">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.35</v>
+        <v>4.45</v>
       </c>
       <c r="O11">
+        <v>3.75</v>
+      </c>
+      <c r="P11">
+        <v>1.47</v>
+      </c>
+      <c r="Q11">
+        <v>5</v>
+      </c>
+      <c r="R11">
+        <v>2.25</v>
+      </c>
+      <c r="S11">
+        <v>1.35</v>
+      </c>
+      <c r="T11">
+        <v>2.95</v>
+      </c>
+      <c r="U11">
+        <v>2.66</v>
+      </c>
+      <c r="V11">
+        <v>1.42</v>
+      </c>
+      <c r="W11">
+        <v>1.05</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.23</v>
+      </c>
+      <c r="Z11">
+        <v>3.61</v>
+      </c>
+      <c r="AA11">
+        <v>1.8</v>
+      </c>
+      <c r="AB11">
+        <v>1.88</v>
+      </c>
+      <c r="AC11">
         <v>3.25</v>
       </c>
-      <c r="P11">
-        <v>2.55</v>
-      </c>
-      <c r="Q11">
-        <v>3.25</v>
-      </c>
-      <c r="R11">
-        <v>2.18</v>
-      </c>
-      <c r="S11">
-        <v>1.36</v>
-      </c>
-      <c r="T11">
-        <v>2.7</v>
-      </c>
-      <c r="U11">
-        <v>2.9</v>
-      </c>
-      <c r="V11">
-        <v>1.38</v>
-      </c>
-      <c r="W11">
-        <v>1.03</v>
-      </c>
-      <c r="X11">
-        <v>1.04</v>
-      </c>
-      <c r="Y11">
+      <c r="AD11">
         <v>1.33</v>
       </c>
-      <c r="Z11">
-        <v>3.4</v>
-      </c>
-      <c r="AA11">
-        <v>1.96</v>
-      </c>
-      <c r="AB11">
-        <v>1.8</v>
-      </c>
-      <c r="AC11">
-        <v>3.42</v>
-      </c>
-      <c r="AD11">
-        <v>1.29</v>
-      </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AG11">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AK11">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.45</v>
+        <v>2.17</v>
       </c>
       <c r="O12">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="P12">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S12">
         <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="U12">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB12">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="P14">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q14">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="R14">
         <v>2.4</v>
@@ -2609,7 +2609,7 @@
         <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
         <v>2.39</v>
@@ -2621,16 +2621,16 @@
         <v>1.13</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
         <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>4.35</v>
+        <v>4.76</v>
       </c>
       <c r="AA14">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
         <v>2.27</v>
@@ -2639,7 +2639,7 @@
         <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
         <v>1.2</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>1.2</v>
+      </c>
+      <c r="O18">
+        <v>4.75</v>
+      </c>
+      <c r="P18">
+        <v>7.5</v>
+      </c>
+      <c r="Q18">
+        <v>1.72</v>
+      </c>
+      <c r="R18">
+        <v>2.39</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.3</v>
+      </c>
+      <c r="U18">
+        <v>2.43</v>
+      </c>
+      <c r="V18">
         <v>1.53</v>
       </c>
-      <c r="O18">
-        <v>3.45</v>
-      </c>
-      <c r="P18">
-        <v>4.2</v>
-      </c>
-      <c r="Q18">
+      <c r="W18">
+        <v>1.13</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.16</v>
+      </c>
+      <c r="Z18">
+        <v>4.05</v>
+      </c>
+      <c r="AA18">
+        <v>1.59</v>
+      </c>
+      <c r="AB18">
         <v>2.1</v>
       </c>
-      <c r="R18">
-        <v>2.02</v>
-      </c>
-      <c r="S18">
-        <v>1.41</v>
-      </c>
-      <c r="T18">
-        <v>2.74</v>
-      </c>
-      <c r="U18">
-        <v>2.92</v>
-      </c>
-      <c r="V18">
-        <v>1.32</v>
-      </c>
-      <c r="W18">
-        <v>1.02</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.33</v>
-      </c>
-      <c r="Z18">
-        <v>3.16</v>
-      </c>
-      <c r="AA18">
-        <v>2.05</v>
-      </c>
-      <c r="AB18">
-        <v>1.74</v>
-      </c>
       <c r="AC18">
-        <v>3.48</v>
+        <v>2.49</v>
       </c>
       <c r="AD18">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG18">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK18">
-        <v>2.04</v>
+        <v>3.04</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="O19">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="U19">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>4.05</v>
+        <v>3.16</v>
       </c>
       <c r="AA19">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AC19">
-        <v>2.49</v>
+        <v>3.48</v>
       </c>
       <c r="AD19">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG19">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>3.04</v>
+        <v>2.04</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P20">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="Q20">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="R20">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="S20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="U20">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AC20">
         <v>1.9</v>
       </c>
       <c r="AD20">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AE20">
         <v>1.4</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG20">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>2.37</v>
+        <v>1.86</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="R21">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="S21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T21">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="U21">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V21">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W21">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB21">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="AC21">
         <v>1.9</v>
       </c>
       <c r="AD21">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AE21">
         <v>1.4</v>
       </c>
       <c r="AF21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG21">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -4076,13 +4076,13 @@
         <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W23">
         <v>1.1</v>
@@ -4100,7 +4100,7 @@
         <v>1.66</v>
       </c>
       <c r="AB23">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
         <v>2.59</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="O26">
-        <v>2.95</v>
+        <v>4.7</v>
       </c>
       <c r="P26">
-        <v>3.18</v>
+        <v>8.6</v>
       </c>
       <c r="Q26">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="R26">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>2.52</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AC26">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG26">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK26">
-        <v>1.64</v>
+        <v>3.54</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
+        <v>1.96</v>
+      </c>
+      <c r="O27">
+        <v>3.3</v>
+      </c>
+      <c r="P27">
+        <v>3.3</v>
+      </c>
+      <c r="Q27">
+        <v>2.62</v>
+      </c>
+      <c r="R27">
+        <v>1.99</v>
+      </c>
+      <c r="S27">
+        <v>1.41</v>
+      </c>
+      <c r="T27">
+        <v>2.53</v>
+      </c>
+      <c r="U27">
+        <v>3.14</v>
+      </c>
+      <c r="V27">
+        <v>1.36</v>
+      </c>
+      <c r="W27">
+        <v>1.03</v>
+      </c>
+      <c r="X27">
+        <v>1.06</v>
+      </c>
+      <c r="Y27">
+        <v>1.36</v>
+      </c>
+      <c r="Z27">
+        <v>3.1</v>
+      </c>
+      <c r="AA27">
+        <v>2.04</v>
+      </c>
+      <c r="AB27">
+        <v>1.69</v>
+      </c>
+      <c r="AC27">
+        <v>3.45</v>
+      </c>
+      <c r="AD27">
         <v>1.22</v>
       </c>
-      <c r="O27">
-        <v>4.7</v>
-      </c>
-      <c r="P27">
-        <v>8.6</v>
-      </c>
-      <c r="Q27">
-        <v>1.65</v>
-      </c>
-      <c r="R27">
-        <v>2.5</v>
-      </c>
-      <c r="S27">
-        <v>1.35</v>
-      </c>
-      <c r="T27">
-        <v>2.88</v>
-      </c>
-      <c r="U27">
-        <v>2.63</v>
-      </c>
-      <c r="V27">
-        <v>1.43</v>
-      </c>
-      <c r="W27">
-        <v>1.1</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.22</v>
-      </c>
-      <c r="Z27">
-        <v>4.1</v>
-      </c>
-      <c r="AA27">
-        <v>1.8</v>
-      </c>
-      <c r="AB27">
-        <v>2.02</v>
-      </c>
-      <c r="AC27">
-        <v>3.1</v>
-      </c>
-      <c r="AD27">
-        <v>1.36</v>
-      </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>3.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P28">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="Q28">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R28">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S28">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="T28">
         <v>2.53</v>
       </c>
       <c r="U28">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W28">
         <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y28">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z28">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="AA28">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
+        <v>1.54</v>
+      </c>
+      <c r="AC28">
+        <v>4.2</v>
+      </c>
+      <c r="AD28">
+        <v>1.18</v>
+      </c>
+      <c r="AE28">
+        <v>1.03</v>
+      </c>
+      <c r="AF28">
+        <v>2.02</v>
+      </c>
+      <c r="AG28">
         <v>1.69</v>
-      </c>
-      <c r="AC28">
-        <v>3.45</v>
-      </c>
-      <c r="AD28">
-        <v>1.22</v>
-      </c>
-      <c r="AE28">
-        <v>1.08</v>
-      </c>
-      <c r="AF28">
-        <v>1.83</v>
-      </c>
-      <c r="AG28">
-        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
         <v>3.03</v>
       </c>
       <c r="Q30">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="R30">
         <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="U30">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
         <v>1.11</v>
@@ -5235,13 +5235,13 @@
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB30">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC30">
         <v>2.55</v>
@@ -5250,13 +5250,13 @@
         <v>1.5</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG30">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>1.68</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
         <v>4.1</v>
@@ -5374,19 +5374,19 @@
         <v>2.25</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S31">
         <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="U31">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
         <v>1.11</v>
@@ -5395,31 +5395,31 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA31">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB31">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
         <v>1.65</v>
       </c>
       <c r="AG31">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="O32">
         <v>3.35</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5546,10 +5546,10 @@
         <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="V32">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
         <v>1.1</v>
@@ -5558,10 +5558,10 @@
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA32">
         <v>1.65</v>
@@ -5570,19 +5570,19 @@
         <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AD32">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
         <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,22 +5688,22 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="Q33">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R33">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
         <v>3.42</v>
@@ -5712,40 +5712,40 @@
         <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W33">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA33">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AB33">
         <v>2.4</v>
       </c>
       <c r="AC33">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AD33">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
         <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="Q44">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="R44">
         <v>2.06</v>
@@ -7520,10 +7520,10 @@
         <v>4.2</v>
       </c>
       <c r="AA44">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB44">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
         <v>2.88</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK44">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O45">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P45">
         <v>1.55</v>
       </c>
       <c r="Q45">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R45">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T45">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U45">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V45">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W45">
         <v>1.11</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z45">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="AA45">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB45">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AC45">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="AD45">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AE45">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG45">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>3.52</v>
       </c>
       <c r="P47">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -8000,16 +8000,16 @@
         <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="AA47">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB47">
         <v>2.03</v>
@@ -8018,7 +8018,7 @@
         <v>2.8</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE47">
         <v>1.15</v>
@@ -8027,7 +8027,7 @@
         <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK47">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9114,7 +9114,7 @@
         <v>2.3</v>
       </c>
       <c r="O54">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
         <v>2.43</v>
@@ -9123,7 +9123,7 @@
         <v>2.91</v>
       </c>
       <c r="R54">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="S54">
         <v>1.29</v>
@@ -9135,28 +9135,28 @@
         <v>2.4</v>
       </c>
       <c r="V54">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W54">
         <v>1.12</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="AA54">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB54">
         <v>2.12</v>
       </c>
       <c r="AC54">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AD54">
         <v>1.45</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,40 +9274,40 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O55">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>4.9</v>
+        <v>5.01</v>
       </c>
       <c r="Q55">
         <v>2</v>
       </c>
       <c r="R55">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="S55">
         <v>1.22</v>
       </c>
       <c r="T55">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U55">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V55">
         <v>1.64</v>
       </c>
       <c r="W55">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z55">
         <v>5.2</v>
@@ -9319,16 +9319,16 @@
         <v>2.6</v>
       </c>
       <c r="AC55">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD55">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE55">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF55">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG55">
         <v>2.39</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK55">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O56">
         <v>3.6</v>
       </c>
       <c r="P56">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q56">
         <v>4</v>
@@ -9461,7 +9461,7 @@
         <v>2.5</v>
       </c>
       <c r="V56">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W56">
         <v>1.06</v>
@@ -9470,28 +9470,28 @@
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z56">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA56">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB56">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AC56">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AD56">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG56">
         <v>2.15</v>
@@ -9510,7 +9510,7 @@
         <v>1.8</v>
       </c>
       <c r="AK56">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O64">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P64">
         <v>2.45</v>
@@ -10753,13 +10753,13 @@
         <v>3.48</v>
       </c>
       <c r="R64">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S64">
         <v>1.46</v>
       </c>
       <c r="T64">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U64">
         <v>3.25</v>
@@ -10771,10 +10771,10 @@
         <v>1.01</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z64">
         <v>2.7</v>
@@ -10783,22 +10783,22 @@
         <v>2.3</v>
       </c>
       <c r="AB64">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC64">
         <v>4.33</v>
       </c>
       <c r="AD64">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE64">
         <v>1.02</v>
       </c>
       <c r="AF64">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG64">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AK64">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,22 +10904,22 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P65">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="Q65">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S65">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T65">
         <v>2.55</v>
@@ -10931,7 +10931,7 @@
         <v>1.29</v>
       </c>
       <c r="W65">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
         <v>1.05</v>
@@ -10943,10 +10943,10 @@
         <v>2.65</v>
       </c>
       <c r="AA65">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB65">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC65">
         <v>4.3</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="N70">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="O70">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P70">
         <v>1.48</v>
@@ -11734,22 +11734,22 @@
         <v>2.55</v>
       </c>
       <c r="S70">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T70">
         <v>3.8</v>
       </c>
       <c r="U70">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V70">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W70">
         <v>1.14</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
         <v>1.16</v>
@@ -11764,19 +11764,19 @@
         <v>2.42</v>
       </c>
       <c r="AC70">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AD70">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE70">
         <v>1.22</v>
       </c>
       <c r="AF70">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG70">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK70">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O71">
         <v>4.05</v>
@@ -11891,25 +11891,25 @@
         <v>2.91</v>
       </c>
       <c r="Q71">
+        <v>2.45</v>
+      </c>
+      <c r="R71">
         <v>2.44</v>
       </c>
-      <c r="R71">
-        <v>2.47</v>
-      </c>
       <c r="S71">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T71">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="U71">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V71">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X71">
         <v>1.01</v>
@@ -11918,22 +11918,22 @@
         <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AA71">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB71">
         <v>2.75</v>
       </c>
       <c r="AC71">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD71">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE71">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF71">
         <v>1.36</v>
@@ -12534,34 +12534,34 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="O75">
-        <v>4.8</v>
+        <v>6.05</v>
       </c>
       <c r="P75">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="Q75">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R75">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="S75">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
         <v>3.25</v>
       </c>
       <c r="U75">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V75">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12570,13 +12570,13 @@
         <v>1.21</v>
       </c>
       <c r="Z75">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="AA75">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB75">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC75">
         <v>2.75</v>
@@ -12585,10 +12585,10 @@
         <v>1.4</v>
       </c>
       <c r="AE75">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF75">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG75">
         <v>1.48</v>
@@ -12697,25 +12697,25 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O76">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Q76">
+        <v>2.94</v>
+      </c>
+      <c r="R76">
+        <v>2.05</v>
+      </c>
+      <c r="S76">
+        <v>1.4</v>
+      </c>
+      <c r="T76">
         <v>3</v>
-      </c>
-      <c r="R76">
-        <v>2.1</v>
-      </c>
-      <c r="S76">
-        <v>1.36</v>
-      </c>
-      <c r="T76">
-        <v>2.88</v>
       </c>
       <c r="U76">
         <v>2.77</v>
@@ -12727,34 +12727,34 @@
         <v>1.08</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y76">
         <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA76">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC76">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="AD76">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE76">
         <v>1.07</v>
       </c>
       <c r="AF76">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG76">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O79">
         <v>3.25</v>
@@ -13207,7 +13207,7 @@
         <v>2.99</v>
       </c>
       <c r="U79">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V79">
         <v>1.44</v>
@@ -13219,16 +13219,16 @@
         <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z79">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA79">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB79">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC79">
         <v>2.83</v>
@@ -13237,7 +13237,7 @@
         <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF79">
         <v>1.7</v>
@@ -13349,25 +13349,25 @@
         </is>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O80">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P80">
+        <v>2.18</v>
+      </c>
+      <c r="Q80">
+        <v>3.15</v>
+      </c>
+      <c r="R80">
         <v>2.16</v>
-      </c>
-      <c r="Q80">
-        <v>3.7</v>
-      </c>
-      <c r="R80">
-        <v>2.19</v>
       </c>
       <c r="S80">
         <v>1.32</v>
       </c>
       <c r="T80">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="U80">
         <v>2.53</v>
@@ -13379,16 +13379,16 @@
         <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z80">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
       <c r="AA80">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB80">
         <v>2.1</v>
@@ -13422,7 +13422,7 @@
         <v>1.27</v>
       </c>
       <c r="AK80">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,7 +13521,7 @@
         <v>5.05</v>
       </c>
       <c r="Q81">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="R81">
         <v>2.3</v>
@@ -13533,31 +13533,31 @@
         <v>3.3</v>
       </c>
       <c r="U81">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="V81">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W81">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA81">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB81">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC81">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD81">
         <v>1.38</v>
@@ -13566,10 +13566,10 @@
         <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG81">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK81">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O88">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="P88">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="Q88">
         <v>3.4</v>
@@ -14668,49 +14668,49 @@
         <v>1.88</v>
       </c>
       <c r="S88">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="T88">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="U88">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="V88">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W88">
         <v>1.02</v>
       </c>
       <c r="X88">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y88">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Z88">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AA88">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AB88">
         <v>1.3</v>
       </c>
       <c r="AC88">
-        <v>7.5</v>
+        <v>6.05</v>
       </c>
       <c r="AD88">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE88">
         <v>1.01</v>
       </c>
       <c r="AF88">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AG88">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14816,16 +14816,16 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O89">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P89">
         <v>2.4</v>
       </c>
       <c r="Q89">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R89">
         <v>2.17</v>
@@ -14843,10 +14843,10 @@
         <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y89">
         <v>1.21</v>
@@ -14858,7 +14858,7 @@
         <v>1.73</v>
       </c>
       <c r="AB89">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC89">
         <v>2.74</v>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O90">
         <v>5.25</v>
       </c>
       <c r="P90">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q90">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R90">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="S90">
         <v>1.25</v>
@@ -15006,10 +15006,10 @@
         <v>1.62</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
         <v>1.14</v>
@@ -15024,13 +15024,13 @@
         <v>2.55</v>
       </c>
       <c r="AC90">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AD90">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE90">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF90">
         <v>1.87</v>
@@ -15631,19 +15631,19 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O94">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P94">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="Q94">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R94">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S94">
         <v>1.67</v>
@@ -15652,10 +15652,10 @@
         <v>2.1</v>
       </c>
       <c r="U94">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="V94">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W94">
         <v>1.02</v>
@@ -15667,7 +15667,7 @@
         <v>1.73</v>
       </c>
       <c r="Z94">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AA94">
         <v>3.08</v>
@@ -15676,16 +15676,16 @@
         <v>1.33</v>
       </c>
       <c r="AC94">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AD94">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE94">
         <v>1.01</v>
       </c>
       <c r="AF94">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AG94">
         <v>1.49</v>
@@ -15794,16 +15794,16 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="O95">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="P95">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="Q95">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="R95">
         <v>1.79</v>
@@ -15812,13 +15812,13 @@
         <v>1.57</v>
       </c>
       <c r="T95">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U95">
         <v>3.75</v>
       </c>
       <c r="V95">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W95">
         <v>1.03</v>
@@ -15830,7 +15830,7 @@
         <v>1.58</v>
       </c>
       <c r="Z95">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AA95">
         <v>2.69</v>
@@ -15851,7 +15851,7 @@
         <v>2.07</v>
       </c>
       <c r="AG95">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AK95">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,34 +15957,34 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O96">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="P96">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="Q96">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="R96">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S96">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T96">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U96">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="V96">
         <v>1.19</v>
       </c>
       <c r="W96">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
         <v>1.06</v>
@@ -16008,13 +16008,13 @@
         <v>1.11</v>
       </c>
       <c r="AE96">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG96">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK96">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,22 +16120,22 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="O97">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P97">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q97">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="R97">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="S97">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="T97">
         <v>2.09</v>
@@ -16150,34 +16150,34 @@
         <v>1.03</v>
       </c>
       <c r="X97">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y97">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="Z97">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AA97">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB97">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC97">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
       <c r="AD97">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AE97">
         <v>1.02</v>
       </c>
       <c r="AF97">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG97">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AK97">
         <v>1.36</v>
@@ -16283,37 +16283,37 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="O98">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P98">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q98">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="R98">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S98">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="T98">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="U98">
         <v>3.5</v>
       </c>
       <c r="V98">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W98">
         <v>1</v>
       </c>
       <c r="X98">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y98">
         <v>1.52</v>
@@ -16325,13 +16325,13 @@
         <v>2.48</v>
       </c>
       <c r="AB98">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC98">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD98">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE98">
         <v>1.04</v>
@@ -16340,7 +16340,7 @@
         <v>2.25</v>
       </c>
       <c r="AG98">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AK98">
         <v>1.17</v>
@@ -16618,7 +16618,7 @@
         <v>6</v>
       </c>
       <c r="Q100">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R100">
         <v>2.3</v>
@@ -16651,7 +16651,7 @@
         <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC100">
         <v>2.85</v>
@@ -16663,10 +16663,10 @@
         <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG100">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK100">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,34 +16772,34 @@
         </is>
       </c>
       <c r="N101">
+        <v>1.27</v>
+      </c>
+      <c r="O101">
+        <v>4.7</v>
+      </c>
+      <c r="P101">
+        <v>8.4</v>
+      </c>
+      <c r="Q101">
+        <v>1.75</v>
+      </c>
+      <c r="R101">
+        <v>2.4</v>
+      </c>
+      <c r="S101">
         <v>1.3</v>
       </c>
-      <c r="O101">
-        <v>4.45</v>
-      </c>
-      <c r="P101">
-        <v>7.75</v>
-      </c>
-      <c r="Q101">
-        <v>1.73</v>
-      </c>
-      <c r="R101">
-        <v>2.5</v>
-      </c>
-      <c r="S101">
-        <v>1.29</v>
-      </c>
       <c r="T101">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V101">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X101">
         <v>1.01</v>
@@ -16829,7 +16829,7 @@
         <v>2.2</v>
       </c>
       <c r="AG101">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK101">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,31 +16935,31 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O102">
         <v>3.55</v>
       </c>
       <c r="P102">
-        <v>5.75</v>
+        <v>5.79</v>
       </c>
       <c r="Q102">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S102">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T102">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U102">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W102">
         <v>1.05</v>
@@ -16974,7 +16974,7 @@
         <v>3</v>
       </c>
       <c r="AA102">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB102">
         <v>1.7</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK102">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,25 +17098,25 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="O103">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P103">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q103">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R103">
         <v>2.1</v>
       </c>
       <c r="S103">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T103">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U103">
         <v>2.8</v>
@@ -17152,10 +17152,10 @@
         <v>1.07</v>
       </c>
       <c r="AF103">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG103">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
         <v>2</v>
@@ -17756,7 +17756,7 @@
         <v>3.4</v>
       </c>
       <c r="P107">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q107">
         <v>2.43</v>
@@ -17765,13 +17765,13 @@
         <v>2.14</v>
       </c>
       <c r="S107">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T107">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="U107">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V107">
         <v>1.37</v>
@@ -17780,16 +17780,16 @@
         <v>1.04</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y107">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z107">
         <v>3.25</v>
       </c>
       <c r="AA107">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB107">
         <v>1.79</v>
@@ -17801,7 +17801,7 @@
         <v>1.24</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
         <v>1.8</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK107">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18245,22 +18245,22 @@
         <v>2.94</v>
       </c>
       <c r="P110">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q110">
         <v>2.43</v>
       </c>
       <c r="R110">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="S110">
         <v>1.65</v>
       </c>
       <c r="T110">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U110">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="V110">
         <v>1.15</v>
@@ -18269,7 +18269,7 @@
         <v>1.03</v>
       </c>
       <c r="X110">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y110">
         <v>1.65</v>
@@ -18284,10 +18284,10 @@
         <v>1.35</v>
       </c>
       <c r="AC110">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="AD110">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE110">
         <v>1.01</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK110">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,22 +18402,22 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O111">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P111">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="Q111">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="R111">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="S111">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="T111">
         <v>2.21</v>
@@ -18432,7 +18432,7 @@
         <v>1.03</v>
       </c>
       <c r="X111">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y111">
         <v>1.59</v>
@@ -18447,19 +18447,19 @@
         <v>1.35</v>
       </c>
       <c r="AC111">
-        <v>5.55</v>
+        <v>6.33</v>
       </c>
       <c r="AD111">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE111">
         <v>1.03</v>
       </c>
       <c r="AF111">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG111">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK111">
         <v>1.41</v>
@@ -18601,7 +18601,7 @@
         <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA112">
         <v>2.05</v>
@@ -18616,13 +18616,13 @@
         <v>1.24</v>
       </c>
       <c r="AE112">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AG112">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="O114">
         <v>3.28</v>
       </c>
       <c r="P114">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q114">
         <v>4</v>
@@ -18906,40 +18906,40 @@
         <v>2.2</v>
       </c>
       <c r="S114">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T114">
         <v>2.85</v>
       </c>
       <c r="U114">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="V114">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W114">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z114">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AA114">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB114">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC114">
         <v>2.92</v>
       </c>
       <c r="AD114">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE114">
         <v>1.08</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="O117">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P117">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -19395,13 +19395,13 @@
         <v>1.95</v>
       </c>
       <c r="S117">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T117">
         <v>2.53</v>
       </c>
       <c r="U117">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="V117">
         <v>1.36</v>
@@ -19419,19 +19419,19 @@
         <v>2.92</v>
       </c>
       <c r="AA117">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB117">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC117">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD117">
         <v>1.23</v>
       </c>
       <c r="AE117">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF117">
         <v>1.79</v>
@@ -19543,58 +19543,58 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O118">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="P118">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
       </c>
       <c r="R118">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S118">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T118">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="U118">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="V118">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W118">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X118">
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z118">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AA118">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB118">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC118">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AD118">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AE118">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF118">
         <v>1.57</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK118">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="O121">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P121">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="Q121">
         <v>3.3</v>
@@ -20047,10 +20047,10 @@
         <v>1.95</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T121">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U121">
         <v>3</v>
@@ -20071,7 +20071,7 @@
         <v>3.1</v>
       </c>
       <c r="AA121">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB121">
         <v>1.65</v>
@@ -20083,13 +20083,13 @@
         <v>1.22</v>
       </c>
       <c r="AE121">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF121">
         <v>1.83</v>
       </c>
       <c r="AG121">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK121">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20521,22 +20521,22 @@
         </is>
       </c>
       <c r="N124">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O124">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P124">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q124">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="R124">
         <v>2</v>
       </c>
       <c r="S124">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T124">
         <v>2.92</v>
@@ -20545,25 +20545,25 @@
         <v>2.69</v>
       </c>
       <c r="V124">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W124">
         <v>1.07</v>
       </c>
       <c r="X124">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z124">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA124">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AB124">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="AC124">
         <v>3.05</v>
@@ -20578,7 +20578,7 @@
         <v>1.68</v>
       </c>
       <c r="AG124">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
         <v>1.64</v>
@@ -20687,31 +20687,31 @@
         <v>1.43</v>
       </c>
       <c r="O125">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P125">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="Q125">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R125">
         <v>2.3</v>
       </c>
       <c r="S125">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T125">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U125">
         <v>2.47</v>
       </c>
       <c r="V125">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W125">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X125">
         <v>1.03</v>
@@ -20720,22 +20720,22 @@
         <v>1.19</v>
       </c>
       <c r="Z125">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA125">
         <v>1.71</v>
       </c>
       <c r="AB125">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC125">
         <v>2.7</v>
       </c>
       <c r="AD125">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE125">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF125">
         <v>1.75</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
         <v>2.2</v>
@@ -20847,49 +20847,49 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="O126">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P126">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q126">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="R126">
         <v>2.2</v>
       </c>
       <c r="S126">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T126">
         <v>2.82</v>
       </c>
       <c r="U126">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="V126">
         <v>1.4</v>
       </c>
       <c r="W126">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X126">
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z126">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA126">
         <v>1.9</v>
       </c>
       <c r="AB126">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC126">
         <v>3.14</v>
@@ -20901,10 +20901,10 @@
         <v>1.06</v>
       </c>
       <c r="AF126">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG126">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -21013,46 +21013,46 @@
         <v>2.03</v>
       </c>
       <c r="O127">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="P127">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q127">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R127">
         <v>2.27</v>
       </c>
       <c r="S127">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T127">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="U127">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="V127">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W127">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
         <v>1.21</v>
       </c>
       <c r="Z127">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA127">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB127">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC127">
         <v>2.83</v>
@@ -21064,10 +21064,10 @@
         <v>1.14</v>
       </c>
       <c r="AF127">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG127">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="O128">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="P128">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q128">
         <v>1.8</v>
@@ -21194,10 +21194,10 @@
         <v>3.96</v>
       </c>
       <c r="U128">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="V128">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="W128">
         <v>1.13</v>
@@ -21206,28 +21206,28 @@
         <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z128">
-        <v>5.19</v>
+        <v>5.26</v>
       </c>
       <c r="AA128">
         <v>1.5</v>
       </c>
       <c r="AB128">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC128">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AD128">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE128">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF128">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG128">
         <v>2.16</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O129">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="P129">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21499,10 +21499,10 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O130">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="P130">
         <v>2.2</v>
@@ -21517,13 +21517,13 @@
         <v>1.36</v>
       </c>
       <c r="T130">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U130">
         <v>2.77</v>
       </c>
       <c r="V130">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W130">
         <v>1.08</v>
@@ -21535,28 +21535,28 @@
         <v>1.27</v>
       </c>
       <c r="Z130">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="AA130">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB130">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC130">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="AD130">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE130">
         <v>1.08</v>
       </c>
       <c r="AF130">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG130">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21662,16 +21662,16 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O131">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="P131">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q131">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R131">
         <v>2.37</v>
@@ -21683,10 +21683,10 @@
         <v>3.64</v>
       </c>
       <c r="U131">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="V131">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W131">
         <v>1.17</v>
@@ -21698,25 +21698,25 @@
         <v>1.12</v>
       </c>
       <c r="Z131">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA131">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB131">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="AC131">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD131">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AE131">
         <v>1.22</v>
       </c>
       <c r="AF131">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG131">
         <v>2.4</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK131">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,34 +21825,34 @@
         </is>
       </c>
       <c r="N132">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O132">
         <v>3.9</v>
       </c>
       <c r="P132">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q132">
         <v>2.3</v>
       </c>
       <c r="R132">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S132">
         <v>1.16</v>
       </c>
       <c r="T132">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="U132">
         <v>1.86</v>
       </c>
       <c r="V132">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="W132">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X132">
         <v>0</v>
@@ -21867,22 +21867,22 @@
         <v>1.26</v>
       </c>
       <c r="AB132">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC132">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AD132">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE132">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF132">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG132">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21991,52 +21991,52 @@
         <v>1.69</v>
       </c>
       <c r="O133">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P133">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="Q133">
         <v>2.15</v>
       </c>
       <c r="R133">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S133">
         <v>1.25</v>
       </c>
       <c r="T133">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="U133">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V133">
         <v>1.55</v>
       </c>
       <c r="W133">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X133">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z133">
-        <v>4.45</v>
+        <v>4.96</v>
       </c>
       <c r="AA133">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AB133">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AC133">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AD133">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE133">
         <v>1.2</v>
@@ -22045,7 +22045,7 @@
         <v>1.6</v>
       </c>
       <c r="AG133">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK133">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,34 +22151,34 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="O134">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="P134">
+        <v>3.51</v>
+      </c>
+      <c r="Q134">
+        <v>2</v>
+      </c>
+      <c r="R134">
         <v>2.63</v>
       </c>
-      <c r="Q134">
-        <v>2.5</v>
-      </c>
-      <c r="R134">
-        <v>2.79</v>
-      </c>
       <c r="S134">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T134">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="U134">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V134">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="W134">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X134">
         <v>0</v>
@@ -22187,28 +22187,28 @@
         <v>1.06</v>
       </c>
       <c r="Z134">
-        <v>7.5</v>
+        <v>6.96</v>
       </c>
       <c r="AA134">
         <v>1.33</v>
       </c>
       <c r="AB134">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC134">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD134">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AE134">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AF134">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AG134">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK134">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
+        <v>2.12</v>
+      </c>
+      <c r="O135">
+        <v>3.93</v>
+      </c>
+      <c r="P135">
+        <v>2.75</v>
+      </c>
+      <c r="Q135">
+        <v>2.5</v>
+      </c>
+      <c r="R135">
+        <v>2.78</v>
+      </c>
+      <c r="S135">
+        <v>1.17</v>
+      </c>
+      <c r="T135">
+        <v>4.8</v>
+      </c>
+      <c r="U135">
+        <v>1.85</v>
+      </c>
+      <c r="V135">
+        <v>1.85</v>
+      </c>
+      <c r="W135">
+        <v>1.22</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>1.07</v>
+      </c>
+      <c r="Z135">
+        <v>8</v>
+      </c>
+      <c r="AA135">
+        <v>1.31</v>
+      </c>
+      <c r="AB135">
+        <v>3.4</v>
+      </c>
+      <c r="AC135">
+        <v>1.8</v>
+      </c>
+      <c r="AD135">
+        <v>1.99</v>
+      </c>
+      <c r="AE135">
+        <v>1.45</v>
+      </c>
+      <c r="AF135">
+        <v>1.3</v>
+      </c>
+      <c r="AG135">
+        <v>3.4</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>1.18</v>
+      </c>
+      <c r="AK135">
         <v>1.67</v>
-      </c>
-      <c r="O135">
-        <v>4</v>
-      </c>
-      <c r="P135">
-        <v>4.2</v>
-      </c>
-      <c r="Q135">
-        <v>2.16</v>
-      </c>
-      <c r="R135">
-        <v>2.61</v>
-      </c>
-      <c r="S135">
-        <v>1.18</v>
-      </c>
-      <c r="T135">
-        <v>4.6</v>
-      </c>
-      <c r="U135">
-        <v>1.9</v>
-      </c>
-      <c r="V135">
-        <v>1.8</v>
-      </c>
-      <c r="W135">
-        <v>1.2</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>1.11</v>
-      </c>
-      <c r="Z135">
-        <v>6.81</v>
-      </c>
-      <c r="AA135">
-        <v>1.35</v>
-      </c>
-      <c r="AB135">
-        <v>3.04</v>
-      </c>
-      <c r="AC135">
-        <v>1.95</v>
-      </c>
-      <c r="AD135">
-        <v>1.88</v>
-      </c>
-      <c r="AE135">
-        <v>1.36</v>
-      </c>
-      <c r="AF135">
-        <v>1.36</v>
-      </c>
-      <c r="AG135">
-        <v>2.88</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.17</v>
-      </c>
-      <c r="AK135">
-        <v>2.08</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="O136">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="P136">
-        <v>3.3</v>
+        <v>2.03</v>
       </c>
       <c r="Q136">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="R136">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="S136">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U136">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="V136">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W136">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z136">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="AA136">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB136">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC136">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="AD136">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE136">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF136">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG136">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AK136">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="O137">
         <v>3.5</v>
       </c>
       <c r="P137">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q137">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="R137">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="U137">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="V137">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W137">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z137">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA137">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AB137">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC137">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AD137">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE137">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF137">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG137">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK137">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O138">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="P138">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="Q138">
         <v>2.57</v>
@@ -22818,16 +22818,16 @@
         <v>2.2</v>
       </c>
       <c r="S138">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T138">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="U138">
         <v>2.6</v>
       </c>
       <c r="V138">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W138">
         <v>1.08</v>
@@ -22839,28 +22839,28 @@
         <v>1.28</v>
       </c>
       <c r="Z138">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA138">
         <v>1.9</v>
       </c>
       <c r="AB138">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC138">
         <v>3.04</v>
       </c>
       <c r="AD138">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE138">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF138">
         <v>1.7</v>
       </c>
       <c r="AG138">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23129,34 +23129,34 @@
         </is>
       </c>
       <c r="N140">
-        <v>6.3</v>
+        <v>4.85</v>
       </c>
       <c r="O140">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="P140">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Q140">
-        <v>5.5</v>
+        <v>5.66</v>
       </c>
       <c r="R140">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S140">
         <v>1.32</v>
       </c>
       <c r="T140">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U140">
         <v>2.41</v>
       </c>
       <c r="V140">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W140">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X140">
         <v>1</v>
@@ -23168,10 +23168,10 @@
         <v>3.65</v>
       </c>
       <c r="AA140">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB140">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC140">
         <v>2.7</v>
@@ -23183,10 +23183,10 @@
         <v>1.13</v>
       </c>
       <c r="AF140">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG140">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK140">
         <v>1.08</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,31 +23292,31 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="O141">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P141">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q141">
-        <v>3.18</v>
+        <v>2.51</v>
       </c>
       <c r="R141">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S141">
         <v>1.25</v>
       </c>
       <c r="T141">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="U141">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V141">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="W141">
         <v>1.15</v>
@@ -23325,31 +23325,31 @@
         <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z141">
-        <v>4.35</v>
+        <v>5.1</v>
       </c>
       <c r="AA141">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AB141">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC141">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AD141">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AE141">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF141">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG141">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK141">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O142">
-        <v>4.08</v>
+        <v>3.5</v>
       </c>
       <c r="P142">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="Q142">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R142">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S142">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T142">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U142">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="V142">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W142">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X142">
         <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z142">
-        <v>5.1</v>
+        <v>5.29</v>
       </c>
       <c r="AA142">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB142">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AC142">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD142">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE142">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF142">
         <v>1.44</v>
       </c>
       <c r="AG142">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK142">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,65 +23618,65 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="O143">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P143">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="Q143">
-        <v>2.46</v>
+        <v>1.95</v>
       </c>
       <c r="R143">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="S143">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T143">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="U143">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="V143">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W143">
+        <v>1.15</v>
+      </c>
+      <c r="X143">
+        <v>0</v>
+      </c>
+      <c r="Y143">
         <v>1.14</v>
       </c>
-      <c r="X143">
-        <v>1.01</v>
-      </c>
-      <c r="Y143">
-        <v>1.17</v>
-      </c>
       <c r="Z143">
-        <v>5.21</v>
+        <v>6</v>
       </c>
       <c r="AA143">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AB143">
+        <v>2.7</v>
+      </c>
+      <c r="AC143">
+        <v>2.03</v>
+      </c>
+      <c r="AD143">
+        <v>1.67</v>
+      </c>
+      <c r="AE143">
+        <v>1.26</v>
+      </c>
+      <c r="AF143">
+        <v>1.54</v>
+      </c>
+      <c r="AG143">
         <v>2.4</v>
       </c>
-      <c r="AC143">
-        <v>2.28</v>
-      </c>
-      <c r="AD143">
-        <v>1.57</v>
-      </c>
-      <c r="AE143">
-        <v>1.2</v>
-      </c>
-      <c r="AF143">
-        <v>1.44</v>
-      </c>
-      <c r="AG143">
-        <v>2.6</v>
-      </c>
       <c r="AH143" t="inlineStr">
         <is>
           <t>[]</t>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK143">
-        <v>1.77</v>
+        <v>2.43</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,61 +23781,61 @@
         </is>
       </c>
       <c r="N144">
+        <v>2.87</v>
+      </c>
+      <c r="O144">
+        <v>3.94</v>
+      </c>
+      <c r="P144">
+        <v>2.16</v>
+      </c>
+      <c r="Q144">
+        <v>3.4</v>
+      </c>
+      <c r="R144">
+        <v>2.25</v>
+      </c>
+      <c r="S144">
+        <v>1.25</v>
+      </c>
+      <c r="T144">
+        <v>3.02</v>
+      </c>
+      <c r="U144">
+        <v>2.4</v>
+      </c>
+      <c r="V144">
+        <v>1.54</v>
+      </c>
+      <c r="W144">
+        <v>1.14</v>
+      </c>
+      <c r="X144">
+        <v>1.01</v>
+      </c>
+      <c r="Y144">
+        <v>1.16</v>
+      </c>
+      <c r="Z144">
+        <v>4.1</v>
+      </c>
+      <c r="AA144">
+        <v>1.7</v>
+      </c>
+      <c r="AB144">
+        <v>2.3</v>
+      </c>
+      <c r="AC144">
+        <v>2.56</v>
+      </c>
+      <c r="AD144">
+        <v>1.49</v>
+      </c>
+      <c r="AE144">
+        <v>1.14</v>
+      </c>
+      <c r="AF144">
         <v>1.5</v>
-      </c>
-      <c r="O144">
-        <v>4.2</v>
-      </c>
-      <c r="P144">
-        <v>4.7</v>
-      </c>
-      <c r="Q144">
-        <v>1.94</v>
-      </c>
-      <c r="R144">
-        <v>2.62</v>
-      </c>
-      <c r="S144">
-        <v>1.2</v>
-      </c>
-      <c r="T144">
-        <v>4.2</v>
-      </c>
-      <c r="U144">
-        <v>2</v>
-      </c>
-      <c r="V144">
-        <v>1.75</v>
-      </c>
-      <c r="W144">
-        <v>1.18</v>
-      </c>
-      <c r="X144">
-        <v>0</v>
-      </c>
-      <c r="Y144">
-        <v>1.07</v>
-      </c>
-      <c r="Z144">
-        <v>6</v>
-      </c>
-      <c r="AA144">
-        <v>1.36</v>
-      </c>
-      <c r="AB144">
-        <v>2.72</v>
-      </c>
-      <c r="AC144">
-        <v>2</v>
-      </c>
-      <c r="AD144">
-        <v>1.69</v>
-      </c>
-      <c r="AE144">
-        <v>1.26</v>
-      </c>
-      <c r="AF144">
-        <v>1.54</v>
       </c>
       <c r="AG144">
         <v>2.4</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK144">
-        <v>2.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q145">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="R145">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T145">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U145">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V145">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W145">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z145">
+        <v>3.58</v>
+      </c>
+      <c r="AA145">
+        <v>1.77</v>
+      </c>
+      <c r="AB145">
+        <v>1.72</v>
+      </c>
+      <c r="AC145">
         <v>2.9</v>
       </c>
-      <c r="AA145">
-        <v>1.59</v>
-      </c>
-      <c r="AB145">
-        <v>1.75</v>
-      </c>
-      <c r="AC145">
-        <v>2.38</v>
-      </c>
       <c r="AD145">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE145">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF145">
         <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
+        <v>1.49</v>
+      </c>
+      <c r="AK145">
         <v>1.36</v>
-      </c>
-      <c r="AK145">
-        <v>1.57</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24282,7 +24282,7 @@
         <v>3.3</v>
       </c>
       <c r="R147">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S147">
         <v>1.31</v>
@@ -24291,43 +24291,43 @@
         <v>3.02</v>
       </c>
       <c r="U147">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V147">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W147">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X147">
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z147">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="AA147">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB147">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC147">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="AD147">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE147">
         <v>1.15</v>
       </c>
       <c r="AF147">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG147">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>1.23</v>
       </c>
       <c r="AK147">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O148">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P148">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="Q148">
         <v>2.25</v>
       </c>
       <c r="R148">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S148">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T148">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="U148">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V148">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W148">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X148">
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z148">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA148">
+        <v>1.68</v>
+      </c>
+      <c r="AB148">
+        <v>2.24</v>
+      </c>
+      <c r="AC148">
+        <v>2.69</v>
+      </c>
+      <c r="AD148">
+        <v>1.47</v>
+      </c>
+      <c r="AE148">
+        <v>1.18</v>
+      </c>
+      <c r="AF148">
         <v>1.57</v>
       </c>
-      <c r="AB148">
-        <v>2.31</v>
-      </c>
-      <c r="AC148">
-        <v>2.58</v>
-      </c>
-      <c r="AD148">
-        <v>1.51</v>
-      </c>
-      <c r="AE148">
-        <v>1.2</v>
-      </c>
-      <c r="AF148">
-        <v>1.6</v>
-      </c>
       <c r="AG148">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24596,19 +24596,19 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O149">
         <v>3.15</v>
       </c>
       <c r="P149">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="Q149">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="R149">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S149">
         <v>1.36</v>
@@ -24623,7 +24623,7 @@
         <v>1.35</v>
       </c>
       <c r="W149">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X149">
         <v>1.02</v>
@@ -24641,10 +24641,10 @@
         <v>1.76</v>
       </c>
       <c r="AC149">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD149">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE149">
         <v>1.06</v>
@@ -24653,7 +24653,7 @@
         <v>1.75</v>
       </c>
       <c r="AG149">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK149">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24768,55 +24768,55 @@
         <v>2.59</v>
       </c>
       <c r="Q150">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R150">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="S150">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T150">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U150">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V150">
         <v>1.44</v>
       </c>
       <c r="W150">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X150">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y150">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z150">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA150">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB150">
         <v>1.96</v>
       </c>
       <c r="AC150">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AD150">
         <v>1.34</v>
       </c>
       <c r="AE150">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF150">
         <v>1.61</v>
       </c>
       <c r="AG150">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK150">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24925,10 +24925,10 @@
         <v>2.2</v>
       </c>
       <c r="O151">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P151">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="Q151">
         <v>3.08</v>
@@ -24940,13 +24940,13 @@
         <v>1.3</v>
       </c>
       <c r="T151">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U151">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="V151">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W151">
         <v>1.09</v>
@@ -24961,22 +24961,22 @@
         <v>3.84</v>
       </c>
       <c r="AA151">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB151">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC151">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="AD151">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE151">
         <v>1.12</v>
       </c>
       <c r="AF151">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG151">
         <v>2.3</v>
@@ -24995,7 +24995,7 @@
         <v>1.43</v>
       </c>
       <c r="AK151">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25085,31 +25085,31 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O152">
-        <v>3.5</v>
+        <v>4.16</v>
       </c>
       <c r="P152">
         <v>3</v>
       </c>
       <c r="Q152">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R152">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="S152">
         <v>1.25</v>
       </c>
       <c r="T152">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U152">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V152">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W152">
         <v>1.17</v>
@@ -25121,22 +25121,22 @@
         <v>1.15</v>
       </c>
       <c r="Z152">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="AA152">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB152">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AC152">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AD152">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE152">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF152">
         <v>1.42</v>
@@ -25248,19 +25248,19 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O153">
         <v>3.75</v>
       </c>
       <c r="P153">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="Q153">
         <v>2.5</v>
       </c>
       <c r="R153">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S153">
         <v>1.2</v>
@@ -25281,28 +25281,28 @@
         <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z153">
         <v>5.5</v>
       </c>
       <c r="AA153">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB153">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AC153">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AD153">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE153">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF153">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AG153">
         <v>2.7</v>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK153">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL153">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O7">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="P7">
-        <v>3.17</v>
+        <v>2.5</v>
       </c>
       <c r="Q7">
-        <v>2.51</v>
+        <v>3.38</v>
       </c>
       <c r="R7">
+        <v>2.21</v>
+      </c>
+      <c r="S7">
+        <v>1.33</v>
+      </c>
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="U7">
+        <v>2.65</v>
+      </c>
+      <c r="V7">
+        <v>1.4</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1.05</v>
+      </c>
+      <c r="Y7">
+        <v>1.24</v>
+      </c>
+      <c r="Z7">
+        <v>3.38</v>
+      </c>
+      <c r="AA7">
+        <v>1.93</v>
+      </c>
+      <c r="AB7">
+        <v>1.9</v>
+      </c>
+      <c r="AC7">
+        <v>3.25</v>
+      </c>
+      <c r="AD7">
+        <v>1.3</v>
+      </c>
+      <c r="AE7">
+        <v>1.08</v>
+      </c>
+      <c r="AF7">
+        <v>1.65</v>
+      </c>
+      <c r="AG7">
         <v>2.08</v>
       </c>
-      <c r="S7">
-        <v>1.44</v>
-      </c>
-      <c r="T7">
-        <v>2.59</v>
-      </c>
-      <c r="U7">
-        <v>3</v>
-      </c>
-      <c r="V7">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.35</v>
       </c>
-      <c r="W7">
-        <v>1.03</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.36</v>
-      </c>
-      <c r="Z7">
-        <v>2.89</v>
-      </c>
-      <c r="AA7">
-        <v>2.15</v>
-      </c>
-      <c r="AB7">
-        <v>1.75</v>
-      </c>
-      <c r="AC7">
-        <v>3.88</v>
-      </c>
-      <c r="AD7">
-        <v>1.22</v>
-      </c>
-      <c r="AE7">
-        <v>1.04</v>
-      </c>
-      <c r="AF7">
-        <v>1.85</v>
-      </c>
-      <c r="AG7">
-        <v>1.85</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.33</v>
-      </c>
       <c r="AK7">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O8">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="P8">
-        <v>2.5</v>
+        <v>3.17</v>
       </c>
       <c r="Q8">
-        <v>3.38</v>
+        <v>2.51</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
+        <v>1.44</v>
+      </c>
+      <c r="T8">
+        <v>2.59</v>
+      </c>
+      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>1.35</v>
+      </c>
+      <c r="W8">
+        <v>1.03</v>
+      </c>
+      <c r="X8">
+        <v>1.03</v>
+      </c>
+      <c r="Y8">
+        <v>1.36</v>
+      </c>
+      <c r="Z8">
+        <v>2.89</v>
+      </c>
+      <c r="AA8">
+        <v>2.15</v>
+      </c>
+      <c r="AB8">
+        <v>1.75</v>
+      </c>
+      <c r="AC8">
+        <v>3.88</v>
+      </c>
+      <c r="AD8">
+        <v>1.22</v>
+      </c>
+      <c r="AE8">
+        <v>1.04</v>
+      </c>
+      <c r="AF8">
+        <v>1.85</v>
+      </c>
+      <c r="AG8">
+        <v>1.85</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.33</v>
       </c>
-      <c r="T8">
-        <v>3</v>
-      </c>
-      <c r="U8">
-        <v>2.65</v>
-      </c>
-      <c r="V8">
-        <v>1.4</v>
-      </c>
-      <c r="W8">
-        <v>1.06</v>
-      </c>
-      <c r="X8">
-        <v>1.05</v>
-      </c>
-      <c r="Y8">
-        <v>1.24</v>
-      </c>
-      <c r="Z8">
-        <v>3.38</v>
-      </c>
-      <c r="AA8">
-        <v>1.93</v>
-      </c>
-      <c r="AB8">
-        <v>1.9</v>
-      </c>
-      <c r="AC8">
-        <v>3.25</v>
-      </c>
-      <c r="AD8">
-        <v>1.3</v>
-      </c>
-      <c r="AE8">
-        <v>1.08</v>
-      </c>
-      <c r="AF8">
-        <v>1.65</v>
-      </c>
-      <c r="AG8">
-        <v>2.08</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.35</v>
-      </c>
       <c r="AK8">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.45</v>
+        <v>2.17</v>
       </c>
       <c r="O11">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="P11">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S11">
         <v>1.35</v>
       </c>
       <c r="T11">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="U11">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC11">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.17</v>
+        <v>4.45</v>
       </c>
       <c r="O12">
-        <v>3.27</v>
+        <v>3.75</v>
       </c>
       <c r="P12">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q12">
-        <v>3.02</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="U12">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="AA12">
+        <v>1.8</v>
+      </c>
+      <c r="AB12">
         <v>1.88</v>
       </c>
-      <c r="AB12">
-        <v>1.9</v>
-      </c>
       <c r="AC12">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
+        <v>1.12</v>
+      </c>
+      <c r="AF12">
+        <v>1.87</v>
+      </c>
+      <c r="AG12">
+        <v>1.86</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>2.25</v>
+      </c>
+      <c r="AK12">
         <v>1.1</v>
-      </c>
-      <c r="AF12">
-        <v>1.65</v>
-      </c>
-      <c r="AG12">
-        <v>2.15</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.3</v>
-      </c>
-      <c r="AK12">
-        <v>1.43</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="O18">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q18">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="R18">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="U18">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
-        <v>4.05</v>
+        <v>3.16</v>
       </c>
       <c r="AA18">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AB18">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AC18">
-        <v>2.49</v>
+        <v>3.48</v>
       </c>
       <c r="AD18">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG18">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>3.04</v>
+        <v>2.04</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
+        <v>1.2</v>
+      </c>
+      <c r="O19">
+        <v>4.75</v>
+      </c>
+      <c r="P19">
+        <v>7.5</v>
+      </c>
+      <c r="Q19">
+        <v>1.72</v>
+      </c>
+      <c r="R19">
+        <v>2.39</v>
+      </c>
+      <c r="S19">
+        <v>1.25</v>
+      </c>
+      <c r="T19">
+        <v>3.3</v>
+      </c>
+      <c r="U19">
+        <v>2.43</v>
+      </c>
+      <c r="V19">
         <v>1.53</v>
       </c>
-      <c r="O19">
-        <v>3.45</v>
-      </c>
-      <c r="P19">
-        <v>4.2</v>
-      </c>
-      <c r="Q19">
+      <c r="W19">
+        <v>1.13</v>
+      </c>
+      <c r="X19">
+        <v>1.02</v>
+      </c>
+      <c r="Y19">
+        <v>1.16</v>
+      </c>
+      <c r="Z19">
+        <v>4.05</v>
+      </c>
+      <c r="AA19">
+        <v>1.59</v>
+      </c>
+      <c r="AB19">
         <v>2.1</v>
       </c>
-      <c r="R19">
-        <v>2.02</v>
-      </c>
-      <c r="S19">
-        <v>1.41</v>
-      </c>
-      <c r="T19">
-        <v>2.74</v>
-      </c>
-      <c r="U19">
-        <v>2.92</v>
-      </c>
-      <c r="V19">
-        <v>1.32</v>
-      </c>
-      <c r="W19">
-        <v>1.02</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>1.33</v>
-      </c>
-      <c r="Z19">
-        <v>3.16</v>
-      </c>
-      <c r="AA19">
-        <v>2.05</v>
-      </c>
-      <c r="AB19">
-        <v>1.74</v>
-      </c>
       <c r="AC19">
-        <v>3.48</v>
+        <v>2.49</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG19">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK19">
-        <v>2.04</v>
+        <v>3.04</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
         <v>3.2</v>
       </c>
       <c r="P25">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -4399,22 +4399,22 @@
         <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
         <v>3.1</v>
       </c>
       <c r="U25">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
         <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.24</v>
@@ -4426,7 +4426,7 @@
         <v>1.84</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC25">
         <v>2.75</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="Q27">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R27">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="T27">
         <v>2.53</v>
       </c>
       <c r="U27">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W27">
         <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z27">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="AA27">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AB27">
+        <v>1.54</v>
+      </c>
+      <c r="AC27">
+        <v>4.2</v>
+      </c>
+      <c r="AD27">
+        <v>1.18</v>
+      </c>
+      <c r="AE27">
+        <v>1.03</v>
+      </c>
+      <c r="AF27">
+        <v>2.02</v>
+      </c>
+      <c r="AG27">
         <v>1.69</v>
-      </c>
-      <c r="AC27">
-        <v>3.45</v>
-      </c>
-      <c r="AD27">
-        <v>1.22</v>
-      </c>
-      <c r="AE27">
-        <v>1.08</v>
-      </c>
-      <c r="AF27">
-        <v>1.83</v>
-      </c>
-      <c r="AG27">
-        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="O28">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="Q28">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S28">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
         <v>2.53</v>
       </c>
       <c r="U28">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="V28">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
         <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="AA28">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="AB28">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AC28">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD28">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P36">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -6195,16 +6195,16 @@
         <v>1.24</v>
       </c>
       <c r="T36">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6219,13 +6219,13 @@
         <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC36">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD36">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE36">
         <v>1.2</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
         <v>1.99</v>
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q37">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R37">
         <v>2.14</v>
       </c>
       <c r="S37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
         <v>2.88</v>
       </c>
       <c r="U37">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6379,16 +6379,16 @@
         <v>3.4</v>
       </c>
       <c r="AA37">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
         <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="AD37">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE37">
         <v>1.04</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK37">
         <v>1.93</v>
@@ -6518,7 +6518,7 @@
         <v>2.19</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
         <v>2.59</v>
@@ -6530,13 +6530,13 @@
         <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
         <v>3.05</v>
@@ -6545,10 +6545,10 @@
         <v>1.96</v>
       </c>
       <c r="AB38">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC38">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="AD38">
         <v>1.25</v>
@@ -6557,10 +6557,10 @@
         <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG38">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="O44">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
         <v>3.07</v>
       </c>
       <c r="Q44">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="R44">
         <v>2.06</v>
@@ -7523,7 +7523,7 @@
         <v>1.76</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC44">
         <v>2.88</v>
@@ -7532,7 +7532,7 @@
         <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF44">
         <v>1.57</v>
@@ -10415,49 +10415,49 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="O62">
         <v>3.37</v>
       </c>
       <c r="P62">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q62">
         <v>3.7</v>
       </c>
       <c r="R62">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S62">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T62">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U62">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V62">
         <v>1.53</v>
       </c>
       <c r="W62">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z62">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AA62">
         <v>1.6</v>
       </c>
       <c r="AB62">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AC62">
         <v>2.55</v>
@@ -10466,13 +10466,13 @@
         <v>1.5</v>
       </c>
       <c r="AE62">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF62">
         <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AK62">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>4.5</v>
@@ -11734,16 +11734,16 @@
         <v>2.55</v>
       </c>
       <c r="S70">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T70">
         <v>3.8</v>
       </c>
       <c r="U70">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V70">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W70">
         <v>1.14</v>
@@ -11761,10 +11761,10 @@
         <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC70">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AD70">
         <v>1.65</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
         <v>1.14</v>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O78">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P78">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q78">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R78">
         <v>2.3</v>
@@ -13050,7 +13050,7 @@
         <v>1.48</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X78">
         <v>1.02</v>
@@ -13059,22 +13059,22 @@
         <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="AA78">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB78">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC78">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AD78">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF78">
         <v>1.64</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="O106">
         <v>3</v>
@@ -17611,7 +17611,7 @@
         <v>3.22</v>
       </c>
       <c r="V106">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W106">
         <v>1.07</v>
@@ -19057,28 +19057,28 @@
         <v>1.57</v>
       </c>
       <c r="O115">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P115">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Q115">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="R115">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S115">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T115">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="U115">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V115">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="W115">
         <v>1.26</v>
@@ -19093,7 +19093,7 @@
         <v>8</v>
       </c>
       <c r="AA115">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AB115">
         <v>3.2</v>
@@ -19102,16 +19102,16 @@
         <v>1.72</v>
       </c>
       <c r="AD115">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AE115">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF115">
         <v>1.3</v>
       </c>
       <c r="AG115">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>1.14</v>
       </c>
       <c r="AK115">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19715,10 +19715,10 @@
         <v>2.7</v>
       </c>
       <c r="Q119">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R119">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S119">
         <v>1.2</v>
@@ -19736,7 +19736,7 @@
         <v>1.17</v>
       </c>
       <c r="X119">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
         <v>1.11</v>
@@ -19754,7 +19754,7 @@
         <v>2.2</v>
       </c>
       <c r="AD119">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE119">
         <v>1.23</v>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK119">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.08</v>
+        <v>2.03</v>
       </c>
       <c r="O126">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="P126">
-        <v>1.86</v>
+        <v>2.7</v>
       </c>
       <c r="Q126">
-        <v>4.25</v>
+        <v>2.86</v>
       </c>
       <c r="R126">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="S126">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T126">
         <v>2.82</v>
       </c>
       <c r="U126">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V126">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z126">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA126">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB126">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AC126">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD126">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE126">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF126">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG126">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK126">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,80 +21010,80 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.03</v>
+        <v>3.08</v>
       </c>
       <c r="O127">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="P127">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="Q127">
-        <v>2.86</v>
+        <v>4.25</v>
       </c>
       <c r="R127">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S127">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T127">
         <v>2.82</v>
       </c>
       <c r="U127">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V127">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
+        <v>1.3</v>
+      </c>
+      <c r="Z127">
+        <v>3.4</v>
+      </c>
+      <c r="AA127">
+        <v>1.9</v>
+      </c>
+      <c r="AB127">
+        <v>1.82</v>
+      </c>
+      <c r="AC127">
+        <v>3.14</v>
+      </c>
+      <c r="AD127">
+        <v>1.27</v>
+      </c>
+      <c r="AE127">
+        <v>1.06</v>
+      </c>
+      <c r="AF127">
+        <v>1.73</v>
+      </c>
+      <c r="AG127">
+        <v>1.96</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
+        <v>1.23</v>
+      </c>
+      <c r="AK127">
         <v>1.21</v>
-      </c>
-      <c r="Z127">
-        <v>3.8</v>
-      </c>
-      <c r="AA127">
-        <v>1.76</v>
-      </c>
-      <c r="AB127">
-        <v>1.94</v>
-      </c>
-      <c r="AC127">
-        <v>2.83</v>
-      </c>
-      <c r="AD127">
-        <v>1.33</v>
-      </c>
-      <c r="AE127">
-        <v>1.14</v>
-      </c>
-      <c r="AF127">
-        <v>1.61</v>
-      </c>
-      <c r="AG127">
-        <v>2.16</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>1.25</v>
-      </c>
-      <c r="AK127">
-        <v>1.51</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
+        <v>1.95</v>
+      </c>
+      <c r="O136">
+        <v>3.5</v>
+      </c>
+      <c r="P136">
         <v>3.1</v>
       </c>
-      <c r="O136">
-        <v>3.35</v>
-      </c>
-      <c r="P136">
-        <v>2.03</v>
-      </c>
       <c r="Q136">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="R136">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T136">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="U136">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="V136">
         <v>1.44</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z136">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA136">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB136">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC136">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AD136">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE136">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF136">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG136">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="AK136">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P137">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q137">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="R137">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S137">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T137">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="U137">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="V137">
         <v>1.44</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z137">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA137">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB137">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC137">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AD137">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE137">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG137">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="AK137">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G141">
@@ -23295,13 +23295,13 @@
         <v>1.95</v>
       </c>
       <c r="O141">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P141">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q141">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R141">
         <v>2.4</v>
@@ -23310,46 +23310,46 @@
         <v>1.25</v>
       </c>
       <c r="T141">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U141">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="V141">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W141">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X141">
         <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z141">
-        <v>5.1</v>
+        <v>5.29</v>
       </c>
       <c r="AA141">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB141">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AC141">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD141">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE141">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF141">
         <v>1.44</v>
       </c>
       <c r="AG141">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK141">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
+        <v>1.5</v>
+      </c>
+      <c r="O142">
+        <v>4.2</v>
+      </c>
+      <c r="P142">
+        <v>4.9</v>
+      </c>
+      <c r="Q142">
         <v>1.95</v>
       </c>
-      <c r="O142">
-        <v>3.5</v>
-      </c>
-      <c r="P142">
-        <v>3.1</v>
-      </c>
-      <c r="Q142">
-        <v>2.5</v>
-      </c>
       <c r="R142">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S142">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T142">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U142">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="V142">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W142">
+        <v>1.15</v>
+      </c>
+      <c r="X142">
+        <v>0</v>
+      </c>
+      <c r="Y142">
         <v>1.14</v>
       </c>
-      <c r="X142">
-        <v>1.01</v>
-      </c>
-      <c r="Y142">
-        <v>1.16</v>
-      </c>
       <c r="Z142">
-        <v>5.29</v>
+        <v>6</v>
       </c>
       <c r="AA142">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB142">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AC142">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AD142">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE142">
         <v>1.26</v>
       </c>
       <c r="AF142">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AG142">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK142">
-        <v>1.67</v>
+        <v>2.43</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,61 +23618,61 @@
         </is>
       </c>
       <c r="N143">
+        <v>2.87</v>
+      </c>
+      <c r="O143">
+        <v>3.94</v>
+      </c>
+      <c r="P143">
+        <v>2.16</v>
+      </c>
+      <c r="Q143">
+        <v>3.4</v>
+      </c>
+      <c r="R143">
+        <v>2.25</v>
+      </c>
+      <c r="S143">
+        <v>1.25</v>
+      </c>
+      <c r="T143">
+        <v>3.02</v>
+      </c>
+      <c r="U143">
+        <v>2.4</v>
+      </c>
+      <c r="V143">
+        <v>1.54</v>
+      </c>
+      <c r="W143">
+        <v>1.14</v>
+      </c>
+      <c r="X143">
+        <v>1.01</v>
+      </c>
+      <c r="Y143">
+        <v>1.16</v>
+      </c>
+      <c r="Z143">
+        <v>4.1</v>
+      </c>
+      <c r="AA143">
+        <v>1.7</v>
+      </c>
+      <c r="AB143">
+        <v>2.3</v>
+      </c>
+      <c r="AC143">
+        <v>2.56</v>
+      </c>
+      <c r="AD143">
+        <v>1.49</v>
+      </c>
+      <c r="AE143">
+        <v>1.14</v>
+      </c>
+      <c r="AF143">
         <v>1.5</v>
-      </c>
-      <c r="O143">
-        <v>4.2</v>
-      </c>
-      <c r="P143">
-        <v>4.9</v>
-      </c>
-      <c r="Q143">
-        <v>1.95</v>
-      </c>
-      <c r="R143">
-        <v>2.6</v>
-      </c>
-      <c r="S143">
-        <v>1.17</v>
-      </c>
-      <c r="T143">
-        <v>4.5</v>
-      </c>
-      <c r="U143">
-        <v>2</v>
-      </c>
-      <c r="V143">
-        <v>1.75</v>
-      </c>
-      <c r="W143">
-        <v>1.15</v>
-      </c>
-      <c r="X143">
-        <v>0</v>
-      </c>
-      <c r="Y143">
-        <v>1.14</v>
-      </c>
-      <c r="Z143">
-        <v>6</v>
-      </c>
-      <c r="AA143">
-        <v>1.4</v>
-      </c>
-      <c r="AB143">
-        <v>2.7</v>
-      </c>
-      <c r="AC143">
-        <v>2.03</v>
-      </c>
-      <c r="AD143">
-        <v>1.67</v>
-      </c>
-      <c r="AE143">
-        <v>1.26</v>
-      </c>
-      <c r="AF143">
-        <v>1.54</v>
       </c>
       <c r="AG143">
         <v>2.4</v>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK143">
-        <v>2.43</v>
+        <v>1.28</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.87</v>
+        <v>1.95</v>
       </c>
       <c r="O144">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="P144">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="Q144">
-        <v>3.4</v>
+        <v>2.51</v>
       </c>
       <c r="R144">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S144">
         <v>1.25</v>
       </c>
       <c r="T144">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="U144">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="V144">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="W144">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X144">
         <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z144">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AA144">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AB144">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC144">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AD144">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AE144">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF144">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG144">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK144">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="AL144">
         <v>0</v>

--- a/jogos_2026-08-01.xlsx
+++ b/jogos_2026-08-01.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O7">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="P7">
-        <v>2.5</v>
+        <v>3.17</v>
       </c>
       <c r="Q7">
-        <v>3.38</v>
+        <v>2.51</v>
       </c>
       <c r="R7">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
+        <v>1.44</v>
+      </c>
+      <c r="T7">
+        <v>2.59</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>1.35</v>
+      </c>
+      <c r="W7">
+        <v>1.03</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
+        <v>1.36</v>
+      </c>
+      <c r="Z7">
+        <v>2.89</v>
+      </c>
+      <c r="AA7">
+        <v>2.15</v>
+      </c>
+      <c r="AB7">
+        <v>1.75</v>
+      </c>
+      <c r="AC7">
+        <v>3.88</v>
+      </c>
+      <c r="AD7">
+        <v>1.22</v>
+      </c>
+      <c r="AE7">
+        <v>1.04</v>
+      </c>
+      <c r="AF7">
+        <v>1.85</v>
+      </c>
+      <c r="AG7">
+        <v>1.85</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.33</v>
       </c>
-      <c r="T7">
-        <v>3</v>
-      </c>
-      <c r="U7">
-        <v>2.65</v>
-      </c>
-      <c r="V7">
-        <v>1.4</v>
-      </c>
-      <c r="W7">
-        <v>1.06</v>
-      </c>
-      <c r="X7">
-        <v>1.05</v>
-      </c>
-      <c r="Y7">
-        <v>1.24</v>
-      </c>
-      <c r="Z7">
-        <v>3.38</v>
-      </c>
-      <c r="AA7">
-        <v>1.93</v>
-      </c>
-      <c r="AB7">
-        <v>1.9</v>
-      </c>
-      <c r="AC7">
-        <v>3.25</v>
-      </c>
-      <c r="AD7">
-        <v>1.3</v>
-      </c>
-      <c r="AE7">
-        <v>1.08</v>
-      </c>
-      <c r="AF7">
-        <v>1.65</v>
-      </c>
-      <c r="AG7">
-        <v>2.08</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.35</v>
-      </c>
       <c r="AK7">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O8">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="P8">
-        <v>3.17</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
-        <v>2.51</v>
+        <v>3.38</v>
       </c>
       <c r="R8">
+        <v>2.21</v>
+      </c>
+      <c r="S8">
+        <v>1.33</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>2.65</v>
+      </c>
+      <c r="V8">
+        <v>1.4</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>1.24</v>
+      </c>
+      <c r="Z8">
+        <v>3.38</v>
+      </c>
+      <c r="AA8">
+        <v>1.93</v>
+      </c>
+      <c r="AB8">
+        <v>1.9</v>
+      </c>
+      <c r="AC8">
+        <v>3.25</v>
+      </c>
+      <c r="AD8">
+        <v>1.3</v>
+      </c>
+      <c r="AE8">
+        <v>1.08</v>
+      </c>
+      <c r="AF8">
+        <v>1.65</v>
+      </c>
+      <c r="AG8">
         <v>2.08</v>
       </c>
-      <c r="S8">
-        <v>1.44</v>
-      </c>
-      <c r="T8">
-        <v>2.59</v>
-      </c>
-      <c r="U8">
-        <v>3</v>
-      </c>
-      <c r="V8">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.35</v>
       </c>
-      <c r="W8">
-        <v>1.03</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.36</v>
-      </c>
-      <c r="Z8">
-        <v>2.89</v>
-      </c>
-      <c r="AA8">
-        <v>2.15</v>
-      </c>
-      <c r="AB8">
-        <v>1.75</v>
-      </c>
-      <c r="AC8">
-        <v>3.88</v>
-      </c>
-      <c r="AD8">
-        <v>1.22</v>
-      </c>
-      <c r="AE8">
-        <v>1.04</v>
-      </c>
-      <c r="AF8">
-        <v>1.85</v>
-      </c>
-      <c r="AG8">
-        <v>1.85</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.33</v>
-      </c>
       <c r="AK8">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.17</v>
+        <v>4.45</v>
       </c>
       <c r="O11">
-        <v>3.27</v>
+        <v>3.75</v>
       </c>
       <c r="P11">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q11">
-        <v>3.02</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
         <v>1.35</v>
       </c>
       <c r="T11">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="U11">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="AA11">
+        <v>1.8</v>
+      </c>
+      <c r="AB11">
         <v>1.88</v>
       </c>
-      <c r="AB11">
-        <v>1.9</v>
-      </c>
       <c r="AC11">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
+        <v>1.12</v>
+      </c>
+      <c r="AF11">
+        <v>1.87</v>
+      </c>
+      <c r="AG11">
+        <v>1.86</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>2.25</v>
+      </c>
+      <c r="AK11">
         <v>1.1</v>
-      </c>
-      <c r="AF11">
-        <v>1.65</v>
-      </c>
-      <c r="AG11">
-        <v>2.15</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.3</v>
-      </c>
-      <c r="AK11">
-        <v>1.43</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.45</v>
+        <v>2.17</v>
       </c>
       <c r="O12">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="P12">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S12">
         <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="U12">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB12">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>3.25</v>
       </c>
       <c r="P15">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="Q15">
         <v>3.62</v>
@@ -2769,10 +2769,10 @@
         <v>2.02</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T15">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U15">
         <v>3.2</v>
@@ -2787,19 +2787,19 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z15">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="AA15">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB15">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>4.03</v>
+        <v>3.94</v>
       </c>
       <c r="AD15">
         <v>1.21</v>
@@ -2811,7 +2811,7 @@
         <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AK15">
         <v>1.44</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,49 +2917,49 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.78</v>
+        <v>2.33</v>
       </c>
       <c r="O16">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="P16">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="Q16">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U16">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="V16">
         <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
         <v>3.28</v>
       </c>
       <c r="AA16">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AB16">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
         <v>3.2</v>
@@ -2968,13 +2968,13 @@
         <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG16">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK16">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,49 +3080,49 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="O17">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="P17">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="Q17">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U17">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="V17">
         <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
         <v>3.28</v>
       </c>
       <c r="AA17">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC17">
         <v>3.2</v>
@@ -3131,13 +3131,13 @@
         <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG17">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>1.2</v>
+      </c>
+      <c r="O18">
+        <v>4.75</v>
+      </c>
+      <c r="P18">
+        <v>7.5</v>
+      </c>
+      <c r="Q18">
+        <v>1.72</v>
+      </c>
+      <c r="R18">
+        <v>2.39</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.3</v>
+      </c>
+      <c r="U18">
+        <v>2.43</v>
+      </c>
+      <c r="V18">
         <v>1.53</v>
       </c>
-      <c r="O18">
-        <v>3.45</v>
-      </c>
-      <c r="P18">
-        <v>4.2</v>
-      </c>
-      <c r="Q18">
+      <c r="W18">
+        <v>1.13</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.16</v>
+      </c>
+      <c r="Z18">
+        <v>4.05</v>
+      </c>
+      <c r="AA18">
+        <v>1.59</v>
+      </c>
+      <c r="AB18">
         <v>2.1</v>
       </c>
-      <c r="R18">
-        <v>2.02</v>
-      </c>
-      <c r="S18">
-        <v>1.41</v>
-      </c>
-      <c r="T18">
-        <v>2.74</v>
-      </c>
-      <c r="U18">
-        <v>2.92</v>
-      </c>
-      <c r="V18">
-        <v>1.32</v>
-      </c>
-      <c r="W18">
-        <v>1.02</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.33</v>
-      </c>
-      <c r="Z18">
-        <v>3.16</v>
-      </c>
-      <c r="AA18">
-        <v>2.05</v>
-      </c>
-      <c r="AB18">
-        <v>1.74</v>
-      </c>
       <c r="AC18">
-        <v>3.48</v>
+        <v>2.49</v>
       </c>
       <c r="AD18">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG18">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK18">
-        <v>2.04</v>
+        <v>3.04</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="O19">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="U19">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>4.05</v>
+        <v>3.16</v>
       </c>
       <c r="AA19">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AC19">
-        <v>2.49</v>
+        <v>3.48</v>
       </c>
       <c r="AD19">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG19">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>3.04</v>
+        <v>2.04</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q24">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="R24">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA24">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AB24">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC24">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="AD24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE24">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,49 +4384,49 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
         <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V25">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
         <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z25">
-        <v>3.34</v>
+        <v>3.77</v>
       </c>
       <c r="AA25">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AB25">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC25">
         <v>2.75</v>
@@ -4435,7 +4435,7 @@
         <v>1.38</v>
       </c>
       <c r="AE25">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
         <v>1.67</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>4.7</v>
+        <v>2.95</v>
       </c>
       <c r="P26">
-        <v>8.6</v>
+        <v>3.18</v>
       </c>
       <c r="Q26">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="T26">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="U26">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="Z26">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AB26">
+        <v>1.54</v>
+      </c>
+      <c r="AC26">
+        <v>4.2</v>
+      </c>
+      <c r="AD26">
+        <v>1.18</v>
+      </c>
+      <c r="AE26">
+        <v>1.03</v>
+      </c>
+      <c r="AF26">
         <v>2.02</v>
       </c>
-      <c r="AC26">
-        <v>3.1</v>
-      </c>
-      <c r="AD26">
-        <v>1.36</v>
-      </c>
-      <c r="AE26">
-        <v>1.14</v>
-      </c>
-      <c r="AF26">
-        <v>2.3</v>
-      </c>
       <c r="AG26">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>3.54</v>
+        <v>1.64</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="O27">
-        <v>2.95</v>
+        <v>4.7</v>
       </c>
       <c r="P27">
-        <v>3.18</v>
+        <v>8.6</v>
       </c>
       <c r="Q27">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="R27">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>2.52</v>
+        <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AC27">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG27">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK27">
-        <v>1.64</v>
+        <v>3.54</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6017,16 +6017,16 @@
         <v>1.48</v>
       </c>
       <c r="O35">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="P35">
         <v>4.8</v>
       </c>
       <c r="Q35">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R35">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S35">
         <v>1.31</v>
@@ -6035,10 +6035,10 @@
         <v>3.32</v>
       </c>
       <c r="U35">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6050,13 +6050,13 @@
         <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA35">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB35">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC35">
         <v>2.74</v>
@@ -6071,7 +6071,7 @@
         <v>1.78</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O47">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7991,43 +7991,43 @@
         <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="V47">
         <v>1.48</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>3.98</v>
+        <v>3.62</v>
       </c>
       <c r="AA47">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB47">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC47">
         <v>2.8</v>
       </c>
       <c r="AD47">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
         <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK47">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="O48">
         <v>3.29</v>
       </c>
       <c r="P48">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q48">
         <v>3.55</v>
@@ -8148,49 +8148,49 @@
         <v>2.04</v>
       </c>
       <c r="S48">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T48">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="U48">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="V48">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W48">
         <v>1.01</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z48">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AA48">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB48">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC48">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AD48">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE48">
         <v>1.02</v>
       </c>
       <c r="AF48">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG48">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AK48">
         <v>1.28</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O58">
         <v>3</v>
       </c>
       <c r="P58">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="Q58">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S58">
         <v>1.42</v>
@@ -9784,31 +9784,31 @@
         <v>2.65</v>
       </c>
       <c r="U58">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="V58">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X58">
         <v>1.06</v>
       </c>
       <c r="Y58">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z58">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA58">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB58">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC58">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AD58">
         <v>1.22</v>
@@ -9817,10 +9817,10 @@
         <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG58">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10415,55 +10415,55 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="O62">
         <v>3.37</v>
       </c>
       <c r="P62">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q62">
-        <v>3.7</v>
+        <v>4.02</v>
       </c>
       <c r="R62">
         <v>2.28</v>
       </c>
       <c r="S62">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U62">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X62">
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z62">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA62">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB62">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AC62">
         <v>2.55</v>
       </c>
       <c r="AD62">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE62">
         <v>1.21</v>
@@ -10472,7 +10472,7 @@
         <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,49 +10578,49 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="O63">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="P63">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q63">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R63">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S63">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T63">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="U63">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="V63">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W63">
         <v>1.04</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z63">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="AA63">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AB63">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC63">
         <v>3.65</v>
@@ -10635,7 +10635,7 @@
         <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O65">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P65">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="Q65">
         <v>3</v>
@@ -10922,10 +10922,10 @@
         <v>1.5</v>
       </c>
       <c r="T65">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="U65">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="V65">
         <v>1.29</v>
@@ -10937,31 +10937,31 @@
         <v>1.05</v>
       </c>
       <c r="Y65">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z65">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AA65">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB65">
         <v>1.53</v>
       </c>
       <c r="AC65">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD65">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE65">
         <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AG65">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11076,55 +11076,55 @@
         <v>2.38</v>
       </c>
       <c r="Q66">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R66">
+        <v>1.91</v>
+      </c>
+      <c r="S66">
+        <v>1.36</v>
+      </c>
+      <c r="T66">
+        <v>2.18</v>
+      </c>
+      <c r="U66">
+        <v>2.32</v>
+      </c>
+      <c r="V66">
+        <v>1.3</v>
+      </c>
+      <c r="W66">
+        <v>1.06</v>
+      </c>
+      <c r="X66">
+        <v>1.01</v>
+      </c>
+      <c r="Y66">
+        <v>1.25</v>
+      </c>
+      <c r="Z66">
+        <v>3.08</v>
+      </c>
+      <c r="AA66">
         <v>2.1</v>
       </c>
-      <c r="S66">
-        <v>1.32</v>
-      </c>
-      <c r="T66">
-        <v>2.92</v>
-      </c>
-      <c r="U66">
-        <v>2.71</v>
-      </c>
-      <c r="V66">
-        <v>1.4</v>
-      </c>
-      <c r="W66">
-        <v>1.08</v>
-      </c>
-      <c r="X66">
-        <v>1</v>
-      </c>
-      <c r="Y66">
-        <v>1.2</v>
-      </c>
-      <c r="Z66">
-        <v>2.75</v>
-      </c>
-      <c r="AA66">
-        <v>1.67</v>
-      </c>
       <c r="AB66">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC66">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD66">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AG66">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -12208,31 +12208,31 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
         <v>2.18</v>
       </c>
       <c r="Q73">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R73">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S73">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T73">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U73">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="V73">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W73">
         <v>1.03</v>
@@ -12241,22 +12241,22 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z73">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA73">
         <v>1.91</v>
       </c>
       <c r="AB73">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC73">
         <v>3.35</v>
       </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE73">
         <v>1.05</v>
@@ -12265,7 +12265,7 @@
         <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O74">
         <v>3.3</v>
@@ -12380,10 +12380,10 @@
         <v>2.75</v>
       </c>
       <c r="Q74">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="R74">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
         <v>1.35</v>
@@ -12395,10 +12395,10 @@
         <v>2.65</v>
       </c>
       <c r="V74">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W74">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
         <v>1.02</v>
@@ -12407,13 +12407,13 @@
         <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA74">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB74">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC74">
         <v>2.83</v>
@@ -12428,7 +12428,7 @@
         <v>1.62</v>
       </c>
       <c r="AG74">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK74">
         <v>1.5</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O76">
         <v>3.25</v>
@@ -12706,55 +12706,55 @@
         <v>2.63</v>
       </c>
       <c r="Q76">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="R76">
         <v>2.05</v>
       </c>
       <c r="S76">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U76">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V76">
         <v>1.38</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
         <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA76">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB76">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC76">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD76">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF76">
         <v>1.7</v>
       </c>
       <c r="AG76">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13349,25 +13349,25 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="O80">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q80">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R80">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="S80">
         <v>1.32</v>
       </c>
       <c r="T80">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="U80">
         <v>2.53</v>
@@ -13391,22 +13391,22 @@
         <v>1.77</v>
       </c>
       <c r="AB80">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC80">
         <v>2.8</v>
       </c>
       <c r="AD80">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE80">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF80">
         <v>1.57</v>
       </c>
       <c r="AG80">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.27</v>
       </c>
       <c r="AK80">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,71 +13521,71 @@
         <v>5.05</v>
       </c>
       <c r="Q81">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S81">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T81">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U81">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V81">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z81">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA81">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB81">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC81">
+        <v>2.55</v>
+      </c>
+      <c r="AD81">
+        <v>1.45</v>
+      </c>
+      <c r="AE81">
+        <v>1.15</v>
+      </c>
+      <c r="AF81">
+        <v>1.78</v>
+      </c>
+      <c r="AG81">
+        <v>1.89</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <v>1.04</v>
+      </c>
+      <c r="AK81">
         <v>2.88</v>
-      </c>
-      <c r="AD81">
-        <v>1.38</v>
-      </c>
-      <c r="AE81">
-        <v>1.12</v>
-      </c>
-      <c r="AF81">
-        <v>1.8</v>
-      </c>
-      <c r="AG81">
-        <v>1.9</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.18</v>
-      </c>
-      <c r="AK81">
-        <v>2.5</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P83">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="Q83">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T83">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="U83">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="V83">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W83">
+        <v>1.06</v>
+      </c>
+      <c r="X83">
         <v>1.04</v>
       </c>
-      <c r="X83">
-        <v>1.03</v>
-      </c>
       <c r="Y83">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z83">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AA83">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="AB83">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AC83">
-        <v>4.05</v>
+        <v>3.13</v>
       </c>
       <c r="AD83">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE83">
         <v>1.02</v>
       </c>
       <c r="AF83">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG83">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK83">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O84">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P84">
-        <v>6.35</v>
+        <v>5.15</v>
       </c>
       <c r="Q84">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R84">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S84">
         <v>1.29</v>
       </c>
       <c r="T84">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="U84">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="V84">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W84">
         <v>1.08</v>
@@ -14034,31 +14034,31 @@
         <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>3.86</v>
+        <v>2.9</v>
       </c>
       <c r="AA84">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB84">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC84">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD84">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE84">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF84">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG84">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,31 +14164,31 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O85">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P85">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q85">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="R85">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S85">
         <v>1.45</v>
       </c>
       <c r="T85">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="U85">
         <v>3.3</v>
       </c>
       <c r="V85">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W85">
         <v>1.03</v>
@@ -14206,7 +14206,7 @@
         <v>2.27</v>
       </c>
       <c r="AB85">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC85">
         <v>4.3</v>
@@ -14218,7 +14218,7 @@
         <v>1</v>
       </c>
       <c r="AF85">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG85">
         <v>1.73</v>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O86">
         <v>3.5</v>
@@ -14336,10 +14336,10 @@
         <v>4.06</v>
       </c>
       <c r="Q86">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R86">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S86">
         <v>1.33</v>
@@ -14351,28 +14351,28 @@
         <v>2.15</v>
       </c>
       <c r="V86">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z86">
         <v>2.8</v>
       </c>
       <c r="AA86">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB86">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC86">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="AD86">
         <v>1.25</v>
@@ -14381,10 +14381,10 @@
         <v>1.1</v>
       </c>
       <c r="AF86">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG86">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,55 +14499,55 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R87">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S87">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U87">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V87">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
         <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA87">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AB87">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AC87">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AD87">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE87">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF87">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG87">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK87">
         <v>1.73</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="O91">
         <v>3.08</v>
@@ -15151,19 +15151,19 @@
         <v>2.35</v>
       </c>
       <c r="Q91">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R91">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="S91">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T91">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U91">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="V91">
         <v>1.36</v>
@@ -15196,10 +15196,10 @@
         <v>1.05</v>
       </c>
       <c r="AF91">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG91">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AK91">
         <v>1.43</v>
@@ -16618,16 +16618,16 @@
         <v>6</v>
       </c>
       <c r="Q100">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="R100">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S100">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T100">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="U100">
         <v>2.5</v>
@@ -16636,31 +16636,31 @@
         <v>1.47</v>
       </c>
       <c r="W100">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z100">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AA100">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB100">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC100">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="AD100">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE100">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF100">
         <v>1.95</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK100">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="O101">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="P101">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="Q101">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="R101">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S101">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U101">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V101">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
         <v>3.8</v>
       </c>
       <c r="AA101">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB101">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC101">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD101">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE101">
         <v>1.12</v>
       </c>
       <c r="AF101">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG101">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK101">
         <v>3.2</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="O102">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="P102">
-        <v>5.79</v>
+        <v>7.3</v>
       </c>
       <c r="Q102">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="R102">
         <v>2.15</v>
       </c>
       <c r="S102">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V102">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
         <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z102">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA102">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
         <v>1.7</v>
       </c>
       <c r="AC102">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD102">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE102">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF102">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AG102">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AK102">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,22 +17107,22 @@
         <v>4.4</v>
       </c>
       <c r="Q103">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S103">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T103">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U103">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V103">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W103">
         <v>1.05</v>
@@ -17131,13 +17131,13 @@
         <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z103">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA103">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB103">
         <v>1.75</v>
@@ -17152,10 +17152,10 @@
         <v>1.07</v>
       </c>
       <c r="AF103">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG103">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK103">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17267,7 +17267,7 @@
         <v>3.15</v>
       </c>
       <c r="P104">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Q104">
         <v>2.5</v>
@@ -17276,10 +17276,10 @@
         <v>1.91</v>
       </c>
       <c r="S104">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T104">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U104">
         <v>3.48</v>
@@ -17291,34 +17291,34 @@
         <v>1.05</v>
       </c>
       <c r="X104">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y104">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z104">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AA104">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AB104">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC104">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD104">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE104">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF104">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG104">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK104">
         <v>1.91</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="O106">
         <v>3</v>
       </c>
       <c r="P106">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="Q106">
         <v>3.65</v>
@@ -17602,10 +17602,10 @@
         <v>1.84</v>
       </c>
       <c r="S106">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T106">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="U106">
         <v>3.22</v>
@@ -17614,7 +17614,7 @@
         <v>1.35</v>
       </c>
       <c r="W106">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X106">
         <v>1.05</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AK106">
         <v>1.39</v>
@@ -18728,10 +18728,10 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O113">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P113">
         <v>4.5</v>
@@ -18752,10 +18752,10 @@
         <v>2.45</v>
       </c>
       <c r="V113">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W113">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X113">
         <v>1.02</v>
@@ -18764,28 +18764,28 @@
         <v>1.16</v>
       </c>
       <c r="Z113">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA113">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB113">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC113">
         <v>2.62</v>
       </c>
       <c r="AD113">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE113">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF113">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG113">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>3.18</v>
       </c>
       <c r="O114">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P114">
         <v>1.95</v>
@@ -18906,7 +18906,7 @@
         <v>2.2</v>
       </c>
       <c r="S114">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T114">
         <v>2.85</v>
@@ -18915,40 +18915,40 @@
         <v>2.65</v>
       </c>
       <c r="V114">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W114">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y114">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z114">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AA114">
+        <v>1.83</v>
+      </c>
+      <c r="AB114">
         <v>1.87</v>
-      </c>
-      <c r="AB114">
-        <v>1.92</v>
       </c>
       <c r="AC114">
         <v>2.92</v>
       </c>
       <c r="AD114">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE114">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG114">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="O115">
         <v>4.2</v>
       </c>
       <c r="P115">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q115">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="R115">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="S115">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="T115">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="U115">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="V115">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W115">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X115">
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z115">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AA115">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB115">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AC115">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AD115">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AE115">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF115">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AG115">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK115">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O116">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P116">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q116">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R116">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="S116">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T116">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="U116">
         <v>3.3</v>
       </c>
       <c r="V116">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W116">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X116">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y116">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z116">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="AA116">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="AB116">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AC116">
-        <v>3.88</v>
+        <v>4.3</v>
       </c>
       <c r="AD116">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE116">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF116">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG116">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK116">
         <v>1.35</v>
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="O118">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="P118">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="Q118">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R118">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S118">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T118">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="U118">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="V118">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W118">
         <v>1.13</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y118">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z118">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB118">
+        <v>2.23</v>
+      </c>
+      <c r="AC118">
+        <v>2.38</v>
+      </c>
+      <c r="AD118">
+        <v>1.47</v>
+      </c>
+      <c r="AE118">
+        <v>1.22</v>
+      </c>
+      <c r="AF118">
+        <v>1.65</v>
+      </c>
+      <c r="AG118">
+        <v>2.05</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <v>1.16</v>
+      </c>
+      <c r="AK118">
         <v>2.21</v>
-      </c>
-      <c r="AC118">
-        <v>2.4</v>
-      </c>
-      <c r="AD118">
-        <v>1.45</v>
-      </c>
-      <c r="AE118">
-        <v>1.13</v>
-      </c>
-      <c r="AF118">
-        <v>1.57</v>
-      </c>
-      <c r="AG118">
-        <v>2.25</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.17</v>
-      </c>
-      <c r="AK118">
-        <v>1.91</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="O119">
         <v>3.6</v>
       </c>
       <c r="P119">
+        <v>2.75</v>
+      </c>
+      <c r="Q119">
+        <v>2.81</v>
+      </c>
+      <c r="R119">
+        <v>2.23</v>
+      </c>
+      <c r="S119">
+        <v>1.22</v>
+      </c>
+      <c r="T119">
+        <v>3.75</v>
+      </c>
+      <c r="U119">
+        <v>2.1</v>
+      </c>
+      <c r="V119">
+        <v>1.62</v>
+      </c>
+      <c r="W119">
+        <v>1.14</v>
+      </c>
+      <c r="X119">
+        <v>1.01</v>
+      </c>
+      <c r="Y119">
+        <v>1.13</v>
+      </c>
+      <c r="Z119">
+        <v>5.25</v>
+      </c>
+      <c r="AA119">
+        <v>1.49</v>
+      </c>
+      <c r="AB119">
+        <v>2.6</v>
+      </c>
+      <c r="AC119">
+        <v>2.21</v>
+      </c>
+      <c r="AD119">
+        <v>1.59</v>
+      </c>
+      <c r="AE119">
+        <v>1.2</v>
+      </c>
+      <c r="AF119">
+        <v>1.42</v>
+      </c>
+      <c r="AG119">
         <v>2.7</v>
       </c>
-      <c r="Q119">
-        <v>2.68</v>
-      </c>
-      <c r="R119">
-        <v>2.32</v>
-      </c>
-      <c r="S119">
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
         <v>1.2</v>
       </c>
-      <c r="T119">
-        <v>4</v>
-      </c>
-      <c r="U119">
-        <v>2.13</v>
-      </c>
-      <c r="V119">
-        <v>1.63</v>
-      </c>
-      <c r="W119">
-        <v>1.17</v>
-      </c>
-      <c r="X119">
-        <v>1.02</v>
-      </c>
-      <c r="Y119">
-        <v>1.11</v>
-      </c>
-      <c r="Z119">
-        <v>5.75</v>
-      </c>
-      <c r="AA119">
-        <v>1.44</v>
-      </c>
-      <c r="AB119">
-        <v>2.63</v>
-      </c>
-      <c r="AC119">
-        <v>2.2</v>
-      </c>
-      <c r="AD119">
-        <v>1.65</v>
-      </c>
-      <c r="AE119">
-        <v>1.23</v>
-      </c>
-      <c r="AF119">
-        <v>1.39</v>
-      </c>
-      <c r="AG119">
-        <v>2.73</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.22</v>
-      </c>
       <c r="AK119">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,52 +19869,52 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O120">
         <v>3</v>
       </c>
       <c r="P120">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q120">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="R120">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="S120">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T120">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U120">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V120">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W120">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X120">
         <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z120">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="AA120">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AB120">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC120">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AD120">
         <v>1.25</v>
@@ -19923,10 +19923,10 @@
         <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG120">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK120">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20035,22 +20035,22 @@
         <v>2.6</v>
       </c>
       <c r="O121">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P121">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="Q121">
         <v>3.3</v>
       </c>
       <c r="R121">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S121">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T121">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U121">
         <v>3</v>
@@ -20062,7 +20062,7 @@
         <v>1.06</v>
       </c>
       <c r="X121">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y121">
         <v>1.36</v>
@@ -20071,22 +20071,22 @@
         <v>3.1</v>
       </c>
       <c r="AA121">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AB121">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC121">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD121">
         <v>1.22</v>
       </c>
       <c r="AE121">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG121">
         <v>1.84</v>
@@ -20105,7 +20105,7 @@
         <v>1.28</v>
       </c>
       <c r="AK121">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20207,52 +20207,52 @@
         <v>1.85</v>
       </c>
       <c r="R122">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T122">
         <v>2.91</v>
       </c>
       <c r="U122">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="V122">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z122">
         <v>3.58</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB122">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC122">
         <v>3.1</v>
       </c>
       <c r="AD122">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE122">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
         <v>2</v>
       </c>
       <c r="AG122">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK122">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O124">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P124">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q124">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="R124">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S124">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T124">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U124">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="V124">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W124">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X124">
         <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z124">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA124">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB124">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC124">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="AD124">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE124">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF124">
         <v>1.68</v>
       </c>
       <c r="AG124">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK124">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20699,13 +20699,13 @@
         <v>2.3</v>
       </c>
       <c r="S125">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T125">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U125">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V125">
         <v>1.45</v>
@@ -20720,10 +20720,10 @@
         <v>1.19</v>
       </c>
       <c r="Z125">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AA125">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB125">
         <v>2.1</v>
@@ -20732,7 +20732,7 @@
         <v>2.7</v>
       </c>
       <c r="AD125">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE125">
         <v>1.13</v>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK125">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,80 +20847,80 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.03</v>
+        <v>3.54</v>
       </c>
       <c r="O126">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="P126">
-        <v>2.7</v>
+        <v>1.87</v>
       </c>
       <c r="Q126">
-        <v>2.86</v>
+        <v>4.25</v>
       </c>
       <c r="R126">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S126">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T126">
         <v>2.82</v>
       </c>
       <c r="U126">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="V126">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W126">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y126">
+        <v>1.3</v>
+      </c>
+      <c r="Z126">
+        <v>3.35</v>
+      </c>
+      <c r="AA126">
+        <v>1.9</v>
+      </c>
+      <c r="AB126">
+        <v>1.86</v>
+      </c>
+      <c r="AC126">
+        <v>3.3</v>
+      </c>
+      <c r="AD126">
+        <v>1.36</v>
+      </c>
+      <c r="AE126">
+        <v>1.06</v>
+      </c>
+      <c r="AF126">
+        <v>1.73</v>
+      </c>
+      <c r="AG126">
+        <v>2.05</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
+        <v>1.23</v>
+      </c>
+      <c r="AK126">
         <v>1.21</v>
-      </c>
-      <c r="Z126">
-        <v>3.8</v>
-      </c>
-      <c r="AA126">
-        <v>1.76</v>
-      </c>
-      <c r="AB126">
-        <v>1.94</v>
-      </c>
-      <c r="AC126">
-        <v>2.83</v>
-      </c>
-      <c r="AD126">
-        <v>1.33</v>
-      </c>
-      <c r="AE126">
-        <v>1.14</v>
-      </c>
-      <c r="AF126">
-        <v>1.61</v>
-      </c>
-      <c r="AG126">
-        <v>2.16</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.25</v>
-      </c>
-      <c r="AK126">
-        <v>1.51</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>3.08</v>
+        <v>2.17</v>
       </c>
       <c r="O127">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P127">
-        <v>1.86</v>
+        <v>2.79</v>
       </c>
       <c r="Q127">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="R127">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S127">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T127">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="U127">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V127">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W127">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z127">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA127">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AB127">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AC127">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD127">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE127">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF127">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AG127">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK127">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O128">
-        <v>4.8</v>
+        <v>4.35</v>
       </c>
       <c r="P128">
-        <v>6.5</v>
+        <v>6.01</v>
       </c>
       <c r="Q128">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R128">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="S128">
         <v>1.2</v>
@@ -21194,7 +21194,7 @@
         <v>3.96</v>
       </c>
       <c r="U128">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="V128">
         <v>1.75</v>
@@ -21206,31 +21206,31 @@
         <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z128">
-        <v>5.26</v>
+        <v>5.45</v>
       </c>
       <c r="AA128">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB128">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AC128">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AD128">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE128">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF128">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG128">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O129">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="P129">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21499,19 +21499,19 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="O130">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="P130">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q130">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R130">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S130">
         <v>1.36</v>
@@ -21520,10 +21520,10 @@
         <v>2.9</v>
       </c>
       <c r="U130">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="V130">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W130">
         <v>1.08</v>
@@ -21535,28 +21535,28 @@
         <v>1.27</v>
       </c>
       <c r="Z130">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA130">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB130">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC130">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AD130">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE130">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF130">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG130">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21662,19 +21662,19 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="O131">
-        <v>3.83</v>
+        <v>4.31</v>
       </c>
       <c r="P131">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q131">
+        <v>2.48</v>
+      </c>
+      <c r="R131">
         <v>2.38</v>
-      </c>
-      <c r="R131">
-        <v>2.37</v>
       </c>
       <c r="S131">
         <v>1.22</v>
@@ -21686,7 +21686,7 @@
         <v>2.15</v>
       </c>
       <c r="V131">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W131">
         <v>1.17</v>
@@ -21695,28 +21695,28 @@
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z131">
-        <v>4.7</v>
+        <v>5.16</v>
       </c>
       <c r="AA131">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB131">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC131">
         <v>2.38</v>
       </c>
       <c r="AD131">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE131">
         <v>1.22</v>
       </c>
       <c r="AF131">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG131">
         <v>2.4</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK131">
         <v>1.8</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O132">
         <v>3.9</v>
       </c>
       <c r="P132">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="Q132">
         <v>2.3</v>
@@ -21843,13 +21843,13 @@
         <v>1.16</v>
       </c>
       <c r="T132">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U132">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V132">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="W132">
         <v>1.25</v>
@@ -21858,31 +21858,31 @@
         <v>0</v>
       </c>
       <c r="Y132">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z132">
         <v>8</v>
       </c>
       <c r="AA132">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AB132">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AC132">
         <v>1.73</v>
       </c>
       <c r="AD132">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE132">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF132">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AG132">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21991,16 +21991,16 @@
         <v>1.69</v>
       </c>
       <c r="O133">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P133">
         <v>4</v>
       </c>
       <c r="Q133">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="R133">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S133">
         <v>1.25</v>
@@ -22009,7 +22009,7 @@
         <v>3.45</v>
       </c>
       <c r="U133">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V133">
         <v>1.55</v>
@@ -22018,31 +22018,31 @@
         <v>1.13</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z133">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="AA133">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB133">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC133">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AD133">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE133">
         <v>1.2</v>
       </c>
       <c r="AF133">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG133">
         <v>2.25</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
         <v>2.2</v>
@@ -22151,19 +22151,19 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O134">
         <v>4</v>
       </c>
       <c r="P134">
-        <v>3.51</v>
+        <v>4.48</v>
       </c>
       <c r="Q134">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R134">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="S134">
         <v>1.14</v>
@@ -22172,13 +22172,13 @@
         <v>4.8</v>
       </c>
       <c r="U134">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V134">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="W134">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X134">
         <v>0</v>
@@ -22187,28 +22187,28 @@
         <v>1.06</v>
       </c>
       <c r="Z134">
-        <v>6.96</v>
+        <v>6.1</v>
       </c>
       <c r="AA134">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AB134">
         <v>3.1</v>
       </c>
       <c r="AC134">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AD134">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AE134">
         <v>1.33</v>
       </c>
       <c r="AF134">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG134">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK134">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O135">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P135">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -22335,19 +22335,19 @@
         <v>4.8</v>
       </c>
       <c r="U135">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="V135">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="W135">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X135">
         <v>0</v>
       </c>
       <c r="Y135">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z135">
         <v>8</v>
@@ -22359,19 +22359,19 @@
         <v>3.4</v>
       </c>
       <c r="AC135">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD135">
         <v>1.99</v>
       </c>
       <c r="AE135">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AF135">
         <v>1.3</v>
       </c>
       <c r="AG135">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22477,37 +22477,37 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O136">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P136">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q136">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R136">
         <v>2.25</v>
       </c>
       <c r="S136">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T136">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U136">
         <v>2.18</v>
       </c>
       <c r="V136">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W136">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
         <v>1.16</v>
@@ -22519,22 +22519,22 @@
         <v>1.66</v>
       </c>
       <c r="AB136">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC136">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD136">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE136">
         <v>1.17</v>
       </c>
       <c r="AF136">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG136">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK136">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22643,25 +22643,25 @@
         <v>3.1</v>
       </c>
       <c r="O137">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P137">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
       </c>
       <c r="R137">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T137">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U137">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V137">
         <v>1.44</v>
@@ -22673,31 +22673,31 @@
         <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z137">
         <v>3.2</v>
       </c>
       <c r="AA137">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB137">
         <v>1.95</v>
       </c>
       <c r="AC137">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="AD137">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE137">
         <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG137">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AK137">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22806,13 +22806,13 @@
         <v>2.05</v>
       </c>
       <c r="O138">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="P138">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="Q138">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="R138">
         <v>2.2</v>
@@ -22824,7 +22824,7 @@
         <v>3.11</v>
       </c>
       <c r="U138">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V138">
         <v>1.43</v>
@@ -22839,25 +22839,25 @@
         <v>1.28</v>
       </c>
       <c r="Z138">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="AA138">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB138">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC138">
         <v>3.04</v>
       </c>
       <c r="AD138">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE138">
         <v>1.08</v>
       </c>
       <c r="AF138">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG138">
         <v>2.05</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK138">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22972,7 +22972,7 @@
         <v>3.1</v>
       </c>
       <c r="P139">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q139">
         <v>2.66</v>
@@ -22981,10 +22981,10 @@
         <v>2.1</v>
       </c>
       <c r="S139">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T139">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U139">
         <v>3.32</v>
@@ -22993,28 +22993,28 @@
         <v>1.26</v>
       </c>
       <c r="W139">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X139">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y139">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z139">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="AA139">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AB139">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AC139">
         <v>3.2</v>
       </c>
       <c r="AD139">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AE139">
         <v>1.01</v>
@@ -23023,7 +23023,7 @@
         <v>2</v>
       </c>
       <c r="AG139">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK139">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23138,13 +23138,13 @@
         <v>1.41</v>
       </c>
       <c r="Q140">
-        <v>5.66</v>
+        <v>5</v>
       </c>
       <c r="R140">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S140">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T140">
         <v>3.1</v>
@@ -23156,25 +23156,25 @@
         <v>1.46</v>
       </c>
       <c r="W140">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X140">
         <v>1</v>
       </c>
       <c r="Y140">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z140">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA140">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AB140">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC140">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD140">
         <v>1.38</v>
@@ -23183,10 +23183,10 @@
         <v>1.13</v>
       </c>
       <c r="AF140">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG140">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK140">
         <v>1.08</v>
@@ -23292,28 +23292,28 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="O141">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P141">
         <v>3.1</v>
       </c>
       <c r="Q141">
+        <v>2.4</v>
+      </c>
+      <c r="R141">
         <v>2.5</v>
       </c>
-      <c r="R141">
-        <v>2.4</v>
-      </c>
       <c r="S141">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T141">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U141">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="V141">
         <v>1.6</v>
@@ -23325,25 +23325,25 @@
         <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z141">
-        <v>5.29</v>
+        <v>5.05</v>
       </c>
       <c r="AA141">
         <v>1.53</v>
       </c>
       <c r="AB141">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AC141">
         <v>2.28</v>
       </c>
       <c r="AD141">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE141">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF141">
         <v>1.44</v>
@@ -23362,7 +23362,7 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK141">
         <v>1.67</v>
@@ -23455,61 +23455,61 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O142">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P142">
-        <v>4.9</v>
+        <v>5.45</v>
       </c>
       <c r="Q142">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R142">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S142">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T142">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U142">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V142">
         <v>1.75</v>
       </c>
       <c r="W142">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X142">
         <v>0</v>
       </c>
       <c r="Y142">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z142">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA142">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB142">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC142">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD142">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE142">
         <v>1.26</v>
       </c>
       <c r="AF142">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG142">
         <v>2.4</v>
@@ -23528,7 +23528,7 @@
         <v>1.15</v>
       </c>
       <c r="AK142">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,31 +23618,31 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.87</v>
+        <v>1.94</v>
       </c>
       <c r="O143">
-        <v>3.94</v>
+        <v>3.71</v>
       </c>
       <c r="P143">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="Q143">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="R143">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S143">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T143">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="U143">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V143">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="W143">
         <v>1.14</v>
@@ -23651,31 +23651,31 @@
         <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z143">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA143">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AB143">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC143">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="AD143">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AE143">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF143">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG143">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK143">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.95</v>
+        <v>2.86</v>
       </c>
       <c r="O144">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="P144">
-        <v>2.95</v>
+        <v>2.29</v>
       </c>
       <c r="Q144">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
       <c r="R144">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S144">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T144">
-        <v>3.75</v>
+        <v>2.99</v>
       </c>
       <c r="U144">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="V144">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W144">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X144">
         <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA144">
+        <v>1.65</v>
+      </c>
+      <c r="AB144">
+        <v>2.1</v>
+      </c>
+      <c r="AC144">
+        <v>2.62</v>
+      </c>
+      <c r="AD144">
         <v>1.47</v>
       </c>
-      <c r="AB144">
-        <v>2.63</v>
-      </c>
-      <c r="AC144">
-        <v>2.25</v>
-      </c>
-      <c r="AD144">
-        <v>1.64</v>
-      </c>
       <c r="AE144">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF144">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG144">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AK144">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23947,31 +23947,31 @@
         <v>2.56</v>
       </c>
       <c r="O145">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P145">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q145">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R145">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S145">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T145">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="U145">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V145">
         <v>1.4</v>
       </c>
       <c r="W145">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X145">
         <v>1</v>
@@ -23980,28 +23980,28 @@
         <v>1.21</v>
       </c>
       <c r="Z145">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="AA145">
         <v>1.77</v>
       </c>
       <c r="AB145">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC145">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AD145">
         <v>1.32</v>
       </c>
       <c r="AE145">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG145">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AK145">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24270,19 +24270,19 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="O147">
         <v>3.45</v>
       </c>
       <c r="P147">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q147">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R147">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S147">
         <v>1.31</v>
@@ -24294,40 +24294,40 @@
         <v>2.47</v>
       </c>
       <c r="V147">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W147">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X147">
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z147">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA147">
         <v>1.71</v>
       </c>
       <c r="AB147">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC147">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD147">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE147">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF147">
         <v>1.59</v>
       </c>
       <c r="AG147">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK147">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24436,7 +24436,7 @@
         <v>1.7</v>
       </c>
       <c r="O148">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P148">
         <v>3.72</v>
@@ -24448,7 +24448,7 @@
         <v>2.3</v>
       </c>
       <c r="S148">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T148">
         <v>3.3</v>
@@ -24466,31 +24466,31 @@
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z148">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA148">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB148">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AC148">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="AD148">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE148">
         <v>1.18</v>
       </c>
       <c r="AF148">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG148">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK148">
         <v>2.04</v>
@@ -24596,55 +24596,55 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O149">
         <v>3.15</v>
       </c>
       <c r="P149">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="Q149">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R149">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S149">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T149">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U149">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="V149">
         <v>1.35</v>
       </c>
       <c r="W149">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X149">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y149">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z149">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AA149">
         <v>2</v>
       </c>
       <c r="AB149">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC149">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD149">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE149">
         <v>1.06</v>
@@ -24666,7 +24666,7 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK149">
         <v>1.48</v>
@@ -24759,7 +24759,7 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="O150">
         <v>3.35</v>
@@ -24771,25 +24771,25 @@
         <v>2.8</v>
       </c>
       <c r="R150">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="S150">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T150">
         <v>3.08</v>
       </c>
       <c r="U150">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V150">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W150">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X150">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y150">
         <v>1.19</v>
@@ -24801,7 +24801,7 @@
         <v>1.73</v>
       </c>
       <c r="AB150">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC150">
         <v>2.95</v>
@@ -24813,10 +24813,10 @@
         <v>1.08</v>
       </c>
       <c r="AF150">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG150">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24922,19 +24922,19 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O151">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="P151">
         <v>2.36</v>
       </c>
       <c r="Q151">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R151">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S151">
         <v>1.3</v>
@@ -24943,10 +24943,10 @@
         <v>3.08</v>
       </c>
       <c r="U151">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="V151">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W151">
         <v>1.09</v>
@@ -24958,22 +24958,22 @@
         <v>1.18</v>
       </c>
       <c r="Z151">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="AA151">
         <v>1.7</v>
       </c>
       <c r="AB151">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC151">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AD151">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE151">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF151">
         <v>1.53</v>
@@ -24992,10 +24992,10 @@
         <